--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122301001</v>
+        <v>122300988</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,16 +708,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651873</v>
+        <v>651926</v>
       </c>
       <c r="R2" t="n">
-        <v>6673779</v>
+        <v>6673844</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122300999</v>
+        <v>122300997</v>
       </c>
       <c r="B3" t="n">
         <v>57390</v>
@@ -841,20 +838,20 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651879</v>
+        <v>651883</v>
       </c>
       <c r="R3" t="n">
-        <v>6673776</v>
+        <v>6673732</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -886,7 +883,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +893,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,7 +920,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122300995</v>
+        <v>122300999</v>
       </c>
       <c r="B4" t="n">
         <v>57390</v>
@@ -975,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651899</v>
+        <v>651879</v>
       </c>
       <c r="R4" t="n">
-        <v>6673777</v>
+        <v>6673776</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1010,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122301064</v>
+        <v>122300994</v>
       </c>
       <c r="B5" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,31 +1056,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,10 +1096,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651993</v>
+        <v>651915</v>
       </c>
       <c r="R5" t="n">
-        <v>6673896</v>
+        <v>6673888</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1126,7 +1131,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1141,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122301068</v>
+        <v>122301004</v>
       </c>
       <c r="B6" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,42 +1180,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651906</v>
+        <v>651888</v>
       </c>
       <c r="R6" t="n">
-        <v>6673752</v>
+        <v>6673877</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1242,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,10 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122301056</v>
+        <v>122301062</v>
       </c>
       <c r="B7" t="n">
-        <v>98175</v>
+        <v>100441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,35 +1304,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1331,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651930</v>
+        <v>651973</v>
       </c>
       <c r="R7" t="n">
-        <v>6673898</v>
+        <v>6673897</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1366,7 +1379,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1376,7 +1389,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,7 +1416,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122300991</v>
+        <v>122300995</v>
       </c>
       <c r="B8" t="n">
         <v>57390</v>
@@ -1445,7 +1458,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1455,10 +1468,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651958</v>
+        <v>651899</v>
       </c>
       <c r="R8" t="n">
-        <v>6673868</v>
+        <v>6673777</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1490,7 +1503,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1500,7 +1513,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122301077</v>
+        <v>122301056</v>
       </c>
       <c r="B9" t="n">
-        <v>100441</v>
+        <v>98175</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,29 +1552,37 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -1571,10 +1592,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651993</v>
+        <v>651930</v>
       </c>
       <c r="R9" t="n">
-        <v>6673867</v>
+        <v>6673898</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1606,7 +1627,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1616,7 +1637,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,7 +1664,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122301007</v>
+        <v>122301006</v>
       </c>
       <c r="B10" t="n">
         <v>57390</v>
@@ -1695,10 +1716,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651778</v>
+        <v>651860</v>
       </c>
       <c r="R10" t="n">
-        <v>6673895</v>
+        <v>6673862</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1730,7 +1751,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1740,7 +1761,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1767,7 +1788,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301062</v>
+        <v>122301071</v>
       </c>
       <c r="B11" t="n">
         <v>100441</v>
@@ -1800,16 +1821,8 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1819,10 +1832,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651973</v>
+        <v>651840</v>
       </c>
       <c r="R11" t="n">
-        <v>6673897</v>
+        <v>6673881</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1854,7 +1867,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1864,7 +1877,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1891,7 +1904,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301071</v>
+        <v>122301064</v>
       </c>
       <c r="B12" t="n">
         <v>100441</v>
@@ -1935,10 +1948,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651840</v>
+        <v>651993</v>
       </c>
       <c r="R12" t="n">
-        <v>6673881</v>
+        <v>6673896</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1970,7 +1983,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1980,7 +1993,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2007,7 +2020,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122301078</v>
+        <v>122301068</v>
       </c>
       <c r="B13" t="n">
         <v>100441</v>
@@ -2047,14 +2060,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>652006</v>
+        <v>651906</v>
       </c>
       <c r="R13" t="n">
-        <v>6673876</v>
+        <v>6673752</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2086,7 +2099,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,7 +2109,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,10 +2136,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301053</v>
+        <v>122301037</v>
       </c>
       <c r="B14" t="n">
-        <v>98175</v>
+        <v>91171</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,39 +2148,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2175,10 +2174,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651986</v>
+        <v>651917</v>
       </c>
       <c r="R14" t="n">
-        <v>6673841</v>
+        <v>6673853</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2210,7 +2209,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2220,12 +2219,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2252,7 +2246,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122300993</v>
+        <v>122301007</v>
       </c>
       <c r="B15" t="n">
         <v>57390</v>
@@ -2294,7 +2288,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2304,13 +2298,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651962</v>
+        <v>651778</v>
       </c>
       <c r="R15" t="n">
-        <v>6673882</v>
+        <v>6673895</v>
       </c>
       <c r="S15" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2339,7 +2333,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2349,12 +2343,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2381,10 +2370,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301036</v>
+        <v>122301053</v>
       </c>
       <c r="B16" t="n">
-        <v>90779</v>
+        <v>98175</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2393,30 +2382,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2424,10 +2422,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>652047</v>
+        <v>651986</v>
       </c>
       <c r="R16" t="n">
-        <v>6673893</v>
+        <v>6673841</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2459,7 +2457,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2469,7 +2467,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2496,10 +2499,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301060</v>
+        <v>122301077</v>
       </c>
       <c r="B17" t="n">
-        <v>98175</v>
+        <v>100441</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2508,37 +2511,29 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2548,10 +2543,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>652000</v>
+        <v>651993</v>
       </c>
       <c r="R17" t="n">
-        <v>6673848</v>
+        <v>6673867</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2583,7 +2578,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2593,7 +2588,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2620,10 +2615,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122301058</v>
+        <v>122301020</v>
       </c>
       <c r="B18" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,39 +2627,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2672,10 +2667,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651981</v>
+        <v>652017</v>
       </c>
       <c r="R18" t="n">
-        <v>6673859</v>
+        <v>6673872</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2707,7 +2702,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2717,7 +2712,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2744,10 +2739,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122301004</v>
+        <v>122301078</v>
       </c>
       <c r="B19" t="n">
-        <v>57390</v>
+        <v>100441</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2756,39 +2751,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2796,10 +2783,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651888</v>
+        <v>652006</v>
       </c>
       <c r="R19" t="n">
-        <v>6673877</v>
+        <v>6673876</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2831,7 +2818,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2841,7 +2828,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2868,10 +2855,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122301037</v>
+        <v>122301019</v>
       </c>
       <c r="B20" t="n">
-        <v>91171</v>
+        <v>57390</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,21 +2871,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040162</v>
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2906,10 +2907,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651917</v>
+        <v>652004</v>
       </c>
       <c r="R20" t="n">
-        <v>6673853</v>
+        <v>6673869</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2941,7 +2942,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2951,7 +2952,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2978,10 +2979,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122301031</v>
+        <v>122301058</v>
       </c>
       <c r="B21" t="n">
-        <v>74686</v>
+        <v>98175</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2990,30 +2991,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3021,10 +3031,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651805</v>
+        <v>651981</v>
       </c>
       <c r="R21" t="n">
-        <v>6673899</v>
+        <v>6673859</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3056,7 +3066,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3066,7 +3076,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3093,10 +3103,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122301006</v>
+        <v>122301060</v>
       </c>
       <c r="B22" t="n">
-        <v>57390</v>
+        <v>98175</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3105,39 +3115,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3145,10 +3155,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651860</v>
+        <v>652000</v>
       </c>
       <c r="R22" t="n">
-        <v>6673862</v>
+        <v>6673848</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3180,7 +3190,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3190,7 +3200,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3217,10 +3227,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122300988</v>
+        <v>122300991</v>
       </c>
       <c r="B23" t="n">
-        <v>5193</v>
+        <v>57390</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3229,20 +3239,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3250,13 +3260,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3266,10 +3279,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651926</v>
+        <v>651958</v>
       </c>
       <c r="R23" t="n">
-        <v>6673844</v>
+        <v>6673868</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3301,7 +3314,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3311,7 +3324,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3338,10 +3351,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122300994</v>
+        <v>122301036</v>
       </c>
       <c r="B24" t="n">
-        <v>57390</v>
+        <v>90779</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3354,35 +3367,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3390,10 +3394,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651915</v>
+        <v>652047</v>
       </c>
       <c r="R24" t="n">
-        <v>6673888</v>
+        <v>6673893</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3425,7 +3429,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3435,7 +3439,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3462,7 +3466,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122300997</v>
+        <v>122301001</v>
       </c>
       <c r="B25" t="n">
         <v>57390</v>
@@ -3504,20 +3508,20 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651883</v>
+        <v>651873</v>
       </c>
       <c r="R25" t="n">
-        <v>6673732</v>
+        <v>6673779</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3549,7 +3553,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3559,7 +3563,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3586,10 +3590,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301021</v>
+        <v>122301031</v>
       </c>
       <c r="B26" t="n">
-        <v>57390</v>
+        <v>74686</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3598,50 +3602,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>652056</v>
+        <v>651805</v>
       </c>
       <c r="R26" t="n">
-        <v>6673872</v>
+        <v>6673899</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3673,7 +3668,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3678,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3710,7 +3705,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301020</v>
+        <v>122301021</v>
       </c>
       <c r="B27" t="n">
         <v>57390</v>
@@ -3758,11 +3753,11 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>652017</v>
+        <v>652056</v>
       </c>
       <c r="R27" t="n">
         <v>6673872</v>
@@ -3797,7 +3792,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3807,7 +3802,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3834,7 +3829,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122301019</v>
+        <v>122300993</v>
       </c>
       <c r="B28" t="n">
         <v>57390</v>
@@ -3876,7 +3871,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3886,13 +3881,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>652004</v>
+        <v>651962</v>
       </c>
       <c r="R28" t="n">
-        <v>6673869</v>
+        <v>6673882</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3921,7 +3916,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3931,7 +3926,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122260096</v>
+        <v>122260116</v>
       </c>
       <c r="B29" t="n">
-        <v>80602</v>
+        <v>100441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3970,30 +3970,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4001,10 +4002,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651930</v>
+        <v>651859</v>
       </c>
       <c r="R29" t="n">
-        <v>6674592</v>
+        <v>6674654</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4036,7 +4037,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4046,7 +4047,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4073,7 +4074,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122260077</v>
+        <v>122260068</v>
       </c>
       <c r="B30" t="n">
         <v>57390</v>
@@ -4115,7 +4116,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4125,10 +4126,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651964</v>
+        <v>651928</v>
       </c>
       <c r="R30" t="n">
-        <v>6674220</v>
+        <v>6674457</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4160,7 +4161,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4170,7 +4171,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4197,10 +4198,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260121</v>
+        <v>122260072</v>
       </c>
       <c r="B31" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4209,31 +4210,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4241,10 +4250,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651955</v>
+        <v>651927</v>
       </c>
       <c r="R31" t="n">
-        <v>6674222</v>
+        <v>6674447</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4276,7 +4285,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4286,7 +4295,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4313,10 +4322,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260125</v>
+        <v>122260084</v>
       </c>
       <c r="B32" t="n">
-        <v>100441</v>
+        <v>57527</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4325,31 +4334,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4357,13 +4374,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651973</v>
+        <v>651900</v>
       </c>
       <c r="R32" t="n">
-        <v>6674332</v>
+        <v>6674551</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4392,7 +4409,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4402,7 +4419,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4429,7 +4446,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260117</v>
+        <v>122260119</v>
       </c>
       <c r="B33" t="n">
         <v>100441</v>
@@ -4473,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651906</v>
+        <v>651950</v>
       </c>
       <c r="R33" t="n">
-        <v>6674571</v>
+        <v>6674465</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4508,7 +4525,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4518,7 +4535,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4545,10 +4562,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260058</v>
+        <v>122260063</v>
       </c>
       <c r="B34" t="n">
-        <v>5193</v>
+        <v>57390</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4557,20 +4574,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4578,13 +4595,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4594,10 +4614,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>652031</v>
+        <v>651872</v>
       </c>
       <c r="R34" t="n">
-        <v>6674226</v>
+        <v>6674674</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4629,7 +4649,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4639,7 +4659,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4650,21 +4670,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4681,10 +4686,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122260100</v>
+        <v>122260125</v>
       </c>
       <c r="B35" t="n">
-        <v>90779</v>
+        <v>100441</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4693,30 +4698,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4724,10 +4730,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>652034</v>
+        <v>651973</v>
       </c>
       <c r="R35" t="n">
-        <v>6674236</v>
+        <v>6674332</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4759,7 +4765,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4769,7 +4775,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4780,21 +4786,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4811,10 +4802,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122260111</v>
+        <v>122260115</v>
       </c>
       <c r="B36" t="n">
-        <v>98175</v>
+        <v>100441</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4823,37 +4814,29 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -4863,10 +4846,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651949</v>
+        <v>651891</v>
       </c>
       <c r="R36" t="n">
-        <v>6674415</v>
+        <v>6674645</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4898,7 +4881,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4908,7 +4891,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4935,10 +4918,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122260113</v>
+        <v>122260066</v>
       </c>
       <c r="B37" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4947,39 +4930,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4987,10 +4970,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651906</v>
+        <v>651934</v>
       </c>
       <c r="R37" t="n">
-        <v>6674392</v>
+        <v>6674510</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5022,7 +5005,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5032,7 +5015,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5059,10 +5042,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122260126</v>
+        <v>122260074</v>
       </c>
       <c r="B38" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5071,31 +5054,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5103,13 +5094,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651941</v>
+        <v>651923</v>
       </c>
       <c r="R38" t="n">
-        <v>6674469</v>
+        <v>6674436</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5138,7 +5129,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5148,7 +5139,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Hörd i norr.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5175,10 +5171,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260103</v>
+        <v>122260117</v>
       </c>
       <c r="B39" t="n">
-        <v>91219</v>
+        <v>100441</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5187,30 +5183,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5218,10 +5215,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651855</v>
+        <v>651906</v>
       </c>
       <c r="R39" t="n">
-        <v>6674655</v>
+        <v>6674571</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5253,7 +5250,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5263,12 +5260,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På klibbtickelåga.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5279,21 +5271,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5310,10 +5287,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260085</v>
+        <v>122260111</v>
       </c>
       <c r="B40" t="n">
-        <v>57744</v>
+        <v>98175</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5322,39 +5299,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5362,13 +5339,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651895</v>
+        <v>651949</v>
       </c>
       <c r="R40" t="n">
-        <v>6674630</v>
+        <v>6674415</v>
       </c>
       <c r="S40" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5397,7 +5374,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5407,7 +5384,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5434,10 +5411,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260063</v>
+        <v>122260096</v>
       </c>
       <c r="B41" t="n">
-        <v>57390</v>
+        <v>80602</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5450,35 +5427,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5486,10 +5454,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651872</v>
+        <v>651930</v>
       </c>
       <c r="R41" t="n">
-        <v>6674674</v>
+        <v>6674592</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5521,7 +5489,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5531,7 +5499,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5558,7 +5526,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122260076</v>
+        <v>122260070</v>
       </c>
       <c r="B42" t="n">
         <v>57390</v>
@@ -5610,10 +5578,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651949</v>
+        <v>651967</v>
       </c>
       <c r="R42" t="n">
-        <v>6674279</v>
+        <v>6674433</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5645,7 +5613,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5655,7 +5623,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5682,7 +5650,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260071</v>
+        <v>122260080</v>
       </c>
       <c r="B43" t="n">
         <v>57390</v>
@@ -5734,10 +5702,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651930</v>
+        <v>652019</v>
       </c>
       <c r="R43" t="n">
-        <v>6674444</v>
+        <v>6674239</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5769,7 +5737,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5779,7 +5747,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5806,10 +5774,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260118</v>
+        <v>122260075</v>
       </c>
       <c r="B44" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5818,31 +5786,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5850,10 +5826,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651893</v>
+        <v>651900</v>
       </c>
       <c r="R44" t="n">
-        <v>6674508</v>
+        <v>6674390</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5885,7 +5861,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5895,7 +5871,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5922,10 +5898,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122260084</v>
+        <v>122260120</v>
       </c>
       <c r="B45" t="n">
-        <v>57527</v>
+        <v>100441</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5934,39 +5910,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5974,13 +5942,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651900</v>
+        <v>651967</v>
       </c>
       <c r="R45" t="n">
-        <v>6674551</v>
+        <v>6674316</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6009,7 +5977,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6019,7 +5987,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6046,7 +6014,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122260115</v>
+        <v>122260118</v>
       </c>
       <c r="B46" t="n">
         <v>100441</v>
@@ -6090,10 +6058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651891</v>
+        <v>651893</v>
       </c>
       <c r="R46" t="n">
-        <v>6674645</v>
+        <v>6674508</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6125,7 +6093,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6135,7 +6103,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6162,10 +6130,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260119</v>
+        <v>122260114</v>
       </c>
       <c r="B47" t="n">
-        <v>100441</v>
+        <v>98175</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6174,29 +6142,37 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
@@ -6206,10 +6182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651950</v>
+        <v>652010</v>
       </c>
       <c r="R47" t="n">
-        <v>6674465</v>
+        <v>6674220</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6241,7 +6217,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6251,7 +6227,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6278,10 +6254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260064</v>
+        <v>122260110</v>
       </c>
       <c r="B48" t="n">
-        <v>57390</v>
+        <v>98175</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6290,39 +6266,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6330,10 +6306,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>651845</v>
+        <v>651949</v>
       </c>
       <c r="R48" t="n">
-        <v>6674626</v>
+        <v>6674420</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6365,7 +6341,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6375,7 +6351,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6402,10 +6383,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260116</v>
+        <v>122260103</v>
       </c>
       <c r="B49" t="n">
-        <v>100441</v>
+        <v>91219</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6414,31 +6395,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6446,10 +6426,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651859</v>
+        <v>651855</v>
       </c>
       <c r="R49" t="n">
-        <v>6674654</v>
+        <v>6674655</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6481,7 +6461,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6491,7 +6471,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På klibbtickelåga.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6502,6 +6487,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6518,7 +6518,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260075</v>
+        <v>122260061</v>
       </c>
       <c r="B50" t="n">
         <v>57390</v>
@@ -6560,7 +6560,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651900</v>
+        <v>651886</v>
       </c>
       <c r="R50" t="n">
-        <v>6674390</v>
+        <v>6674654</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6642,10 +6642,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122260114</v>
+        <v>122260085</v>
       </c>
       <c r="B51" t="n">
-        <v>98175</v>
+        <v>57744</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6654,39 +6654,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6694,13 +6694,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>652010</v>
+        <v>651895</v>
       </c>
       <c r="R51" t="n">
-        <v>6674220</v>
+        <v>6674630</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6766,7 +6766,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260068</v>
+        <v>122260077</v>
       </c>
       <c r="B52" t="n">
         <v>57390</v>
@@ -6808,7 +6808,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651928</v>
+        <v>651964</v>
       </c>
       <c r="R52" t="n">
-        <v>6674457</v>
+        <v>6674220</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6890,10 +6890,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260070</v>
+        <v>122260121</v>
       </c>
       <c r="B53" t="n">
-        <v>57390</v>
+        <v>100441</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6902,39 +6902,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6942,10 +6934,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651967</v>
+        <v>651955</v>
       </c>
       <c r="R53" t="n">
-        <v>6674433</v>
+        <v>6674222</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6977,7 +6969,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6987,7 +6979,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7014,7 +7006,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260072</v>
+        <v>122260064</v>
       </c>
       <c r="B54" t="n">
         <v>57390</v>
@@ -7056,7 +7048,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7066,10 +7058,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651927</v>
+        <v>651845</v>
       </c>
       <c r="R54" t="n">
-        <v>6674447</v>
+        <v>6674626</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7101,7 +7093,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7111,7 +7103,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7138,7 +7130,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122260080</v>
+        <v>122260071</v>
       </c>
       <c r="B55" t="n">
         <v>57390</v>
@@ -7190,10 +7182,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>652019</v>
+        <v>651930</v>
       </c>
       <c r="R55" t="n">
-        <v>6674239</v>
+        <v>6674444</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7225,7 +7217,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7235,7 +7227,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7262,10 +7254,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260110</v>
+        <v>122260058</v>
       </c>
       <c r="B56" t="n">
-        <v>98175</v>
+        <v>5193</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7274,39 +7266,36 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7314,10 +7303,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>651949</v>
+        <v>652031</v>
       </c>
       <c r="R56" t="n">
-        <v>6674420</v>
+        <v>6674226</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7349,7 +7338,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7359,12 +7348,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7375,6 +7359,21 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7391,10 +7390,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260066</v>
+        <v>122260100</v>
       </c>
       <c r="B57" t="n">
-        <v>57390</v>
+        <v>90779</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7407,35 +7406,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7443,10 +7433,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651934</v>
+        <v>652034</v>
       </c>
       <c r="R57" t="n">
-        <v>6674510</v>
+        <v>6674236</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7478,7 +7468,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7488,7 +7478,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7499,6 +7489,21 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7515,7 +7520,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260120</v>
+        <v>122260126</v>
       </c>
       <c r="B58" t="n">
         <v>100441</v>
@@ -7559,10 +7564,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>651967</v>
+        <v>651941</v>
       </c>
       <c r="R58" t="n">
-        <v>6674316</v>
+        <v>6674469</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7594,7 +7599,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7604,7 +7609,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7631,7 +7636,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260061</v>
+        <v>122260076</v>
       </c>
       <c r="B59" t="n">
         <v>57390</v>
@@ -7673,7 +7678,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7683,10 +7688,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651886</v>
+        <v>651949</v>
       </c>
       <c r="R59" t="n">
-        <v>6674654</v>
+        <v>6674279</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7718,7 +7723,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7728,7 +7733,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7755,10 +7760,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260074</v>
+        <v>122260113</v>
       </c>
       <c r="B60" t="n">
-        <v>57390</v>
+        <v>98175</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7767,39 +7772,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7807,13 +7812,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651923</v>
+        <v>651906</v>
       </c>
       <c r="R60" t="n">
-        <v>6674436</v>
+        <v>6674392</v>
       </c>
       <c r="S60" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7842,7 +7847,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7852,12 +7857,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Hörd i norr.</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7884,10 +7884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301013</v>
+        <v>122301074</v>
       </c>
       <c r="B61" t="n">
-        <v>57390</v>
+        <v>100441</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7896,39 +7896,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7936,10 +7928,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651745</v>
+        <v>651855</v>
       </c>
       <c r="R61" t="n">
-        <v>6673922</v>
+        <v>6673907</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7971,7 +7963,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7981,7 +7973,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8240,10 +8232,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301075</v>
+        <v>122301015</v>
       </c>
       <c r="B64" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8252,31 +8244,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651975</v>
+        <v>651777</v>
       </c>
       <c r="R64" t="n">
-        <v>6673928</v>
+        <v>6673975</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8356,10 +8356,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301026</v>
+        <v>122301075</v>
       </c>
       <c r="B65" t="n">
-        <v>57527</v>
+        <v>100441</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8368,39 +8368,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8408,13 +8400,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651977</v>
+        <v>651975</v>
       </c>
       <c r="R65" t="n">
-        <v>6673906</v>
+        <v>6673928</v>
       </c>
       <c r="S65" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8443,7 +8435,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8453,7 +8445,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8480,10 +8472,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301066</v>
+        <v>122301050</v>
       </c>
       <c r="B66" t="n">
-        <v>100441</v>
+        <v>98175</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8492,29 +8484,37 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -8524,10 +8524,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>652079</v>
+        <v>651948</v>
       </c>
       <c r="R66" t="n">
-        <v>6673929</v>
+        <v>6673906</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8596,7 +8596,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301074</v>
+        <v>122301063</v>
       </c>
       <c r="B67" t="n">
         <v>100441</v>
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>651855</v>
+        <v>651949</v>
       </c>
       <c r="R67" t="n">
-        <v>6673907</v>
+        <v>6673910</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8675,7 +8675,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8685,7 +8685,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8712,10 +8712,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301050</v>
+        <v>122301067</v>
       </c>
       <c r="B68" t="n">
-        <v>98175</v>
+        <v>100441</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8724,37 +8724,29 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
@@ -8764,10 +8756,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651948</v>
+        <v>652040</v>
       </c>
       <c r="R68" t="n">
-        <v>6673906</v>
+        <v>6673920</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8799,7 +8791,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8809,7 +8801,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8836,10 +8828,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301025</v>
+        <v>122301027</v>
       </c>
       <c r="B69" t="n">
-        <v>57527</v>
+        <v>57744</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8848,25 +8840,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8876,25 +8868,21 @@
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651941</v>
+        <v>651983</v>
       </c>
       <c r="R69" t="n">
-        <v>6674093</v>
+        <v>6673930</v>
       </c>
       <c r="S69" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8923,7 +8911,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8933,7 +8921,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8960,10 +8948,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301027</v>
+        <v>122301066</v>
       </c>
       <c r="B70" t="n">
-        <v>57744</v>
+        <v>100441</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8976,31 +8964,27 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9008,13 +8992,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651983</v>
+        <v>652079</v>
       </c>
       <c r="R70" t="n">
-        <v>6673930</v>
+        <v>6673929</v>
       </c>
       <c r="S70" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9043,7 +9027,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9053,7 +9037,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9080,10 +9064,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301015</v>
+        <v>122301026</v>
       </c>
       <c r="B71" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9096,21 +9080,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -9122,7 +9106,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9132,13 +9116,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651777</v>
+        <v>651977</v>
       </c>
       <c r="R71" t="n">
-        <v>6673975</v>
+        <v>6673906</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9167,7 +9151,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9177,7 +9161,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9204,10 +9188,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301067</v>
+        <v>122301013</v>
       </c>
       <c r="B72" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9216,31 +9200,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9248,10 +9240,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>652040</v>
+        <v>651745</v>
       </c>
       <c r="R72" t="n">
-        <v>6673920</v>
+        <v>6673922</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9283,7 +9275,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9293,7 +9285,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9320,7 +9312,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301080</v>
+        <v>122301079</v>
       </c>
       <c r="B73" t="n">
         <v>100441</v>
@@ -9364,10 +9356,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>652011</v>
+        <v>652014</v>
       </c>
       <c r="R73" t="n">
-        <v>6673969</v>
+        <v>6673954</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9399,7 +9391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9409,7 +9401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9436,10 +9428,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301079</v>
+        <v>122301017</v>
       </c>
       <c r="B74" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9448,31 +9440,39 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>652014</v>
+        <v>651776</v>
       </c>
       <c r="R74" t="n">
-        <v>6673954</v>
+        <v>6673944</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9552,7 +9552,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301063</v>
+        <v>122301081</v>
       </c>
       <c r="B75" t="n">
         <v>100441</v>
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651949</v>
+        <v>652036</v>
       </c>
       <c r="R75" t="n">
-        <v>6673910</v>
+        <v>6673988</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9668,10 +9668,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301017</v>
+        <v>122301025</v>
       </c>
       <c r="B76" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9684,49 +9684,49 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651776</v>
+        <v>651941</v>
       </c>
       <c r="R76" t="n">
-        <v>6673944</v>
+        <v>6674093</v>
       </c>
       <c r="S76" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9792,7 +9792,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301081</v>
+        <v>122301080</v>
       </c>
       <c r="B77" t="n">
         <v>100441</v>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>652036</v>
+        <v>652011</v>
       </c>
       <c r="R77" t="n">
-        <v>6673988</v>
+        <v>6673969</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -1416,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122300995</v>
+        <v>122301056</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>98175</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,39 +1428,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1468,10 +1468,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651899</v>
+        <v>651930</v>
       </c>
       <c r="R8" t="n">
-        <v>6673777</v>
+        <v>6673898</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122301056</v>
+        <v>122300995</v>
       </c>
       <c r="B9" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1552,39 +1552,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1592,10 +1592,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651930</v>
+        <v>651899</v>
       </c>
       <c r="R9" t="n">
-        <v>6673898</v>
+        <v>6673777</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,10 +1664,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122301006</v>
+        <v>122301071</v>
       </c>
       <c r="B10" t="n">
-        <v>57390</v>
+        <v>100441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,39 +1676,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1716,10 +1708,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651860</v>
+        <v>651840</v>
       </c>
       <c r="R10" t="n">
-        <v>6673862</v>
+        <v>6673881</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1751,7 +1743,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1761,7 +1753,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1788,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301071</v>
+        <v>122301006</v>
       </c>
       <c r="B11" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1800,31 +1792,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651840</v>
+        <v>651860</v>
       </c>
       <c r="R11" t="n">
-        <v>6673881</v>
+        <v>6673862</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2136,10 +2136,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301037</v>
+        <v>122301007</v>
       </c>
       <c r="B14" t="n">
-        <v>91171</v>
+        <v>57390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2152,21 +2152,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040162</v>
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2174,10 +2188,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651917</v>
+        <v>651778</v>
       </c>
       <c r="R14" t="n">
-        <v>6673853</v>
+        <v>6673895</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2209,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2219,7 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2246,10 +2260,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122301007</v>
+        <v>122301053</v>
       </c>
       <c r="B15" t="n">
-        <v>57390</v>
+        <v>98175</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2258,39 +2272,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2298,10 +2312,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651778</v>
+        <v>651986</v>
       </c>
       <c r="R15" t="n">
-        <v>6673895</v>
+        <v>6673841</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2333,7 +2347,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2343,7 +2357,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2370,10 +2389,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301053</v>
+        <v>122301037</v>
       </c>
       <c r="B16" t="n">
-        <v>98175</v>
+        <v>91171</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2382,39 +2401,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2422,10 +2427,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651986</v>
+        <v>651917</v>
       </c>
       <c r="R16" t="n">
-        <v>6673841</v>
+        <v>6673853</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2457,7 +2462,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2467,12 +2472,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3227,10 +3227,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122300991</v>
+        <v>122301036</v>
       </c>
       <c r="B23" t="n">
-        <v>57390</v>
+        <v>90779</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3243,35 +3243,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3279,10 +3270,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651958</v>
+        <v>652047</v>
       </c>
       <c r="R23" t="n">
-        <v>6673868</v>
+        <v>6673893</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3314,7 +3305,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3324,7 +3315,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3351,10 +3342,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122301036</v>
+        <v>122300991</v>
       </c>
       <c r="B24" t="n">
-        <v>90779</v>
+        <v>57390</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3367,26 +3358,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>652047</v>
+        <v>651958</v>
       </c>
       <c r="R24" t="n">
-        <v>6673893</v>
+        <v>6673868</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3429,7 +3429,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -5650,10 +5650,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260080</v>
+        <v>122260120</v>
       </c>
       <c r="B43" t="n">
-        <v>57390</v>
+        <v>100441</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5662,39 +5662,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5702,10 +5694,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>652019</v>
+        <v>651967</v>
       </c>
       <c r="R43" t="n">
-        <v>6674239</v>
+        <v>6674316</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5737,7 +5729,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5747,7 +5739,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5774,7 +5766,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260075</v>
+        <v>122260080</v>
       </c>
       <c r="B44" t="n">
         <v>57390</v>
@@ -5816,7 +5808,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5826,10 +5818,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651900</v>
+        <v>652019</v>
       </c>
       <c r="R44" t="n">
-        <v>6674390</v>
+        <v>6674239</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5861,7 +5853,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5871,7 +5863,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5898,10 +5890,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122260120</v>
+        <v>122260075</v>
       </c>
       <c r="B45" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5910,31 +5902,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5942,10 +5942,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651967</v>
+        <v>651900</v>
       </c>
       <c r="R45" t="n">
-        <v>6674316</v>
+        <v>6674390</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6130,7 +6130,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260114</v>
+        <v>122260110</v>
       </c>
       <c r="B47" t="n">
         <v>98175</v>
@@ -6165,7 +6165,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>652010</v>
+        <v>651949</v>
       </c>
       <c r="R47" t="n">
-        <v>6674220</v>
+        <v>6674420</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6227,7 +6227,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6254,7 +6259,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260110</v>
+        <v>122260114</v>
       </c>
       <c r="B48" t="n">
         <v>98175</v>
@@ -6289,7 +6294,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6306,10 +6311,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>651949</v>
+        <v>652010</v>
       </c>
       <c r="R48" t="n">
-        <v>6674420</v>
+        <v>6674220</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6341,7 +6346,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6351,12 +6356,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7254,10 +7254,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260058</v>
+        <v>122260100</v>
       </c>
       <c r="B56" t="n">
-        <v>5193</v>
+        <v>90779</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7266,36 +7266,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7303,10 +7297,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>652031</v>
+        <v>652034</v>
       </c>
       <c r="R56" t="n">
-        <v>6674226</v>
+        <v>6674236</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7338,7 +7332,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7348,7 +7342,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7390,10 +7384,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260100</v>
+        <v>122260126</v>
       </c>
       <c r="B57" t="n">
-        <v>90779</v>
+        <v>100441</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7402,30 +7396,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7433,10 +7428,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>652034</v>
+        <v>651941</v>
       </c>
       <c r="R57" t="n">
-        <v>6674236</v>
+        <v>6674469</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7468,7 +7463,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7478,7 +7473,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7489,21 +7484,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7520,10 +7500,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260126</v>
+        <v>122260058</v>
       </c>
       <c r="B58" t="n">
-        <v>100441</v>
+        <v>5193</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7536,27 +7516,32 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7564,10 +7549,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>651941</v>
+        <v>652031</v>
       </c>
       <c r="R58" t="n">
-        <v>6674469</v>
+        <v>6674226</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7599,7 +7584,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7609,7 +7594,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7620,6 +7605,21 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -8000,10 +8000,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301065</v>
+        <v>122301015</v>
       </c>
       <c r="B62" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8012,31 +8012,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8044,10 +8052,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>652034</v>
+        <v>651777</v>
       </c>
       <c r="R62" t="n">
-        <v>6673906</v>
+        <v>6673975</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8079,7 +8087,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8089,7 +8097,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8116,7 +8124,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301073</v>
+        <v>122301065</v>
       </c>
       <c r="B63" t="n">
         <v>100441</v>
@@ -8160,10 +8168,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>651817</v>
+        <v>652034</v>
       </c>
       <c r="R63" t="n">
-        <v>6673939</v>
+        <v>6673906</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8195,7 +8203,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8205,7 +8213,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8232,10 +8240,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301015</v>
+        <v>122301073</v>
       </c>
       <c r="B64" t="n">
-        <v>57390</v>
+        <v>100441</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8244,39 +8252,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651777</v>
+        <v>651817</v>
       </c>
       <c r="R64" t="n">
-        <v>6673975</v>
+        <v>6673939</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -9668,10 +9668,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301025</v>
+        <v>122301080</v>
       </c>
       <c r="B76" t="n">
-        <v>57527</v>
+        <v>100441</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9680,53 +9680,45 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651941</v>
+        <v>652011</v>
       </c>
       <c r="R76" t="n">
-        <v>6674093</v>
+        <v>6673969</v>
       </c>
       <c r="S76" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9755,7 +9747,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9765,7 +9757,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9792,10 +9784,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301080</v>
+        <v>122301025</v>
       </c>
       <c r="B77" t="n">
-        <v>100441</v>
+        <v>57527</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9804,45 +9796,53 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>652011</v>
+        <v>651941</v>
       </c>
       <c r="R77" t="n">
-        <v>6673969</v>
+        <v>6674093</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122300988</v>
+        <v>122300997</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,26 +708,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651926</v>
+        <v>651883</v>
       </c>
       <c r="R2" t="n">
-        <v>6673844</v>
+        <v>6673732</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122300997</v>
+        <v>122301062</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,50 +811,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651883</v>
+        <v>651973</v>
       </c>
       <c r="R3" t="n">
-        <v>6673732</v>
+        <v>6673897</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -883,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -893,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122300999</v>
+        <v>122301001</v>
       </c>
       <c r="B4" t="n">
         <v>57390</v>
@@ -972,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651879</v>
+        <v>651873</v>
       </c>
       <c r="R4" t="n">
-        <v>6673776</v>
+        <v>6673779</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1007,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122300994</v>
+        <v>122301068</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,50 +1059,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651915</v>
+        <v>651906</v>
       </c>
       <c r="R5" t="n">
-        <v>6673888</v>
+        <v>6673752</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1131,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1141,7 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1292,10 +1287,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122301062</v>
+        <v>122301064</v>
       </c>
       <c r="B7" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1325,16 +1320,8 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1344,10 +1331,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651973</v>
+        <v>651993</v>
       </c>
       <c r="R7" t="n">
-        <v>6673897</v>
+        <v>6673896</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1379,7 +1366,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1389,7 +1376,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,10 +1403,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122301056</v>
+        <v>122301021</v>
       </c>
       <c r="B8" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,50 +1415,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651930</v>
+        <v>652056</v>
       </c>
       <c r="R8" t="n">
-        <v>6673898</v>
+        <v>6673872</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1503,7 +1490,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1513,7 +1500,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1664,10 +1651,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122301071</v>
+        <v>122300991</v>
       </c>
       <c r="B10" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1676,31 +1663,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1708,10 +1703,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651840</v>
+        <v>651958</v>
       </c>
       <c r="R10" t="n">
-        <v>6673881</v>
+        <v>6673868</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1743,7 +1738,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1753,7 +1748,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1780,7 +1775,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301006</v>
+        <v>122300999</v>
       </c>
       <c r="B11" t="n">
         <v>57390</v>
@@ -1832,10 +1827,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651860</v>
+        <v>651879</v>
       </c>
       <c r="R11" t="n">
-        <v>6673862</v>
+        <v>6673776</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1867,7 +1862,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1877,7 +1872,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301064</v>
+        <v>122300993</v>
       </c>
       <c r="B12" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1916,31 +1911,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1948,13 +1951,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651993</v>
+        <v>651962</v>
       </c>
       <c r="R12" t="n">
-        <v>6673896</v>
+        <v>6673882</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1983,7 +1986,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1993,7 +1996,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2020,10 +2028,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122301068</v>
+        <v>122301071</v>
       </c>
       <c r="B13" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2060,14 +2068,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651906</v>
+        <v>651840</v>
       </c>
       <c r="R13" t="n">
-        <v>6673752</v>
+        <v>6673881</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2099,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2109,7 +2117,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301007</v>
+        <v>122301077</v>
       </c>
       <c r="B14" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,39 +2156,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651778</v>
+        <v>651993</v>
       </c>
       <c r="R14" t="n">
-        <v>6673895</v>
+        <v>6673867</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2260,10 +2260,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122301053</v>
+        <v>122301060</v>
       </c>
       <c r="B15" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651986</v>
+        <v>652000</v>
       </c>
       <c r="R15" t="n">
-        <v>6673841</v>
+        <v>6673848</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2357,12 +2357,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2389,10 +2384,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301037</v>
+        <v>122301078</v>
       </c>
       <c r="B16" t="n">
-        <v>91171</v>
+        <v>100451</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2401,25 +2396,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6040162</v>
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2427,10 +2428,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651917</v>
+        <v>652006</v>
       </c>
       <c r="R16" t="n">
-        <v>6673853</v>
+        <v>6673876</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2462,7 +2463,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2472,7 +2473,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2499,10 +2500,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301077</v>
+        <v>122301056</v>
       </c>
       <c r="B17" t="n">
-        <v>100441</v>
+        <v>98185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2511,29 +2512,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -2543,10 +2552,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651993</v>
+        <v>651930</v>
       </c>
       <c r="R17" t="n">
-        <v>6673867</v>
+        <v>6673898</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2578,7 +2587,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2588,7 +2597,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2615,10 +2624,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122301020</v>
+        <v>122301053</v>
       </c>
       <c r="B18" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2627,39 +2636,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2667,10 +2676,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>652017</v>
+        <v>651986</v>
       </c>
       <c r="R18" t="n">
-        <v>6673872</v>
+        <v>6673841</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2702,7 +2711,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2712,7 +2721,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2739,10 +2753,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122301078</v>
+        <v>122301031</v>
       </c>
       <c r="B19" t="n">
-        <v>100441</v>
+        <v>74686</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2755,27 +2769,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2783,10 +2796,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652006</v>
+        <v>651805</v>
       </c>
       <c r="R19" t="n">
-        <v>6673876</v>
+        <v>6673899</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2818,7 +2831,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2828,7 +2841,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2855,7 +2868,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122301019</v>
+        <v>122300994</v>
       </c>
       <c r="B20" t="n">
         <v>57390</v>
@@ -2907,10 +2920,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>652004</v>
+        <v>651915</v>
       </c>
       <c r="R20" t="n">
-        <v>6673869</v>
+        <v>6673888</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2942,7 +2955,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2952,7 +2965,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2979,10 +2992,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122301058</v>
+        <v>122300988</v>
       </c>
       <c r="B21" t="n">
-        <v>98175</v>
+        <v>5193</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2991,39 +3004,36 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3031,10 +3041,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651981</v>
+        <v>651926</v>
       </c>
       <c r="R21" t="n">
-        <v>6673859</v>
+        <v>6673844</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3066,7 +3076,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3076,7 +3086,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3103,10 +3113,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122301060</v>
+        <v>122301058</v>
       </c>
       <c r="B22" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3138,12 +3148,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -3155,10 +3165,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652000</v>
+        <v>651981</v>
       </c>
       <c r="R22" t="n">
-        <v>6673848</v>
+        <v>6673859</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3190,7 +3200,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3200,7 +3210,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3230,7 +3240,7 @@
         <v>122301036</v>
       </c>
       <c r="B23" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3342,7 +3352,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122300991</v>
+        <v>122301006</v>
       </c>
       <c r="B24" t="n">
         <v>57390</v>
@@ -3384,7 +3394,7 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3394,10 +3404,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651958</v>
+        <v>651860</v>
       </c>
       <c r="R24" t="n">
-        <v>6673868</v>
+        <v>6673862</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3429,7 +3439,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3439,7 +3449,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3466,10 +3476,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301001</v>
+        <v>122301037</v>
       </c>
       <c r="B25" t="n">
-        <v>57390</v>
+        <v>91181</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3482,35 +3492,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3518,10 +3514,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651873</v>
+        <v>651917</v>
       </c>
       <c r="R25" t="n">
-        <v>6673779</v>
+        <v>6673853</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3553,7 +3549,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3563,7 +3559,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3590,10 +3586,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301031</v>
+        <v>122301019</v>
       </c>
       <c r="B26" t="n">
-        <v>74686</v>
+        <v>57390</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3602,30 +3598,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3633,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651805</v>
+        <v>652004</v>
       </c>
       <c r="R26" t="n">
-        <v>6673899</v>
+        <v>6673869</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3668,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3678,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3705,7 +3710,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301021</v>
+        <v>122301020</v>
       </c>
       <c r="B27" t="n">
         <v>57390</v>
@@ -3753,11 +3758,11 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>652056</v>
+        <v>652017</v>
       </c>
       <c r="R27" t="n">
         <v>6673872</v>
@@ -3792,7 +3797,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3802,7 +3807,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3829,7 +3834,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122300993</v>
+        <v>122301007</v>
       </c>
       <c r="B28" t="n">
         <v>57390</v>
@@ -3871,7 +3876,7 @@
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -3881,13 +3886,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651962</v>
+        <v>651778</v>
       </c>
       <c r="R28" t="n">
-        <v>6673882</v>
+        <v>6673895</v>
       </c>
       <c r="S28" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3916,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3926,12 +3931,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122260116</v>
+        <v>122260103</v>
       </c>
       <c r="B29" t="n">
-        <v>100441</v>
+        <v>91229</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3970,31 +3970,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4002,10 +4001,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651859</v>
+        <v>651855</v>
       </c>
       <c r="R29" t="n">
-        <v>6674654</v>
+        <v>6674655</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4037,7 +4036,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4047,7 +4046,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På klibbtickelåga.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4058,6 +4062,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4074,10 +4093,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122260068</v>
+        <v>122260058</v>
       </c>
       <c r="B30" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4086,20 +4105,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4107,16 +4126,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4126,10 +4142,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651928</v>
+        <v>652031</v>
       </c>
       <c r="R30" t="n">
-        <v>6674457</v>
+        <v>6674226</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4161,7 +4177,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4171,7 +4187,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4182,6 +4198,21 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4198,10 +4229,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260072</v>
+        <v>122260096</v>
       </c>
       <c r="B31" t="n">
-        <v>57390</v>
+        <v>80603</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4214,35 +4245,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4250,10 +4272,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651927</v>
+        <v>651930</v>
       </c>
       <c r="R31" t="n">
-        <v>6674447</v>
+        <v>6674592</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4285,7 +4307,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4295,7 +4317,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4322,10 +4344,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260084</v>
+        <v>122260121</v>
       </c>
       <c r="B32" t="n">
-        <v>57527</v>
+        <v>100451</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4334,39 +4356,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4374,13 +4388,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651900</v>
+        <v>651955</v>
       </c>
       <c r="R32" t="n">
-        <v>6674551</v>
+        <v>6674222</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4409,7 +4423,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4419,7 +4433,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,10 +4460,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260119</v>
+        <v>122260084</v>
       </c>
       <c r="B33" t="n">
-        <v>100441</v>
+        <v>57527</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4458,31 +4472,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4490,13 +4512,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651950</v>
+        <v>651900</v>
       </c>
       <c r="R33" t="n">
-        <v>6674465</v>
+        <v>6674551</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4525,7 +4547,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4535,7 +4557,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4562,10 +4584,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260063</v>
+        <v>122260115</v>
       </c>
       <c r="B34" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4574,39 +4596,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4614,10 +4628,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651872</v>
+        <v>651891</v>
       </c>
       <c r="R34" t="n">
-        <v>6674674</v>
+        <v>6674645</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4649,7 +4663,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4659,7 +4673,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4686,10 +4700,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122260125</v>
+        <v>122260118</v>
       </c>
       <c r="B35" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4730,10 +4744,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651973</v>
+        <v>651893</v>
       </c>
       <c r="R35" t="n">
-        <v>6674332</v>
+        <v>6674508</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4765,7 +4779,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4775,7 +4789,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4802,10 +4816,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122260115</v>
+        <v>122260126</v>
       </c>
       <c r="B36" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4846,10 +4860,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651891</v>
+        <v>651941</v>
       </c>
       <c r="R36" t="n">
-        <v>6674645</v>
+        <v>6674469</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4881,7 +4895,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4891,7 +4905,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4918,7 +4932,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122260066</v>
+        <v>122260064</v>
       </c>
       <c r="B37" t="n">
         <v>57390</v>
@@ -4960,7 +4974,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4970,10 +4984,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651934</v>
+        <v>651845</v>
       </c>
       <c r="R37" t="n">
-        <v>6674510</v>
+        <v>6674626</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5005,7 +5019,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5015,7 +5029,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5042,10 +5056,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122260074</v>
+        <v>122260085</v>
       </c>
       <c r="B38" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5054,20 +5068,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5094,13 +5108,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651923</v>
+        <v>651895</v>
       </c>
       <c r="R38" t="n">
-        <v>6674436</v>
+        <v>6674630</v>
       </c>
       <c r="S38" t="n">
-        <v>98</v>
+        <v>45</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5129,7 +5143,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5139,12 +5153,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Hörd i norr.</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5171,10 +5180,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260117</v>
+        <v>122260111</v>
       </c>
       <c r="B39" t="n">
-        <v>100441</v>
+        <v>98185</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5183,29 +5192,37 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
@@ -5215,10 +5232,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651906</v>
+        <v>651949</v>
       </c>
       <c r="R39" t="n">
-        <v>6674571</v>
+        <v>6674415</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5250,7 +5267,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5260,7 +5277,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5287,10 +5304,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260111</v>
+        <v>122260110</v>
       </c>
       <c r="B40" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5322,7 +5339,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5342,7 +5359,7 @@
         <v>651949</v>
       </c>
       <c r="R40" t="n">
-        <v>6674415</v>
+        <v>6674420</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5374,7 +5391,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5384,7 +5401,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5411,10 +5433,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260096</v>
+        <v>122260077</v>
       </c>
       <c r="B41" t="n">
-        <v>80602</v>
+        <v>57390</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5427,26 +5449,35 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5454,10 +5485,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651930</v>
+        <v>651964</v>
       </c>
       <c r="R41" t="n">
-        <v>6674592</v>
+        <v>6674220</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5489,7 +5520,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5499,7 +5530,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5526,7 +5557,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122260070</v>
+        <v>122260072</v>
       </c>
       <c r="B42" t="n">
         <v>57390</v>
@@ -5568,7 +5599,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5578,10 +5609,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651967</v>
+        <v>651927</v>
       </c>
       <c r="R42" t="n">
-        <v>6674433</v>
+        <v>6674447</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5613,7 +5644,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5623,7 +5654,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5650,10 +5681,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260120</v>
+        <v>122260117</v>
       </c>
       <c r="B43" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5694,10 +5725,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651967</v>
+        <v>651906</v>
       </c>
       <c r="R43" t="n">
-        <v>6674316</v>
+        <v>6674571</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5729,7 +5760,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5739,7 +5770,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5766,7 +5797,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260080</v>
+        <v>122260063</v>
       </c>
       <c r="B44" t="n">
         <v>57390</v>
@@ -5818,10 +5849,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>652019</v>
+        <v>651872</v>
       </c>
       <c r="R44" t="n">
-        <v>6674239</v>
+        <v>6674674</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5853,7 +5884,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5863,7 +5894,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5890,7 +5921,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122260075</v>
+        <v>122260061</v>
       </c>
       <c r="B45" t="n">
         <v>57390</v>
@@ -5932,7 +5963,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5942,10 +5973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651900</v>
+        <v>651886</v>
       </c>
       <c r="R45" t="n">
-        <v>6674390</v>
+        <v>6674654</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5977,7 +6008,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5987,7 +6018,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6014,10 +6045,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122260118</v>
+        <v>122260066</v>
       </c>
       <c r="B46" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6026,31 +6057,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6058,10 +6097,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651893</v>
+        <v>651934</v>
       </c>
       <c r="R46" t="n">
-        <v>6674508</v>
+        <v>6674510</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6093,7 +6132,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6103,7 +6142,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6130,10 +6169,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260110</v>
+        <v>122260071</v>
       </c>
       <c r="B47" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6142,39 +6181,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6182,10 +6221,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651949</v>
+        <v>651930</v>
       </c>
       <c r="R47" t="n">
-        <v>6674420</v>
+        <v>6674444</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6217,7 +6256,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6227,12 +6266,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6259,10 +6293,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260114</v>
+        <v>122260076</v>
       </c>
       <c r="B48" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6271,39 +6305,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6311,10 +6345,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>652010</v>
+        <v>651949</v>
       </c>
       <c r="R48" t="n">
-        <v>6674220</v>
+        <v>6674279</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6346,7 +6380,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6356,7 +6390,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6383,10 +6417,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260103</v>
+        <v>122260080</v>
       </c>
       <c r="B49" t="n">
-        <v>91219</v>
+        <v>57390</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6395,30 +6429,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6426,10 +6469,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651855</v>
+        <v>652019</v>
       </c>
       <c r="R49" t="n">
-        <v>6674655</v>
+        <v>6674239</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6461,7 +6504,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6471,12 +6514,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På klibbtickelåga.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6487,21 +6525,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6518,10 +6541,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260061</v>
+        <v>122260125</v>
       </c>
       <c r="B50" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6530,39 +6553,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6570,10 +6585,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651886</v>
+        <v>651973</v>
       </c>
       <c r="R50" t="n">
-        <v>6674654</v>
+        <v>6674332</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6605,7 +6620,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6615,7 +6630,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6642,10 +6657,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122260085</v>
+        <v>122260114</v>
       </c>
       <c r="B51" t="n">
-        <v>57744</v>
+        <v>98185</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6654,39 +6669,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6694,13 +6709,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651895</v>
+        <v>652010</v>
       </c>
       <c r="R51" t="n">
-        <v>6674630</v>
+        <v>6674220</v>
       </c>
       <c r="S51" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6729,7 +6744,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6739,7 +6754,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6766,7 +6781,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260077</v>
+        <v>122260070</v>
       </c>
       <c r="B52" t="n">
         <v>57390</v>
@@ -6818,10 +6833,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651964</v>
+        <v>651967</v>
       </c>
       <c r="R52" t="n">
-        <v>6674220</v>
+        <v>6674433</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6853,7 +6868,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6863,7 +6878,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6890,10 +6905,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260121</v>
+        <v>122260074</v>
       </c>
       <c r="B53" t="n">
-        <v>100441</v>
+        <v>57390</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6902,31 +6917,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6934,13 +6957,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651955</v>
+        <v>651923</v>
       </c>
       <c r="R53" t="n">
-        <v>6674222</v>
+        <v>6674436</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6969,7 +6992,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6979,7 +7002,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Hörd i norr.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7006,7 +7034,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260064</v>
+        <v>122260068</v>
       </c>
       <c r="B54" t="n">
         <v>57390</v>
@@ -7048,7 +7076,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7058,10 +7086,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651845</v>
+        <v>651928</v>
       </c>
       <c r="R54" t="n">
-        <v>6674626</v>
+        <v>6674457</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7093,7 +7121,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7103,7 +7131,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7130,10 +7158,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122260071</v>
+        <v>122260113</v>
       </c>
       <c r="B55" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7142,39 +7170,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7182,10 +7210,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651930</v>
+        <v>651906</v>
       </c>
       <c r="R55" t="n">
-        <v>6674444</v>
+        <v>6674392</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7217,7 +7245,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7227,7 +7255,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7257,7 +7285,7 @@
         <v>122260100</v>
       </c>
       <c r="B56" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7384,10 +7412,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260126</v>
+        <v>122260120</v>
       </c>
       <c r="B57" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7428,10 +7456,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651941</v>
+        <v>651967</v>
       </c>
       <c r="R57" t="n">
-        <v>6674469</v>
+        <v>6674316</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7463,7 +7491,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7473,7 +7501,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7500,10 +7528,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260058</v>
+        <v>122260119</v>
       </c>
       <c r="B58" t="n">
-        <v>5193</v>
+        <v>100451</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7516,32 +7544,27 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7549,10 +7572,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>652031</v>
+        <v>651950</v>
       </c>
       <c r="R58" t="n">
-        <v>6674226</v>
+        <v>6674465</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7584,7 +7607,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7594,7 +7617,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7605,21 +7628,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7636,10 +7644,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260076</v>
+        <v>122260116</v>
       </c>
       <c r="B59" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7648,39 +7656,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7688,10 +7688,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651949</v>
+        <v>651859</v>
       </c>
       <c r="R59" t="n">
-        <v>6674279</v>
+        <v>6674654</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7760,10 +7760,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260113</v>
+        <v>122260075</v>
       </c>
       <c r="B60" t="n">
-        <v>98175</v>
+        <v>57390</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7772,39 +7772,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651906</v>
+        <v>651900</v>
       </c>
       <c r="R60" t="n">
-        <v>6674392</v>
+        <v>6674390</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7884,10 +7884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301074</v>
+        <v>122301026</v>
       </c>
       <c r="B61" t="n">
-        <v>100441</v>
+        <v>57527</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7896,31 +7896,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7928,13 +7936,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651855</v>
+        <v>651977</v>
       </c>
       <c r="R61" t="n">
-        <v>6673907</v>
+        <v>6673906</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7963,7 +7971,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7973,7 +7981,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8000,10 +8008,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301015</v>
+        <v>122301027</v>
       </c>
       <c r="B62" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8012,20 +8020,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -8035,16 +8043,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8052,13 +8056,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651777</v>
+        <v>651983</v>
       </c>
       <c r="R62" t="n">
-        <v>6673975</v>
+        <v>6673930</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8087,7 +8091,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8097,7 +8101,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8127,7 +8131,7 @@
         <v>122301065</v>
       </c>
       <c r="B63" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8240,10 +8244,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301073</v>
+        <v>122301050</v>
       </c>
       <c r="B64" t="n">
-        <v>100441</v>
+        <v>98185</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8252,29 +8256,37 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
@@ -8284,10 +8296,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651817</v>
+        <v>651948</v>
       </c>
       <c r="R64" t="n">
-        <v>6673939</v>
+        <v>6673906</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8319,7 +8331,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8329,7 +8341,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8356,10 +8368,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301075</v>
+        <v>122301063</v>
       </c>
       <c r="B65" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8400,10 +8412,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651975</v>
+        <v>651949</v>
       </c>
       <c r="R65" t="n">
-        <v>6673928</v>
+        <v>6673910</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8435,7 +8447,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8445,7 +8457,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8472,10 +8484,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301050</v>
+        <v>122301067</v>
       </c>
       <c r="B66" t="n">
-        <v>98175</v>
+        <v>100451</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8484,37 +8496,29 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -8524,10 +8528,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651948</v>
+        <v>652040</v>
       </c>
       <c r="R66" t="n">
-        <v>6673906</v>
+        <v>6673920</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8559,7 +8563,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8569,7 +8573,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8596,10 +8600,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301063</v>
+        <v>122301075</v>
       </c>
       <c r="B67" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8640,10 +8644,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>651949</v>
+        <v>651975</v>
       </c>
       <c r="R67" t="n">
-        <v>6673910</v>
+        <v>6673928</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8675,7 +8679,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8685,7 +8689,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8712,10 +8716,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301067</v>
+        <v>122301066</v>
       </c>
       <c r="B68" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8756,10 +8760,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>652040</v>
+        <v>652079</v>
       </c>
       <c r="R68" t="n">
-        <v>6673920</v>
+        <v>6673929</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8791,7 +8795,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8801,7 +8805,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8828,10 +8832,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301027</v>
+        <v>122301013</v>
       </c>
       <c r="B69" t="n">
-        <v>57744</v>
+        <v>57390</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8840,20 +8844,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8863,12 +8867,16 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8876,13 +8884,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651983</v>
+        <v>651745</v>
       </c>
       <c r="R69" t="n">
-        <v>6673930</v>
+        <v>6673922</v>
       </c>
       <c r="S69" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8911,7 +8919,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8921,7 +8929,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8948,10 +8956,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301066</v>
+        <v>122301081</v>
       </c>
       <c r="B70" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8992,10 +9000,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>652079</v>
+        <v>652036</v>
       </c>
       <c r="R70" t="n">
-        <v>6673929</v>
+        <v>6673988</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -9027,7 +9035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9037,7 +9045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9064,10 +9072,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301026</v>
+        <v>122301015</v>
       </c>
       <c r="B71" t="n">
-        <v>57527</v>
+        <v>57390</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9080,21 +9088,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -9106,7 +9114,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -9116,13 +9124,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651977</v>
+        <v>651777</v>
       </c>
       <c r="R71" t="n">
-        <v>6673906</v>
+        <v>6673975</v>
       </c>
       <c r="S71" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9151,7 +9159,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9161,7 +9169,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9188,10 +9196,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301013</v>
+        <v>122301079</v>
       </c>
       <c r="B72" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9200,39 +9208,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9240,10 +9240,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651745</v>
+        <v>652014</v>
       </c>
       <c r="R72" t="n">
-        <v>6673922</v>
+        <v>6673954</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9312,10 +9312,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301079</v>
+        <v>122301025</v>
       </c>
       <c r="B73" t="n">
-        <v>100441</v>
+        <v>57527</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9324,45 +9324,53 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>652014</v>
+        <v>651941</v>
       </c>
       <c r="R73" t="n">
-        <v>6673954</v>
+        <v>6674093</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9391,7 +9399,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9401,7 +9409,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9552,10 +9560,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301081</v>
+        <v>122301080</v>
       </c>
       <c r="B75" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9596,10 +9604,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>652036</v>
+        <v>652011</v>
       </c>
       <c r="R75" t="n">
-        <v>6673988</v>
+        <v>6673969</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9631,7 +9639,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9641,7 +9649,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9668,10 +9676,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301080</v>
+        <v>122301073</v>
       </c>
       <c r="B76" t="n">
-        <v>100441</v>
+        <v>100451</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9712,10 +9720,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>652011</v>
+        <v>651817</v>
       </c>
       <c r="R76" t="n">
-        <v>6673969</v>
+        <v>6673939</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9747,7 +9755,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9757,7 +9765,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9784,10 +9792,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301025</v>
+        <v>122301074</v>
       </c>
       <c r="B77" t="n">
-        <v>57527</v>
+        <v>100451</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9796,53 +9804,45 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651941</v>
+        <v>651855</v>
       </c>
       <c r="R77" t="n">
-        <v>6674093</v>
+        <v>6673907</v>
       </c>
       <c r="S77" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9911,7 +9911,7 @@
         <v>122260107</v>
       </c>
       <c r="B78" t="n">
-        <v>95722</v>
+        <v>95732</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122300997</v>
+        <v>122301036</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>90789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651883</v>
+        <v>652047</v>
       </c>
       <c r="R2" t="n">
-        <v>6673732</v>
+        <v>6673893</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122301062</v>
+        <v>122300997</v>
       </c>
       <c r="B3" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,50 +802,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651973</v>
+        <v>651883</v>
       </c>
       <c r="R3" t="n">
-        <v>6673897</v>
+        <v>6673732</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -886,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1047,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122301068</v>
+        <v>122301004</v>
       </c>
       <c r="B5" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,42 +1050,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651906</v>
+        <v>651888</v>
       </c>
       <c r="R5" t="n">
-        <v>6673752</v>
+        <v>6673877</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1126,7 +1125,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1135,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1162,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122301004</v>
+        <v>122301021</v>
       </c>
       <c r="B6" t="n">
         <v>57390</v>
@@ -1205,20 +1204,20 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651888</v>
+        <v>652056</v>
       </c>
       <c r="R6" t="n">
-        <v>6673877</v>
+        <v>6673872</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1250,7 +1249,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1260,7 +1259,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,10 +1286,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122301064</v>
+        <v>122301007</v>
       </c>
       <c r="B7" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1299,31 +1298,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1331,10 +1338,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651993</v>
+        <v>651778</v>
       </c>
       <c r="R7" t="n">
-        <v>6673896</v>
+        <v>6673895</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1366,7 +1373,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1376,7 +1383,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122301021</v>
+        <v>122301053</v>
       </c>
       <c r="B8" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,50 +1422,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>652056</v>
+        <v>651986</v>
       </c>
       <c r="R8" t="n">
-        <v>6673872</v>
+        <v>6673841</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1490,7 +1497,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1500,7 +1507,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122300995</v>
+        <v>122300988</v>
       </c>
       <c r="B9" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,20 +1551,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1560,16 +1572,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1579,10 +1588,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651899</v>
+        <v>651926</v>
       </c>
       <c r="R9" t="n">
-        <v>6673777</v>
+        <v>6673844</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1614,7 +1623,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1633,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1651,10 +1660,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122300991</v>
+        <v>122301056</v>
       </c>
       <c r="B10" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1663,39 +1672,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1703,10 +1712,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651958</v>
+        <v>651930</v>
       </c>
       <c r="R10" t="n">
-        <v>6673868</v>
+        <v>6673898</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1738,7 +1747,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1748,7 +1757,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,10 +1784,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122300999</v>
+        <v>122301071</v>
       </c>
       <c r="B11" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1787,39 +1796,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1827,10 +1828,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651879</v>
+        <v>651840</v>
       </c>
       <c r="R11" t="n">
-        <v>6673776</v>
+        <v>6673881</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1862,7 +1863,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1872,7 +1873,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1899,7 +1900,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122300993</v>
+        <v>122301020</v>
       </c>
       <c r="B12" t="n">
         <v>57390</v>
@@ -1941,7 +1942,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1951,13 +1952,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651962</v>
+        <v>652017</v>
       </c>
       <c r="R12" t="n">
-        <v>6673882</v>
+        <v>6673872</v>
       </c>
       <c r="S12" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1986,7 +1987,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1996,12 +1997,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2028,10 +2024,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122301071</v>
+        <v>122301019</v>
       </c>
       <c r="B13" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2040,31 +2036,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2072,10 +2076,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651840</v>
+        <v>652004</v>
       </c>
       <c r="R13" t="n">
-        <v>6673881</v>
+        <v>6673869</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2107,7 +2111,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,7 +2121,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2144,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301077</v>
+        <v>122300991</v>
       </c>
       <c r="B14" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2156,31 +2160,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2188,10 +2200,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651993</v>
+        <v>651958</v>
       </c>
       <c r="R14" t="n">
-        <v>6673867</v>
+        <v>6673868</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2223,7 +2235,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2233,7 +2245,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2260,10 +2272,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122301060</v>
+        <v>122300995</v>
       </c>
       <c r="B15" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2272,39 +2284,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2312,10 +2324,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>652000</v>
+        <v>651899</v>
       </c>
       <c r="R15" t="n">
-        <v>6673848</v>
+        <v>6673777</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2347,7 +2359,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2357,7 +2369,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2384,10 +2396,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301078</v>
+        <v>122301060</v>
       </c>
       <c r="B16" t="n">
-        <v>100451</v>
+        <v>98185</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2396,29 +2408,37 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -2428,10 +2448,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>652006</v>
+        <v>652000</v>
       </c>
       <c r="R16" t="n">
-        <v>6673876</v>
+        <v>6673848</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2463,7 +2483,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2473,7 +2493,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2500,10 +2520,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301056</v>
+        <v>122300999</v>
       </c>
       <c r="B17" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2512,39 +2532,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2552,10 +2572,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651930</v>
+        <v>651879</v>
       </c>
       <c r="R17" t="n">
-        <v>6673898</v>
+        <v>6673776</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2587,7 +2607,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2597,7 +2617,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2624,10 +2644,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122301053</v>
+        <v>122301006</v>
       </c>
       <c r="B18" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2636,39 +2656,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2676,10 +2696,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651986</v>
+        <v>651860</v>
       </c>
       <c r="R18" t="n">
-        <v>6673841</v>
+        <v>6673862</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2711,7 +2731,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2721,12 +2741,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2753,10 +2768,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122301031</v>
+        <v>122300993</v>
       </c>
       <c r="B19" t="n">
-        <v>74686</v>
+        <v>57390</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2765,30 +2780,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2796,13 +2820,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651805</v>
+        <v>651962</v>
       </c>
       <c r="R19" t="n">
-        <v>6673899</v>
+        <v>6673882</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2831,7 +2855,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2841,7 +2865,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2868,10 +2897,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122300994</v>
+        <v>122301037</v>
       </c>
       <c r="B20" t="n">
-        <v>57390</v>
+        <v>91181</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,35 +2913,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2920,10 +2935,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651915</v>
+        <v>651917</v>
       </c>
       <c r="R20" t="n">
-        <v>6673888</v>
+        <v>6673853</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2955,7 +2970,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2965,7 +2980,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2992,10 +3007,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122300988</v>
+        <v>122301031</v>
       </c>
       <c r="B21" t="n">
-        <v>5193</v>
+        <v>74686</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3008,32 +3023,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>6426</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3041,10 +3050,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651926</v>
+        <v>651805</v>
       </c>
       <c r="R21" t="n">
-        <v>6673844</v>
+        <v>6673899</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3076,7 +3085,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3086,7 +3095,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3113,10 +3122,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122301058</v>
+        <v>122300994</v>
       </c>
       <c r="B22" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3125,39 +3134,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3165,10 +3174,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651981</v>
+        <v>651915</v>
       </c>
       <c r="R22" t="n">
-        <v>6673859</v>
+        <v>6673888</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3200,7 +3209,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3210,7 +3219,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3237,10 +3246,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122301036</v>
+        <v>122301078</v>
       </c>
       <c r="B23" t="n">
-        <v>90789</v>
+        <v>100451</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3249,30 +3258,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3280,10 +3290,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>652047</v>
+        <v>652006</v>
       </c>
       <c r="R23" t="n">
-        <v>6673893</v>
+        <v>6673876</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3315,7 +3325,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3325,7 +3335,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3352,10 +3362,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122301006</v>
+        <v>122301068</v>
       </c>
       <c r="B24" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3364,50 +3374,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651860</v>
+        <v>651906</v>
       </c>
       <c r="R24" t="n">
-        <v>6673862</v>
+        <v>6673752</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3439,7 +3441,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3449,7 +3451,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3476,10 +3478,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301037</v>
+        <v>122301064</v>
       </c>
       <c r="B25" t="n">
-        <v>91181</v>
+        <v>100451</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3488,25 +3490,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040162</v>
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3514,10 +3522,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651917</v>
+        <v>651993</v>
       </c>
       <c r="R25" t="n">
-        <v>6673853</v>
+        <v>6673896</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3549,7 +3557,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3559,7 +3567,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3586,10 +3594,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301019</v>
+        <v>122301077</v>
       </c>
       <c r="B26" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3598,39 +3606,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3638,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>652004</v>
+        <v>651993</v>
       </c>
       <c r="R26" t="n">
-        <v>6673869</v>
+        <v>6673867</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3710,10 +3710,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301020</v>
+        <v>122301058</v>
       </c>
       <c r="B27" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3722,39 +3722,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>652017</v>
+        <v>651981</v>
       </c>
       <c r="R27" t="n">
-        <v>6673872</v>
+        <v>6673859</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3834,10 +3834,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122301007</v>
+        <v>122301062</v>
       </c>
       <c r="B28" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3846,39 +3846,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651778</v>
+        <v>651973</v>
       </c>
       <c r="R28" t="n">
-        <v>6673895</v>
+        <v>6673897</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122260103</v>
+        <v>122260064</v>
       </c>
       <c r="B29" t="n">
-        <v>91229</v>
+        <v>57390</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3970,30 +3970,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4001,10 +4010,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651855</v>
+        <v>651845</v>
       </c>
       <c r="R29" t="n">
-        <v>6674655</v>
+        <v>6674626</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4036,7 +4045,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4046,12 +4055,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På klibbtickelåga.</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4062,21 +4066,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4093,10 +4082,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122260058</v>
+        <v>122260066</v>
       </c>
       <c r="B30" t="n">
-        <v>5193</v>
+        <v>57390</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4105,20 +4094,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4126,13 +4115,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4142,10 +4134,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>652031</v>
+        <v>651934</v>
       </c>
       <c r="R30" t="n">
-        <v>6674226</v>
+        <v>6674510</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4177,7 +4169,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4187,7 +4179,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4198,21 +4190,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4229,10 +4206,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260096</v>
+        <v>122260116</v>
       </c>
       <c r="B31" t="n">
-        <v>80603</v>
+        <v>100451</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4241,30 +4218,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4272,10 +4250,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651930</v>
+        <v>651859</v>
       </c>
       <c r="R31" t="n">
-        <v>6674592</v>
+        <v>6674654</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4307,7 +4285,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4317,7 +4295,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4344,10 +4322,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260121</v>
+        <v>122260103</v>
       </c>
       <c r="B32" t="n">
-        <v>100451</v>
+        <v>91229</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4356,31 +4334,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4388,10 +4365,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651955</v>
+        <v>651855</v>
       </c>
       <c r="R32" t="n">
-        <v>6674222</v>
+        <v>6674655</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4423,7 +4400,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4433,7 +4410,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På klibbtickelåga.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4444,6 +4426,21 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4460,10 +4457,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260084</v>
+        <v>122260125</v>
       </c>
       <c r="B33" t="n">
-        <v>57527</v>
+        <v>100451</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4472,39 +4469,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4512,13 +4501,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651900</v>
+        <v>651973</v>
       </c>
       <c r="R33" t="n">
-        <v>6674551</v>
+        <v>6674332</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4547,7 +4536,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4557,7 +4546,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4584,10 +4573,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260115</v>
+        <v>122260063</v>
       </c>
       <c r="B34" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4596,31 +4585,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4628,10 +4625,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651891</v>
+        <v>651872</v>
       </c>
       <c r="R34" t="n">
-        <v>6674645</v>
+        <v>6674674</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4663,7 +4660,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4673,7 +4670,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4816,10 +4813,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122260126</v>
+        <v>122260100</v>
       </c>
       <c r="B36" t="n">
-        <v>100451</v>
+        <v>90789</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4828,31 +4825,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4860,10 +4856,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651941</v>
+        <v>652034</v>
       </c>
       <c r="R36" t="n">
-        <v>6674469</v>
+        <v>6674236</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4895,7 +4891,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4905,7 +4901,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4916,6 +4912,21 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4932,10 +4943,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122260064</v>
+        <v>122260085</v>
       </c>
       <c r="B37" t="n">
-        <v>57390</v>
+        <v>57744</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4944,20 +4955,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4974,7 +4985,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -4984,13 +4995,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651845</v>
+        <v>651895</v>
       </c>
       <c r="R37" t="n">
-        <v>6674626</v>
+        <v>6674630</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5019,7 +5030,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5029,7 +5040,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5056,10 +5067,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122260085</v>
+        <v>122260061</v>
       </c>
       <c r="B38" t="n">
-        <v>57744</v>
+        <v>57390</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5068,20 +5079,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5098,7 +5109,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5108,13 +5119,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651895</v>
+        <v>651886</v>
       </c>
       <c r="R38" t="n">
-        <v>6674630</v>
+        <v>6674654</v>
       </c>
       <c r="S38" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5143,7 +5154,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5153,7 +5164,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5180,10 +5191,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260111</v>
+        <v>122260071</v>
       </c>
       <c r="B39" t="n">
-        <v>98185</v>
+        <v>57390</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5192,39 +5203,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5232,10 +5243,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651949</v>
+        <v>651930</v>
       </c>
       <c r="R39" t="n">
-        <v>6674415</v>
+        <v>6674444</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5267,7 +5278,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5277,7 +5288,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5304,10 +5315,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260110</v>
+        <v>122260119</v>
       </c>
       <c r="B40" t="n">
-        <v>98185</v>
+        <v>100451</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5316,37 +5327,29 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5356,10 +5359,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651949</v>
+        <v>651950</v>
       </c>
       <c r="R40" t="n">
-        <v>6674420</v>
+        <v>6674465</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5391,7 +5394,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5401,12 +5404,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5433,7 +5431,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260077</v>
+        <v>122260080</v>
       </c>
       <c r="B41" t="n">
         <v>57390</v>
@@ -5475,7 +5473,7 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -5485,10 +5483,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651964</v>
+        <v>652019</v>
       </c>
       <c r="R41" t="n">
-        <v>6674220</v>
+        <v>6674239</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5520,7 +5518,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5530,7 +5528,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5557,10 +5555,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122260072</v>
+        <v>122260113</v>
       </c>
       <c r="B42" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5569,39 +5567,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5609,10 +5607,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651927</v>
+        <v>651906</v>
       </c>
       <c r="R42" t="n">
-        <v>6674447</v>
+        <v>6674392</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5644,7 +5642,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5654,7 +5652,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5681,7 +5679,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260117</v>
+        <v>122260126</v>
       </c>
       <c r="B43" t="n">
         <v>100451</v>
@@ -5725,10 +5723,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651906</v>
+        <v>651941</v>
       </c>
       <c r="R43" t="n">
-        <v>6674571</v>
+        <v>6674469</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5760,7 +5758,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5770,7 +5768,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5797,10 +5795,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260063</v>
+        <v>122260084</v>
       </c>
       <c r="B44" t="n">
-        <v>57390</v>
+        <v>57527</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5813,33 +5811,33 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5849,13 +5847,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651872</v>
+        <v>651900</v>
       </c>
       <c r="R44" t="n">
-        <v>6674674</v>
+        <v>6674551</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5884,7 +5882,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5894,7 +5892,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5921,10 +5919,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122260061</v>
+        <v>122260121</v>
       </c>
       <c r="B45" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5933,39 +5931,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5973,10 +5963,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651886</v>
+        <v>651955</v>
       </c>
       <c r="R45" t="n">
-        <v>6674654</v>
+        <v>6674222</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -6008,7 +5998,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6018,7 +6008,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6045,10 +6035,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122260066</v>
+        <v>122260117</v>
       </c>
       <c r="B46" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6057,39 +6047,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6097,10 +6079,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651934</v>
+        <v>651906</v>
       </c>
       <c r="R46" t="n">
-        <v>6674510</v>
+        <v>6674571</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6132,7 +6114,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6142,7 +6124,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6169,7 +6151,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260071</v>
+        <v>122260072</v>
       </c>
       <c r="B47" t="n">
         <v>57390</v>
@@ -6221,10 +6203,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651930</v>
+        <v>651927</v>
       </c>
       <c r="R47" t="n">
-        <v>6674444</v>
+        <v>6674447</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6256,7 +6238,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6266,7 +6248,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6293,7 +6275,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260076</v>
+        <v>122260074</v>
       </c>
       <c r="B48" t="n">
         <v>57390</v>
@@ -6335,7 +6317,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6345,13 +6327,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>651949</v>
+        <v>651923</v>
       </c>
       <c r="R48" t="n">
-        <v>6674279</v>
+        <v>6674436</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6380,7 +6362,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6390,7 +6372,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Hörd i norr.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6417,10 +6404,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260080</v>
+        <v>122260110</v>
       </c>
       <c r="B49" t="n">
-        <v>57390</v>
+        <v>98185</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6429,39 +6416,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6469,10 +6456,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>652019</v>
+        <v>651949</v>
       </c>
       <c r="R49" t="n">
-        <v>6674239</v>
+        <v>6674420</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6504,7 +6491,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6514,7 +6501,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6541,10 +6533,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260125</v>
+        <v>122260096</v>
       </c>
       <c r="B50" t="n">
-        <v>100451</v>
+        <v>80603</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6553,31 +6545,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6585,10 +6576,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651973</v>
+        <v>651930</v>
       </c>
       <c r="R50" t="n">
-        <v>6674332</v>
+        <v>6674592</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6620,7 +6611,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6630,7 +6621,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6781,7 +6772,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260070</v>
+        <v>122260077</v>
       </c>
       <c r="B52" t="n">
         <v>57390</v>
@@ -6833,10 +6824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651967</v>
+        <v>651964</v>
       </c>
       <c r="R52" t="n">
-        <v>6674433</v>
+        <v>6674220</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6868,7 +6859,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6878,7 +6869,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6905,7 +6896,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260074</v>
+        <v>122260076</v>
       </c>
       <c r="B53" t="n">
         <v>57390</v>
@@ -6947,7 +6938,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6957,13 +6948,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651923</v>
+        <v>651949</v>
       </c>
       <c r="R53" t="n">
-        <v>6674436</v>
+        <v>6674279</v>
       </c>
       <c r="S53" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6992,7 +6983,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7002,12 +6993,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Hörd i norr.</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7034,7 +7020,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260068</v>
+        <v>122260075</v>
       </c>
       <c r="B54" t="n">
         <v>57390</v>
@@ -7076,7 +7062,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7086,10 +7072,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651928</v>
+        <v>651900</v>
       </c>
       <c r="R54" t="n">
-        <v>6674457</v>
+        <v>6674390</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7121,7 +7107,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7131,7 +7117,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7158,10 +7144,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122260113</v>
+        <v>122260120</v>
       </c>
       <c r="B55" t="n">
-        <v>98185</v>
+        <v>100451</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7170,37 +7156,29 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -7210,10 +7188,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651906</v>
+        <v>651967</v>
       </c>
       <c r="R55" t="n">
-        <v>6674392</v>
+        <v>6674316</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7245,7 +7223,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7255,7 +7233,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7282,10 +7260,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260100</v>
+        <v>122260111</v>
       </c>
       <c r="B56" t="n">
-        <v>90789</v>
+        <v>98185</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7294,30 +7272,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7325,10 +7312,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>652034</v>
+        <v>651949</v>
       </c>
       <c r="R56" t="n">
-        <v>6674236</v>
+        <v>6674415</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7360,7 +7347,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7370,7 +7357,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7381,21 +7368,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7412,7 +7384,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260120</v>
+        <v>122260115</v>
       </c>
       <c r="B57" t="n">
         <v>100451</v>
@@ -7456,10 +7428,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651967</v>
+        <v>651891</v>
       </c>
       <c r="R57" t="n">
-        <v>6674316</v>
+        <v>6674645</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7491,7 +7463,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7501,7 +7473,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7528,10 +7500,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260119</v>
+        <v>122260068</v>
       </c>
       <c r="B58" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7540,31 +7512,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7572,10 +7552,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>651950</v>
+        <v>651928</v>
       </c>
       <c r="R58" t="n">
-        <v>6674465</v>
+        <v>6674457</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7607,7 +7587,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7617,7 +7597,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7644,10 +7624,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260116</v>
+        <v>122260070</v>
       </c>
       <c r="B59" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7656,31 +7636,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7688,10 +7676,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651859</v>
+        <v>651967</v>
       </c>
       <c r="R59" t="n">
-        <v>6674654</v>
+        <v>6674433</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7723,7 +7711,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7733,7 +7721,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7760,10 +7748,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260075</v>
+        <v>122260058</v>
       </c>
       <c r="B60" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7772,20 +7760,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7793,16 +7781,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7812,10 +7797,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651900</v>
+        <v>652031</v>
       </c>
       <c r="R60" t="n">
-        <v>6674390</v>
+        <v>6674226</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7847,7 +7832,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7857,7 +7842,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7868,6 +7853,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7884,10 +7884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301026</v>
+        <v>122301050</v>
       </c>
       <c r="B61" t="n">
-        <v>57527</v>
+        <v>98185</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7896,39 +7896,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7936,13 +7936,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651977</v>
+        <v>651948</v>
       </c>
       <c r="R61" t="n">
         <v>6673906</v>
       </c>
       <c r="S61" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8008,10 +8008,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301027</v>
+        <v>122301079</v>
       </c>
       <c r="B62" t="n">
-        <v>57744</v>
+        <v>100451</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8024,31 +8024,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8056,13 +8052,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651983</v>
+        <v>652014</v>
       </c>
       <c r="R62" t="n">
-        <v>6673930</v>
+        <v>6673954</v>
       </c>
       <c r="S62" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8091,7 +8087,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8101,7 +8097,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8128,7 +8124,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301065</v>
+        <v>122301066</v>
       </c>
       <c r="B63" t="n">
         <v>100451</v>
@@ -8172,10 +8168,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>652034</v>
+        <v>652079</v>
       </c>
       <c r="R63" t="n">
-        <v>6673906</v>
+        <v>6673929</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8207,7 +8203,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8217,7 +8213,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8244,10 +8240,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301050</v>
+        <v>122301063</v>
       </c>
       <c r="B64" t="n">
-        <v>98185</v>
+        <v>100451</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8256,37 +8252,29 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
@@ -8296,10 +8284,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651948</v>
+        <v>651949</v>
       </c>
       <c r="R64" t="n">
-        <v>6673906</v>
+        <v>6673910</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8331,7 +8319,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8341,7 +8329,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8368,7 +8356,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301063</v>
+        <v>122301081</v>
       </c>
       <c r="B65" t="n">
         <v>100451</v>
@@ -8412,10 +8400,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651949</v>
+        <v>652036</v>
       </c>
       <c r="R65" t="n">
-        <v>6673910</v>
+        <v>6673988</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8447,7 +8435,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8457,7 +8445,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8484,7 +8472,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301067</v>
+        <v>122301080</v>
       </c>
       <c r="B66" t="n">
         <v>100451</v>
@@ -8528,10 +8516,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>652040</v>
+        <v>652011</v>
       </c>
       <c r="R66" t="n">
-        <v>6673920</v>
+        <v>6673969</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8563,7 +8551,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8573,7 +8561,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8600,7 +8588,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301075</v>
+        <v>122301073</v>
       </c>
       <c r="B67" t="n">
         <v>100451</v>
@@ -8644,10 +8632,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>651975</v>
+        <v>651817</v>
       </c>
       <c r="R67" t="n">
-        <v>6673928</v>
+        <v>6673939</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8679,7 +8667,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8689,7 +8677,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8716,10 +8704,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301066</v>
+        <v>122301026</v>
       </c>
       <c r="B68" t="n">
-        <v>100451</v>
+        <v>57527</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8728,31 +8716,39 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8760,13 +8756,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>652079</v>
+        <v>651977</v>
       </c>
       <c r="R68" t="n">
-        <v>6673929</v>
+        <v>6673906</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8795,7 +8791,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8805,7 +8801,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8832,10 +8828,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301013</v>
+        <v>122301067</v>
       </c>
       <c r="B69" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8844,39 +8840,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8884,10 +8872,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651745</v>
+        <v>652040</v>
       </c>
       <c r="R69" t="n">
-        <v>6673922</v>
+        <v>6673920</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8919,7 +8907,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8929,7 +8917,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8956,10 +8944,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301081</v>
+        <v>122301025</v>
       </c>
       <c r="B70" t="n">
-        <v>100451</v>
+        <v>57527</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8968,45 +8956,53 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>652036</v>
+        <v>651941</v>
       </c>
       <c r="R70" t="n">
-        <v>6673988</v>
+        <v>6674093</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9035,7 +9031,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9045,7 +9041,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9072,10 +9068,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301015</v>
+        <v>122301075</v>
       </c>
       <c r="B71" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9084,39 +9080,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9124,10 +9112,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651777</v>
+        <v>651975</v>
       </c>
       <c r="R71" t="n">
-        <v>6673975</v>
+        <v>6673928</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9159,7 +9147,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9169,7 +9157,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9196,10 +9184,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301079</v>
+        <v>122301017</v>
       </c>
       <c r="B72" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9208,31 +9196,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9240,10 +9236,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>652014</v>
+        <v>651776</v>
       </c>
       <c r="R72" t="n">
-        <v>6673954</v>
+        <v>6673944</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9275,7 +9271,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9285,7 +9281,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9312,10 +9308,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301025</v>
+        <v>122301015</v>
       </c>
       <c r="B73" t="n">
-        <v>57527</v>
+        <v>57390</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9328,49 +9324,49 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651941</v>
+        <v>651777</v>
       </c>
       <c r="R73" t="n">
-        <v>6674093</v>
+        <v>6673975</v>
       </c>
       <c r="S73" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9399,7 +9395,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9409,7 +9405,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9436,7 +9432,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301017</v>
+        <v>122301013</v>
       </c>
       <c r="B74" t="n">
         <v>57390</v>
@@ -9488,10 +9484,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>651776</v>
+        <v>651745</v>
       </c>
       <c r="R74" t="n">
-        <v>6673944</v>
+        <v>6673922</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9523,7 +9519,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9533,7 +9529,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9560,7 +9556,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301080</v>
+        <v>122301065</v>
       </c>
       <c r="B75" t="n">
         <v>100451</v>
@@ -9604,10 +9600,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>652011</v>
+        <v>652034</v>
       </c>
       <c r="R75" t="n">
-        <v>6673969</v>
+        <v>6673906</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9639,7 +9635,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9649,7 +9645,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9676,7 +9672,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301073</v>
+        <v>122301074</v>
       </c>
       <c r="B76" t="n">
         <v>100451</v>
@@ -9720,10 +9716,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651817</v>
+        <v>651855</v>
       </c>
       <c r="R76" t="n">
-        <v>6673939</v>
+        <v>6673907</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9755,7 +9751,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9765,7 +9761,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9792,10 +9788,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301074</v>
+        <v>122301027</v>
       </c>
       <c r="B77" t="n">
-        <v>100451</v>
+        <v>57744</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9808,27 +9804,31 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9836,13 +9836,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651855</v>
+        <v>651983</v>
       </c>
       <c r="R77" t="n">
-        <v>6673907</v>
+        <v>6673930</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -1784,10 +1784,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301071</v>
+        <v>122301020</v>
       </c>
       <c r="B11" t="n">
-        <v>100451</v>
+        <v>57390</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1796,31 +1796,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1828,10 +1836,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651840</v>
+        <v>652017</v>
       </c>
       <c r="R11" t="n">
-        <v>6673881</v>
+        <v>6673872</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1863,7 +1871,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,7 +1881,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,10 +1908,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301020</v>
+        <v>122301071</v>
       </c>
       <c r="B12" t="n">
-        <v>57390</v>
+        <v>100451</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1912,39 +1920,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>652017</v>
+        <v>651840</v>
       </c>
       <c r="R12" t="n">
-        <v>6673872</v>
+        <v>6673881</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122301036</v>
+        <v>122301031</v>
       </c>
       <c r="B2" t="n">
-        <v>90789</v>
+        <v>74691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>652047</v>
+        <v>651805</v>
       </c>
       <c r="R2" t="n">
-        <v>6673893</v>
+        <v>6673899</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122300997</v>
+        <v>122301053</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,50 +802,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651883</v>
+        <v>651986</v>
       </c>
       <c r="R3" t="n">
-        <v>6673732</v>
+        <v>6673841</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122301001</v>
+        <v>122300994</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -966,10 +971,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651873</v>
+        <v>651915</v>
       </c>
       <c r="R4" t="n">
-        <v>6673779</v>
+        <v>6673888</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1001,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1016,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122301004</v>
+        <v>122301062</v>
       </c>
       <c r="B5" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,39 +1055,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651888</v>
+        <v>651973</v>
       </c>
       <c r="R5" t="n">
-        <v>6673877</v>
+        <v>6673897</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1125,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122301021</v>
+        <v>122301078</v>
       </c>
       <c r="B6" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,50 +1179,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652056</v>
+        <v>652006</v>
       </c>
       <c r="R6" t="n">
-        <v>6673872</v>
+        <v>6673876</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1249,7 +1246,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1259,7 +1256,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122301007</v>
+        <v>122301077</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,39 +1295,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1338,10 +1327,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651778</v>
+        <v>651993</v>
       </c>
       <c r="R7" t="n">
-        <v>6673895</v>
+        <v>6673867</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1373,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1383,7 +1372,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122301053</v>
+        <v>122301007</v>
       </c>
       <c r="B8" t="n">
-        <v>98185</v>
+        <v>57395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,39 +1411,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1462,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651986</v>
+        <v>651778</v>
       </c>
       <c r="R8" t="n">
-        <v>6673841</v>
+        <v>6673895</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1497,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1507,12 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122300988</v>
+        <v>122301021</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1551,20 +1535,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1572,26 +1556,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651926</v>
+        <v>652056</v>
       </c>
       <c r="R9" t="n">
-        <v>6673844</v>
+        <v>6673872</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1623,7 +1610,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1633,7 +1620,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1660,10 +1647,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122301056</v>
+        <v>122300999</v>
       </c>
       <c r="B10" t="n">
-        <v>98185</v>
+        <v>57395</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1672,39 +1659,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1712,10 +1699,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651930</v>
+        <v>651879</v>
       </c>
       <c r="R10" t="n">
-        <v>6673898</v>
+        <v>6673776</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1747,7 +1734,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1757,7 +1744,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1784,10 +1771,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301020</v>
+        <v>122301001</v>
       </c>
       <c r="B11" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1826,7 +1813,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1836,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>652017</v>
+        <v>651873</v>
       </c>
       <c r="R11" t="n">
-        <v>6673872</v>
+        <v>6673779</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1871,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1881,7 +1868,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1908,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301071</v>
+        <v>122301056</v>
       </c>
       <c r="B12" t="n">
-        <v>100451</v>
+        <v>98197</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,29 +1907,37 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1952,10 +1947,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651840</v>
+        <v>651930</v>
       </c>
       <c r="R12" t="n">
-        <v>6673881</v>
+        <v>6673898</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1987,7 +1982,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1997,7 +1992,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,10 +2019,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122301019</v>
+        <v>122301068</v>
       </c>
       <c r="B13" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2036,50 +2031,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>652004</v>
+        <v>651906</v>
       </c>
       <c r="R13" t="n">
-        <v>6673869</v>
+        <v>6673752</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2111,7 +2098,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2121,7 +2108,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,10 +2135,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122300991</v>
+        <v>122300988</v>
       </c>
       <c r="B14" t="n">
-        <v>57390</v>
+        <v>5193</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,20 +2147,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2181,16 +2168,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2200,10 +2184,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651958</v>
+        <v>651926</v>
       </c>
       <c r="R14" t="n">
-        <v>6673868</v>
+        <v>6673844</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2235,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2245,7 +2229,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2272,10 +2256,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122300995</v>
+        <v>122300997</v>
       </c>
       <c r="B15" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2314,20 +2298,20 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651899</v>
+        <v>651883</v>
       </c>
       <c r="R15" t="n">
-        <v>6673777</v>
+        <v>6673732</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2359,7 +2343,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2369,7 +2353,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2396,10 +2380,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301060</v>
+        <v>122301020</v>
       </c>
       <c r="B16" t="n">
-        <v>98185</v>
+        <v>57395</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2408,39 +2392,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2448,10 +2432,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>652000</v>
+        <v>652017</v>
       </c>
       <c r="R16" t="n">
-        <v>6673848</v>
+        <v>6673872</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2483,7 +2467,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2493,7 +2477,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2520,10 +2504,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122300999</v>
+        <v>122300991</v>
       </c>
       <c r="B17" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2562,7 +2546,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2572,10 +2556,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651879</v>
+        <v>651958</v>
       </c>
       <c r="R17" t="n">
-        <v>6673776</v>
+        <v>6673868</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2607,7 +2591,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2617,7 +2601,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2644,10 +2628,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122301006</v>
+        <v>122301019</v>
       </c>
       <c r="B18" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2696,10 +2680,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651860</v>
+        <v>652004</v>
       </c>
       <c r="R18" t="n">
-        <v>6673862</v>
+        <v>6673869</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2731,7 +2715,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2741,7 +2725,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2771,7 +2755,7 @@
         <v>122300993</v>
       </c>
       <c r="B19" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2897,10 +2881,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122301037</v>
+        <v>122301058</v>
       </c>
       <c r="B20" t="n">
-        <v>91181</v>
+        <v>98197</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2909,25 +2893,39 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040162</v>
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2935,10 +2933,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651917</v>
+        <v>651981</v>
       </c>
       <c r="R20" t="n">
-        <v>6673853</v>
+        <v>6673859</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2970,7 +2968,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2980,7 +2978,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3007,10 +3005,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122301031</v>
+        <v>122301037</v>
       </c>
       <c r="B21" t="n">
-        <v>74686</v>
+        <v>91193</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3019,25 +3017,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3050,10 +3043,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651805</v>
+        <v>651917</v>
       </c>
       <c r="R21" t="n">
-        <v>6673899</v>
+        <v>6673853</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3085,7 +3078,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3095,7 +3088,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3122,10 +3115,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122300994</v>
+        <v>122301064</v>
       </c>
       <c r="B22" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3134,39 +3127,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3174,10 +3159,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651915</v>
+        <v>651993</v>
       </c>
       <c r="R22" t="n">
-        <v>6673888</v>
+        <v>6673896</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3209,7 +3194,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3219,7 +3204,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3246,10 +3231,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122301078</v>
+        <v>122301004</v>
       </c>
       <c r="B23" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3258,31 +3243,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3290,10 +3283,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>652006</v>
+        <v>651888</v>
       </c>
       <c r="R23" t="n">
-        <v>6673876</v>
+        <v>6673877</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3325,7 +3318,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3335,7 +3328,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3362,10 +3355,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122301068</v>
+        <v>122300995</v>
       </c>
       <c r="B24" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3374,42 +3367,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651906</v>
+        <v>651899</v>
       </c>
       <c r="R24" t="n">
-        <v>6673752</v>
+        <v>6673777</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3441,7 +3442,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3451,7 +3452,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3478,10 +3479,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301064</v>
+        <v>122301071</v>
       </c>
       <c r="B25" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3522,10 +3523,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651993</v>
+        <v>651840</v>
       </c>
       <c r="R25" t="n">
-        <v>6673896</v>
+        <v>6673881</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3557,7 +3558,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3567,7 +3568,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3594,10 +3595,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301077</v>
+        <v>122301006</v>
       </c>
       <c r="B26" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3606,31 +3607,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3638,10 +3647,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651993</v>
+        <v>651860</v>
       </c>
       <c r="R26" t="n">
-        <v>6673867</v>
+        <v>6673862</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3673,7 +3682,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3692,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3710,10 +3719,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301058</v>
+        <v>122301036</v>
       </c>
       <c r="B27" t="n">
-        <v>98185</v>
+        <v>90801</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3722,39 +3731,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>651981</v>
+        <v>652047</v>
       </c>
       <c r="R27" t="n">
-        <v>6673859</v>
+        <v>6673893</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3834,10 +3834,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122301062</v>
+        <v>122301060</v>
       </c>
       <c r="B28" t="n">
-        <v>100451</v>
+        <v>98197</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3846,35 +3846,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651973</v>
+        <v>652000</v>
       </c>
       <c r="R28" t="n">
-        <v>6673897</v>
+        <v>6673848</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122260064</v>
+        <v>122260076</v>
       </c>
       <c r="B29" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651845</v>
+        <v>651949</v>
       </c>
       <c r="R29" t="n">
-        <v>6674626</v>
+        <v>6674279</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4082,10 +4082,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122260066</v>
+        <v>122260064</v>
       </c>
       <c r="B30" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651934</v>
+        <v>651845</v>
       </c>
       <c r="R30" t="n">
-        <v>6674510</v>
+        <v>6674626</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4206,10 +4206,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260116</v>
+        <v>122260068</v>
       </c>
       <c r="B31" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4218,31 +4218,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4250,10 +4258,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651859</v>
+        <v>651928</v>
       </c>
       <c r="R31" t="n">
-        <v>6674654</v>
+        <v>6674457</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4285,7 +4293,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4295,7 +4303,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4322,10 +4330,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260103</v>
+        <v>122260121</v>
       </c>
       <c r="B32" t="n">
-        <v>91229</v>
+        <v>100463</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4334,30 +4342,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4365,10 +4374,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651855</v>
+        <v>651955</v>
       </c>
       <c r="R32" t="n">
-        <v>6674655</v>
+        <v>6674222</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4400,7 +4409,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4410,12 +4419,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På klibbtickelåga.</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4426,21 +4430,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4457,10 +4446,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260125</v>
+        <v>122260096</v>
       </c>
       <c r="B33" t="n">
-        <v>100451</v>
+        <v>80608</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4469,31 +4458,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4501,10 +4489,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651973</v>
+        <v>651930</v>
       </c>
       <c r="R33" t="n">
-        <v>6674332</v>
+        <v>6674592</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4536,7 +4524,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4546,7 +4534,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4573,10 +4561,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260063</v>
+        <v>122260103</v>
       </c>
       <c r="B34" t="n">
-        <v>57390</v>
+        <v>91241</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4585,39 +4573,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4625,10 +4604,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651872</v>
+        <v>651855</v>
       </c>
       <c r="R34" t="n">
-        <v>6674674</v>
+        <v>6674655</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4660,7 +4639,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4670,7 +4649,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På klibbtickelåga.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4681,6 +4665,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4697,10 +4696,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122260118</v>
+        <v>122260085</v>
       </c>
       <c r="B35" t="n">
-        <v>100451</v>
+        <v>57749</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4713,27 +4712,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4741,13 +4748,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651893</v>
+        <v>651895</v>
       </c>
       <c r="R35" t="n">
-        <v>6674508</v>
+        <v>6674630</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4776,7 +4783,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4786,7 +4793,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4813,10 +4820,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122260100</v>
+        <v>122260066</v>
       </c>
       <c r="B36" t="n">
-        <v>90789</v>
+        <v>57395</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4829,26 +4836,35 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4856,10 +4872,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>652034</v>
+        <v>651934</v>
       </c>
       <c r="R36" t="n">
-        <v>6674236</v>
+        <v>6674510</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4891,7 +4907,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4901,7 +4917,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4912,21 +4928,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4943,10 +4944,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122260085</v>
+        <v>122260125</v>
       </c>
       <c r="B37" t="n">
-        <v>57744</v>
+        <v>100463</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4959,35 +4960,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4995,13 +4988,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651895</v>
+        <v>651973</v>
       </c>
       <c r="R37" t="n">
-        <v>6674630</v>
+        <v>6674332</v>
       </c>
       <c r="S37" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5030,7 +5023,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5040,7 +5033,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5067,10 +5060,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122260061</v>
+        <v>122260119</v>
       </c>
       <c r="B38" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5079,39 +5072,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5119,10 +5104,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651886</v>
+        <v>651950</v>
       </c>
       <c r="R38" t="n">
-        <v>6674654</v>
+        <v>6674465</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5154,7 +5139,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5164,7 +5149,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5191,10 +5176,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260071</v>
+        <v>122260077</v>
       </c>
       <c r="B39" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5233,7 +5218,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -5243,10 +5228,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651930</v>
+        <v>651964</v>
       </c>
       <c r="R39" t="n">
-        <v>6674444</v>
+        <v>6674220</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5278,7 +5263,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5288,7 +5273,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5315,10 +5300,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260119</v>
+        <v>122260110</v>
       </c>
       <c r="B40" t="n">
-        <v>100451</v>
+        <v>98197</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5327,29 +5312,37 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5359,10 +5352,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651950</v>
+        <v>651949</v>
       </c>
       <c r="R40" t="n">
-        <v>6674465</v>
+        <v>6674420</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5394,7 +5387,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5404,7 +5397,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5431,10 +5429,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260080</v>
+        <v>122260116</v>
       </c>
       <c r="B41" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5443,39 +5441,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5483,10 +5473,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>652019</v>
+        <v>651859</v>
       </c>
       <c r="R41" t="n">
-        <v>6674239</v>
+        <v>6674654</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5518,7 +5508,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5528,7 +5518,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5555,10 +5545,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122260113</v>
+        <v>122260126</v>
       </c>
       <c r="B42" t="n">
-        <v>98185</v>
+        <v>100463</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5567,37 +5557,29 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
@@ -5607,10 +5589,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651906</v>
+        <v>651941</v>
       </c>
       <c r="R42" t="n">
-        <v>6674392</v>
+        <v>6674469</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5642,7 +5624,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5652,7 +5634,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5679,10 +5661,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260126</v>
+        <v>122260075</v>
       </c>
       <c r="B43" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5691,31 +5673,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5723,10 +5713,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651941</v>
+        <v>651900</v>
       </c>
       <c r="R43" t="n">
-        <v>6674469</v>
+        <v>6674390</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5758,7 +5748,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5768,7 +5758,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5795,10 +5785,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260084</v>
+        <v>122260061</v>
       </c>
       <c r="B44" t="n">
-        <v>57527</v>
+        <v>57395</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5811,33 +5801,33 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5847,13 +5837,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651900</v>
+        <v>651886</v>
       </c>
       <c r="R44" t="n">
-        <v>6674551</v>
+        <v>6674654</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5882,7 +5872,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5892,7 +5882,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5919,10 +5909,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122260121</v>
+        <v>122260111</v>
       </c>
       <c r="B45" t="n">
-        <v>100451</v>
+        <v>98197</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5931,29 +5921,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
@@ -5963,10 +5961,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651955</v>
+        <v>651949</v>
       </c>
       <c r="R45" t="n">
-        <v>6674222</v>
+        <v>6674415</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5998,7 +5996,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6008,7 +6006,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6035,10 +6033,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122260117</v>
+        <v>122260058</v>
       </c>
       <c r="B46" t="n">
-        <v>100451</v>
+        <v>5193</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6051,27 +6049,32 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6079,10 +6082,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651906</v>
+        <v>652031</v>
       </c>
       <c r="R46" t="n">
-        <v>6674571</v>
+        <v>6674226</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6114,7 +6117,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6124,7 +6127,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6135,6 +6138,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6151,10 +6169,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260072</v>
+        <v>122260071</v>
       </c>
       <c r="B47" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6203,10 +6221,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651927</v>
+        <v>651930</v>
       </c>
       <c r="R47" t="n">
-        <v>6674447</v>
+        <v>6674444</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6238,7 +6256,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6248,7 +6266,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6275,10 +6293,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260074</v>
+        <v>122260115</v>
       </c>
       <c r="B48" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6287,39 +6305,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6327,13 +6337,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>651923</v>
+        <v>651891</v>
       </c>
       <c r="R48" t="n">
-        <v>6674436</v>
+        <v>6674645</v>
       </c>
       <c r="S48" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6362,7 +6372,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6372,12 +6382,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Hörd i norr.</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6404,10 +6409,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260110</v>
+        <v>122260072</v>
       </c>
       <c r="B49" t="n">
-        <v>98185</v>
+        <v>57395</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6416,39 +6421,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6456,10 +6461,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651949</v>
+        <v>651927</v>
       </c>
       <c r="R49" t="n">
-        <v>6674420</v>
+        <v>6674447</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6491,7 +6496,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6501,12 +6506,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6533,10 +6533,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260096</v>
+        <v>122260084</v>
       </c>
       <c r="B50" t="n">
-        <v>80603</v>
+        <v>57532</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6549,26 +6549,35 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6576,13 +6585,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651930</v>
+        <v>651900</v>
       </c>
       <c r="R50" t="n">
-        <v>6674592</v>
+        <v>6674551</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6611,7 +6620,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6621,7 +6630,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6648,10 +6657,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122260114</v>
+        <v>122260113</v>
       </c>
       <c r="B51" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6683,7 +6692,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6700,10 +6709,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>652010</v>
+        <v>651906</v>
       </c>
       <c r="R51" t="n">
-        <v>6674220</v>
+        <v>6674392</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6735,7 +6744,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6745,7 +6754,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6772,10 +6781,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260077</v>
+        <v>122260100</v>
       </c>
       <c r="B52" t="n">
-        <v>57390</v>
+        <v>90801</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6788,35 +6797,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6824,10 +6824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651964</v>
+        <v>652034</v>
       </c>
       <c r="R52" t="n">
-        <v>6674220</v>
+        <v>6674236</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6880,6 +6880,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6896,10 +6911,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260076</v>
+        <v>122260074</v>
       </c>
       <c r="B53" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6938,7 +6953,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6948,13 +6963,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651949</v>
+        <v>651923</v>
       </c>
       <c r="R53" t="n">
-        <v>6674279</v>
+        <v>6674436</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6983,7 +6998,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6993,7 +7008,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Hörd i norr.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7020,10 +7040,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260075</v>
+        <v>122260063</v>
       </c>
       <c r="B54" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7062,7 +7082,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -7072,10 +7092,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651900</v>
+        <v>651872</v>
       </c>
       <c r="R54" t="n">
-        <v>6674390</v>
+        <v>6674674</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7107,7 +7127,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7117,7 +7137,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7144,10 +7164,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122260120</v>
+        <v>122260070</v>
       </c>
       <c r="B55" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7156,31 +7176,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7191,7 +7219,7 @@
         <v>651967</v>
       </c>
       <c r="R55" t="n">
-        <v>6674316</v>
+        <v>6674433</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7223,7 +7251,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7233,7 +7261,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7260,10 +7288,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260111</v>
+        <v>122260120</v>
       </c>
       <c r="B56" t="n">
-        <v>98185</v>
+        <v>100463</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7272,37 +7300,29 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
@@ -7312,10 +7332,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>651949</v>
+        <v>651967</v>
       </c>
       <c r="R56" t="n">
-        <v>6674415</v>
+        <v>6674316</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7347,7 +7367,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7357,7 +7377,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7384,10 +7404,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260115</v>
+        <v>122260118</v>
       </c>
       <c r="B57" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7428,10 +7448,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651891</v>
+        <v>651893</v>
       </c>
       <c r="R57" t="n">
-        <v>6674645</v>
+        <v>6674508</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7463,7 +7483,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7473,7 +7493,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7500,10 +7520,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260068</v>
+        <v>122260117</v>
       </c>
       <c r="B58" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7512,39 +7532,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7552,10 +7564,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>651928</v>
+        <v>651906</v>
       </c>
       <c r="R58" t="n">
-        <v>6674457</v>
+        <v>6674571</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7587,7 +7599,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7597,7 +7609,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7624,10 +7636,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260070</v>
+        <v>122260114</v>
       </c>
       <c r="B59" t="n">
-        <v>57390</v>
+        <v>98197</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7636,39 +7648,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7676,10 +7688,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651967</v>
+        <v>652010</v>
       </c>
       <c r="R59" t="n">
-        <v>6674433</v>
+        <v>6674220</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7711,7 +7723,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7721,7 +7733,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7748,10 +7760,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260058</v>
+        <v>122260080</v>
       </c>
       <c r="B60" t="n">
-        <v>5193</v>
+        <v>57395</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7760,20 +7772,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7781,13 +7793,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7797,10 +7812,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>652031</v>
+        <v>652019</v>
       </c>
       <c r="R60" t="n">
-        <v>6674226</v>
+        <v>6674239</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7832,7 +7847,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7842,7 +7857,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7853,21 +7868,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7884,10 +7884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301050</v>
+        <v>122301026</v>
       </c>
       <c r="B61" t="n">
-        <v>98185</v>
+        <v>57532</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7896,39 +7896,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7936,13 +7936,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651948</v>
+        <v>651977</v>
       </c>
       <c r="R61" t="n">
         <v>6673906</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8011,7 +8011,7 @@
         <v>122301079</v>
       </c>
       <c r="B62" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8124,10 +8124,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301066</v>
+        <v>122301067</v>
       </c>
       <c r="B63" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8168,10 +8168,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>652079</v>
+        <v>652040</v>
       </c>
       <c r="R63" t="n">
-        <v>6673929</v>
+        <v>6673920</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8240,10 +8240,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301063</v>
+        <v>122301080</v>
       </c>
       <c r="B64" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8284,10 +8284,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651949</v>
+        <v>652011</v>
       </c>
       <c r="R64" t="n">
-        <v>6673910</v>
+        <v>6673969</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8356,10 +8356,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301081</v>
+        <v>122301050</v>
       </c>
       <c r="B65" t="n">
-        <v>100451</v>
+        <v>98197</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8368,29 +8368,37 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -8400,10 +8408,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>652036</v>
+        <v>651948</v>
       </c>
       <c r="R65" t="n">
-        <v>6673988</v>
+        <v>6673906</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8435,7 +8443,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8445,7 +8453,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8472,10 +8480,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301080</v>
+        <v>122301066</v>
       </c>
       <c r="B66" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8516,10 +8524,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>652011</v>
+        <v>652079</v>
       </c>
       <c r="R66" t="n">
-        <v>6673969</v>
+        <v>6673929</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8551,7 +8559,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8561,7 +8569,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8588,10 +8596,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301073</v>
+        <v>122301015</v>
       </c>
       <c r="B67" t="n">
-        <v>100451</v>
+        <v>57395</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8600,31 +8608,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8632,10 +8648,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>651817</v>
+        <v>651777</v>
       </c>
       <c r="R67" t="n">
-        <v>6673939</v>
+        <v>6673975</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8667,7 +8683,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8677,7 +8693,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8704,10 +8720,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301026</v>
+        <v>122301075</v>
       </c>
       <c r="B68" t="n">
-        <v>57527</v>
+        <v>100463</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8716,39 +8732,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8756,13 +8764,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651977</v>
+        <v>651975</v>
       </c>
       <c r="R68" t="n">
-        <v>6673906</v>
+        <v>6673928</v>
       </c>
       <c r="S68" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8791,7 +8799,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8801,7 +8809,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8828,10 +8836,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301067</v>
+        <v>122301063</v>
       </c>
       <c r="B69" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8872,10 +8880,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>652040</v>
+        <v>651949</v>
       </c>
       <c r="R69" t="n">
-        <v>6673920</v>
+        <v>6673910</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8907,7 +8915,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8917,7 +8925,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8944,10 +8952,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301025</v>
+        <v>122301027</v>
       </c>
       <c r="B70" t="n">
-        <v>57527</v>
+        <v>57749</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8956,25 +8964,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8984,25 +8992,21 @@
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651941</v>
+        <v>651983</v>
       </c>
       <c r="R70" t="n">
-        <v>6674093</v>
+        <v>6673930</v>
       </c>
       <c r="S70" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9031,7 +9035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9041,7 +9045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9068,10 +9072,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301075</v>
+        <v>122301065</v>
       </c>
       <c r="B71" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9112,10 +9116,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651975</v>
+        <v>652034</v>
       </c>
       <c r="R71" t="n">
-        <v>6673928</v>
+        <v>6673906</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9147,7 +9151,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9157,7 +9161,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9184,10 +9188,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301017</v>
+        <v>122301074</v>
       </c>
       <c r="B72" t="n">
-        <v>57390</v>
+        <v>100463</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9196,39 +9200,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9236,10 +9232,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651776</v>
+        <v>651855</v>
       </c>
       <c r="R72" t="n">
-        <v>6673944</v>
+        <v>6673907</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9271,7 +9267,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9281,7 +9277,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9308,10 +9304,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301015</v>
+        <v>122301013</v>
       </c>
       <c r="B73" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9360,10 +9356,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651777</v>
+        <v>651745</v>
       </c>
       <c r="R73" t="n">
-        <v>6673975</v>
+        <v>6673922</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9395,7 +9391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9405,7 +9401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9432,10 +9428,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301013</v>
+        <v>122301017</v>
       </c>
       <c r="B74" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9484,10 +9480,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>651745</v>
+        <v>651776</v>
       </c>
       <c r="R74" t="n">
-        <v>6673922</v>
+        <v>6673944</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9519,7 +9515,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9529,7 +9525,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9556,10 +9552,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301065</v>
+        <v>122301025</v>
       </c>
       <c r="B75" t="n">
-        <v>100451</v>
+        <v>57532</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9568,45 +9564,53 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>652034</v>
+        <v>651941</v>
       </c>
       <c r="R75" t="n">
-        <v>6673906</v>
+        <v>6674093</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9635,7 +9639,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9645,7 +9649,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9672,10 +9676,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301074</v>
+        <v>122301073</v>
       </c>
       <c r="B76" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9716,10 +9720,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651855</v>
+        <v>651817</v>
       </c>
       <c r="R76" t="n">
-        <v>6673907</v>
+        <v>6673939</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9751,7 +9755,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9761,7 +9765,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9788,10 +9792,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301027</v>
+        <v>122301081</v>
       </c>
       <c r="B77" t="n">
-        <v>57744</v>
+        <v>100463</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9804,31 +9808,27 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9836,13 +9836,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651983</v>
+        <v>652036</v>
       </c>
       <c r="R77" t="n">
-        <v>6673930</v>
+        <v>6673988</v>
       </c>
       <c r="S77" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9911,7 +9911,7 @@
         <v>122260107</v>
       </c>
       <c r="B78" t="n">
-        <v>95732</v>
+        <v>95744</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122301031</v>
+        <v>122301006</v>
       </c>
       <c r="B2" t="n">
-        <v>74691</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651805</v>
+        <v>651860</v>
       </c>
       <c r="R2" t="n">
-        <v>6673899</v>
+        <v>6673862</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122301053</v>
+        <v>122301064</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>100468</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,37 +811,29 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -842,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651986</v>
+        <v>651993</v>
       </c>
       <c r="R3" t="n">
-        <v>6673841</v>
+        <v>6673896</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122300994</v>
+        <v>122301078</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,39 +927,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -971,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651915</v>
+        <v>652006</v>
       </c>
       <c r="R4" t="n">
-        <v>6673888</v>
+        <v>6673876</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1006,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122301062</v>
+        <v>122301036</v>
       </c>
       <c r="B5" t="n">
-        <v>100463</v>
+        <v>90808</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,39 +1043,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1095,10 +1074,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651973</v>
+        <v>652047</v>
       </c>
       <c r="R5" t="n">
-        <v>6673897</v>
+        <v>6673893</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1130,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122301078</v>
+        <v>122300997</v>
       </c>
       <c r="B6" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,42 +1158,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652006</v>
+        <v>651883</v>
       </c>
       <c r="R6" t="n">
-        <v>6673876</v>
+        <v>6673732</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1246,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1256,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122301077</v>
+        <v>122300993</v>
       </c>
       <c r="B7" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,31 +1282,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1327,13 +1322,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651993</v>
+        <v>651962</v>
       </c>
       <c r="R7" t="n">
-        <v>6673867</v>
+        <v>6673882</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1372,7 +1367,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1399,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122301007</v>
+        <v>122301019</v>
       </c>
       <c r="B8" t="n">
         <v>57395</v>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651778</v>
+        <v>652004</v>
       </c>
       <c r="R8" t="n">
-        <v>6673895</v>
+        <v>6673869</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,7 +1523,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122301021</v>
+        <v>122301020</v>
       </c>
       <c r="B9" t="n">
         <v>57395</v>
@@ -1571,11 +1571,11 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>652056</v>
+        <v>652017</v>
       </c>
       <c r="R9" t="n">
         <v>6673872</v>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,10 +1647,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122300999</v>
+        <v>122301071</v>
       </c>
       <c r="B10" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1659,39 +1659,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1699,10 +1691,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651879</v>
+        <v>651840</v>
       </c>
       <c r="R10" t="n">
-        <v>6673776</v>
+        <v>6673881</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1734,7 +1726,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1744,7 +1736,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1771,10 +1763,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301001</v>
+        <v>122301077</v>
       </c>
       <c r="B11" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1783,39 +1775,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1823,10 +1807,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651873</v>
+        <v>651993</v>
       </c>
       <c r="R11" t="n">
-        <v>6673779</v>
+        <v>6673867</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1858,7 +1842,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,7 +1852,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,10 +1879,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301056</v>
+        <v>122301058</v>
       </c>
       <c r="B12" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1930,12 +1914,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1947,10 +1931,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651930</v>
+        <v>651981</v>
       </c>
       <c r="R12" t="n">
-        <v>6673898</v>
+        <v>6673859</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1982,7 +1966,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1992,7 +1976,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2019,10 +2003,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122301068</v>
+        <v>122300999</v>
       </c>
       <c r="B13" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2031,42 +2015,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651906</v>
+        <v>651879</v>
       </c>
       <c r="R13" t="n">
-        <v>6673752</v>
+        <v>6673776</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2098,7 +2090,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2108,7 +2100,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2135,10 +2127,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122300988</v>
+        <v>122301068</v>
       </c>
       <c r="B14" t="n">
-        <v>5193</v>
+        <v>100468</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2151,43 +2143,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651926</v>
+        <v>651906</v>
       </c>
       <c r="R14" t="n">
-        <v>6673844</v>
+        <v>6673752</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2219,7 +2206,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,7 +2216,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,7 +2243,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122300997</v>
+        <v>122301001</v>
       </c>
       <c r="B15" t="n">
         <v>57395</v>
@@ -2298,20 +2285,20 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651883</v>
+        <v>651873</v>
       </c>
       <c r="R15" t="n">
-        <v>6673732</v>
+        <v>6673779</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2343,7 +2330,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2353,7 +2340,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2380,10 +2367,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301020</v>
+        <v>122301062</v>
       </c>
       <c r="B16" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2392,39 +2379,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2432,10 +2419,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>652017</v>
+        <v>651973</v>
       </c>
       <c r="R16" t="n">
-        <v>6673872</v>
+        <v>6673897</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2467,7 +2454,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2477,7 +2464,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2504,10 +2491,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122300991</v>
+        <v>122301056</v>
       </c>
       <c r="B17" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2516,39 +2503,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2556,10 +2543,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651958</v>
+        <v>651930</v>
       </c>
       <c r="R17" t="n">
-        <v>6673868</v>
+        <v>6673898</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2591,7 +2578,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2601,7 +2588,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2628,7 +2615,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122301019</v>
+        <v>122300991</v>
       </c>
       <c r="B18" t="n">
         <v>57395</v>
@@ -2670,7 +2657,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2680,10 +2667,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>652004</v>
+        <v>651958</v>
       </c>
       <c r="R18" t="n">
-        <v>6673869</v>
+        <v>6673868</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2715,7 +2702,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2725,7 +2712,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2752,10 +2739,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122300993</v>
+        <v>122300988</v>
       </c>
       <c r="B19" t="n">
-        <v>57395</v>
+        <v>5193</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2764,20 +2751,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2785,16 +2772,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2804,13 +2788,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651962</v>
+        <v>651926</v>
       </c>
       <c r="R19" t="n">
-        <v>6673882</v>
+        <v>6673844</v>
       </c>
       <c r="S19" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2839,7 +2823,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2849,12 +2833,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2881,10 +2860,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122301058</v>
+        <v>122301031</v>
       </c>
       <c r="B20" t="n">
-        <v>98197</v>
+        <v>74691</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2893,39 +2872,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2933,10 +2903,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651981</v>
+        <v>651805</v>
       </c>
       <c r="R20" t="n">
-        <v>6673859</v>
+        <v>6673899</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2968,7 +2938,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2978,7 +2948,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3005,10 +2975,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122301037</v>
+        <v>122301021</v>
       </c>
       <c r="B21" t="n">
-        <v>91193</v>
+        <v>57395</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3021,32 +2991,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6040162</v>
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651917</v>
+        <v>652056</v>
       </c>
       <c r="R21" t="n">
-        <v>6673853</v>
+        <v>6673872</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3078,7 +3062,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3088,7 +3072,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3115,10 +3099,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122301064</v>
+        <v>122301053</v>
       </c>
       <c r="B22" t="n">
-        <v>100463</v>
+        <v>98202</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3127,29 +3111,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651993</v>
+        <v>651986</v>
       </c>
       <c r="R22" t="n">
-        <v>6673896</v>
+        <v>6673841</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3194,7 +3186,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3204,7 +3196,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3231,7 +3228,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122301004</v>
+        <v>122301007</v>
       </c>
       <c r="B23" t="n">
         <v>57395</v>
@@ -3283,10 +3280,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651888</v>
+        <v>651778</v>
       </c>
       <c r="R23" t="n">
-        <v>6673877</v>
+        <v>6673895</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3318,7 +3315,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3328,7 +3325,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3355,10 +3352,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122300995</v>
+        <v>122301037</v>
       </c>
       <c r="B24" t="n">
-        <v>57395</v>
+        <v>91198</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3371,35 +3368,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3407,10 +3390,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651899</v>
+        <v>651917</v>
       </c>
       <c r="R24" t="n">
-        <v>6673777</v>
+        <v>6673853</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3442,7 +3425,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3452,7 +3435,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3479,10 +3462,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301071</v>
+        <v>122301004</v>
       </c>
       <c r="B25" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3491,31 +3474,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3523,10 +3514,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651840</v>
+        <v>651888</v>
       </c>
       <c r="R25" t="n">
-        <v>6673881</v>
+        <v>6673877</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3558,7 +3549,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3568,7 +3559,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3595,7 +3586,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301006</v>
+        <v>122300994</v>
       </c>
       <c r="B26" t="n">
         <v>57395</v>
@@ -3647,10 +3638,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651860</v>
+        <v>651915</v>
       </c>
       <c r="R26" t="n">
-        <v>6673862</v>
+        <v>6673888</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3682,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3692,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3719,10 +3710,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301036</v>
+        <v>122301060</v>
       </c>
       <c r="B27" t="n">
-        <v>90801</v>
+        <v>98202</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3731,30 +3722,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3762,10 +3762,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>652047</v>
+        <v>652000</v>
       </c>
       <c r="R27" t="n">
-        <v>6673893</v>
+        <v>6673848</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3797,7 +3797,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3834,10 +3834,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122301060</v>
+        <v>122300995</v>
       </c>
       <c r="B28" t="n">
-        <v>98197</v>
+        <v>57395</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3846,39 +3846,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>652000</v>
+        <v>651899</v>
       </c>
       <c r="R28" t="n">
-        <v>6673848</v>
+        <v>6673777</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122260076</v>
+        <v>122260110</v>
       </c>
       <c r="B29" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3970,39 +3970,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>651949</v>
       </c>
       <c r="R29" t="n">
-        <v>6674279</v>
+        <v>6674420</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4055,7 +4055,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4082,7 +4087,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122260064</v>
+        <v>122260066</v>
       </c>
       <c r="B30" t="n">
         <v>57395</v>
@@ -4124,7 +4129,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4134,10 +4139,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651845</v>
+        <v>651934</v>
       </c>
       <c r="R30" t="n">
-        <v>6674626</v>
+        <v>6674510</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4169,7 +4174,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4179,7 +4184,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4206,10 +4211,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260068</v>
+        <v>122260120</v>
       </c>
       <c r="B31" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4218,39 +4223,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4258,10 +4255,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651928</v>
+        <v>651967</v>
       </c>
       <c r="R31" t="n">
-        <v>6674457</v>
+        <v>6674316</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4293,7 +4290,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4303,7 +4300,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4330,10 +4327,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260121</v>
+        <v>122260126</v>
       </c>
       <c r="B32" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4374,10 +4371,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651955</v>
+        <v>651941</v>
       </c>
       <c r="R32" t="n">
-        <v>6674222</v>
+        <v>6674469</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4409,7 +4406,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4419,7 +4416,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,10 +4443,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260096</v>
+        <v>122260075</v>
       </c>
       <c r="B33" t="n">
-        <v>80608</v>
+        <v>57395</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4462,26 +4459,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4489,10 +4495,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651930</v>
+        <v>651900</v>
       </c>
       <c r="R33" t="n">
-        <v>6674592</v>
+        <v>6674390</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4524,7 +4530,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4534,7 +4540,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4561,10 +4567,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260103</v>
+        <v>122260068</v>
       </c>
       <c r="B34" t="n">
-        <v>91241</v>
+        <v>57395</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4573,30 +4579,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4604,10 +4619,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651855</v>
+        <v>651928</v>
       </c>
       <c r="R34" t="n">
-        <v>6674655</v>
+        <v>6674457</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4639,7 +4654,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4649,12 +4664,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På klibbtickelåga.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4665,21 +4675,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4696,10 +4691,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122260085</v>
+        <v>122260058</v>
       </c>
       <c r="B35" t="n">
-        <v>57749</v>
+        <v>5193</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4712,16 +4707,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4729,16 +4724,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4748,13 +4740,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651895</v>
+        <v>652031</v>
       </c>
       <c r="R35" t="n">
-        <v>6674630</v>
+        <v>6674226</v>
       </c>
       <c r="S35" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4783,7 +4775,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4793,7 +4785,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4804,6 +4796,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4820,10 +4827,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122260066</v>
+        <v>122260125</v>
       </c>
       <c r="B36" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4832,39 +4839,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4872,10 +4871,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651934</v>
+        <v>651973</v>
       </c>
       <c r="R36" t="n">
-        <v>6674510</v>
+        <v>6674332</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4907,7 +4906,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4917,7 +4916,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4944,10 +4943,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122260125</v>
+        <v>122260116</v>
       </c>
       <c r="B37" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4988,10 +4987,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651973</v>
+        <v>651859</v>
       </c>
       <c r="R37" t="n">
-        <v>6674332</v>
+        <v>6674654</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5023,7 +5022,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5033,7 +5032,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5063,7 +5062,7 @@
         <v>122260119</v>
       </c>
       <c r="B38" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5176,10 +5175,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260077</v>
+        <v>122260103</v>
       </c>
       <c r="B39" t="n">
-        <v>57395</v>
+        <v>91246</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5188,39 +5187,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5228,10 +5218,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651964</v>
+        <v>651855</v>
       </c>
       <c r="R39" t="n">
-        <v>6674220</v>
+        <v>6674655</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5263,7 +5253,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5273,7 +5263,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På klibbtickelåga.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5284,6 +5279,21 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5300,10 +5310,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260110</v>
+        <v>122260063</v>
       </c>
       <c r="B40" t="n">
-        <v>98197</v>
+        <v>57395</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5312,39 +5322,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5352,10 +5362,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651949</v>
+        <v>651872</v>
       </c>
       <c r="R40" t="n">
-        <v>6674420</v>
+        <v>6674674</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5387,7 +5397,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5397,12 +5407,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5429,10 +5434,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260116</v>
+        <v>122260076</v>
       </c>
       <c r="B41" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5441,31 +5446,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5473,10 +5486,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651859</v>
+        <v>651949</v>
       </c>
       <c r="R41" t="n">
-        <v>6674654</v>
+        <v>6674279</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5508,7 +5521,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5518,7 +5531,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5545,10 +5558,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122260126</v>
+        <v>122260117</v>
       </c>
       <c r="B42" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5589,10 +5602,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651941</v>
+        <v>651906</v>
       </c>
       <c r="R42" t="n">
-        <v>6674469</v>
+        <v>6674571</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5624,7 +5637,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5634,7 +5647,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5661,10 +5674,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260075</v>
+        <v>122260121</v>
       </c>
       <c r="B43" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5673,39 +5686,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5713,10 +5718,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651900</v>
+        <v>651955</v>
       </c>
       <c r="R43" t="n">
-        <v>6674390</v>
+        <v>6674222</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5748,7 +5753,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5758,7 +5763,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5785,10 +5790,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260061</v>
+        <v>122260100</v>
       </c>
       <c r="B44" t="n">
-        <v>57395</v>
+        <v>90808</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5801,35 +5806,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5837,10 +5833,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651886</v>
+        <v>652034</v>
       </c>
       <c r="R44" t="n">
-        <v>6674654</v>
+        <v>6674236</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5872,7 +5868,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5882,7 +5878,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5893,6 +5889,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5909,10 +5920,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122260111</v>
+        <v>122260070</v>
       </c>
       <c r="B45" t="n">
-        <v>98197</v>
+        <v>57395</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5921,39 +5932,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5961,10 +5972,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651949</v>
+        <v>651967</v>
       </c>
       <c r="R45" t="n">
-        <v>6674415</v>
+        <v>6674433</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5996,7 +6007,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6006,7 +6017,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6033,10 +6044,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122260058</v>
+        <v>122260064</v>
       </c>
       <c r="B46" t="n">
-        <v>5193</v>
+        <v>57395</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6045,20 +6056,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -6066,13 +6077,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6082,10 +6096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>652031</v>
+        <v>651845</v>
       </c>
       <c r="R46" t="n">
-        <v>6674226</v>
+        <v>6674626</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6117,7 +6131,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6127,7 +6141,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6138,21 +6152,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6169,10 +6168,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260071</v>
+        <v>122260118</v>
       </c>
       <c r="B47" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6181,39 +6180,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6221,10 +6212,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651930</v>
+        <v>651893</v>
       </c>
       <c r="R47" t="n">
-        <v>6674444</v>
+        <v>6674508</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6256,7 +6247,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6266,7 +6257,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6293,10 +6284,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260115</v>
+        <v>122260080</v>
       </c>
       <c r="B48" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6305,31 +6296,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6337,10 +6336,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>651891</v>
+        <v>652019</v>
       </c>
       <c r="R48" t="n">
-        <v>6674645</v>
+        <v>6674239</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6372,7 +6371,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6382,7 +6381,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6409,10 +6408,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260072</v>
+        <v>122260085</v>
       </c>
       <c r="B49" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6421,20 +6420,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6451,7 +6450,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6461,13 +6460,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651927</v>
+        <v>651895</v>
       </c>
       <c r="R49" t="n">
-        <v>6674447</v>
+        <v>6674630</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6496,7 +6495,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6506,7 +6505,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6533,10 +6532,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260084</v>
+        <v>122260115</v>
       </c>
       <c r="B50" t="n">
-        <v>57532</v>
+        <v>100468</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6545,39 +6544,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6585,13 +6576,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651900</v>
+        <v>651891</v>
       </c>
       <c r="R50" t="n">
-        <v>6674551</v>
+        <v>6674645</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6620,7 +6611,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6630,7 +6621,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6657,10 +6648,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122260113</v>
+        <v>122260071</v>
       </c>
       <c r="B51" t="n">
-        <v>98197</v>
+        <v>57395</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6669,39 +6660,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6709,10 +6700,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651906</v>
+        <v>651930</v>
       </c>
       <c r="R51" t="n">
-        <v>6674392</v>
+        <v>6674444</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6744,7 +6735,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6754,7 +6745,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6781,10 +6772,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260100</v>
+        <v>122260074</v>
       </c>
       <c r="B52" t="n">
-        <v>90801</v>
+        <v>57395</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6797,26 +6788,35 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6824,13 +6824,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>652034</v>
+        <v>651923</v>
       </c>
       <c r="R52" t="n">
-        <v>6674236</v>
+        <v>6674436</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6869,7 +6869,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Hörd i norr.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6880,21 +6885,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6911,10 +6901,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260074</v>
+        <v>122260114</v>
       </c>
       <c r="B53" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6923,39 +6913,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6963,13 +6953,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651923</v>
+        <v>652010</v>
       </c>
       <c r="R53" t="n">
-        <v>6674436</v>
+        <v>6674220</v>
       </c>
       <c r="S53" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6998,7 +6988,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7008,12 +6998,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Hörd i norr.</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7040,7 +7025,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260063</v>
+        <v>122260061</v>
       </c>
       <c r="B54" t="n">
         <v>57395</v>
@@ -7092,10 +7077,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651872</v>
+        <v>651886</v>
       </c>
       <c r="R54" t="n">
-        <v>6674674</v>
+        <v>6674654</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7127,7 +7112,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7137,7 +7122,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7164,7 +7149,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122260070</v>
+        <v>122260072</v>
       </c>
       <c r="B55" t="n">
         <v>57395</v>
@@ -7206,7 +7191,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7216,10 +7201,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651967</v>
+        <v>651927</v>
       </c>
       <c r="R55" t="n">
-        <v>6674433</v>
+        <v>6674447</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7251,7 +7236,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7261,7 +7246,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7288,10 +7273,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260120</v>
+        <v>122260096</v>
       </c>
       <c r="B56" t="n">
-        <v>100463</v>
+        <v>80608</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7300,31 +7285,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7332,10 +7316,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>651967</v>
+        <v>651930</v>
       </c>
       <c r="R56" t="n">
-        <v>6674316</v>
+        <v>6674592</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7367,7 +7351,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7377,7 +7361,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7404,10 +7388,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260118</v>
+        <v>122260084</v>
       </c>
       <c r="B57" t="n">
-        <v>100463</v>
+        <v>57532</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7416,31 +7400,39 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7448,13 +7440,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651893</v>
+        <v>651900</v>
       </c>
       <c r="R57" t="n">
-        <v>6674508</v>
+        <v>6674551</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7483,7 +7475,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7493,7 +7485,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7520,10 +7512,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260117</v>
+        <v>122260111</v>
       </c>
       <c r="B58" t="n">
-        <v>100463</v>
+        <v>98202</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7532,29 +7524,37 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -7564,10 +7564,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>651906</v>
+        <v>651949</v>
       </c>
       <c r="R58" t="n">
-        <v>6674571</v>
+        <v>6674415</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7636,10 +7636,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260114</v>
+        <v>122260113</v>
       </c>
       <c r="B59" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7688,10 +7688,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>652010</v>
+        <v>651906</v>
       </c>
       <c r="R59" t="n">
-        <v>6674220</v>
+        <v>6674392</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7760,7 +7760,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260080</v>
+        <v>122260077</v>
       </c>
       <c r="B60" t="n">
         <v>57395</v>
@@ -7802,7 +7802,7 @@
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>652019</v>
+        <v>651964</v>
       </c>
       <c r="R60" t="n">
-        <v>6674239</v>
+        <v>6674220</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7884,10 +7884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301026</v>
+        <v>122301067</v>
       </c>
       <c r="B61" t="n">
-        <v>57532</v>
+        <v>100468</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7896,39 +7896,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7936,13 +7928,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651977</v>
+        <v>652040</v>
       </c>
       <c r="R61" t="n">
-        <v>6673906</v>
+        <v>6673920</v>
       </c>
       <c r="S61" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7971,7 +7963,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7981,7 +7973,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8008,10 +8000,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301079</v>
+        <v>122301066</v>
       </c>
       <c r="B62" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8052,10 +8044,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>652014</v>
+        <v>652079</v>
       </c>
       <c r="R62" t="n">
-        <v>6673954</v>
+        <v>6673929</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8087,7 +8079,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8097,7 +8089,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8124,10 +8116,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301067</v>
+        <v>122301017</v>
       </c>
       <c r="B63" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8136,31 +8128,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8168,10 +8168,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>652040</v>
+        <v>651776</v>
       </c>
       <c r="R63" t="n">
-        <v>6673920</v>
+        <v>6673944</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8240,10 +8240,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301080</v>
+        <v>122301013</v>
       </c>
       <c r="B64" t="n">
-        <v>100463</v>
+        <v>57395</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8252,31 +8252,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8284,10 +8292,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>652011</v>
+        <v>651745</v>
       </c>
       <c r="R64" t="n">
-        <v>6673969</v>
+        <v>6673922</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8319,7 +8327,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8329,7 +8337,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8356,10 +8364,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301050</v>
+        <v>122301079</v>
       </c>
       <c r="B65" t="n">
-        <v>98197</v>
+        <v>100468</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8368,37 +8376,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -8408,10 +8408,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651948</v>
+        <v>652014</v>
       </c>
       <c r="R65" t="n">
-        <v>6673906</v>
+        <v>6673954</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8480,10 +8480,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301066</v>
+        <v>122301026</v>
       </c>
       <c r="B66" t="n">
-        <v>100463</v>
+        <v>57532</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8492,31 +8492,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8524,13 +8532,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>652079</v>
+        <v>651977</v>
       </c>
       <c r="R66" t="n">
-        <v>6673929</v>
+        <v>6673906</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8559,7 +8567,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8569,7 +8577,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8596,10 +8604,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301015</v>
+        <v>122301080</v>
       </c>
       <c r="B67" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8608,39 +8616,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8648,10 +8648,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>651777</v>
+        <v>652011</v>
       </c>
       <c r="R67" t="n">
-        <v>6673975</v>
+        <v>6673969</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8720,10 +8720,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301075</v>
+        <v>122301027</v>
       </c>
       <c r="B68" t="n">
-        <v>100463</v>
+        <v>57749</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8736,27 +8736,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8764,13 +8768,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651975</v>
+        <v>651983</v>
       </c>
       <c r="R68" t="n">
-        <v>6673928</v>
+        <v>6673930</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8799,7 +8803,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8809,7 +8813,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8836,10 +8840,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301063</v>
+        <v>122301081</v>
       </c>
       <c r="B69" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8880,10 +8884,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651949</v>
+        <v>652036</v>
       </c>
       <c r="R69" t="n">
-        <v>6673910</v>
+        <v>6673988</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8915,7 +8919,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8925,7 +8929,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8952,10 +8956,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301027</v>
+        <v>122301065</v>
       </c>
       <c r="B70" t="n">
-        <v>57749</v>
+        <v>100468</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8968,31 +8972,27 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9000,13 +9000,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651983</v>
+        <v>652034</v>
       </c>
       <c r="R70" t="n">
-        <v>6673930</v>
+        <v>6673906</v>
       </c>
       <c r="S70" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9072,10 +9072,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301065</v>
+        <v>122301050</v>
       </c>
       <c r="B71" t="n">
-        <v>100463</v>
+        <v>98202</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9084,29 +9084,37 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
@@ -9116,7 +9124,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>652034</v>
+        <v>651948</v>
       </c>
       <c r="R71" t="n">
         <v>6673906</v>
@@ -9151,7 +9159,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9161,7 +9169,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9191,7 +9199,7 @@
         <v>122301074</v>
       </c>
       <c r="B72" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9304,10 +9312,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301013</v>
+        <v>122301025</v>
       </c>
       <c r="B73" t="n">
-        <v>57395</v>
+        <v>57532</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9320,49 +9328,49 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651745</v>
+        <v>651941</v>
       </c>
       <c r="R73" t="n">
-        <v>6673922</v>
+        <v>6674093</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9391,7 +9399,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9401,7 +9409,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9428,10 +9436,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301017</v>
+        <v>122301073</v>
       </c>
       <c r="B74" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9440,39 +9448,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>651776</v>
+        <v>651817</v>
       </c>
       <c r="R74" t="n">
-        <v>6673944</v>
+        <v>6673939</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9552,10 +9552,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301025</v>
+        <v>122301015</v>
       </c>
       <c r="B75" t="n">
-        <v>57532</v>
+        <v>57395</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9568,49 +9568,49 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651941</v>
+        <v>651777</v>
       </c>
       <c r="R75" t="n">
-        <v>6674093</v>
+        <v>6673975</v>
       </c>
       <c r="S75" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9676,10 +9676,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301073</v>
+        <v>122301075</v>
       </c>
       <c r="B76" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651817</v>
+        <v>651975</v>
       </c>
       <c r="R76" t="n">
-        <v>6673939</v>
+        <v>6673928</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9792,10 +9792,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301081</v>
+        <v>122301063</v>
       </c>
       <c r="B77" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>652036</v>
+        <v>651949</v>
       </c>
       <c r="R77" t="n">
-        <v>6673988</v>
+        <v>6673910</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9911,7 +9911,7 @@
         <v>122260107</v>
       </c>
       <c r="B78" t="n">
-        <v>95744</v>
+        <v>95749</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122301064</v>
+        <v>122300997</v>
       </c>
       <c r="B3" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,42 +811,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651993</v>
+        <v>651883</v>
       </c>
       <c r="R3" t="n">
-        <v>6673896</v>
+        <v>6673732</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122301078</v>
+        <v>122301064</v>
       </c>
       <c r="B4" t="n">
         <v>100468</v>
@@ -959,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>652006</v>
+        <v>651993</v>
       </c>
       <c r="R4" t="n">
-        <v>6673876</v>
+        <v>6673896</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -994,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1146,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122300997</v>
+        <v>122301078</v>
       </c>
       <c r="B6" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,50 +1166,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651883</v>
+        <v>652006</v>
       </c>
       <c r="R6" t="n">
-        <v>6673732</v>
+        <v>6673876</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1233,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -7273,10 +7273,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260096</v>
+        <v>122260084</v>
       </c>
       <c r="B56" t="n">
-        <v>80608</v>
+        <v>57532</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7289,26 +7289,35 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7316,13 +7325,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>651930</v>
+        <v>651900</v>
       </c>
       <c r="R56" t="n">
-        <v>6674592</v>
+        <v>6674551</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7351,7 +7360,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7361,7 +7370,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7388,10 +7397,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260084</v>
+        <v>122260096</v>
       </c>
       <c r="B57" t="n">
-        <v>57532</v>
+        <v>80608</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7404,35 +7413,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7440,13 +7440,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651900</v>
+        <v>651930</v>
       </c>
       <c r="R57" t="n">
-        <v>6674551</v>
+        <v>6674592</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -1270,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122300993</v>
+        <v>122301019</v>
       </c>
       <c r="B7" t="n">
         <v>57395</v>
@@ -1312,7 +1312,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1322,13 +1322,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651962</v>
+        <v>652004</v>
       </c>
       <c r="R7" t="n">
-        <v>6673882</v>
+        <v>6673869</v>
       </c>
       <c r="S7" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,12 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,7 +1394,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122301019</v>
+        <v>122300993</v>
       </c>
       <c r="B8" t="n">
         <v>57395</v>
@@ -1441,7 +1436,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1451,13 +1446,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>652004</v>
+        <v>651962</v>
       </c>
       <c r="R8" t="n">
-        <v>6673869</v>
+        <v>6673882</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1491,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1763,10 +1763,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301077</v>
+        <v>122300999</v>
       </c>
       <c r="B11" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,31 +1775,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1807,10 +1815,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651993</v>
+        <v>651879</v>
       </c>
       <c r="R11" t="n">
-        <v>6673867</v>
+        <v>6673776</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1842,7 +1850,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1852,7 +1860,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2003,10 +2011,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122300999</v>
+        <v>122301077</v>
       </c>
       <c r="B13" t="n">
-        <v>57395</v>
+        <v>100468</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2015,39 +2023,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651879</v>
+        <v>651993</v>
       </c>
       <c r="R13" t="n">
-        <v>6673776</v>
+        <v>6673867</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2243,10 +2243,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122301001</v>
+        <v>122301056</v>
       </c>
       <c r="B15" t="n">
-        <v>57395</v>
+        <v>98202</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2255,39 +2255,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651873</v>
+        <v>651930</v>
       </c>
       <c r="R15" t="n">
-        <v>6673779</v>
+        <v>6673898</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2367,10 +2367,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301062</v>
+        <v>122301001</v>
       </c>
       <c r="B16" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2379,39 +2379,39 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651973</v>
+        <v>651873</v>
       </c>
       <c r="R16" t="n">
-        <v>6673897</v>
+        <v>6673779</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2491,10 +2491,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301056</v>
+        <v>122301062</v>
       </c>
       <c r="B17" t="n">
-        <v>98202</v>
+        <v>100468</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2503,35 +2503,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651930</v>
+        <v>651973</v>
       </c>
       <c r="R17" t="n">
-        <v>6673898</v>
+        <v>6673897</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122301006</v>
+        <v>122301021</v>
       </c>
       <c r="B2" t="n">
         <v>57395</v>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>100049</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -717,20 +712,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651860</v>
+        <v>652056</v>
       </c>
       <c r="R2" t="n">
-        <v>6673862</v>
+        <v>6673872</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +757,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +767,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122300997</v>
+        <v>122300991</v>
       </c>
       <c r="B3" t="n">
         <v>57395</v>
@@ -816,11 +811,6 @@
       </c>
       <c r="E3" t="n">
         <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -847,14 +837,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651883</v>
+        <v>651958</v>
       </c>
       <c r="R3" t="n">
-        <v>6673732</v>
+        <v>6673868</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -886,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122301064</v>
+        <v>122301019</v>
       </c>
       <c r="B4" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,31 +925,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651993</v>
+        <v>652004</v>
       </c>
       <c r="R4" t="n">
-        <v>6673896</v>
+        <v>6673869</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1002,7 +995,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1005,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122301036</v>
+        <v>122301006</v>
       </c>
       <c r="B5" t="n">
-        <v>90808</v>
+        <v>57395</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,26 +1048,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1082,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652047</v>
+        <v>651860</v>
       </c>
       <c r="R5" t="n">
-        <v>6673893</v>
+        <v>6673862</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1117,7 +1114,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1127,7 +1124,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1154,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122301078</v>
+        <v>122301037</v>
       </c>
       <c r="B6" t="n">
-        <v>100468</v>
+        <v>91203</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,31 +1163,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1198,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652006</v>
+        <v>651917</v>
       </c>
       <c r="R6" t="n">
-        <v>6673876</v>
+        <v>6673853</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1233,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122301019</v>
+        <v>122301077</v>
       </c>
       <c r="B7" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,39 +1273,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1322,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>652004</v>
+        <v>651993</v>
       </c>
       <c r="R7" t="n">
-        <v>6673869</v>
+        <v>6673867</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1357,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122300993</v>
+        <v>122301056</v>
       </c>
       <c r="B8" t="n">
-        <v>57395</v>
+        <v>98211</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,39 +1384,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1446,13 +1419,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651962</v>
+        <v>651930</v>
       </c>
       <c r="R8" t="n">
-        <v>6673882</v>
+        <v>6673898</v>
       </c>
       <c r="S8" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,12 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122301020</v>
+        <v>122300988</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>5193</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,20 +1503,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>105930</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1556,16 +1519,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1575,10 +1535,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>652017</v>
+        <v>651926</v>
       </c>
       <c r="R9" t="n">
-        <v>6673872</v>
+        <v>6673844</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1610,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1620,7 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,10 +1607,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122301071</v>
+        <v>122301031</v>
       </c>
       <c r="B10" t="n">
-        <v>100468</v>
+        <v>74692</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1663,27 +1623,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>6426</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1691,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651840</v>
+        <v>651805</v>
       </c>
       <c r="R10" t="n">
-        <v>6673881</v>
+        <v>6673899</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1726,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1736,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,7 +1717,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122300999</v>
+        <v>122301020</v>
       </c>
       <c r="B11" t="n">
         <v>57395</v>
@@ -1780,11 +1734,6 @@
       </c>
       <c r="E11" t="n">
         <v>100049</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1805,7 +1754,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1815,10 +1764,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651879</v>
+        <v>652017</v>
       </c>
       <c r="R11" t="n">
-        <v>6673776</v>
+        <v>6673872</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1850,7 +1799,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1860,7 +1809,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1887,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301058</v>
+        <v>122301064</v>
       </c>
       <c r="B12" t="n">
-        <v>98202</v>
+        <v>100477</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,37 +1848,24 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1939,10 +1875,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651981</v>
+        <v>651993</v>
       </c>
       <c r="R12" t="n">
-        <v>6673859</v>
+        <v>6673896</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1974,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1984,7 +1920,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2011,10 +1947,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122301077</v>
+        <v>122300997</v>
       </c>
       <c r="B13" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2023,42 +1959,45 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651993</v>
+        <v>651883</v>
       </c>
       <c r="R13" t="n">
-        <v>6673867</v>
+        <v>6673732</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2090,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2100,7 +2039,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2127,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301068</v>
+        <v>122301001</v>
       </c>
       <c r="B14" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2139,42 +2078,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651906</v>
+        <v>651873</v>
       </c>
       <c r="R14" t="n">
-        <v>6673752</v>
+        <v>6673779</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2206,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2216,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122301056</v>
+        <v>122300993</v>
       </c>
       <c r="B15" t="n">
-        <v>98202</v>
+        <v>57395</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2255,39 +2197,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2295,13 +2232,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651930</v>
+        <v>651962</v>
       </c>
       <c r="R15" t="n">
-        <v>6673898</v>
+        <v>6673882</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2330,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2340,7 +2277,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2367,7 +2309,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301001</v>
+        <v>122300999</v>
       </c>
       <c r="B16" t="n">
         <v>57395</v>
@@ -2384,11 +2326,6 @@
       </c>
       <c r="E16" t="n">
         <v>100049</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2419,10 +2356,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651873</v>
+        <v>651879</v>
       </c>
       <c r="R16" t="n">
-        <v>6673779</v>
+        <v>6673776</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2454,7 +2391,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2464,7 +2401,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2491,10 +2428,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301062</v>
+        <v>122301036</v>
       </c>
       <c r="B17" t="n">
-        <v>100468</v>
+        <v>90813</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2503,39 +2440,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2543,10 +2466,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651973</v>
+        <v>652047</v>
       </c>
       <c r="R17" t="n">
-        <v>6673897</v>
+        <v>6673893</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2578,7 +2501,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2588,7 +2511,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2615,7 +2538,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122300991</v>
+        <v>122301007</v>
       </c>
       <c r="B18" t="n">
         <v>57395</v>
@@ -2632,11 +2555,6 @@
       </c>
       <c r="E18" t="n">
         <v>100049</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2657,7 +2575,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2667,10 +2585,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651958</v>
+        <v>651778</v>
       </c>
       <c r="R18" t="n">
-        <v>6673868</v>
+        <v>6673895</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2702,7 +2620,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2712,7 +2630,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2739,10 +2657,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122300988</v>
+        <v>122301058</v>
       </c>
       <c r="B19" t="n">
-        <v>5193</v>
+        <v>98211</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2751,36 +2669,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2788,10 +2704,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651926</v>
+        <v>651981</v>
       </c>
       <c r="R19" t="n">
-        <v>6673844</v>
+        <v>6673859</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2823,7 +2739,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2833,7 +2749,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2860,10 +2776,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122301031</v>
+        <v>122301004</v>
       </c>
       <c r="B20" t="n">
-        <v>74691</v>
+        <v>57395</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2872,30 +2788,34 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6426</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Kattfotslav</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2903,10 +2823,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651805</v>
+        <v>651888</v>
       </c>
       <c r="R20" t="n">
-        <v>6673899</v>
+        <v>6673877</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2938,7 +2858,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2948,7 +2868,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2975,7 +2895,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122301021</v>
+        <v>122300995</v>
       </c>
       <c r="B21" t="n">
         <v>57395</v>
@@ -2992,11 +2912,6 @@
       </c>
       <c r="E21" t="n">
         <v>100049</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3017,20 +2932,20 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652056</v>
+        <v>651899</v>
       </c>
       <c r="R21" t="n">
-        <v>6673872</v>
+        <v>6673777</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3062,7 +2977,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3072,7 +2987,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3099,10 +3014,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122301053</v>
+        <v>122301060</v>
       </c>
       <c r="B22" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3117,11 +3032,6 @@
       <c r="E22" t="n">
         <v>220787</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -3134,7 +3044,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3151,10 +3061,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651986</v>
+        <v>652000</v>
       </c>
       <c r="R22" t="n">
-        <v>6673841</v>
+        <v>6673848</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3186,7 +3096,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3196,12 +3106,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3228,10 +3133,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122301007</v>
+        <v>122301062</v>
       </c>
       <c r="B23" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3240,39 +3145,34 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3280,10 +3180,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651778</v>
+        <v>651973</v>
       </c>
       <c r="R23" t="n">
-        <v>6673895</v>
+        <v>6673897</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3315,7 +3215,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3325,7 +3225,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3352,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122301037</v>
+        <v>122300994</v>
       </c>
       <c r="B24" t="n">
-        <v>91198</v>
+        <v>57395</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3368,21 +3268,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040162</v>
+        <v>100049</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3390,10 +3299,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651917</v>
+        <v>651915</v>
       </c>
       <c r="R24" t="n">
-        <v>6673853</v>
+        <v>6673888</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3425,7 +3334,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3435,7 +3344,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3462,10 +3371,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301004</v>
+        <v>122301071</v>
       </c>
       <c r="B25" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3474,39 +3383,26 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3514,10 +3410,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651888</v>
+        <v>651840</v>
       </c>
       <c r="R25" t="n">
-        <v>6673877</v>
+        <v>6673881</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3549,7 +3445,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3559,7 +3455,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3586,10 +3482,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122300994</v>
+        <v>122301078</v>
       </c>
       <c r="B26" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3598,39 +3494,26 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3638,10 +3521,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651915</v>
+        <v>652006</v>
       </c>
       <c r="R26" t="n">
-        <v>6673888</v>
+        <v>6673876</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3673,7 +3556,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3566,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3710,10 +3593,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301060</v>
+        <v>122301068</v>
       </c>
       <c r="B27" t="n">
-        <v>98202</v>
+        <v>100477</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3722,50 +3605,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>652000</v>
+        <v>651906</v>
       </c>
       <c r="R27" t="n">
-        <v>6673848</v>
+        <v>6673752</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3797,7 +3667,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3807,7 +3677,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3834,10 +3704,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122300995</v>
+        <v>122301053</v>
       </c>
       <c r="B28" t="n">
-        <v>57395</v>
+        <v>98211</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3846,39 +3716,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3886,10 +3751,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651899</v>
+        <v>651986</v>
       </c>
       <c r="R28" t="n">
-        <v>6673777</v>
+        <v>6673841</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3921,7 +3786,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3931,7 +3796,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,10 +3828,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122260110</v>
+        <v>122260100</v>
       </c>
       <c r="B29" t="n">
-        <v>98202</v>
+        <v>90813</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3970,39 +3840,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4010,10 +3866,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651949</v>
+        <v>652034</v>
       </c>
       <c r="R29" t="n">
-        <v>6674420</v>
+        <v>6674236</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4045,7 +3901,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4055,12 +3911,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4071,6 +3922,16 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4087,7 +3948,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122260066</v>
+        <v>122260074</v>
       </c>
       <c r="B30" t="n">
         <v>57395</v>
@@ -4104,11 +3965,6 @@
       </c>
       <c r="E30" t="n">
         <v>100049</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4129,7 +3985,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4139,13 +3995,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651934</v>
+        <v>651923</v>
       </c>
       <c r="R30" t="n">
-        <v>6674510</v>
+        <v>6674436</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4174,7 +4030,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4184,7 +4040,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hörd i norr.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4211,10 +4072,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260120</v>
+        <v>122260126</v>
       </c>
       <c r="B31" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4228,11 +4089,6 @@
       </c>
       <c r="E31" t="n">
         <v>222498</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4255,10 +4111,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651967</v>
+        <v>651941</v>
       </c>
       <c r="R31" t="n">
-        <v>6674316</v>
+        <v>6674469</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4290,7 +4146,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4300,7 +4156,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4327,10 +4183,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260126</v>
+        <v>122260072</v>
       </c>
       <c r="B32" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4339,31 +4195,34 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4371,10 +4230,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651941</v>
+        <v>651927</v>
       </c>
       <c r="R32" t="n">
-        <v>6674469</v>
+        <v>6674447</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4406,7 +4265,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4416,7 +4275,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4443,10 +4302,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260075</v>
+        <v>122260119</v>
       </c>
       <c r="B33" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4455,39 +4314,26 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4495,10 +4341,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651900</v>
+        <v>651950</v>
       </c>
       <c r="R33" t="n">
-        <v>6674390</v>
+        <v>6674465</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4530,7 +4376,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4540,7 +4386,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4567,7 +4413,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260068</v>
+        <v>122260061</v>
       </c>
       <c r="B34" t="n">
         <v>57395</v>
@@ -4584,11 +4430,6 @@
       </c>
       <c r="E34" t="n">
         <v>100049</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -4619,10 +4460,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651928</v>
+        <v>651886</v>
       </c>
       <c r="R34" t="n">
-        <v>6674457</v>
+        <v>6674654</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4654,7 +4495,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4664,7 +4505,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4691,10 +4532,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122260058</v>
+        <v>122260116</v>
       </c>
       <c r="B35" t="n">
-        <v>5193</v>
+        <v>100477</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4707,32 +4548,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Vågbandad barkbock</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4740,10 +4571,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>652031</v>
+        <v>651859</v>
       </c>
       <c r="R35" t="n">
-        <v>6674226</v>
+        <v>6674654</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4775,7 +4606,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4785,7 +4616,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4796,21 +4627,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4827,10 +4643,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122260125</v>
+        <v>122260076</v>
       </c>
       <c r="B36" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4839,31 +4655,34 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4871,10 +4690,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651973</v>
+        <v>651949</v>
       </c>
       <c r="R36" t="n">
-        <v>6674332</v>
+        <v>6674279</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4906,7 +4725,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4916,7 +4735,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4943,10 +4762,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122260116</v>
+        <v>122260113</v>
       </c>
       <c r="B37" t="n">
-        <v>100468</v>
+        <v>98211</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4955,29 +4774,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -4987,10 +4809,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651859</v>
+        <v>651906</v>
       </c>
       <c r="R37" t="n">
-        <v>6674654</v>
+        <v>6674392</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5022,7 +4844,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5032,7 +4854,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5059,10 +4881,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122260119</v>
+        <v>122260115</v>
       </c>
       <c r="B38" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5076,11 +4898,6 @@
       </c>
       <c r="E38" t="n">
         <v>222498</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -5103,10 +4920,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651950</v>
+        <v>651891</v>
       </c>
       <c r="R38" t="n">
-        <v>6674465</v>
+        <v>6674645</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5138,7 +4955,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5148,7 +4965,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5175,10 +4992,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260103</v>
+        <v>122260117</v>
       </c>
       <c r="B39" t="n">
-        <v>91246</v>
+        <v>100477</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5187,30 +5004,26 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5218,10 +5031,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651855</v>
+        <v>651906</v>
       </c>
       <c r="R39" t="n">
-        <v>6674655</v>
+        <v>6674571</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5253,7 +5066,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5263,12 +5076,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På klibbtickelåga.</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5279,21 +5087,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5310,7 +5103,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260063</v>
+        <v>122260080</v>
       </c>
       <c r="B40" t="n">
         <v>57395</v>
@@ -5327,11 +5120,6 @@
       </c>
       <c r="E40" t="n">
         <v>100049</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -5362,10 +5150,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651872</v>
+        <v>652019</v>
       </c>
       <c r="R40" t="n">
-        <v>6674674</v>
+        <v>6674239</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5397,7 +5185,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5407,7 +5195,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5434,10 +5222,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260076</v>
+        <v>122260111</v>
       </c>
       <c r="B41" t="n">
-        <v>57395</v>
+        <v>98211</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5446,39 +5234,34 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5489,7 +5272,7 @@
         <v>651949</v>
       </c>
       <c r="R41" t="n">
-        <v>6674279</v>
+        <v>6674415</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5521,7 +5304,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5531,7 +5314,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5558,10 +5341,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122260117</v>
+        <v>122260118</v>
       </c>
       <c r="B42" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5575,11 +5358,6 @@
       </c>
       <c r="E42" t="n">
         <v>222498</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -5602,10 +5380,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651906</v>
+        <v>651893</v>
       </c>
       <c r="R42" t="n">
-        <v>6674571</v>
+        <v>6674508</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5637,7 +5415,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5647,7 +5425,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5674,10 +5452,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260121</v>
+        <v>122260114</v>
       </c>
       <c r="B43" t="n">
-        <v>100468</v>
+        <v>98211</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5686,29 +5464,32 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
@@ -5718,10 +5499,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651955</v>
+        <v>652010</v>
       </c>
       <c r="R43" t="n">
-        <v>6674222</v>
+        <v>6674220</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5753,7 +5534,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5763,7 +5544,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5790,10 +5571,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260100</v>
+        <v>122260103</v>
       </c>
       <c r="B44" t="n">
-        <v>90808</v>
+        <v>91251</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5802,25 +5583,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>1209</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5833,10 +5609,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>652034</v>
+        <v>651855</v>
       </c>
       <c r="R44" t="n">
-        <v>6674236</v>
+        <v>6674655</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5868,7 +5644,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5878,7 +5654,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På klibbtickelåga.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5889,11 +5670,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
@@ -5938,11 +5714,6 @@
       <c r="E45" t="n">
         <v>100049</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -6044,7 +5815,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122260064</v>
+        <v>122260071</v>
       </c>
       <c r="B46" t="n">
         <v>57395</v>
@@ -6061,11 +5832,6 @@
       </c>
       <c r="E46" t="n">
         <v>100049</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -6086,7 +5852,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6096,10 +5862,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651845</v>
+        <v>651930</v>
       </c>
       <c r="R46" t="n">
-        <v>6674626</v>
+        <v>6674444</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6131,7 +5897,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6141,7 +5907,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6168,10 +5934,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260118</v>
+        <v>122260077</v>
       </c>
       <c r="B47" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6180,31 +5946,34 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6212,10 +5981,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651893</v>
+        <v>651964</v>
       </c>
       <c r="R47" t="n">
-        <v>6674508</v>
+        <v>6674220</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6247,7 +6016,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6257,7 +6026,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6284,7 +6053,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260080</v>
+        <v>122260075</v>
       </c>
       <c r="B48" t="n">
         <v>57395</v>
@@ -6301,11 +6070,6 @@
       </c>
       <c r="E48" t="n">
         <v>100049</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -6326,7 +6090,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -6336,10 +6100,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>652019</v>
+        <v>651900</v>
       </c>
       <c r="R48" t="n">
-        <v>6674239</v>
+        <v>6674390</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6371,7 +6135,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6381,7 +6145,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6408,10 +6172,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260085</v>
+        <v>122260064</v>
       </c>
       <c r="B49" t="n">
-        <v>57749</v>
+        <v>57395</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6420,20 +6184,15 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6450,7 +6209,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6460,13 +6219,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651895</v>
+        <v>651845</v>
       </c>
       <c r="R49" t="n">
-        <v>6674630</v>
+        <v>6674626</v>
       </c>
       <c r="S49" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6495,7 +6254,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6505,7 +6264,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6532,10 +6291,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260115</v>
+        <v>122260063</v>
       </c>
       <c r="B50" t="n">
-        <v>100468</v>
+        <v>57395</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6544,31 +6303,34 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6576,10 +6338,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651891</v>
+        <v>651872</v>
       </c>
       <c r="R50" t="n">
-        <v>6674645</v>
+        <v>6674674</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6611,7 +6373,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6621,7 +6383,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6648,10 +6410,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122260071</v>
+        <v>122260110</v>
       </c>
       <c r="B51" t="n">
-        <v>57395</v>
+        <v>98211</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6660,39 +6422,34 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6700,10 +6457,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651930</v>
+        <v>651949</v>
       </c>
       <c r="R51" t="n">
-        <v>6674444</v>
+        <v>6674420</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6735,7 +6492,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6745,7 +6502,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6772,10 +6534,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260074</v>
+        <v>122260096</v>
       </c>
       <c r="B52" t="n">
-        <v>57395</v>
+        <v>80609</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6788,35 +6550,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>1049</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6824,13 +6572,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651923</v>
+        <v>651930</v>
       </c>
       <c r="R52" t="n">
-        <v>6674436</v>
+        <v>6674592</v>
       </c>
       <c r="S52" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6859,7 +6607,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6869,12 +6617,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Hörd i norr.</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6901,10 +6644,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260114</v>
+        <v>122260121</v>
       </c>
       <c r="B53" t="n">
-        <v>98202</v>
+        <v>100477</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6913,37 +6656,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
@@ -6953,10 +6683,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>652010</v>
+        <v>651955</v>
       </c>
       <c r="R53" t="n">
-        <v>6674220</v>
+        <v>6674222</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6988,7 +6718,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6998,7 +6728,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7025,10 +6755,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260061</v>
+        <v>122260125</v>
       </c>
       <c r="B54" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7037,39 +6767,26 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7077,10 +6794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651886</v>
+        <v>651973</v>
       </c>
       <c r="R54" t="n">
-        <v>6674654</v>
+        <v>6674332</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7112,7 +6829,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7122,7 +6839,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7149,7 +6866,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122260072</v>
+        <v>122260068</v>
       </c>
       <c r="B55" t="n">
         <v>57395</v>
@@ -7166,11 +6883,6 @@
       </c>
       <c r="E55" t="n">
         <v>100049</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7201,10 +6913,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651927</v>
+        <v>651928</v>
       </c>
       <c r="R55" t="n">
-        <v>6674447</v>
+        <v>6674457</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7236,7 +6948,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7246,7 +6958,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7273,10 +6985,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260084</v>
+        <v>122260066</v>
       </c>
       <c r="B56" t="n">
-        <v>57532</v>
+        <v>57395</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7289,33 +7001,28 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7325,13 +7032,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>651900</v>
+        <v>651934</v>
       </c>
       <c r="R56" t="n">
-        <v>6674551</v>
+        <v>6674510</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7360,7 +7067,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7370,7 +7077,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7397,10 +7104,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260096</v>
+        <v>122260085</v>
       </c>
       <c r="B57" t="n">
-        <v>80608</v>
+        <v>57749</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7409,30 +7116,34 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1049</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Kortskaftad ärgspik</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7440,13 +7151,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651930</v>
+        <v>651895</v>
       </c>
       <c r="R57" t="n">
-        <v>6674592</v>
+        <v>6674630</v>
       </c>
       <c r="S57" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7475,7 +7186,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7485,7 +7196,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7512,10 +7223,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260111</v>
+        <v>122260058</v>
       </c>
       <c r="B58" t="n">
-        <v>98202</v>
+        <v>5193</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7524,39 +7235,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>105930</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7564,10 +7267,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>651949</v>
+        <v>652031</v>
       </c>
       <c r="R58" t="n">
-        <v>6674415</v>
+        <v>6674226</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7599,7 +7302,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7609,7 +7312,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7620,6 +7323,16 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7636,10 +7349,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260113</v>
+        <v>122260120</v>
       </c>
       <c r="B59" t="n">
-        <v>98202</v>
+        <v>100477</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7648,37 +7361,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -7688,10 +7388,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651906</v>
+        <v>651967</v>
       </c>
       <c r="R59" t="n">
-        <v>6674392</v>
+        <v>6674316</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7723,7 +7423,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7733,7 +7433,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7760,10 +7460,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260077</v>
+        <v>122260084</v>
       </c>
       <c r="B60" t="n">
-        <v>57395</v>
+        <v>57532</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7776,33 +7476,28 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
@@ -7812,13 +7507,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651964</v>
+        <v>651900</v>
       </c>
       <c r="R60" t="n">
-        <v>6674220</v>
+        <v>6674551</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7847,7 +7542,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7857,7 +7552,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7884,10 +7579,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301067</v>
+        <v>122301026</v>
       </c>
       <c r="B61" t="n">
-        <v>100468</v>
+        <v>57532</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7896,31 +7591,34 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7928,13 +7626,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>652040</v>
+        <v>651977</v>
       </c>
       <c r="R61" t="n">
-        <v>6673920</v>
+        <v>6673906</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7963,7 +7661,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7973,7 +7671,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8000,10 +7698,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301066</v>
+        <v>122301050</v>
       </c>
       <c r="B62" t="n">
-        <v>100468</v>
+        <v>98211</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8012,29 +7710,32 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -8044,10 +7745,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>652079</v>
+        <v>651948</v>
       </c>
       <c r="R62" t="n">
-        <v>6673929</v>
+        <v>6673906</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8079,7 +7780,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8089,7 +7790,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8116,7 +7817,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301017</v>
+        <v>122301013</v>
       </c>
       <c r="B63" t="n">
         <v>57395</v>
@@ -8133,11 +7834,6 @@
       </c>
       <c r="E63" t="n">
         <v>100049</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -8168,10 +7864,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>651776</v>
+        <v>651745</v>
       </c>
       <c r="R63" t="n">
-        <v>6673944</v>
+        <v>6673922</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8203,7 +7899,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8213,7 +7909,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8240,10 +7936,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301013</v>
+        <v>122301066</v>
       </c>
       <c r="B64" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8252,39 +7948,26 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8292,10 +7975,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651745</v>
+        <v>652079</v>
       </c>
       <c r="R64" t="n">
-        <v>6673922</v>
+        <v>6673929</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8327,7 +8010,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8337,7 +8020,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8364,10 +8047,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301079</v>
+        <v>122301025</v>
       </c>
       <c r="B65" t="n">
-        <v>100468</v>
+        <v>57532</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8376,45 +8059,48 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>652014</v>
+        <v>651941</v>
       </c>
       <c r="R65" t="n">
-        <v>6673954</v>
+        <v>6674093</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8443,7 +8129,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8453,7 +8139,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8480,10 +8166,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301026</v>
+        <v>122301067</v>
       </c>
       <c r="B66" t="n">
-        <v>57532</v>
+        <v>100477</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8492,39 +8178,26 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8532,13 +8205,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651977</v>
+        <v>652040</v>
       </c>
       <c r="R66" t="n">
-        <v>6673906</v>
+        <v>6673920</v>
       </c>
       <c r="S66" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8567,7 +8240,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8577,7 +8250,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8604,10 +8277,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301080</v>
+        <v>122301075</v>
       </c>
       <c r="B67" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8621,11 +8294,6 @@
       </c>
       <c r="E67" t="n">
         <v>222498</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -8648,10 +8316,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>652011</v>
+        <v>651975</v>
       </c>
       <c r="R67" t="n">
-        <v>6673969</v>
+        <v>6673928</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8683,7 +8351,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8693,7 +8361,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8720,10 +8388,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301027</v>
+        <v>122301079</v>
       </c>
       <c r="B68" t="n">
-        <v>57749</v>
+        <v>100477</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8736,31 +8404,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8768,13 +8427,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651983</v>
+        <v>652014</v>
       </c>
       <c r="R68" t="n">
-        <v>6673930</v>
+        <v>6673954</v>
       </c>
       <c r="S68" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8803,7 +8462,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8813,7 +8472,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8840,10 +8499,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301081</v>
+        <v>122301074</v>
       </c>
       <c r="B69" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8857,11 +8516,6 @@
       </c>
       <c r="E69" t="n">
         <v>222498</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8884,10 +8538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>652036</v>
+        <v>651855</v>
       </c>
       <c r="R69" t="n">
-        <v>6673988</v>
+        <v>6673907</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8919,7 +8573,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8929,7 +8583,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8956,10 +8610,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301065</v>
+        <v>122301027</v>
       </c>
       <c r="B70" t="n">
-        <v>100468</v>
+        <v>57749</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8972,27 +8626,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9000,13 +8653,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>652034</v>
+        <v>651983</v>
       </c>
       <c r="R70" t="n">
-        <v>6673906</v>
+        <v>6673930</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9035,7 +8688,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9045,7 +8698,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9072,10 +8725,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301050</v>
+        <v>122301015</v>
       </c>
       <c r="B71" t="n">
-        <v>98202</v>
+        <v>57395</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9084,39 +8737,34 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -9124,10 +8772,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651948</v>
+        <v>651777</v>
       </c>
       <c r="R71" t="n">
-        <v>6673906</v>
+        <v>6673975</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9159,7 +8807,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9169,7 +8817,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9196,10 +8844,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301074</v>
+        <v>122301080</v>
       </c>
       <c r="B72" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9213,11 +8861,6 @@
       </c>
       <c r="E72" t="n">
         <v>222498</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -9240,10 +8883,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651855</v>
+        <v>652011</v>
       </c>
       <c r="R72" t="n">
-        <v>6673907</v>
+        <v>6673969</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9275,7 +8918,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9285,7 +8928,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9312,10 +8955,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301025</v>
+        <v>122301017</v>
       </c>
       <c r="B73" t="n">
-        <v>57532</v>
+        <v>57395</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9328,49 +8971,44 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651941</v>
+        <v>651776</v>
       </c>
       <c r="R73" t="n">
-        <v>6674093</v>
+        <v>6673944</v>
       </c>
       <c r="S73" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9399,7 +9037,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9409,7 +9047,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9436,10 +9074,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301073</v>
+        <v>122301081</v>
       </c>
       <c r="B74" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9453,11 +9091,6 @@
       </c>
       <c r="E74" t="n">
         <v>222498</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9480,10 +9113,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>651817</v>
+        <v>652036</v>
       </c>
       <c r="R74" t="n">
-        <v>6673939</v>
+        <v>6673988</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9515,7 +9148,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9525,7 +9158,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9552,10 +9185,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301015</v>
+        <v>122301065</v>
       </c>
       <c r="B75" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9564,39 +9197,26 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9604,10 +9224,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651777</v>
+        <v>652034</v>
       </c>
       <c r="R75" t="n">
-        <v>6673975</v>
+        <v>6673906</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9639,7 +9259,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9649,7 +9269,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9676,10 +9296,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301075</v>
+        <v>122301073</v>
       </c>
       <c r="B76" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9693,11 +9313,6 @@
       </c>
       <c r="E76" t="n">
         <v>222498</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9720,10 +9335,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651975</v>
+        <v>651817</v>
       </c>
       <c r="R76" t="n">
-        <v>6673928</v>
+        <v>6673939</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9755,7 +9370,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9765,7 +9380,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9795,7 +9410,7 @@
         <v>122301063</v>
       </c>
       <c r="B77" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9809,11 +9424,6 @@
       </c>
       <c r="E77" t="n">
         <v>222498</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9911,7 +9521,7 @@
         <v>122260107</v>
       </c>
       <c r="B78" t="n">
-        <v>95749</v>
+        <v>95758</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9925,11 +9535,6 @@
       </c>
       <c r="E78" t="n">
         <v>53</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Vedtrappmossa</t>
-        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -2066,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301001</v>
+        <v>122301036</v>
       </c>
       <c r="B14" t="n">
-        <v>57395</v>
+        <v>90813</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,30 +2082,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2113,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651873</v>
+        <v>652047</v>
       </c>
       <c r="R14" t="n">
-        <v>6673779</v>
+        <v>6673893</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2148,7 +2139,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,7 +2149,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,7 +2176,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122300993</v>
+        <v>122301001</v>
       </c>
       <c r="B15" t="n">
         <v>57395</v>
@@ -2222,7 +2213,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2232,13 +2223,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651962</v>
+        <v>651873</v>
       </c>
       <c r="R15" t="n">
-        <v>6673882</v>
+        <v>6673779</v>
       </c>
       <c r="S15" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2267,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,12 +2268,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,7 +2295,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122300999</v>
+        <v>122300993</v>
       </c>
       <c r="B16" t="n">
         <v>57395</v>
@@ -2346,7 +2332,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2356,13 +2342,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651879</v>
+        <v>651962</v>
       </c>
       <c r="R16" t="n">
-        <v>6673776</v>
+        <v>6673882</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2391,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2401,7 +2387,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2428,10 +2419,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301036</v>
+        <v>122300999</v>
       </c>
       <c r="B17" t="n">
-        <v>90813</v>
+        <v>57395</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2444,21 +2435,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>652047</v>
+        <v>651879</v>
       </c>
       <c r="R17" t="n">
-        <v>6673893</v>
+        <v>6673776</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3371,10 +3371,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301071</v>
+        <v>122301053</v>
       </c>
       <c r="B25" t="n">
-        <v>100477</v>
+        <v>98211</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3383,24 +3383,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3410,10 +3418,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651840</v>
+        <v>651986</v>
       </c>
       <c r="R25" t="n">
-        <v>6673881</v>
+        <v>6673841</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3445,7 +3453,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3455,7 +3463,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3482,7 +3495,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301078</v>
+        <v>122301071</v>
       </c>
       <c r="B26" t="n">
         <v>100477</v>
@@ -3521,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>652006</v>
+        <v>651840</v>
       </c>
       <c r="R26" t="n">
-        <v>6673876</v>
+        <v>6673881</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3556,7 +3569,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3566,7 +3579,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3593,7 +3606,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301068</v>
+        <v>122301078</v>
       </c>
       <c r="B27" t="n">
         <v>100477</v>
@@ -3628,14 +3641,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>651906</v>
+        <v>652006</v>
       </c>
       <c r="R27" t="n">
-        <v>6673752</v>
+        <v>6673876</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3667,7 +3680,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3677,7 +3690,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3704,10 +3717,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122301053</v>
+        <v>122301068</v>
       </c>
       <c r="B28" t="n">
-        <v>98211</v>
+        <v>100477</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3716,45 +3729,37 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651986</v>
+        <v>651906</v>
       </c>
       <c r="R28" t="n">
-        <v>6673841</v>
+        <v>6673752</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3786,7 +3791,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3796,12 +3801,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -6534,10 +6534,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260096</v>
+        <v>122260121</v>
       </c>
       <c r="B52" t="n">
-        <v>80609</v>
+        <v>100477</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6546,25 +6546,26 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6572,10 +6573,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651930</v>
+        <v>651955</v>
       </c>
       <c r="R52" t="n">
-        <v>6674592</v>
+        <v>6674222</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6607,7 +6608,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6617,7 +6618,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6644,7 +6645,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260121</v>
+        <v>122260125</v>
       </c>
       <c r="B53" t="n">
         <v>100477</v>
@@ -6683,10 +6684,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651955</v>
+        <v>651973</v>
       </c>
       <c r="R53" t="n">
-        <v>6674222</v>
+        <v>6674332</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6718,7 +6719,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6728,7 +6729,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6755,10 +6756,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260125</v>
+        <v>122260096</v>
       </c>
       <c r="B54" t="n">
-        <v>100477</v>
+        <v>80609</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6767,26 +6768,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6794,10 +6794,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651973</v>
+        <v>651930</v>
       </c>
       <c r="R54" t="n">
-        <v>6674332</v>
+        <v>6674592</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6829,7 +6829,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8610,10 +8610,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301027</v>
+        <v>122301015</v>
       </c>
       <c r="B70" t="n">
-        <v>57749</v>
+        <v>57395</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8622,15 +8622,15 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8640,12 +8640,16 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8653,13 +8657,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651983</v>
+        <v>651777</v>
       </c>
       <c r="R70" t="n">
-        <v>6673930</v>
+        <v>6673975</v>
       </c>
       <c r="S70" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8688,7 +8692,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8698,7 +8702,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8725,10 +8729,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301015</v>
+        <v>122301027</v>
       </c>
       <c r="B71" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8737,15 +8741,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8755,16 +8759,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8772,13 +8772,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651777</v>
+        <v>651983</v>
       </c>
       <c r="R71" t="n">
-        <v>6673975</v>
+        <v>6673930</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD71" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -3371,10 +3371,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301053</v>
+        <v>122301071</v>
       </c>
       <c r="B25" t="n">
-        <v>98211</v>
+        <v>100477</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3383,32 +3383,24 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -3418,10 +3410,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651986</v>
+        <v>651840</v>
       </c>
       <c r="R25" t="n">
-        <v>6673841</v>
+        <v>6673881</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3453,7 +3445,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3463,12 +3455,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3495,7 +3482,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301071</v>
+        <v>122301078</v>
       </c>
       <c r="B26" t="n">
         <v>100477</v>
@@ -3534,10 +3521,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651840</v>
+        <v>652006</v>
       </c>
       <c r="R26" t="n">
-        <v>6673881</v>
+        <v>6673876</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3569,7 +3556,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3579,7 +3566,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3606,7 +3593,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301078</v>
+        <v>122301068</v>
       </c>
       <c r="B27" t="n">
         <v>100477</v>
@@ -3641,14 +3628,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>652006</v>
+        <v>651906</v>
       </c>
       <c r="R27" t="n">
-        <v>6673876</v>
+        <v>6673752</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3680,7 +3667,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3690,7 +3677,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3717,10 +3704,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122301068</v>
+        <v>122301053</v>
       </c>
       <c r="B28" t="n">
-        <v>100477</v>
+        <v>98211</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3729,37 +3716,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651906</v>
+        <v>651986</v>
       </c>
       <c r="R28" t="n">
-        <v>6673752</v>
+        <v>6673841</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3791,7 +3786,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,7 +3796,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4413,10 +4413,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260061</v>
+        <v>122260116</v>
       </c>
       <c r="B34" t="n">
-        <v>57395</v>
+        <v>100477</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4425,34 +4425,26 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4460,7 +4452,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651886</v>
+        <v>651859</v>
       </c>
       <c r="R34" t="n">
         <v>6674654</v>
@@ -4495,7 +4487,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4505,7 +4497,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4532,10 +4524,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122260116</v>
+        <v>122260061</v>
       </c>
       <c r="B35" t="n">
-        <v>100477</v>
+        <v>57395</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4544,26 +4536,34 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651859</v>
+        <v>651886</v>
       </c>
       <c r="R35" t="n">
         <v>6674654</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122301021</v>
+        <v>122301037</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>91216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,41 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6040162</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>652056</v>
+        <v>651917</v>
       </c>
       <c r="R2" t="n">
-        <v>6673872</v>
+        <v>6673853</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -757,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -767,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122300991</v>
+        <v>122300993</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,6 +802,11 @@
       </c>
       <c r="E3" t="n">
         <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -831,7 +827,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651958</v>
+        <v>651962</v>
       </c>
       <c r="R3" t="n">
-        <v>6673868</v>
+        <v>6673882</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +882,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122301019</v>
+        <v>122300999</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,6 +931,11 @@
       </c>
       <c r="E4" t="n">
         <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -960,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>652004</v>
+        <v>651879</v>
       </c>
       <c r="R4" t="n">
-        <v>6673869</v>
+        <v>6673776</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -995,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,7 +1041,7 @@
         <v>122301006</v>
       </c>
       <c r="B5" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1049,6 +1055,11 @@
       </c>
       <c r="E5" t="n">
         <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1151,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122301037</v>
+        <v>122301058</v>
       </c>
       <c r="B6" t="n">
-        <v>91203</v>
+        <v>98224</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,25 +1174,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040162</v>
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1189,10 +1214,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651917</v>
+        <v>651981</v>
       </c>
       <c r="R6" t="n">
-        <v>6673853</v>
+        <v>6673859</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1224,7 +1249,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1259,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1286,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122301077</v>
+        <v>122301071</v>
       </c>
       <c r="B7" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1278,6 +1303,11 @@
       </c>
       <c r="E7" t="n">
         <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1300,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651993</v>
+        <v>651840</v>
       </c>
       <c r="R7" t="n">
-        <v>6673867</v>
+        <v>6673881</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1335,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122301056</v>
+        <v>122301053</v>
       </c>
       <c r="B8" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,6 +1420,11 @@
       <c r="E8" t="n">
         <v>220787</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Goodyera repens</t>
@@ -1402,7 +1437,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1419,10 +1454,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651930</v>
+        <v>651986</v>
       </c>
       <c r="R8" t="n">
-        <v>6673898</v>
+        <v>6673841</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1454,7 +1489,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1499,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1509,6 +1549,11 @@
       <c r="E9" t="n">
         <v>105930</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Semanotus undatus</t>
@@ -1607,10 +1652,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122301031</v>
+        <v>122301064</v>
       </c>
       <c r="B10" t="n">
-        <v>74692</v>
+        <v>100490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1623,21 +1668,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1645,10 +1696,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651805</v>
+        <v>651993</v>
       </c>
       <c r="R10" t="n">
-        <v>6673899</v>
+        <v>6673896</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1680,7 +1731,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1741,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1768,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301020</v>
+        <v>122301062</v>
       </c>
       <c r="B11" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,34 +1780,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1764,10 +1820,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>652017</v>
+        <v>651973</v>
       </c>
       <c r="R11" t="n">
-        <v>6673872</v>
+        <v>6673897</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1799,7 +1855,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1809,7 +1865,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,10 +1892,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301064</v>
+        <v>122301019</v>
       </c>
       <c r="B12" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,26 +1904,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1875,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651993</v>
+        <v>652004</v>
       </c>
       <c r="R12" t="n">
-        <v>6673896</v>
+        <v>6673869</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1910,7 +1979,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,7 +1989,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,10 +2016,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122300997</v>
+        <v>122301077</v>
       </c>
       <c r="B13" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,45 +2028,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651883</v>
+        <v>651993</v>
       </c>
       <c r="R13" t="n">
-        <v>6673732</v>
+        <v>6673867</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2029,7 +2095,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,7 +2105,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2132,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301036</v>
+        <v>122301007</v>
       </c>
       <c r="B14" t="n">
-        <v>90813</v>
+        <v>57399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,21 +2148,35 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2104,10 +2184,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>652047</v>
+        <v>651778</v>
       </c>
       <c r="R14" t="n">
-        <v>6673893</v>
+        <v>6673895</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2139,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2149,7 +2229,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,10 +2256,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122301001</v>
+        <v>122301031</v>
       </c>
       <c r="B15" t="n">
-        <v>57395</v>
+        <v>74696</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,34 +2268,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6426</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2223,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651873</v>
+        <v>651805</v>
       </c>
       <c r="R15" t="n">
-        <v>6673779</v>
+        <v>6673899</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2258,7 +2334,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2344,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2295,10 +2371,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122300993</v>
+        <v>122301068</v>
       </c>
       <c r="B16" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,48 +2383,45 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651962</v>
+        <v>651906</v>
       </c>
       <c r="R16" t="n">
-        <v>6673882</v>
+        <v>6673752</v>
       </c>
       <c r="S16" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2377,7 +2450,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,12 +2460,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,10 +2487,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122300999</v>
+        <v>122301056</v>
       </c>
       <c r="B17" t="n">
-        <v>57395</v>
+        <v>98224</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,34 +2499,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2466,10 +2539,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651879</v>
+        <v>651930</v>
       </c>
       <c r="R17" t="n">
-        <v>6673776</v>
+        <v>6673898</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2501,7 +2574,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2511,7 +2584,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,10 +2611,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122301007</v>
+        <v>122300991</v>
       </c>
       <c r="B18" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2555,6 +2628,11 @@
       </c>
       <c r="E18" t="n">
         <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2575,7 +2653,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2585,10 +2663,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651778</v>
+        <v>651958</v>
       </c>
       <c r="R18" t="n">
-        <v>6673895</v>
+        <v>6673868</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2620,7 +2698,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2630,7 +2708,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2657,10 +2735,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122301058</v>
+        <v>122300995</v>
       </c>
       <c r="B19" t="n">
-        <v>98211</v>
+        <v>57399</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2669,34 +2747,39 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2704,10 +2787,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651981</v>
+        <v>651899</v>
       </c>
       <c r="R19" t="n">
-        <v>6673859</v>
+        <v>6673777</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2739,7 +2822,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2749,7 +2832,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,10 +2859,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122301004</v>
+        <v>122300994</v>
       </c>
       <c r="B20" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2793,6 +2876,11 @@
       </c>
       <c r="E20" t="n">
         <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2823,10 +2911,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651888</v>
+        <v>651915</v>
       </c>
       <c r="R20" t="n">
-        <v>6673877</v>
+        <v>6673888</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2858,7 +2946,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2868,7 +2956,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2895,10 +2983,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122300995</v>
+        <v>122301060</v>
       </c>
       <c r="B21" t="n">
-        <v>57395</v>
+        <v>98224</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2907,34 +2995,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2942,10 +3035,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651899</v>
+        <v>652000</v>
       </c>
       <c r="R21" t="n">
-        <v>6673777</v>
+        <v>6673848</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -2977,7 +3070,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2987,7 +3080,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3014,10 +3107,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122301060</v>
+        <v>122300997</v>
       </c>
       <c r="B22" t="n">
-        <v>98211</v>
+        <v>57399</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3026,45 +3119,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652000</v>
+        <v>651883</v>
       </c>
       <c r="R22" t="n">
-        <v>6673848</v>
+        <v>6673732</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3096,7 +3194,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3106,7 +3204,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3133,10 +3231,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122301062</v>
+        <v>122301004</v>
       </c>
       <c r="B23" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3145,34 +3243,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3180,10 +3283,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651973</v>
+        <v>651888</v>
       </c>
       <c r="R23" t="n">
-        <v>6673897</v>
+        <v>6673877</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3215,7 +3318,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3225,7 +3328,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3252,10 +3355,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122300994</v>
+        <v>122301036</v>
       </c>
       <c r="B24" t="n">
-        <v>57395</v>
+        <v>90826</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,30 +3371,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3299,10 +3398,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651915</v>
+        <v>652047</v>
       </c>
       <c r="R24" t="n">
-        <v>6673888</v>
+        <v>6673893</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3334,7 +3433,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3344,7 +3443,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3371,10 +3470,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301071</v>
+        <v>122301001</v>
       </c>
       <c r="B25" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3383,26 +3482,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3410,10 +3522,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651840</v>
+        <v>651873</v>
       </c>
       <c r="R25" t="n">
-        <v>6673881</v>
+        <v>6673779</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3445,7 +3557,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3455,7 +3567,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3482,10 +3594,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301078</v>
+        <v>122301021</v>
       </c>
       <c r="B26" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3494,37 +3606,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>652006</v>
+        <v>652056</v>
       </c>
       <c r="R26" t="n">
-        <v>6673876</v>
+        <v>6673872</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3556,7 +3681,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3566,7 +3691,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3593,10 +3718,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301068</v>
+        <v>122301020</v>
       </c>
       <c r="B27" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3605,37 +3730,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>651906</v>
+        <v>652017</v>
       </c>
       <c r="R27" t="n">
-        <v>6673752</v>
+        <v>6673872</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3667,7 +3805,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3677,7 +3815,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3704,10 +3842,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122301053</v>
+        <v>122301078</v>
       </c>
       <c r="B28" t="n">
-        <v>98211</v>
+        <v>100490</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3716,32 +3854,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3751,10 +3886,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651986</v>
+        <v>652006</v>
       </c>
       <c r="R28" t="n">
-        <v>6673841</v>
+        <v>6673876</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3786,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3796,12 +3931,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3828,10 +3958,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122260100</v>
+        <v>122260085</v>
       </c>
       <c r="B29" t="n">
-        <v>90813</v>
+        <v>57753</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3840,25 +3970,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>103015</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3866,13 +4010,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>652034</v>
+        <v>651895</v>
       </c>
       <c r="R29" t="n">
-        <v>6674236</v>
+        <v>6674630</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3901,7 +4045,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3911,7 +4055,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3922,16 +4066,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3948,10 +4082,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122260074</v>
+        <v>122260066</v>
       </c>
       <c r="B30" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3965,6 +4099,11 @@
       </c>
       <c r="E30" t="n">
         <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3985,7 +4124,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3995,13 +4134,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651923</v>
+        <v>651934</v>
       </c>
       <c r="R30" t="n">
-        <v>6674436</v>
+        <v>6674510</v>
       </c>
       <c r="S30" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4030,7 +4169,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4040,12 +4179,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hörd i norr.</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4072,10 +4206,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260126</v>
+        <v>122260120</v>
       </c>
       <c r="B31" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4089,6 +4223,11 @@
       </c>
       <c r="E31" t="n">
         <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4111,10 +4250,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651941</v>
+        <v>651967</v>
       </c>
       <c r="R31" t="n">
-        <v>6674469</v>
+        <v>6674316</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4146,7 +4285,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4156,7 +4295,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4183,10 +4322,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260072</v>
+        <v>122260077</v>
       </c>
       <c r="B32" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4200,6 +4339,11 @@
       </c>
       <c r="E32" t="n">
         <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4220,7 +4364,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4230,10 +4374,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651927</v>
+        <v>651964</v>
       </c>
       <c r="R32" t="n">
-        <v>6674447</v>
+        <v>6674220</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4265,7 +4409,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4275,7 +4419,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4302,10 +4446,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260119</v>
+        <v>122260115</v>
       </c>
       <c r="B33" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4319,6 +4463,11 @@
       </c>
       <c r="E33" t="n">
         <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4341,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651950</v>
+        <v>651891</v>
       </c>
       <c r="R33" t="n">
-        <v>6674465</v>
+        <v>6674645</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4376,7 +4525,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4386,7 +4535,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4413,10 +4562,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260116</v>
+        <v>122260103</v>
       </c>
       <c r="B34" t="n">
-        <v>100477</v>
+        <v>91264</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4425,26 +4574,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222498</v>
+        <v>1209</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4452,10 +4605,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651859</v>
+        <v>651855</v>
       </c>
       <c r="R34" t="n">
-        <v>6674654</v>
+        <v>6674655</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4487,7 +4640,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4497,7 +4650,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På klibbtickelåga.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4508,6 +4666,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4524,10 +4697,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122260061</v>
+        <v>122260100</v>
       </c>
       <c r="B35" t="n">
-        <v>57395</v>
+        <v>90826</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4540,30 +4713,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4571,10 +4740,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651886</v>
+        <v>652034</v>
       </c>
       <c r="R35" t="n">
-        <v>6674654</v>
+        <v>6674236</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4606,7 +4775,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4616,7 +4785,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4627,6 +4796,21 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4643,10 +4827,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122260076</v>
+        <v>122260074</v>
       </c>
       <c r="B36" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4660,6 +4844,11 @@
       </c>
       <c r="E36" t="n">
         <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4680,7 +4869,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4690,13 +4879,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651949</v>
+        <v>651923</v>
       </c>
       <c r="R36" t="n">
-        <v>6674279</v>
+        <v>6674436</v>
       </c>
       <c r="S36" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4725,7 +4914,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4735,7 +4924,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Hörd i norr.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4765,7 +4959,7 @@
         <v>122260113</v>
       </c>
       <c r="B37" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4779,6 +4973,11 @@
       </c>
       <c r="E37" t="n">
         <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -4881,10 +5080,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122260115</v>
+        <v>122260118</v>
       </c>
       <c r="B38" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4898,6 +5097,11 @@
       </c>
       <c r="E38" t="n">
         <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4920,10 +5124,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651891</v>
+        <v>651893</v>
       </c>
       <c r="R38" t="n">
-        <v>6674645</v>
+        <v>6674508</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -4955,7 +5159,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4965,7 +5169,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4992,10 +5196,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260117</v>
+        <v>122260125</v>
       </c>
       <c r="B39" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5009,6 +5213,11 @@
       </c>
       <c r="E39" t="n">
         <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -5031,10 +5240,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651906</v>
+        <v>651973</v>
       </c>
       <c r="R39" t="n">
-        <v>6674571</v>
+        <v>6674332</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5066,7 +5275,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5076,7 +5285,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5103,10 +5312,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260080</v>
+        <v>122260116</v>
       </c>
       <c r="B40" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5115,34 +5324,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5150,10 +5356,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>652019</v>
+        <v>651859</v>
       </c>
       <c r="R40" t="n">
-        <v>6674239</v>
+        <v>6674654</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5185,7 +5391,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5195,7 +5401,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5222,10 +5428,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260111</v>
+        <v>122260096</v>
       </c>
       <c r="B41" t="n">
-        <v>98211</v>
+        <v>80613</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5234,34 +5440,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1049</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5269,10 +5471,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651949</v>
+        <v>651930</v>
       </c>
       <c r="R41" t="n">
-        <v>6674415</v>
+        <v>6674592</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5304,7 +5506,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5314,7 +5516,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5341,10 +5543,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122260118</v>
+        <v>122260072</v>
       </c>
       <c r="B42" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5353,26 +5555,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5380,10 +5595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651893</v>
+        <v>651927</v>
       </c>
       <c r="R42" t="n">
-        <v>6674508</v>
+        <v>6674447</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5415,7 +5630,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5425,7 +5640,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5452,10 +5667,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260114</v>
+        <v>122260075</v>
       </c>
       <c r="B43" t="n">
-        <v>98211</v>
+        <v>57399</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5464,34 +5679,39 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5499,10 +5719,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>652010</v>
+        <v>651900</v>
       </c>
       <c r="R43" t="n">
-        <v>6674220</v>
+        <v>6674390</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5534,7 +5754,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5544,7 +5764,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5571,10 +5791,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260103</v>
+        <v>122260058</v>
       </c>
       <c r="B44" t="n">
-        <v>91251</v>
+        <v>5193</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5583,25 +5803,36 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>105930</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5609,10 +5840,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651855</v>
+        <v>652031</v>
       </c>
       <c r="R44" t="n">
-        <v>6674655</v>
+        <v>6674226</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5644,7 +5875,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5654,12 +5885,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På klibbtickelåga.</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5670,6 +5896,11 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
@@ -5696,10 +5927,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122260070</v>
+        <v>122260063</v>
       </c>
       <c r="B45" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5713,6 +5944,11 @@
       </c>
       <c r="E45" t="n">
         <v>100049</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -5733,7 +5969,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5743,10 +5979,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651967</v>
+        <v>651872</v>
       </c>
       <c r="R45" t="n">
-        <v>6674433</v>
+        <v>6674674</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5778,7 +6014,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5788,7 +6024,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5815,10 +6051,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122260071</v>
+        <v>122260070</v>
       </c>
       <c r="B46" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5832,6 +6068,11 @@
       </c>
       <c r="E46" t="n">
         <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -5852,7 +6093,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5862,10 +6103,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651930</v>
+        <v>651967</v>
       </c>
       <c r="R46" t="n">
-        <v>6674444</v>
+        <v>6674433</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -5897,7 +6138,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5907,7 +6148,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5934,10 +6175,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260077</v>
+        <v>122260126</v>
       </c>
       <c r="B47" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5946,34 +6187,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5981,10 +6219,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651964</v>
+        <v>651941</v>
       </c>
       <c r="R47" t="n">
-        <v>6674220</v>
+        <v>6674469</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6016,7 +6254,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6026,7 +6264,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6053,10 +6291,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260075</v>
+        <v>122260114</v>
       </c>
       <c r="B48" t="n">
-        <v>57395</v>
+        <v>98224</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6065,34 +6303,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6100,10 +6343,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>651900</v>
+        <v>652010</v>
       </c>
       <c r="R48" t="n">
-        <v>6674390</v>
+        <v>6674220</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6135,7 +6378,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6145,7 +6388,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6172,10 +6415,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260064</v>
+        <v>122260119</v>
       </c>
       <c r="B49" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6184,34 +6427,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6219,10 +6459,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651845</v>
+        <v>651950</v>
       </c>
       <c r="R49" t="n">
-        <v>6674626</v>
+        <v>6674465</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6254,7 +6494,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6264,7 +6504,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6291,10 +6531,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260063</v>
+        <v>122260121</v>
       </c>
       <c r="B50" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6303,34 +6543,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6338,10 +6575,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651872</v>
+        <v>651955</v>
       </c>
       <c r="R50" t="n">
-        <v>6674674</v>
+        <v>6674222</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6373,7 +6610,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6383,7 +6620,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6410,10 +6647,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122260110</v>
+        <v>122260071</v>
       </c>
       <c r="B51" t="n">
-        <v>98211</v>
+        <v>57399</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6422,34 +6659,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6457,10 +6699,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651949</v>
+        <v>651930</v>
       </c>
       <c r="R51" t="n">
-        <v>6674420</v>
+        <v>6674444</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6492,7 +6734,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6502,12 +6744,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6534,10 +6771,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260121</v>
+        <v>122260084</v>
       </c>
       <c r="B52" t="n">
-        <v>100477</v>
+        <v>57536</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6546,26 +6783,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>222498</v>
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6573,13 +6823,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651955</v>
+        <v>651900</v>
       </c>
       <c r="R52" t="n">
-        <v>6674222</v>
+        <v>6674551</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6608,7 +6858,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6618,7 +6868,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6645,10 +6895,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260125</v>
+        <v>122260064</v>
       </c>
       <c r="B53" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6657,26 +6907,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6684,10 +6947,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651973</v>
+        <v>651845</v>
       </c>
       <c r="R53" t="n">
-        <v>6674332</v>
+        <v>6674626</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6719,7 +6982,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6729,7 +6992,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6756,10 +7019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260096</v>
+        <v>122260111</v>
       </c>
       <c r="B54" t="n">
-        <v>80609</v>
+        <v>98224</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6768,25 +7031,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1049</v>
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6794,10 +7071,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651930</v>
+        <v>651949</v>
       </c>
       <c r="R54" t="n">
-        <v>6674592</v>
+        <v>6674415</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6829,7 +7106,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6839,7 +7116,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6869,7 +7146,7 @@
         <v>122260068</v>
       </c>
       <c r="B55" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6883,6 +7160,11 @@
       </c>
       <c r="E55" t="n">
         <v>100049</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -6985,10 +7267,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260066</v>
+        <v>122260076</v>
       </c>
       <c r="B56" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7002,6 +7284,11 @@
       </c>
       <c r="E56" t="n">
         <v>100049</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -7022,7 +7309,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7032,10 +7319,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>651934</v>
+        <v>651949</v>
       </c>
       <c r="R56" t="n">
-        <v>6674510</v>
+        <v>6674279</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7067,7 +7354,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7077,7 +7364,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7104,10 +7391,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260085</v>
+        <v>122260061</v>
       </c>
       <c r="B57" t="n">
-        <v>57749</v>
+        <v>57399</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7116,15 +7403,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103015</v>
+        <v>100049</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7141,7 +7433,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7151,13 +7443,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651895</v>
+        <v>651886</v>
       </c>
       <c r="R57" t="n">
-        <v>6674630</v>
+        <v>6674654</v>
       </c>
       <c r="S57" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7186,7 +7478,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7196,7 +7488,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7223,10 +7515,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260058</v>
+        <v>122260110</v>
       </c>
       <c r="B58" t="n">
-        <v>5193</v>
+        <v>98224</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7235,31 +7527,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7267,10 +7567,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>652031</v>
+        <v>651949</v>
       </c>
       <c r="R58" t="n">
-        <v>6674226</v>
+        <v>6674420</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7302,7 +7602,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7312,7 +7612,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7323,16 +7628,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7349,10 +7644,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260120</v>
+        <v>122260080</v>
       </c>
       <c r="B59" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7361,26 +7656,39 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7388,10 +7696,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651967</v>
+        <v>652019</v>
       </c>
       <c r="R59" t="n">
-        <v>6674316</v>
+        <v>6674239</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7423,7 +7731,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7433,7 +7741,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7460,10 +7768,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260084</v>
+        <v>122260117</v>
       </c>
       <c r="B60" t="n">
-        <v>57532</v>
+        <v>100490</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7472,34 +7780,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>103021</v>
+        <v>222498</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7507,13 +7812,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651900</v>
+        <v>651906</v>
       </c>
       <c r="R60" t="n">
-        <v>6674551</v>
+        <v>6674571</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7542,7 +7847,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7552,7 +7857,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7579,10 +7884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301026</v>
+        <v>122301080</v>
       </c>
       <c r="B61" t="n">
-        <v>57532</v>
+        <v>100490</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7591,34 +7896,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>222498</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7626,13 +7928,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651977</v>
+        <v>652011</v>
       </c>
       <c r="R61" t="n">
-        <v>6673906</v>
+        <v>6673969</v>
       </c>
       <c r="S61" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7661,7 +7963,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7671,7 +7973,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7698,10 +8000,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301050</v>
+        <v>122301081</v>
       </c>
       <c r="B62" t="n">
-        <v>98211</v>
+        <v>100490</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7710,32 +8012,29 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>222498</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
@@ -7745,10 +8044,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651948</v>
+        <v>652036</v>
       </c>
       <c r="R62" t="n">
-        <v>6673906</v>
+        <v>6673988</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -7780,7 +8079,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7790,7 +8089,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7817,10 +8116,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301013</v>
+        <v>122301079</v>
       </c>
       <c r="B63" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7829,34 +8128,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7864,10 +8160,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>651745</v>
+        <v>652014</v>
       </c>
       <c r="R63" t="n">
-        <v>6673922</v>
+        <v>6673954</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -7899,7 +8195,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7909,7 +8205,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7936,10 +8232,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301066</v>
+        <v>122301013</v>
       </c>
       <c r="B64" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7948,26 +8244,39 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7975,10 +8284,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>652079</v>
+        <v>651745</v>
       </c>
       <c r="R64" t="n">
-        <v>6673929</v>
+        <v>6673922</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8010,7 +8319,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8020,7 +8329,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8047,10 +8356,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301025</v>
+        <v>122301050</v>
       </c>
       <c r="B65" t="n">
-        <v>57532</v>
+        <v>98224</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8059,48 +8368,53 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651941</v>
+        <v>651948</v>
       </c>
       <c r="R65" t="n">
-        <v>6674093</v>
+        <v>6673906</v>
       </c>
       <c r="S65" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8129,7 +8443,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8139,7 +8453,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8166,10 +8480,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301067</v>
+        <v>122301017</v>
       </c>
       <c r="B66" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8178,26 +8492,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8205,10 +8532,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>652040</v>
+        <v>651776</v>
       </c>
       <c r="R66" t="n">
-        <v>6673920</v>
+        <v>6673944</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8240,7 +8567,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8250,7 +8577,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8277,10 +8604,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301075</v>
+        <v>122301027</v>
       </c>
       <c r="B67" t="n">
-        <v>100477</v>
+        <v>57753</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8293,22 +8620,31 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>103015</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8316,13 +8652,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>651975</v>
+        <v>651983</v>
       </c>
       <c r="R67" t="n">
-        <v>6673928</v>
+        <v>6673930</v>
       </c>
       <c r="S67" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8351,7 +8687,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8361,7 +8697,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8388,10 +8724,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301079</v>
+        <v>122301025</v>
       </c>
       <c r="B68" t="n">
-        <v>100477</v>
+        <v>57536</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8400,40 +8736,53 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>103021</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>652014</v>
+        <v>651941</v>
       </c>
       <c r="R68" t="n">
-        <v>6673954</v>
+        <v>6674093</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8462,7 +8811,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8472,7 +8821,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8499,10 +8848,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301074</v>
+        <v>122301026</v>
       </c>
       <c r="B69" t="n">
-        <v>100477</v>
+        <v>57536</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8511,26 +8860,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>103021</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8538,13 +8900,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651855</v>
+        <v>651977</v>
       </c>
       <c r="R69" t="n">
-        <v>6673907</v>
+        <v>6673906</v>
       </c>
       <c r="S69" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8573,7 +8935,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8583,7 +8945,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8610,10 +8972,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301015</v>
+        <v>122301073</v>
       </c>
       <c r="B70" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8622,34 +8984,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8657,10 +9016,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651777</v>
+        <v>651817</v>
       </c>
       <c r="R70" t="n">
-        <v>6673975</v>
+        <v>6673939</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -8692,7 +9051,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8702,7 +9061,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8729,10 +9088,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301027</v>
+        <v>122301066</v>
       </c>
       <c r="B71" t="n">
-        <v>57749</v>
+        <v>100490</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8745,26 +9104,27 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103015</v>
+        <v>222498</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8772,13 +9132,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651983</v>
+        <v>652079</v>
       </c>
       <c r="R71" t="n">
-        <v>6673930</v>
+        <v>6673929</v>
       </c>
       <c r="S71" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8807,7 +9167,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8817,7 +9177,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8844,10 +9204,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301080</v>
+        <v>122301065</v>
       </c>
       <c r="B72" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8861,6 +9221,11 @@
       </c>
       <c r="E72" t="n">
         <v>222498</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -8883,10 +9248,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>652011</v>
+        <v>652034</v>
       </c>
       <c r="R72" t="n">
-        <v>6673969</v>
+        <v>6673906</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -8918,7 +9283,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8928,7 +9293,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8955,10 +9320,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301017</v>
+        <v>122301074</v>
       </c>
       <c r="B73" t="n">
-        <v>57395</v>
+        <v>100490</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8967,34 +9332,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>222498</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9002,10 +9364,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651776</v>
+        <v>651855</v>
       </c>
       <c r="R73" t="n">
-        <v>6673944</v>
+        <v>6673907</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9037,7 +9399,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9047,7 +9409,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9074,10 +9436,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301081</v>
+        <v>122301063</v>
       </c>
       <c r="B74" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9091,6 +9453,11 @@
       </c>
       <c r="E74" t="n">
         <v>222498</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9113,10 +9480,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>652036</v>
+        <v>651949</v>
       </c>
       <c r="R74" t="n">
-        <v>6673988</v>
+        <v>6673910</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9148,7 +9515,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9158,7 +9525,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9185,10 +9552,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301065</v>
+        <v>122301075</v>
       </c>
       <c r="B75" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9202,6 +9569,11 @@
       </c>
       <c r="E75" t="n">
         <v>222498</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9224,10 +9596,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>652034</v>
+        <v>651975</v>
       </c>
       <c r="R75" t="n">
-        <v>6673906</v>
+        <v>6673928</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9259,7 +9631,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9269,7 +9641,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9296,10 +9668,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301073</v>
+        <v>122301067</v>
       </c>
       <c r="B76" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9313,6 +9685,11 @@
       </c>
       <c r="E76" t="n">
         <v>222498</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9335,10 +9712,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651817</v>
+        <v>652040</v>
       </c>
       <c r="R76" t="n">
-        <v>6673939</v>
+        <v>6673920</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9370,7 +9747,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9380,7 +9757,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9407,10 +9784,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301063</v>
+        <v>122301015</v>
       </c>
       <c r="B77" t="n">
-        <v>100477</v>
+        <v>57399</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9419,26 +9796,39 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>100049</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9446,10 +9836,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651949</v>
+        <v>651777</v>
       </c>
       <c r="R77" t="n">
-        <v>6673910</v>
+        <v>6673975</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9481,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9491,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9521,7 +9911,7 @@
         <v>122260107</v>
       </c>
       <c r="B78" t="n">
-        <v>95758</v>
+        <v>95771</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9535,6 +9925,11 @@
       </c>
       <c r="E78" t="n">
         <v>53</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122301037</v>
+        <v>122301036</v>
       </c>
       <c r="B2" t="n">
-        <v>91216</v>
+        <v>90839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6040162</v>
+        <v>1202</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651917</v>
+        <v>652047</v>
       </c>
       <c r="R2" t="n">
-        <v>6673853</v>
+        <v>6673893</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -748,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +790,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122300993</v>
+        <v>122300994</v>
       </c>
       <c r="B3" t="n">
         <v>57399</v>
@@ -827,7 +832,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651962</v>
+        <v>651915</v>
       </c>
       <c r="R3" t="n">
-        <v>6673882</v>
+        <v>6673888</v>
       </c>
       <c r="S3" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122300999</v>
+        <v>122301031</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>74696</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,39 +926,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -966,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651879</v>
+        <v>651805</v>
       </c>
       <c r="R4" t="n">
-        <v>6673776</v>
+        <v>6673899</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1001,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122301006</v>
+        <v>122301020</v>
       </c>
       <c r="B5" t="n">
         <v>57399</v>
@@ -1080,7 +1071,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1090,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651860</v>
+        <v>652017</v>
       </c>
       <c r="R5" t="n">
-        <v>6673862</v>
+        <v>6673872</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1125,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122301058</v>
+        <v>122300988</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>5193</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,39 +1165,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1214,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651981</v>
+        <v>651926</v>
       </c>
       <c r="R6" t="n">
-        <v>6673859</v>
+        <v>6673844</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1249,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1259,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1286,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122301071</v>
+        <v>122301006</v>
       </c>
       <c r="B7" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1298,31 +1286,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1330,10 +1326,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651840</v>
+        <v>651860</v>
       </c>
       <c r="R7" t="n">
-        <v>6673881</v>
+        <v>6673862</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1365,7 +1361,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1371,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122301053</v>
+        <v>122301056</v>
       </c>
       <c r="B8" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1437,7 +1433,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1454,10 +1450,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651986</v>
+        <v>651930</v>
       </c>
       <c r="R8" t="n">
-        <v>6673841</v>
+        <v>6673898</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1489,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1499,12 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1522,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122300988</v>
+        <v>122301077</v>
       </c>
       <c r="B9" t="n">
-        <v>5193</v>
+        <v>100503</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1547,32 +1538,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1580,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651926</v>
+        <v>651993</v>
       </c>
       <c r="R9" t="n">
-        <v>6673844</v>
+        <v>6673867</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1615,7 +1601,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1625,7 +1611,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,10 +1638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122301064</v>
+        <v>122301068</v>
       </c>
       <c r="B10" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1692,14 +1678,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651993</v>
+        <v>651906</v>
       </c>
       <c r="R10" t="n">
-        <v>6673896</v>
+        <v>6673752</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1731,7 +1717,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1741,7 +1727,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1768,10 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301062</v>
+        <v>122301021</v>
       </c>
       <c r="B11" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,50 +1766,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651973</v>
+        <v>652056</v>
       </c>
       <c r="R11" t="n">
-        <v>6673897</v>
+        <v>6673872</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1855,7 +1841,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1865,7 +1851,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1892,7 +1878,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301019</v>
+        <v>122300991</v>
       </c>
       <c r="B12" t="n">
         <v>57399</v>
@@ -1934,7 +1920,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1944,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>652004</v>
+        <v>651958</v>
       </c>
       <c r="R12" t="n">
-        <v>6673869</v>
+        <v>6673868</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1979,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1989,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,10 +2002,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122301077</v>
+        <v>122301019</v>
       </c>
       <c r="B13" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2028,31 +2014,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2060,10 +2054,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651993</v>
+        <v>652004</v>
       </c>
       <c r="R13" t="n">
-        <v>6673867</v>
+        <v>6673869</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2095,7 +2089,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2105,7 +2099,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2132,10 +2126,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301007</v>
+        <v>122301071</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2144,39 +2138,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2184,10 +2170,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651778</v>
+        <v>651840</v>
       </c>
       <c r="R14" t="n">
-        <v>6673895</v>
+        <v>6673881</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2219,7 +2205,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,7 +2215,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2256,10 +2242,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122301031</v>
+        <v>122301058</v>
       </c>
       <c r="B15" t="n">
-        <v>74696</v>
+        <v>98237</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2268,30 +2254,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2299,10 +2294,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651805</v>
+        <v>651981</v>
       </c>
       <c r="R15" t="n">
-        <v>6673899</v>
+        <v>6673859</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2334,7 +2329,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2344,7 +2339,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2371,10 +2366,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301068</v>
+        <v>122301053</v>
       </c>
       <c r="B16" t="n">
-        <v>100490</v>
+        <v>98237</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2383,42 +2378,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651906</v>
+        <v>651986</v>
       </c>
       <c r="R16" t="n">
-        <v>6673752</v>
+        <v>6673841</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2450,7 +2453,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2460,7 +2463,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2487,10 +2495,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301056</v>
+        <v>122301004</v>
       </c>
       <c r="B17" t="n">
-        <v>98224</v>
+        <v>57399</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2499,39 +2507,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2539,10 +2547,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651930</v>
+        <v>651888</v>
       </c>
       <c r="R17" t="n">
-        <v>6673898</v>
+        <v>6673877</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2574,7 +2582,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2584,7 +2592,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2611,10 +2619,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122300991</v>
+        <v>122301062</v>
       </c>
       <c r="B18" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2623,39 +2631,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2663,10 +2671,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651958</v>
+        <v>651973</v>
       </c>
       <c r="R18" t="n">
-        <v>6673868</v>
+        <v>6673897</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2698,7 +2706,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2708,7 +2716,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2735,7 +2743,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122300995</v>
+        <v>122300999</v>
       </c>
       <c r="B19" t="n">
         <v>57399</v>
@@ -2787,10 +2795,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651899</v>
+        <v>651879</v>
       </c>
       <c r="R19" t="n">
-        <v>6673777</v>
+        <v>6673776</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2822,7 +2830,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2832,7 +2840,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2859,7 +2867,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122300994</v>
+        <v>122301001</v>
       </c>
       <c r="B20" t="n">
         <v>57399</v>
@@ -2911,10 +2919,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651915</v>
+        <v>651873</v>
       </c>
       <c r="R20" t="n">
-        <v>6673888</v>
+        <v>6673779</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2946,7 +2954,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2956,7 +2964,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2983,10 +2991,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122301060</v>
+        <v>122301078</v>
       </c>
       <c r="B21" t="n">
-        <v>98224</v>
+        <v>100503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2995,37 +3003,29 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3035,10 +3035,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652000</v>
+        <v>652006</v>
       </c>
       <c r="R21" t="n">
-        <v>6673848</v>
+        <v>6673876</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3231,10 +3231,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122301004</v>
+        <v>122301037</v>
       </c>
       <c r="B23" t="n">
-        <v>57399</v>
+        <v>91229</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3247,35 +3247,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3283,10 +3269,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651888</v>
+        <v>651917</v>
       </c>
       <c r="R23" t="n">
-        <v>6673877</v>
+        <v>6673853</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3318,7 +3304,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3328,7 +3314,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3355,10 +3341,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122301036</v>
+        <v>122300995</v>
       </c>
       <c r="B24" t="n">
-        <v>90826</v>
+        <v>57399</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3371,26 +3357,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3398,10 +3393,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>652047</v>
+        <v>651899</v>
       </c>
       <c r="R24" t="n">
-        <v>6673893</v>
+        <v>6673777</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3433,7 +3428,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3443,7 +3438,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3470,7 +3465,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301001</v>
+        <v>122300993</v>
       </c>
       <c r="B25" t="n">
         <v>57399</v>
@@ -3512,7 +3507,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3522,13 +3517,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651873</v>
+        <v>651962</v>
       </c>
       <c r="R25" t="n">
-        <v>6673779</v>
+        <v>6673882</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3557,7 +3552,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3567,7 +3562,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3594,7 +3594,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301021</v>
+        <v>122301007</v>
       </c>
       <c r="B26" t="n">
         <v>57399</v>
@@ -3636,20 +3636,20 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>652056</v>
+        <v>651778</v>
       </c>
       <c r="R26" t="n">
-        <v>6673872</v>
+        <v>6673895</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3718,10 +3718,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301020</v>
+        <v>122301060</v>
       </c>
       <c r="B27" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3730,39 +3730,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>652017</v>
+        <v>652000</v>
       </c>
       <c r="R27" t="n">
-        <v>6673872</v>
+        <v>6673848</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122301078</v>
+        <v>122301064</v>
       </c>
       <c r="B28" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>652006</v>
+        <v>651993</v>
       </c>
       <c r="R28" t="n">
-        <v>6673876</v>
+        <v>6673896</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122260085</v>
+        <v>122260119</v>
       </c>
       <c r="B29" t="n">
-        <v>57753</v>
+        <v>100503</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3974,35 +3974,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4010,13 +4002,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651895</v>
+        <v>651950</v>
       </c>
       <c r="R29" t="n">
-        <v>6674630</v>
+        <v>6674465</v>
       </c>
       <c r="S29" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4045,7 +4037,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4055,7 +4047,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4082,10 +4074,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122260066</v>
+        <v>122260125</v>
       </c>
       <c r="B30" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4094,39 +4086,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4134,10 +4118,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651934</v>
+        <v>651973</v>
       </c>
       <c r="R30" t="n">
-        <v>6674510</v>
+        <v>6674332</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4169,7 +4153,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4179,7 +4163,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4206,10 +4190,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260120</v>
+        <v>122260077</v>
       </c>
       <c r="B31" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4218,31 +4202,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4250,10 +4242,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651967</v>
+        <v>651964</v>
       </c>
       <c r="R31" t="n">
-        <v>6674316</v>
+        <v>6674220</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4285,7 +4277,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4295,7 +4287,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4322,10 +4314,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260077</v>
+        <v>122260118</v>
       </c>
       <c r="B32" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4334,39 +4326,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4374,10 +4358,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651964</v>
+        <v>651893</v>
       </c>
       <c r="R32" t="n">
-        <v>6674220</v>
+        <v>6674508</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4409,7 +4393,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4419,7 +4403,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,10 +4430,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260115</v>
+        <v>122260121</v>
       </c>
       <c r="B33" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4490,10 +4474,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651891</v>
+        <v>651955</v>
       </c>
       <c r="R33" t="n">
-        <v>6674645</v>
+        <v>6674222</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4525,7 +4509,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4535,7 +4519,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4562,10 +4546,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260103</v>
+        <v>122260080</v>
       </c>
       <c r="B34" t="n">
-        <v>91264</v>
+        <v>57399</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4574,30 +4558,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4605,10 +4598,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651855</v>
+        <v>652019</v>
       </c>
       <c r="R34" t="n">
-        <v>6674655</v>
+        <v>6674239</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4640,7 +4633,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4650,12 +4643,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På klibbtickelåga.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4666,21 +4654,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4697,10 +4670,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122260100</v>
+        <v>122260103</v>
       </c>
       <c r="B35" t="n">
-        <v>90826</v>
+        <v>91277</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4709,25 +4682,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4740,10 +4713,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>652034</v>
+        <v>651855</v>
       </c>
       <c r="R35" t="n">
-        <v>6674236</v>
+        <v>6674655</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4775,7 +4748,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4785,7 +4758,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På klibbtickelåga.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4956,10 +4934,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122260113</v>
+        <v>122260120</v>
       </c>
       <c r="B37" t="n">
-        <v>98224</v>
+        <v>100503</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4968,37 +4946,29 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
@@ -5008,10 +4978,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651906</v>
+        <v>651967</v>
       </c>
       <c r="R37" t="n">
-        <v>6674392</v>
+        <v>6674316</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5043,7 +5013,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5053,7 +5023,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5080,10 +5050,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122260118</v>
+        <v>122260114</v>
       </c>
       <c r="B38" t="n">
-        <v>100490</v>
+        <v>98237</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5092,29 +5062,37 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5124,10 +5102,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651893</v>
+        <v>652010</v>
       </c>
       <c r="R38" t="n">
-        <v>6674508</v>
+        <v>6674220</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5159,7 +5137,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5169,7 +5147,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5196,10 +5174,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260125</v>
+        <v>122260071</v>
       </c>
       <c r="B39" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5208,31 +5186,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5240,10 +5226,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651973</v>
+        <v>651930</v>
       </c>
       <c r="R39" t="n">
-        <v>6674332</v>
+        <v>6674444</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5275,7 +5261,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5285,7 +5271,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5312,10 +5298,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260116</v>
+        <v>122260115</v>
       </c>
       <c r="B40" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5356,10 +5342,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651859</v>
+        <v>651891</v>
       </c>
       <c r="R40" t="n">
-        <v>6674654</v>
+        <v>6674645</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5391,7 +5377,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5401,7 +5387,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5428,10 +5414,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260096</v>
+        <v>122260126</v>
       </c>
       <c r="B41" t="n">
-        <v>80613</v>
+        <v>100503</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5440,30 +5426,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5471,10 +5458,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651930</v>
+        <v>651941</v>
       </c>
       <c r="R41" t="n">
-        <v>6674592</v>
+        <v>6674469</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5506,7 +5493,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5516,7 +5503,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5543,10 +5530,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122260072</v>
+        <v>122260111</v>
       </c>
       <c r="B42" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5555,39 +5542,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5595,10 +5582,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651927</v>
+        <v>651949</v>
       </c>
       <c r="R42" t="n">
-        <v>6674447</v>
+        <v>6674415</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5630,7 +5617,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5640,7 +5627,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5667,10 +5654,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260075</v>
+        <v>122260100</v>
       </c>
       <c r="B43" t="n">
-        <v>57399</v>
+        <v>90839</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5683,35 +5670,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5719,10 +5697,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651900</v>
+        <v>652034</v>
       </c>
       <c r="R43" t="n">
-        <v>6674390</v>
+        <v>6674236</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5754,7 +5732,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5764,7 +5742,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5775,6 +5753,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5791,10 +5784,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260058</v>
+        <v>122260116</v>
       </c>
       <c r="B44" t="n">
-        <v>5193</v>
+        <v>100503</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5807,32 +5800,27 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5840,10 +5828,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>652031</v>
+        <v>651859</v>
       </c>
       <c r="R44" t="n">
-        <v>6674226</v>
+        <v>6674654</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5875,7 +5863,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5885,7 +5873,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5896,21 +5884,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5927,7 +5900,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122260063</v>
+        <v>122260064</v>
       </c>
       <c r="B45" t="n">
         <v>57399</v>
@@ -5969,7 +5942,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5979,10 +5952,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651872</v>
+        <v>651845</v>
       </c>
       <c r="R45" t="n">
-        <v>6674674</v>
+        <v>6674626</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -6014,7 +5987,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6024,7 +5997,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6051,7 +6024,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122260070</v>
+        <v>122260068</v>
       </c>
       <c r="B46" t="n">
         <v>57399</v>
@@ -6093,7 +6066,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6103,10 +6076,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651967</v>
+        <v>651928</v>
       </c>
       <c r="R46" t="n">
-        <v>6674433</v>
+        <v>6674457</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6138,7 +6111,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6148,7 +6121,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6175,10 +6148,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260126</v>
+        <v>122260072</v>
       </c>
       <c r="B47" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6187,31 +6160,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6219,10 +6200,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651941</v>
+        <v>651927</v>
       </c>
       <c r="R47" t="n">
-        <v>6674469</v>
+        <v>6674447</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6254,7 +6235,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6264,7 +6245,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6291,10 +6272,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260114</v>
+        <v>122260075</v>
       </c>
       <c r="B48" t="n">
-        <v>98224</v>
+        <v>57399</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6303,39 +6284,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6343,10 +6324,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>652010</v>
+        <v>651900</v>
       </c>
       <c r="R48" t="n">
-        <v>6674220</v>
+        <v>6674390</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6378,7 +6359,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6388,7 +6369,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6415,10 +6396,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260119</v>
+        <v>122260058</v>
       </c>
       <c r="B49" t="n">
-        <v>100490</v>
+        <v>5193</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6431,27 +6412,32 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6459,10 +6445,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651950</v>
+        <v>652031</v>
       </c>
       <c r="R49" t="n">
-        <v>6674465</v>
+        <v>6674226</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6494,7 +6480,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6504,7 +6490,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6515,6 +6501,21 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6531,10 +6532,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260121</v>
+        <v>122260076</v>
       </c>
       <c r="B50" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6543,31 +6544,39 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6575,10 +6584,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651955</v>
+        <v>651949</v>
       </c>
       <c r="R50" t="n">
-        <v>6674222</v>
+        <v>6674279</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6610,7 +6619,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6620,7 +6629,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6647,10 +6656,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122260071</v>
+        <v>122260113</v>
       </c>
       <c r="B51" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6659,39 +6668,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6699,10 +6708,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651930</v>
+        <v>651906</v>
       </c>
       <c r="R51" t="n">
-        <v>6674444</v>
+        <v>6674392</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6734,7 +6743,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6744,7 +6753,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6771,10 +6780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260084</v>
+        <v>122260096</v>
       </c>
       <c r="B52" t="n">
-        <v>57536</v>
+        <v>80613</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6787,35 +6796,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6823,13 +6823,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651900</v>
+        <v>651930</v>
       </c>
       <c r="R52" t="n">
-        <v>6674551</v>
+        <v>6674592</v>
       </c>
       <c r="S52" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6895,7 +6895,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260064</v>
+        <v>122260061</v>
       </c>
       <c r="B53" t="n">
         <v>57399</v>
@@ -6937,7 +6937,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6947,10 +6947,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651845</v>
+        <v>651886</v>
       </c>
       <c r="R53" t="n">
-        <v>6674626</v>
+        <v>6674654</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7019,10 +7019,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260111</v>
+        <v>122260084</v>
       </c>
       <c r="B54" t="n">
-        <v>98224</v>
+        <v>57536</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7031,39 +7031,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651949</v>
+        <v>651900</v>
       </c>
       <c r="R54" t="n">
-        <v>6674415</v>
+        <v>6674551</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7143,10 +7143,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122260068</v>
+        <v>122260117</v>
       </c>
       <c r="B55" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7155,39 +7155,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7195,10 +7187,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651928</v>
+        <v>651906</v>
       </c>
       <c r="R55" t="n">
-        <v>6674457</v>
+        <v>6674571</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7230,7 +7222,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7240,7 +7232,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7267,10 +7259,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260076</v>
+        <v>122260085</v>
       </c>
       <c r="B56" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7279,20 +7271,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7309,7 +7301,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7319,13 +7311,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>651949</v>
+        <v>651895</v>
       </c>
       <c r="R56" t="n">
-        <v>6674279</v>
+        <v>6674630</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7354,7 +7346,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7364,7 +7356,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7391,7 +7383,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260061</v>
+        <v>122260063</v>
       </c>
       <c r="B57" t="n">
         <v>57399</v>
@@ -7443,10 +7435,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651886</v>
+        <v>651872</v>
       </c>
       <c r="R57" t="n">
-        <v>6674654</v>
+        <v>6674674</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7478,7 +7470,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7488,7 +7480,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7515,10 +7507,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260110</v>
+        <v>122260066</v>
       </c>
       <c r="B58" t="n">
-        <v>98224</v>
+        <v>57399</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7527,39 +7519,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7567,10 +7559,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>651949</v>
+        <v>651934</v>
       </c>
       <c r="R58" t="n">
-        <v>6674420</v>
+        <v>6674510</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7602,7 +7594,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7612,12 +7604,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7644,7 +7631,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260080</v>
+        <v>122260070</v>
       </c>
       <c r="B59" t="n">
         <v>57399</v>
@@ -7686,7 +7673,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7696,10 +7683,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>652019</v>
+        <v>651967</v>
       </c>
       <c r="R59" t="n">
-        <v>6674239</v>
+        <v>6674433</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7731,7 +7718,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7741,7 +7728,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7768,10 +7755,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260117</v>
+        <v>122260110</v>
       </c>
       <c r="B60" t="n">
-        <v>100490</v>
+        <v>98237</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7780,29 +7767,37 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -7812,10 +7807,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651906</v>
+        <v>651949</v>
       </c>
       <c r="R60" t="n">
-        <v>6674571</v>
+        <v>6674420</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7847,7 +7842,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7857,7 +7852,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7884,10 +7884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301080</v>
+        <v>122301025</v>
       </c>
       <c r="B61" t="n">
-        <v>100490</v>
+        <v>57536</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7896,45 +7896,53 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>652011</v>
+        <v>651941</v>
       </c>
       <c r="R61" t="n">
-        <v>6673969</v>
+        <v>6674093</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7963,7 +7971,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7973,7 +7981,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8000,10 +8008,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301081</v>
+        <v>122301073</v>
       </c>
       <c r="B62" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8044,10 +8052,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>652036</v>
+        <v>651817</v>
       </c>
       <c r="R62" t="n">
-        <v>6673988</v>
+        <v>6673939</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8079,7 +8087,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8089,7 +8097,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8116,10 +8124,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301079</v>
+        <v>122301017</v>
       </c>
       <c r="B63" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8128,31 +8136,39 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8160,10 +8176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>652014</v>
+        <v>651776</v>
       </c>
       <c r="R63" t="n">
-        <v>6673954</v>
+        <v>6673944</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8195,7 +8211,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8205,7 +8221,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8232,10 +8248,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301013</v>
+        <v>122301081</v>
       </c>
       <c r="B64" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8244,39 +8260,31 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8284,10 +8292,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651745</v>
+        <v>652036</v>
       </c>
       <c r="R64" t="n">
-        <v>6673922</v>
+        <v>6673988</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8319,7 +8327,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8329,7 +8337,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8356,10 +8364,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301050</v>
+        <v>122301075</v>
       </c>
       <c r="B65" t="n">
-        <v>98224</v>
+        <v>100503</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8368,37 +8376,29 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
@@ -8408,10 +8408,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651948</v>
+        <v>651975</v>
       </c>
       <c r="R65" t="n">
-        <v>6673906</v>
+        <v>6673928</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8480,10 +8480,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301017</v>
+        <v>122301066</v>
       </c>
       <c r="B66" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8492,39 +8492,31 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8532,10 +8524,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651776</v>
+        <v>652079</v>
       </c>
       <c r="R66" t="n">
-        <v>6673944</v>
+        <v>6673929</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8567,7 +8559,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8577,7 +8569,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8604,10 +8596,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301027</v>
+        <v>122301026</v>
       </c>
       <c r="B67" t="n">
-        <v>57753</v>
+        <v>57536</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8616,35 +8608,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8652,13 +8648,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>651983</v>
+        <v>651977</v>
       </c>
       <c r="R67" t="n">
-        <v>6673930</v>
+        <v>6673906</v>
       </c>
       <c r="S67" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8687,7 +8683,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8697,7 +8693,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8724,10 +8720,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301025</v>
+        <v>122301027</v>
       </c>
       <c r="B68" t="n">
-        <v>57536</v>
+        <v>57753</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8736,25 +8732,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8764,25 +8760,21 @@
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651941</v>
+        <v>651983</v>
       </c>
       <c r="R68" t="n">
-        <v>6674093</v>
+        <v>6673930</v>
       </c>
       <c r="S68" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8811,7 +8803,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8821,7 +8813,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8848,10 +8840,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301026</v>
+        <v>122301080</v>
       </c>
       <c r="B69" t="n">
-        <v>57536</v>
+        <v>100503</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8860,39 +8852,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8900,13 +8884,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651977</v>
+        <v>652011</v>
       </c>
       <c r="R69" t="n">
-        <v>6673906</v>
+        <v>6673969</v>
       </c>
       <c r="S69" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8935,7 +8919,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8945,7 +8929,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8972,10 +8956,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301073</v>
+        <v>122301015</v>
       </c>
       <c r="B70" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8984,31 +8968,39 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9016,10 +9008,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651817</v>
+        <v>651777</v>
       </c>
       <c r="R70" t="n">
-        <v>6673939</v>
+        <v>6673975</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -9051,7 +9043,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9061,7 +9053,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9088,10 +9080,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301066</v>
+        <v>122301074</v>
       </c>
       <c r="B71" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9132,10 +9124,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>652079</v>
+        <v>651855</v>
       </c>
       <c r="R71" t="n">
-        <v>6673929</v>
+        <v>6673907</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9167,7 +9159,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9177,7 +9169,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9204,10 +9196,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301065</v>
+        <v>122301050</v>
       </c>
       <c r="B72" t="n">
-        <v>100490</v>
+        <v>98237</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9216,29 +9208,37 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>652034</v>
+        <v>651948</v>
       </c>
       <c r="R72" t="n">
         <v>6673906</v>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9320,10 +9320,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301074</v>
+        <v>122301079</v>
       </c>
       <c r="B73" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651855</v>
+        <v>652014</v>
       </c>
       <c r="R73" t="n">
-        <v>6673907</v>
+        <v>6673954</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9439,7 +9439,7 @@
         <v>122301063</v>
       </c>
       <c r="B74" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9552,10 +9552,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301075</v>
+        <v>122301013</v>
       </c>
       <c r="B75" t="n">
-        <v>100490</v>
+        <v>57399</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9564,31 +9564,39 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9596,10 +9604,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651975</v>
+        <v>651745</v>
       </c>
       <c r="R75" t="n">
-        <v>6673928</v>
+        <v>6673922</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9631,7 +9639,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9641,7 +9649,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9671,7 +9679,7 @@
         <v>122301067</v>
       </c>
       <c r="B76" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9784,10 +9792,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301015</v>
+        <v>122301065</v>
       </c>
       <c r="B77" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9796,39 +9804,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651777</v>
+        <v>652034</v>
       </c>
       <c r="R77" t="n">
-        <v>6673975</v>
+        <v>6673906</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9911,7 +9911,7 @@
         <v>122260107</v>
       </c>
       <c r="B78" t="n">
-        <v>95771</v>
+        <v>95784</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -4074,10 +4074,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122260125</v>
+        <v>122260077</v>
       </c>
       <c r="B30" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4086,31 +4086,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4118,10 +4126,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651973</v>
+        <v>651964</v>
       </c>
       <c r="R30" t="n">
-        <v>6674332</v>
+        <v>6674220</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4153,7 +4161,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4163,7 +4171,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4190,10 +4198,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260077</v>
+        <v>122260125</v>
       </c>
       <c r="B31" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4202,39 +4210,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651964</v>
+        <v>651973</v>
       </c>
       <c r="R31" t="n">
-        <v>6674220</v>
+        <v>6674332</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -6532,10 +6532,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260076</v>
+        <v>122260113</v>
       </c>
       <c r="B50" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6544,39 +6544,39 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6584,10 +6584,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651949</v>
+        <v>651906</v>
       </c>
       <c r="R50" t="n">
-        <v>6674279</v>
+        <v>6674392</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6656,10 +6656,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122260113</v>
+        <v>122260076</v>
       </c>
       <c r="B51" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6668,39 +6668,39 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6708,10 +6708,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651906</v>
+        <v>651949</v>
       </c>
       <c r="R51" t="n">
-        <v>6674392</v>
+        <v>6674279</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7383,7 +7383,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260063</v>
+        <v>122260066</v>
       </c>
       <c r="B57" t="n">
         <v>57399</v>
@@ -7435,10 +7435,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651872</v>
+        <v>651934</v>
       </c>
       <c r="R57" t="n">
-        <v>6674674</v>
+        <v>6674510</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7480,7 +7480,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7507,10 +7507,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260066</v>
+        <v>122260110</v>
       </c>
       <c r="B58" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7519,39 +7519,39 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7559,10 +7559,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>651934</v>
+        <v>651949</v>
       </c>
       <c r="R58" t="n">
-        <v>6674510</v>
+        <v>6674420</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7604,7 +7604,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7631,7 +7636,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260070</v>
+        <v>122260063</v>
       </c>
       <c r="B59" t="n">
         <v>57399</v>
@@ -7673,7 +7678,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7683,10 +7688,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651967</v>
+        <v>651872</v>
       </c>
       <c r="R59" t="n">
-        <v>6674433</v>
+        <v>6674674</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7718,7 +7723,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7728,7 +7733,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7755,10 +7760,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260110</v>
+        <v>122260070</v>
       </c>
       <c r="B60" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7767,39 +7772,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7807,10 +7812,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651949</v>
+        <v>651967</v>
       </c>
       <c r="R60" t="n">
-        <v>6674420</v>
+        <v>6674433</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7842,7 +7847,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7852,12 +7857,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -9080,10 +9080,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301074</v>
+        <v>122301050</v>
       </c>
       <c r="B71" t="n">
-        <v>100503</v>
+        <v>98237</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9092,29 +9092,37 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
@@ -9124,10 +9132,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651855</v>
+        <v>651948</v>
       </c>
       <c r="R71" t="n">
-        <v>6673907</v>
+        <v>6673906</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9159,7 +9167,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9169,7 +9177,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9196,10 +9204,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301050</v>
+        <v>122301074</v>
       </c>
       <c r="B72" t="n">
-        <v>98237</v>
+        <v>100503</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9208,37 +9216,29 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
@@ -9248,10 +9248,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651948</v>
+        <v>651855</v>
       </c>
       <c r="R72" t="n">
-        <v>6673906</v>
+        <v>6673907</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9283,7 +9283,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9293,7 +9293,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122301036</v>
+        <v>122301071</v>
       </c>
       <c r="B2" t="n">
-        <v>90839</v>
+        <v>100503</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>652047</v>
+        <v>651840</v>
       </c>
       <c r="R2" t="n">
-        <v>6673893</v>
+        <v>6673881</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122300994</v>
+        <v>122301078</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +803,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651915</v>
+        <v>652006</v>
       </c>
       <c r="R3" t="n">
-        <v>6673888</v>
+        <v>6673876</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -877,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122301031</v>
+        <v>122300999</v>
       </c>
       <c r="B4" t="n">
-        <v>74696</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -926,30 +919,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -957,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651805</v>
+        <v>651879</v>
       </c>
       <c r="R4" t="n">
-        <v>6673899</v>
+        <v>6673776</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -992,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1031,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122301020</v>
+        <v>122301004</v>
       </c>
       <c r="B5" t="n">
         <v>57399</v>
@@ -1071,7 +1073,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1081,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652017</v>
+        <v>651888</v>
       </c>
       <c r="R5" t="n">
-        <v>6673872</v>
+        <v>6673877</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1116,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122300988</v>
+        <v>122301020</v>
       </c>
       <c r="B6" t="n">
-        <v>5193</v>
+        <v>57399</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,20 +1167,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1186,13 +1188,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1202,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651926</v>
+        <v>652017</v>
       </c>
       <c r="R6" t="n">
-        <v>6673844</v>
+        <v>6673872</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1237,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,7 +1279,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122301006</v>
+        <v>122300997</v>
       </c>
       <c r="B7" t="n">
         <v>57399</v>
@@ -1316,20 +1321,20 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651860</v>
+        <v>651883</v>
       </c>
       <c r="R7" t="n">
-        <v>6673862</v>
+        <v>6673732</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1361,7 +1366,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1371,7 +1376,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1522,10 +1527,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122301077</v>
+        <v>122301021</v>
       </c>
       <c r="B9" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,42 +1539,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651993</v>
+        <v>652056</v>
       </c>
       <c r="R9" t="n">
-        <v>6673867</v>
+        <v>6673872</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1601,7 +1614,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1624,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,10 +1651,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122301068</v>
+        <v>122301060</v>
       </c>
       <c r="B10" t="n">
-        <v>100503</v>
+        <v>98237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1650,42 +1663,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651906</v>
+        <v>652000</v>
       </c>
       <c r="R10" t="n">
-        <v>6673752</v>
+        <v>6673848</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1717,7 +1738,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1727,7 +1748,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1754,10 +1775,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301021</v>
+        <v>122301036</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>90839</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1770,46 +1791,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>652056</v>
+        <v>652047</v>
       </c>
       <c r="R11" t="n">
-        <v>6673872</v>
+        <v>6673893</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1841,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1851,7 +1863,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1878,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122300991</v>
+        <v>122301031</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>74696</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1890,39 +1902,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1930,10 +1933,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651958</v>
+        <v>651805</v>
       </c>
       <c r="R12" t="n">
-        <v>6673868</v>
+        <v>6673899</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1965,7 +1968,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1978,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,7 +2005,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122301019</v>
+        <v>122300993</v>
       </c>
       <c r="B13" t="n">
         <v>57399</v>
@@ -2044,7 +2047,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2054,13 +2057,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>652004</v>
+        <v>651962</v>
       </c>
       <c r="R13" t="n">
-        <v>6673869</v>
+        <v>6673882</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2089,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2099,7 +2102,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2126,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301071</v>
+        <v>122301019</v>
       </c>
       <c r="B14" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2138,31 +2146,39 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2170,10 +2186,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651840</v>
+        <v>652004</v>
       </c>
       <c r="R14" t="n">
-        <v>6673881</v>
+        <v>6673869</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2205,7 +2221,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2215,7 +2231,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2242,7 +2258,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122301058</v>
+        <v>122301053</v>
       </c>
       <c r="B15" t="n">
         <v>98237</v>
@@ -2277,12 +2293,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2294,10 +2310,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651981</v>
+        <v>651986</v>
       </c>
       <c r="R15" t="n">
-        <v>6673859</v>
+        <v>6673841</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2329,7 +2345,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2339,7 +2355,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2366,10 +2387,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301053</v>
+        <v>122301068</v>
       </c>
       <c r="B16" t="n">
-        <v>98237</v>
+        <v>100503</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2378,50 +2399,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651986</v>
+        <v>651906</v>
       </c>
       <c r="R16" t="n">
-        <v>6673841</v>
+        <v>6673752</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2453,7 +2466,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2463,12 +2476,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2495,10 +2503,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301004</v>
+        <v>122301037</v>
       </c>
       <c r="B17" t="n">
-        <v>57399</v>
+        <v>91229</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2511,35 +2519,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2547,10 +2541,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651888</v>
+        <v>651917</v>
       </c>
       <c r="R17" t="n">
-        <v>6673877</v>
+        <v>6673853</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2582,7 +2576,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2592,7 +2586,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2619,7 +2613,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122301062</v>
+        <v>122301077</v>
       </c>
       <c r="B18" t="n">
         <v>100503</v>
@@ -2652,16 +2646,8 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2671,10 +2657,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651973</v>
+        <v>651993</v>
       </c>
       <c r="R18" t="n">
-        <v>6673897</v>
+        <v>6673867</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2706,7 +2692,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2716,7 +2702,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2743,7 +2729,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122300999</v>
+        <v>122300995</v>
       </c>
       <c r="B19" t="n">
         <v>57399</v>
@@ -2795,10 +2781,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651879</v>
+        <v>651899</v>
       </c>
       <c r="R19" t="n">
-        <v>6673776</v>
+        <v>6673777</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2830,7 +2816,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2840,7 +2826,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2867,7 +2853,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122301001</v>
+        <v>122300994</v>
       </c>
       <c r="B20" t="n">
         <v>57399</v>
@@ -2919,10 +2905,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651873</v>
+        <v>651915</v>
       </c>
       <c r="R20" t="n">
-        <v>6673779</v>
+        <v>6673888</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2954,7 +2940,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2964,7 +2950,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2991,10 +2977,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122301078</v>
+        <v>122301058</v>
       </c>
       <c r="B21" t="n">
-        <v>100503</v>
+        <v>98237</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3003,29 +2989,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3035,10 +3029,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652006</v>
+        <v>651981</v>
       </c>
       <c r="R21" t="n">
-        <v>6673876</v>
+        <v>6673859</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3070,7 +3064,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3080,7 +3074,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3107,10 +3101,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122300997</v>
+        <v>122300988</v>
       </c>
       <c r="B22" t="n">
-        <v>57399</v>
+        <v>5193</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3119,20 +3113,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3140,29 +3134,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651883</v>
+        <v>651926</v>
       </c>
       <c r="R22" t="n">
-        <v>6673732</v>
+        <v>6673844</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3194,7 +3185,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3204,7 +3195,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3231,10 +3222,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122301037</v>
+        <v>122301001</v>
       </c>
       <c r="B23" t="n">
-        <v>91229</v>
+        <v>57399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3247,21 +3238,35 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040162</v>
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3269,10 +3274,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651917</v>
+        <v>651873</v>
       </c>
       <c r="R23" t="n">
-        <v>6673853</v>
+        <v>6673779</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3304,7 +3309,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3314,7 +3319,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3341,7 +3346,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122300995</v>
+        <v>122301007</v>
       </c>
       <c r="B24" t="n">
         <v>57399</v>
@@ -3393,10 +3398,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651899</v>
+        <v>651778</v>
       </c>
       <c r="R24" t="n">
-        <v>6673777</v>
+        <v>6673895</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3428,7 +3433,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3438,7 +3443,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3465,7 +3470,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122300993</v>
+        <v>122301006</v>
       </c>
       <c r="B25" t="n">
         <v>57399</v>
@@ -3507,7 +3512,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3517,13 +3522,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651962</v>
+        <v>651860</v>
       </c>
       <c r="R25" t="n">
-        <v>6673882</v>
+        <v>6673862</v>
       </c>
       <c r="S25" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3552,7 +3557,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3562,12 +3567,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3594,10 +3594,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301007</v>
+        <v>122301062</v>
       </c>
       <c r="B26" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3606,39 +3606,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651778</v>
+        <v>651973</v>
       </c>
       <c r="R26" t="n">
-        <v>6673895</v>
+        <v>6673897</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3718,10 +3718,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301060</v>
+        <v>122300991</v>
       </c>
       <c r="B27" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3730,39 +3730,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>652000</v>
+        <v>651958</v>
       </c>
       <c r="R27" t="n">
-        <v>6673848</v>
+        <v>6673868</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122260119</v>
+        <v>122260084</v>
       </c>
       <c r="B29" t="n">
-        <v>100503</v>
+        <v>57536</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3970,31 +3970,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4002,13 +4010,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651950</v>
+        <v>651900</v>
       </c>
       <c r="R29" t="n">
-        <v>6674465</v>
+        <v>6674551</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4037,7 +4045,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4047,7 +4055,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4074,10 +4082,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122260077</v>
+        <v>122260115</v>
       </c>
       <c r="B30" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4086,39 +4094,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651964</v>
+        <v>651891</v>
       </c>
       <c r="R30" t="n">
-        <v>6674220</v>
+        <v>6674645</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4198,10 +4198,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260125</v>
+        <v>122260114</v>
       </c>
       <c r="B31" t="n">
-        <v>100503</v>
+        <v>98237</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4210,29 +4210,37 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
@@ -4242,10 +4250,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651973</v>
+        <v>652010</v>
       </c>
       <c r="R31" t="n">
-        <v>6674332</v>
+        <v>6674220</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4277,7 +4285,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4287,7 +4295,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4314,10 +4322,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260118</v>
+        <v>122260071</v>
       </c>
       <c r="B32" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4326,31 +4334,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4358,10 +4374,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651893</v>
+        <v>651930</v>
       </c>
       <c r="R32" t="n">
-        <v>6674508</v>
+        <v>6674444</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4393,7 +4409,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4403,7 +4419,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4430,10 +4446,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260121</v>
+        <v>122260085</v>
       </c>
       <c r="B33" t="n">
-        <v>100503</v>
+        <v>57753</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4446,27 +4462,35 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4474,13 +4498,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651955</v>
+        <v>651895</v>
       </c>
       <c r="R33" t="n">
-        <v>6674222</v>
+        <v>6674630</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4509,7 +4533,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4519,7 +4543,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4546,10 +4570,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260080</v>
+        <v>122260113</v>
       </c>
       <c r="B34" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4558,39 +4582,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4598,10 +4622,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>652019</v>
+        <v>651906</v>
       </c>
       <c r="R34" t="n">
-        <v>6674239</v>
+        <v>6674392</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4633,7 +4657,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4643,7 +4667,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4670,10 +4694,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122260103</v>
+        <v>122260119</v>
       </c>
       <c r="B35" t="n">
-        <v>91277</v>
+        <v>100503</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4682,30 +4706,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1209</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4713,10 +4738,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651855</v>
+        <v>651950</v>
       </c>
       <c r="R35" t="n">
-        <v>6674655</v>
+        <v>6674465</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4748,7 +4773,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4758,12 +4783,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På klibbtickelåga.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4774,21 +4794,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4805,7 +4810,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122260074</v>
+        <v>122260080</v>
       </c>
       <c r="B36" t="n">
         <v>57399</v>
@@ -4847,7 +4852,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4857,13 +4862,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651923</v>
+        <v>652019</v>
       </c>
       <c r="R36" t="n">
-        <v>6674436</v>
+        <v>6674239</v>
       </c>
       <c r="S36" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4892,7 +4897,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4902,12 +4907,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Hörd i norr.</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4934,7 +4934,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122260120</v>
+        <v>122260126</v>
       </c>
       <c r="B37" t="n">
         <v>100503</v>
@@ -4978,10 +4978,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651967</v>
+        <v>651941</v>
       </c>
       <c r="R37" t="n">
-        <v>6674316</v>
+        <v>6674469</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5050,10 +5050,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122260114</v>
+        <v>122260121</v>
       </c>
       <c r="B38" t="n">
-        <v>98237</v>
+        <v>100503</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5062,37 +5062,29 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -5102,10 +5094,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>652010</v>
+        <v>651955</v>
       </c>
       <c r="R38" t="n">
-        <v>6674220</v>
+        <v>6674222</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5137,7 +5129,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5147,7 +5139,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5174,7 +5166,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260071</v>
+        <v>122260061</v>
       </c>
       <c r="B39" t="n">
         <v>57399</v>
@@ -5226,10 +5218,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651930</v>
+        <v>651886</v>
       </c>
       <c r="R39" t="n">
-        <v>6674444</v>
+        <v>6674654</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5261,7 +5253,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5271,7 +5263,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5298,10 +5290,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260115</v>
+        <v>122260096</v>
       </c>
       <c r="B40" t="n">
-        <v>100503</v>
+        <v>80613</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5310,31 +5302,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5342,10 +5333,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651891</v>
+        <v>651930</v>
       </c>
       <c r="R40" t="n">
-        <v>6674645</v>
+        <v>6674592</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5377,7 +5368,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5387,7 +5378,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5414,7 +5405,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260126</v>
+        <v>122260117</v>
       </c>
       <c r="B41" t="n">
         <v>100503</v>
@@ -5458,10 +5449,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651941</v>
+        <v>651906</v>
       </c>
       <c r="R41" t="n">
-        <v>6674469</v>
+        <v>6674571</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5493,7 +5484,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5503,7 +5494,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5530,10 +5521,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122260111</v>
+        <v>122260064</v>
       </c>
       <c r="B42" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5542,39 +5533,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5582,10 +5573,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651949</v>
+        <v>651845</v>
       </c>
       <c r="R42" t="n">
-        <v>6674415</v>
+        <v>6674626</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5617,7 +5608,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5627,7 +5618,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5654,10 +5645,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260100</v>
+        <v>122260074</v>
       </c>
       <c r="B43" t="n">
-        <v>90839</v>
+        <v>57399</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5670,26 +5661,35 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>652034</v>
+        <v>651923</v>
       </c>
       <c r="R43" t="n">
-        <v>6674236</v>
+        <v>6674436</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5742,7 +5742,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Hörd i norr.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5753,21 +5758,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5784,10 +5774,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260116</v>
+        <v>122260063</v>
       </c>
       <c r="B44" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5796,31 +5786,39 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5828,10 +5826,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651859</v>
+        <v>651872</v>
       </c>
       <c r="R44" t="n">
-        <v>6674654</v>
+        <v>6674674</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5863,7 +5861,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5873,7 +5871,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5900,10 +5898,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122260064</v>
+        <v>122260118</v>
       </c>
       <c r="B45" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5912,39 +5910,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5952,10 +5942,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651845</v>
+        <v>651893</v>
       </c>
       <c r="R45" t="n">
-        <v>6674626</v>
+        <v>6674508</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5987,7 +5977,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5997,7 +5987,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6024,10 +6014,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122260068</v>
+        <v>122260125</v>
       </c>
       <c r="B46" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6036,39 +6026,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6076,10 +6058,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651928</v>
+        <v>651973</v>
       </c>
       <c r="R46" t="n">
-        <v>6674457</v>
+        <v>6674332</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6111,7 +6093,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6121,7 +6103,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6148,10 +6130,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260072</v>
+        <v>122260111</v>
       </c>
       <c r="B47" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6160,39 +6142,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6200,10 +6182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651927</v>
+        <v>651949</v>
       </c>
       <c r="R47" t="n">
-        <v>6674447</v>
+        <v>6674415</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6235,7 +6217,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6245,7 +6227,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6272,10 +6254,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260075</v>
+        <v>122260110</v>
       </c>
       <c r="B48" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6284,39 +6266,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6324,10 +6306,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>651900</v>
+        <v>651949</v>
       </c>
       <c r="R48" t="n">
-        <v>6674390</v>
+        <v>6674420</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6359,7 +6341,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6369,7 +6351,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6396,10 +6383,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260058</v>
+        <v>122260070</v>
       </c>
       <c r="B49" t="n">
-        <v>5193</v>
+        <v>57399</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6408,20 +6395,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6429,13 +6416,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6445,10 +6435,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>652031</v>
+        <v>651967</v>
       </c>
       <c r="R49" t="n">
-        <v>6674226</v>
+        <v>6674433</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6480,7 +6470,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6490,7 +6480,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6501,21 +6491,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6532,10 +6507,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260113</v>
+        <v>122260103</v>
       </c>
       <c r="B50" t="n">
-        <v>98237</v>
+        <v>91277</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6548,35 +6523,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6584,10 +6550,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651906</v>
+        <v>651855</v>
       </c>
       <c r="R50" t="n">
-        <v>6674392</v>
+        <v>6674655</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6619,7 +6585,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6629,7 +6595,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På klibbtickelåga.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6640,6 +6611,21 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6656,7 +6642,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122260076</v>
+        <v>122260066</v>
       </c>
       <c r="B51" t="n">
         <v>57399</v>
@@ -6698,7 +6684,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6708,10 +6694,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651949</v>
+        <v>651934</v>
       </c>
       <c r="R51" t="n">
-        <v>6674279</v>
+        <v>6674510</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6743,7 +6729,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6753,7 +6739,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6780,10 +6766,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260096</v>
+        <v>122260077</v>
       </c>
       <c r="B52" t="n">
-        <v>80613</v>
+        <v>57399</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6796,26 +6782,35 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6823,10 +6818,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651930</v>
+        <v>651964</v>
       </c>
       <c r="R52" t="n">
-        <v>6674592</v>
+        <v>6674220</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6858,7 +6853,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6868,7 +6863,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6895,10 +6890,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260061</v>
+        <v>122260120</v>
       </c>
       <c r="B53" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6907,39 +6902,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6947,10 +6934,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651886</v>
+        <v>651967</v>
       </c>
       <c r="R53" t="n">
-        <v>6674654</v>
+        <v>6674316</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6982,7 +6969,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6992,7 +6979,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7019,10 +7006,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260084</v>
+        <v>122260100</v>
       </c>
       <c r="B54" t="n">
-        <v>57536</v>
+        <v>90839</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7035,35 +7022,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7071,13 +7049,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651900</v>
+        <v>652034</v>
       </c>
       <c r="R54" t="n">
-        <v>6674551</v>
+        <v>6674236</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7106,7 +7084,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7116,7 +7094,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7127,6 +7105,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7143,10 +7136,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122260117</v>
+        <v>122260068</v>
       </c>
       <c r="B55" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7155,31 +7148,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7187,10 +7188,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651906</v>
+        <v>651928</v>
       </c>
       <c r="R55" t="n">
-        <v>6674571</v>
+        <v>6674457</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7222,7 +7223,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7232,7 +7233,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7259,10 +7260,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260085</v>
+        <v>122260072</v>
       </c>
       <c r="B56" t="n">
-        <v>57753</v>
+        <v>57399</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7271,20 +7272,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -7301,7 +7302,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7311,13 +7312,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>651895</v>
+        <v>651927</v>
       </c>
       <c r="R56" t="n">
-        <v>6674630</v>
+        <v>6674447</v>
       </c>
       <c r="S56" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7346,7 +7347,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7356,7 +7357,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7383,10 +7384,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260066</v>
+        <v>122260058</v>
       </c>
       <c r="B57" t="n">
-        <v>57399</v>
+        <v>5193</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7395,20 +7396,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -7416,16 +7417,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -7435,10 +7433,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651934</v>
+        <v>652031</v>
       </c>
       <c r="R57" t="n">
-        <v>6674510</v>
+        <v>6674226</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7470,7 +7468,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7480,7 +7478,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7491,6 +7489,21 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7507,10 +7520,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260110</v>
+        <v>122260116</v>
       </c>
       <c r="B58" t="n">
-        <v>98237</v>
+        <v>100503</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7519,37 +7532,29 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -7559,10 +7564,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>651949</v>
+        <v>651859</v>
       </c>
       <c r="R58" t="n">
-        <v>6674420</v>
+        <v>6674654</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7594,7 +7599,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7604,12 +7609,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7636,7 +7636,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260063</v>
+        <v>122260076</v>
       </c>
       <c r="B59" t="n">
         <v>57399</v>
@@ -7678,7 +7678,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7688,10 +7688,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651872</v>
+        <v>651949</v>
       </c>
       <c r="R59" t="n">
-        <v>6674674</v>
+        <v>6674279</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7760,7 +7760,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260070</v>
+        <v>122260075</v>
       </c>
       <c r="B60" t="n">
         <v>57399</v>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651967</v>
+        <v>651900</v>
       </c>
       <c r="R60" t="n">
-        <v>6674433</v>
+        <v>6674390</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7884,10 +7884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301025</v>
+        <v>122301017</v>
       </c>
       <c r="B61" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7900,49 +7900,49 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651941</v>
+        <v>651776</v>
       </c>
       <c r="R61" t="n">
-        <v>6674093</v>
+        <v>6673944</v>
       </c>
       <c r="S61" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8008,7 +8008,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301073</v>
+        <v>122301075</v>
       </c>
       <c r="B62" t="n">
         <v>100503</v>
@@ -8052,10 +8052,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651817</v>
+        <v>651975</v>
       </c>
       <c r="R62" t="n">
-        <v>6673939</v>
+        <v>6673928</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8124,10 +8124,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301017</v>
+        <v>122301074</v>
       </c>
       <c r="B63" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8136,39 +8136,31 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -8176,10 +8168,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>651776</v>
+        <v>651855</v>
       </c>
       <c r="R63" t="n">
-        <v>6673944</v>
+        <v>6673907</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8211,7 +8203,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8221,7 +8213,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8248,7 +8240,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301081</v>
+        <v>122301079</v>
       </c>
       <c r="B64" t="n">
         <v>100503</v>
@@ -8292,10 +8284,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>652036</v>
+        <v>652014</v>
       </c>
       <c r="R64" t="n">
-        <v>6673988</v>
+        <v>6673954</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8327,7 +8319,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8337,7 +8329,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8364,10 +8356,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301075</v>
+        <v>122301026</v>
       </c>
       <c r="B65" t="n">
-        <v>100503</v>
+        <v>57536</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8376,31 +8368,39 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8408,13 +8408,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651975</v>
+        <v>651977</v>
       </c>
       <c r="R65" t="n">
-        <v>6673928</v>
+        <v>6673906</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8480,10 +8480,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301066</v>
+        <v>122301050</v>
       </c>
       <c r="B66" t="n">
-        <v>100503</v>
+        <v>98237</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8492,29 +8492,37 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -8524,10 +8532,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>652079</v>
+        <v>651948</v>
       </c>
       <c r="R66" t="n">
-        <v>6673929</v>
+        <v>6673906</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8559,7 +8567,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8569,7 +8577,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8596,10 +8604,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301026</v>
+        <v>122301067</v>
       </c>
       <c r="B67" t="n">
-        <v>57536</v>
+        <v>100503</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8608,39 +8616,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8648,13 +8648,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>651977</v>
+        <v>652040</v>
       </c>
       <c r="R67" t="n">
-        <v>6673906</v>
+        <v>6673920</v>
       </c>
       <c r="S67" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8720,10 +8720,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301027</v>
+        <v>122301081</v>
       </c>
       <c r="B68" t="n">
-        <v>57753</v>
+        <v>100503</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8736,31 +8736,27 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8768,13 +8764,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651983</v>
+        <v>652036</v>
       </c>
       <c r="R68" t="n">
-        <v>6673930</v>
+        <v>6673988</v>
       </c>
       <c r="S68" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8803,7 +8799,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8813,7 +8809,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8840,7 +8836,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301080</v>
+        <v>122301065</v>
       </c>
       <c r="B69" t="n">
         <v>100503</v>
@@ -8884,10 +8880,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>652011</v>
+        <v>652034</v>
       </c>
       <c r="R69" t="n">
-        <v>6673969</v>
+        <v>6673906</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8919,7 +8915,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8929,7 +8925,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8956,10 +8952,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301015</v>
+        <v>122301073</v>
       </c>
       <c r="B70" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8968,39 +8964,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9008,10 +8996,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651777</v>
+        <v>651817</v>
       </c>
       <c r="R70" t="n">
-        <v>6673975</v>
+        <v>6673939</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -9043,7 +9031,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9053,7 +9041,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9080,10 +9068,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301050</v>
+        <v>122301025</v>
       </c>
       <c r="B71" t="n">
-        <v>98237</v>
+        <v>57536</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9092,53 +9080,53 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651948</v>
+        <v>651941</v>
       </c>
       <c r="R71" t="n">
-        <v>6673906</v>
+        <v>6674093</v>
       </c>
       <c r="S71" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9167,7 +9155,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9177,7 +9165,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9204,10 +9192,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301074</v>
+        <v>122301027</v>
       </c>
       <c r="B72" t="n">
-        <v>100503</v>
+        <v>57753</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9220,27 +9208,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9248,13 +9240,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651855</v>
+        <v>651983</v>
       </c>
       <c r="R72" t="n">
-        <v>6673907</v>
+        <v>6673930</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9283,7 +9275,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9293,7 +9285,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9320,10 +9312,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301079</v>
+        <v>122301013</v>
       </c>
       <c r="B73" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9332,31 +9324,39 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9364,10 +9364,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>652014</v>
+        <v>651745</v>
       </c>
       <c r="R73" t="n">
-        <v>6673954</v>
+        <v>6673922</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9436,7 +9436,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301063</v>
+        <v>122301066</v>
       </c>
       <c r="B74" t="n">
         <v>100503</v>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>651949</v>
+        <v>652079</v>
       </c>
       <c r="R74" t="n">
-        <v>6673910</v>
+        <v>6673929</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9552,10 +9552,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301013</v>
+        <v>122301080</v>
       </c>
       <c r="B75" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9564,39 +9564,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9604,10 +9596,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651745</v>
+        <v>652011</v>
       </c>
       <c r="R75" t="n">
-        <v>6673922</v>
+        <v>6673969</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9639,7 +9631,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9649,7 +9641,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9676,7 +9668,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301067</v>
+        <v>122301063</v>
       </c>
       <c r="B76" t="n">
         <v>100503</v>
@@ -9720,10 +9712,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>652040</v>
+        <v>651949</v>
       </c>
       <c r="R76" t="n">
-        <v>6673920</v>
+        <v>6673910</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9755,7 +9747,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9765,7 +9757,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9792,10 +9784,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301065</v>
+        <v>122301015</v>
       </c>
       <c r="B77" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9804,31 +9796,39 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>652034</v>
+        <v>651777</v>
       </c>
       <c r="R77" t="n">
-        <v>6673906</v>
+        <v>6673975</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -2503,10 +2503,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301037</v>
+        <v>122301077</v>
       </c>
       <c r="B17" t="n">
-        <v>91229</v>
+        <v>100503</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2515,25 +2515,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6040162</v>
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2541,10 +2547,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651917</v>
+        <v>651993</v>
       </c>
       <c r="R17" t="n">
-        <v>6673853</v>
+        <v>6673867</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2576,7 +2582,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2586,7 +2592,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2613,10 +2619,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122301077</v>
+        <v>122301037</v>
       </c>
       <c r="B18" t="n">
-        <v>100503</v>
+        <v>91229</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2625,31 +2631,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651993</v>
+        <v>651917</v>
       </c>
       <c r="R18" t="n">
-        <v>6673867</v>
+        <v>6673853</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3222,7 +3222,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122301001</v>
+        <v>122301007</v>
       </c>
       <c r="B23" t="n">
         <v>57399</v>
@@ -3274,10 +3274,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651873</v>
+        <v>651778</v>
       </c>
       <c r="R23" t="n">
-        <v>6673779</v>
+        <v>6673895</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3309,7 +3309,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3346,7 +3346,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122301007</v>
+        <v>122301001</v>
       </c>
       <c r="B24" t="n">
         <v>57399</v>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651778</v>
+        <v>651873</v>
       </c>
       <c r="R24" t="n">
-        <v>6673895</v>
+        <v>6673779</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3718,10 +3718,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122300991</v>
+        <v>122301064</v>
       </c>
       <c r="B27" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3730,39 +3730,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3770,10 +3762,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>651958</v>
+        <v>651993</v>
       </c>
       <c r="R27" t="n">
-        <v>6673868</v>
+        <v>6673896</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3805,7 +3797,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3815,7 +3807,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3842,10 +3834,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122301064</v>
+        <v>122300991</v>
       </c>
       <c r="B28" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3854,31 +3846,39 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651993</v>
+        <v>651958</v>
       </c>
       <c r="R28" t="n">
-        <v>6673896</v>
+        <v>6673868</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4322,10 +4322,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260071</v>
+        <v>122260085</v>
       </c>
       <c r="B32" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4334,20 +4334,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4364,7 +4364,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4374,13 +4374,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651930</v>
+        <v>651895</v>
       </c>
       <c r="R32" t="n">
-        <v>6674444</v>
+        <v>6674630</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,10 +4446,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260085</v>
+        <v>122260071</v>
       </c>
       <c r="B33" t="n">
-        <v>57753</v>
+        <v>57399</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4458,20 +4458,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4488,7 +4488,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4498,13 +4498,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651895</v>
+        <v>651930</v>
       </c>
       <c r="R33" t="n">
-        <v>6674630</v>
+        <v>6674444</v>
       </c>
       <c r="S33" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5050,10 +5050,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122260121</v>
+        <v>122260061</v>
       </c>
       <c r="B38" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5062,31 +5062,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5094,10 +5102,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651955</v>
+        <v>651886</v>
       </c>
       <c r="R38" t="n">
-        <v>6674222</v>
+        <v>6674654</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5129,7 +5137,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5139,7 +5147,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5166,10 +5174,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260061</v>
+        <v>122260121</v>
       </c>
       <c r="B39" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5178,39 +5186,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5218,10 +5218,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651886</v>
+        <v>651955</v>
       </c>
       <c r="R39" t="n">
-        <v>6674654</v>
+        <v>6674222</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5290,10 +5290,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260096</v>
+        <v>122260117</v>
       </c>
       <c r="B40" t="n">
-        <v>80613</v>
+        <v>100503</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5302,30 +5302,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5333,10 +5334,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651930</v>
+        <v>651906</v>
       </c>
       <c r="R40" t="n">
-        <v>6674592</v>
+        <v>6674571</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5368,7 +5369,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5378,7 +5379,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5405,10 +5406,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260117</v>
+        <v>122260096</v>
       </c>
       <c r="B41" t="n">
-        <v>100503</v>
+        <v>80613</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5417,31 +5418,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651906</v>
+        <v>651930</v>
       </c>
       <c r="R41" t="n">
-        <v>6674571</v>
+        <v>6674592</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6130,10 +6130,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260111</v>
+        <v>122260070</v>
       </c>
       <c r="B47" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6142,39 +6142,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651949</v>
+        <v>651967</v>
       </c>
       <c r="R47" t="n">
-        <v>6674415</v>
+        <v>6674433</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6254,7 +6254,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260110</v>
+        <v>122260111</v>
       </c>
       <c r="B48" t="n">
         <v>98237</v>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6309,7 +6309,7 @@
         <v>651949</v>
       </c>
       <c r="R48" t="n">
-        <v>6674420</v>
+        <v>6674415</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6351,12 +6351,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6383,10 +6378,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260070</v>
+        <v>122260110</v>
       </c>
       <c r="B49" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6395,39 +6390,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6435,10 +6430,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651967</v>
+        <v>651949</v>
       </c>
       <c r="R49" t="n">
-        <v>6674433</v>
+        <v>6674420</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6470,7 +6465,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6480,7 +6475,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -9312,10 +9312,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301013</v>
+        <v>122301066</v>
       </c>
       <c r="B73" t="n">
-        <v>57399</v>
+        <v>100503</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9324,39 +9324,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9364,10 +9356,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651745</v>
+        <v>652079</v>
       </c>
       <c r="R73" t="n">
-        <v>6673922</v>
+        <v>6673929</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9399,7 +9391,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9409,7 +9401,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9436,7 +9428,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301066</v>
+        <v>122301080</v>
       </c>
       <c r="B74" t="n">
         <v>100503</v>
@@ -9480,10 +9472,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>652079</v>
+        <v>652011</v>
       </c>
       <c r="R74" t="n">
-        <v>6673929</v>
+        <v>6673969</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9515,7 +9507,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9525,7 +9517,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9552,10 +9544,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301080</v>
+        <v>122301013</v>
       </c>
       <c r="B75" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9564,31 +9556,39 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9596,10 +9596,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>652011</v>
+        <v>651745</v>
       </c>
       <c r="R75" t="n">
-        <v>6673969</v>
+        <v>6673922</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122301071</v>
+        <v>122301001</v>
       </c>
       <c r="B2" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651840</v>
+        <v>651873</v>
       </c>
       <c r="R2" t="n">
-        <v>6673881</v>
+        <v>6673779</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122301078</v>
+        <v>122301062</v>
       </c>
       <c r="B3" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -824,8 +832,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -835,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>652006</v>
+        <v>651973</v>
       </c>
       <c r="R3" t="n">
-        <v>6673876</v>
+        <v>6673897</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -870,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122300999</v>
+        <v>122301053</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,39 +935,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -959,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651879</v>
+        <v>651986</v>
       </c>
       <c r="R4" t="n">
-        <v>6673776</v>
+        <v>6673841</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -994,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1020,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,7 +1052,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122301004</v>
+        <v>122301019</v>
       </c>
       <c r="B5" t="n">
         <v>57399</v>
@@ -1083,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651888</v>
+        <v>652004</v>
       </c>
       <c r="R5" t="n">
-        <v>6673877</v>
+        <v>6673869</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1118,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1128,7 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,10 +1176,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122301020</v>
+        <v>122301078</v>
       </c>
       <c r="B6" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,39 +1188,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,10 +1220,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652017</v>
+        <v>652006</v>
       </c>
       <c r="R6" t="n">
-        <v>6673872</v>
+        <v>6673876</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1242,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,7 +1292,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122300997</v>
+        <v>122300993</v>
       </c>
       <c r="B7" t="n">
         <v>57399</v>
@@ -1321,23 +1334,23 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651883</v>
+        <v>651962</v>
       </c>
       <c r="R7" t="n">
-        <v>6673732</v>
+        <v>6673882</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,7 +1379,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1376,7 +1389,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122301056</v>
+        <v>122301071</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>100506</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,37 +1433,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1455,10 +1465,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651930</v>
+        <v>651840</v>
       </c>
       <c r="R8" t="n">
-        <v>6673898</v>
+        <v>6673881</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1490,7 +1500,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1500,7 +1510,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,10 +1537,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122301021</v>
+        <v>122301056</v>
       </c>
       <c r="B9" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,50 +1549,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>652056</v>
+        <v>651930</v>
       </c>
       <c r="R9" t="n">
-        <v>6673872</v>
+        <v>6673898</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1614,7 +1624,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1624,7 +1634,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1651,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122301060</v>
+        <v>122301021</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1663,50 +1673,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>652000</v>
+        <v>652056</v>
       </c>
       <c r="R10" t="n">
-        <v>6673848</v>
+        <v>6673872</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1738,7 +1748,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1748,7 +1758,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1775,10 +1785,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301036</v>
+        <v>122301060</v>
       </c>
       <c r="B11" t="n">
-        <v>90839</v>
+        <v>98240</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1787,30 +1797,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1818,10 +1837,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>652047</v>
+        <v>652000</v>
       </c>
       <c r="R11" t="n">
-        <v>6673893</v>
+        <v>6673848</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1853,7 +1872,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,7 +1882,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1890,10 +1909,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301031</v>
+        <v>122301006</v>
       </c>
       <c r="B12" t="n">
-        <v>74696</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1902,30 +1921,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1933,10 +1961,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651805</v>
+        <v>651860</v>
       </c>
       <c r="R12" t="n">
-        <v>6673899</v>
+        <v>6673862</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1968,7 +1996,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1978,7 +2006,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2005,7 +2033,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122300993</v>
+        <v>122300995</v>
       </c>
       <c r="B13" t="n">
         <v>57399</v>
@@ -2047,7 +2075,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2057,13 +2085,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651962</v>
+        <v>651899</v>
       </c>
       <c r="R13" t="n">
-        <v>6673882</v>
+        <v>6673777</v>
       </c>
       <c r="S13" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2092,7 +2120,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,12 +2130,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,7 +2157,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301019</v>
+        <v>122301020</v>
       </c>
       <c r="B14" t="n">
         <v>57399</v>
@@ -2176,7 +2199,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2186,10 +2209,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>652004</v>
+        <v>652017</v>
       </c>
       <c r="R14" t="n">
-        <v>6673869</v>
+        <v>6673872</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2221,7 +2244,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2231,7 +2254,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2258,10 +2281,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122301053</v>
+        <v>122300994</v>
       </c>
       <c r="B15" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2270,39 +2293,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2310,10 +2333,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651986</v>
+        <v>651915</v>
       </c>
       <c r="R15" t="n">
-        <v>6673841</v>
+        <v>6673888</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2345,7 +2368,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2355,12 +2378,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,10 +2405,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301068</v>
+        <v>122301058</v>
       </c>
       <c r="B16" t="n">
-        <v>100503</v>
+        <v>98240</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2399,42 +2417,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651906</v>
+        <v>651981</v>
       </c>
       <c r="R16" t="n">
-        <v>6673752</v>
+        <v>6673859</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2466,7 +2492,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2476,7 +2502,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2503,10 +2529,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301077</v>
+        <v>122301068</v>
       </c>
       <c r="B17" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2543,14 +2569,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651993</v>
+        <v>651906</v>
       </c>
       <c r="R17" t="n">
-        <v>6673867</v>
+        <v>6673752</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2582,7 +2608,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2592,7 +2618,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2619,10 +2645,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122301037</v>
+        <v>122300997</v>
       </c>
       <c r="B18" t="n">
-        <v>91229</v>
+        <v>57399</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2635,32 +2661,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6040162</v>
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651917</v>
+        <v>651883</v>
       </c>
       <c r="R18" t="n">
-        <v>6673853</v>
+        <v>6673732</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2692,7 +2732,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2702,7 +2742,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2729,7 +2769,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122300995</v>
+        <v>122300999</v>
       </c>
       <c r="B19" t="n">
         <v>57399</v>
@@ -2781,10 +2821,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651899</v>
+        <v>651879</v>
       </c>
       <c r="R19" t="n">
-        <v>6673777</v>
+        <v>6673776</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2816,7 +2856,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2826,7 +2866,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2853,10 +2893,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122300994</v>
+        <v>122301037</v>
       </c>
       <c r="B20" t="n">
-        <v>57399</v>
+        <v>91230</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2869,35 +2909,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2905,10 +2931,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651915</v>
+        <v>651917</v>
       </c>
       <c r="R20" t="n">
-        <v>6673888</v>
+        <v>6673853</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2940,7 +2966,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2950,7 +2976,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2977,10 +3003,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122301058</v>
+        <v>122300991</v>
       </c>
       <c r="B21" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2989,39 +3015,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3029,10 +3055,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651981</v>
+        <v>651958</v>
       </c>
       <c r="R21" t="n">
-        <v>6673859</v>
+        <v>6673868</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3064,7 +3090,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3074,7 +3100,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3101,10 +3127,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122300988</v>
+        <v>122301064</v>
       </c>
       <c r="B22" t="n">
-        <v>5193</v>
+        <v>100506</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3117,32 +3143,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3150,10 +3171,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651926</v>
+        <v>651993</v>
       </c>
       <c r="R22" t="n">
-        <v>6673844</v>
+        <v>6673896</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3185,7 +3206,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3195,7 +3216,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3222,10 +3243,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122301007</v>
+        <v>122300988</v>
       </c>
       <c r="B23" t="n">
-        <v>57399</v>
+        <v>5193</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3234,20 +3255,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3255,16 +3276,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3274,10 +3292,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651778</v>
+        <v>651926</v>
       </c>
       <c r="R23" t="n">
-        <v>6673895</v>
+        <v>6673844</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3309,7 +3327,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3319,7 +3337,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3346,10 +3364,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122301001</v>
+        <v>122301031</v>
       </c>
       <c r="B24" t="n">
-        <v>57399</v>
+        <v>74696</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3358,39 +3376,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3398,10 +3407,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651873</v>
+        <v>651805</v>
       </c>
       <c r="R24" t="n">
-        <v>6673779</v>
+        <v>6673899</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3433,7 +3442,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3443,7 +3452,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3470,7 +3479,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301006</v>
+        <v>122301004</v>
       </c>
       <c r="B25" t="n">
         <v>57399</v>
@@ -3522,10 +3531,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651860</v>
+        <v>651888</v>
       </c>
       <c r="R25" t="n">
-        <v>6673862</v>
+        <v>6673877</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3557,7 +3566,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3567,7 +3576,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3594,10 +3603,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301062</v>
+        <v>122301077</v>
       </c>
       <c r="B26" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3627,16 +3636,8 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3646,10 +3647,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651973</v>
+        <v>651993</v>
       </c>
       <c r="R26" t="n">
-        <v>6673897</v>
+        <v>6673867</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3681,7 +3682,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3691,7 +3692,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3718,10 +3719,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301064</v>
+        <v>122301007</v>
       </c>
       <c r="B27" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3730,31 +3731,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3762,10 +3771,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>651993</v>
+        <v>651778</v>
       </c>
       <c r="R27" t="n">
-        <v>6673896</v>
+        <v>6673895</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3797,7 +3806,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3807,7 +3816,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3834,10 +3843,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122300991</v>
+        <v>122301036</v>
       </c>
       <c r="B28" t="n">
-        <v>57399</v>
+        <v>90833</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3850,35 +3859,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651958</v>
+        <v>652047</v>
       </c>
       <c r="R28" t="n">
-        <v>6673868</v>
+        <v>6673893</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122260084</v>
+        <v>122260117</v>
       </c>
       <c r="B29" t="n">
-        <v>57536</v>
+        <v>100506</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3970,39 +3970,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4010,13 +4002,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651900</v>
+        <v>651906</v>
       </c>
       <c r="R29" t="n">
-        <v>6674551</v>
+        <v>6674571</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4045,7 +4037,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4055,7 +4047,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4085,7 +4077,7 @@
         <v>122260115</v>
       </c>
       <c r="B30" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4198,10 +4190,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260114</v>
+        <v>122260100</v>
       </c>
       <c r="B31" t="n">
-        <v>98237</v>
+        <v>90833</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4210,39 +4202,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4250,10 +4233,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>652010</v>
+        <v>652034</v>
       </c>
       <c r="R31" t="n">
-        <v>6674220</v>
+        <v>6674236</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4285,7 +4268,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4295,7 +4278,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4306,6 +4289,21 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4322,10 +4320,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260085</v>
+        <v>122260121</v>
       </c>
       <c r="B32" t="n">
-        <v>57753</v>
+        <v>100506</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4338,35 +4336,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4374,13 +4364,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651895</v>
+        <v>651955</v>
       </c>
       <c r="R32" t="n">
-        <v>6674630</v>
+        <v>6674222</v>
       </c>
       <c r="S32" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4409,7 +4399,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4419,7 +4409,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4446,10 +4436,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260071</v>
+        <v>122260126</v>
       </c>
       <c r="B33" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4458,39 +4448,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4498,10 +4480,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651930</v>
+        <v>651941</v>
       </c>
       <c r="R33" t="n">
-        <v>6674444</v>
+        <v>6674469</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4533,7 +4515,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4543,7 +4525,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4570,10 +4552,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260113</v>
+        <v>122260070</v>
       </c>
       <c r="B34" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4582,39 +4564,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4622,10 +4604,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651906</v>
+        <v>651967</v>
       </c>
       <c r="R34" t="n">
-        <v>6674392</v>
+        <v>6674433</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4657,7 +4639,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4667,7 +4649,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4694,10 +4676,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122260119</v>
+        <v>122260085</v>
       </c>
       <c r="B35" t="n">
-        <v>100503</v>
+        <v>57753</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4710,27 +4692,35 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4738,13 +4728,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651950</v>
+        <v>651895</v>
       </c>
       <c r="R35" t="n">
-        <v>6674465</v>
+        <v>6674630</v>
       </c>
       <c r="S35" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4773,7 +4763,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4783,7 +4773,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4810,7 +4800,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122260080</v>
+        <v>122260066</v>
       </c>
       <c r="B36" t="n">
         <v>57399</v>
@@ -4862,10 +4852,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>652019</v>
+        <v>651934</v>
       </c>
       <c r="R36" t="n">
-        <v>6674239</v>
+        <v>6674510</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4897,7 +4887,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4907,7 +4897,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4934,10 +4924,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122260126</v>
+        <v>122260096</v>
       </c>
       <c r="B37" t="n">
-        <v>100503</v>
+        <v>80613</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4946,31 +4936,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>1049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4978,10 +4967,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651941</v>
+        <v>651930</v>
       </c>
       <c r="R37" t="n">
-        <v>6674469</v>
+        <v>6674592</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5013,7 +5002,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5023,7 +5012,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5050,10 +5039,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122260061</v>
+        <v>122260118</v>
       </c>
       <c r="B38" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5062,39 +5051,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5102,10 +5083,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651886</v>
+        <v>651893</v>
       </c>
       <c r="R38" t="n">
-        <v>6674654</v>
+        <v>6674508</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5137,7 +5118,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5147,7 +5128,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5174,10 +5155,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260121</v>
+        <v>122260061</v>
       </c>
       <c r="B39" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5186,31 +5167,39 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5218,10 +5207,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651955</v>
+        <v>651886</v>
       </c>
       <c r="R39" t="n">
-        <v>6674222</v>
+        <v>6674654</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5253,7 +5242,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5263,7 +5252,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5290,10 +5279,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260117</v>
+        <v>122260080</v>
       </c>
       <c r="B40" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5302,31 +5291,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5334,10 +5331,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651906</v>
+        <v>652019</v>
       </c>
       <c r="R40" t="n">
-        <v>6674571</v>
+        <v>6674239</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5369,7 +5366,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5379,7 +5376,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5406,10 +5403,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260096</v>
+        <v>122260103</v>
       </c>
       <c r="B41" t="n">
-        <v>80613</v>
+        <v>91278</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5418,25 +5415,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1049</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5449,10 +5446,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651930</v>
+        <v>651855</v>
       </c>
       <c r="R41" t="n">
-        <v>6674592</v>
+        <v>6674655</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5484,7 +5481,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5494,7 +5491,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På klibbtickelåga.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5505,6 +5507,21 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5645,7 +5662,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260074</v>
+        <v>122260071</v>
       </c>
       <c r="B43" t="n">
         <v>57399</v>
@@ -5687,7 +5704,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5697,13 +5714,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651923</v>
+        <v>651930</v>
       </c>
       <c r="R43" t="n">
-        <v>6674436</v>
+        <v>6674444</v>
       </c>
       <c r="S43" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5732,7 +5749,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5742,12 +5759,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Hörd i norr.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5774,10 +5786,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260063</v>
+        <v>122260120</v>
       </c>
       <c r="B44" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5786,39 +5798,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5826,10 +5830,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651872</v>
+        <v>651967</v>
       </c>
       <c r="R44" t="n">
-        <v>6674674</v>
+        <v>6674316</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5861,7 +5865,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5871,7 +5875,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5898,10 +5902,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122260118</v>
+        <v>122260077</v>
       </c>
       <c r="B45" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5910,31 +5914,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5942,10 +5954,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651893</v>
+        <v>651964</v>
       </c>
       <c r="R45" t="n">
-        <v>6674508</v>
+        <v>6674220</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5977,7 +5989,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5987,7 +5999,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6014,10 +6026,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122260125</v>
+        <v>122260063</v>
       </c>
       <c r="B46" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6026,31 +6038,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6058,10 +6078,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651973</v>
+        <v>651872</v>
       </c>
       <c r="R46" t="n">
-        <v>6674332</v>
+        <v>6674674</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6093,7 +6113,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6103,7 +6123,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6130,7 +6150,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260070</v>
+        <v>122260072</v>
       </c>
       <c r="B47" t="n">
         <v>57399</v>
@@ -6172,7 +6192,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6182,10 +6202,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651967</v>
+        <v>651927</v>
       </c>
       <c r="R47" t="n">
-        <v>6674433</v>
+        <v>6674447</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6217,7 +6237,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6227,7 +6247,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6254,10 +6274,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260111</v>
+        <v>122260076</v>
       </c>
       <c r="B48" t="n">
-        <v>98237</v>
+        <v>57399</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6266,39 +6286,39 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6309,7 +6329,7 @@
         <v>651949</v>
       </c>
       <c r="R48" t="n">
-        <v>6674415</v>
+        <v>6674279</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6341,7 +6361,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6351,7 +6371,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6378,10 +6398,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260110</v>
+        <v>122260084</v>
       </c>
       <c r="B49" t="n">
-        <v>98237</v>
+        <v>57536</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6390,39 +6410,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6430,13 +6450,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651949</v>
+        <v>651900</v>
       </c>
       <c r="R49" t="n">
-        <v>6674420</v>
+        <v>6674551</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6465,7 +6485,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6475,12 +6495,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6507,10 +6522,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260103</v>
+        <v>122260068</v>
       </c>
       <c r="B50" t="n">
-        <v>91277</v>
+        <v>57399</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6519,30 +6534,39 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6550,10 +6574,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651855</v>
+        <v>651928</v>
       </c>
       <c r="R50" t="n">
-        <v>6674655</v>
+        <v>6674457</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6585,7 +6609,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6595,12 +6619,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På klibbtickelåga.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6611,21 +6630,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6642,7 +6646,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122260066</v>
+        <v>122260075</v>
       </c>
       <c r="B51" t="n">
         <v>57399</v>
@@ -6684,7 +6688,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6694,10 +6698,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651934</v>
+        <v>651900</v>
       </c>
       <c r="R51" t="n">
-        <v>6674510</v>
+        <v>6674390</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6729,7 +6733,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6739,7 +6743,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6766,10 +6770,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260077</v>
+        <v>122260113</v>
       </c>
       <c r="B52" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6778,39 +6782,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6818,10 +6822,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651964</v>
+        <v>651906</v>
       </c>
       <c r="R52" t="n">
-        <v>6674220</v>
+        <v>6674392</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6853,7 +6857,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6863,7 +6867,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6890,10 +6894,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260120</v>
+        <v>122260125</v>
       </c>
       <c r="B53" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6934,10 +6938,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651967</v>
+        <v>651973</v>
       </c>
       <c r="R53" t="n">
-        <v>6674316</v>
+        <v>6674332</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6969,7 +6973,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6979,7 +6983,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7006,10 +7010,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260100</v>
+        <v>122260114</v>
       </c>
       <c r="B54" t="n">
-        <v>90839</v>
+        <v>98240</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7018,30 +7022,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7049,10 +7062,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>652034</v>
+        <v>652010</v>
       </c>
       <c r="R54" t="n">
-        <v>6674236</v>
+        <v>6674220</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7084,7 +7097,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7094,7 +7107,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7105,21 +7118,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -7136,10 +7134,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122260068</v>
+        <v>122260110</v>
       </c>
       <c r="B55" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7148,39 +7146,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7188,10 +7186,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651928</v>
+        <v>651949</v>
       </c>
       <c r="R55" t="n">
-        <v>6674457</v>
+        <v>6674420</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7223,7 +7221,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7233,7 +7231,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7260,10 +7263,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260072</v>
+        <v>122260119</v>
       </c>
       <c r="B56" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7272,39 +7275,31 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7312,10 +7307,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>651927</v>
+        <v>651950</v>
       </c>
       <c r="R56" t="n">
-        <v>6674447</v>
+        <v>6674465</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7347,7 +7342,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7357,7 +7352,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7384,10 +7379,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260058</v>
+        <v>122260111</v>
       </c>
       <c r="B57" t="n">
-        <v>5193</v>
+        <v>98240</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7396,36 +7391,39 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7433,10 +7431,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>652031</v>
+        <v>651949</v>
       </c>
       <c r="R57" t="n">
-        <v>6674226</v>
+        <v>6674415</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7468,7 +7466,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7478,7 +7476,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7489,21 +7487,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7520,10 +7503,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260116</v>
+        <v>122260058</v>
       </c>
       <c r="B58" t="n">
-        <v>100503</v>
+        <v>5193</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7536,27 +7519,32 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7564,10 +7552,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>651859</v>
+        <v>652031</v>
       </c>
       <c r="R58" t="n">
-        <v>6674654</v>
+        <v>6674226</v>
       </c>
       <c r="S58" t="n">
         <v>4</v>
@@ -7599,7 +7587,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7609,7 +7597,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7620,6 +7608,21 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7636,7 +7639,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260076</v>
+        <v>122260074</v>
       </c>
       <c r="B59" t="n">
         <v>57399</v>
@@ -7678,7 +7681,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7688,13 +7691,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651949</v>
+        <v>651923</v>
       </c>
       <c r="R59" t="n">
-        <v>6674279</v>
+        <v>6674436</v>
       </c>
       <c r="S59" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7723,7 +7726,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7733,7 +7736,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Hörd i norr.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7760,10 +7768,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260075</v>
+        <v>122260116</v>
       </c>
       <c r="B60" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7772,39 +7780,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7812,10 +7812,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651900</v>
+        <v>651859</v>
       </c>
       <c r="R60" t="n">
-        <v>6674390</v>
+        <v>6674654</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7847,7 +7847,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7884,10 +7884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301017</v>
+        <v>122301026</v>
       </c>
       <c r="B61" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7900,21 +7900,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -7926,7 +7926,7 @@
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
@@ -7936,13 +7936,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651776</v>
+        <v>651977</v>
       </c>
       <c r="R61" t="n">
-        <v>6673944</v>
+        <v>6673906</v>
       </c>
       <c r="S61" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8008,10 +8008,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301075</v>
+        <v>122301027</v>
       </c>
       <c r="B62" t="n">
-        <v>100503</v>
+        <v>57753</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8024,27 +8024,31 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8052,13 +8056,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651975</v>
+        <v>651983</v>
       </c>
       <c r="R62" t="n">
-        <v>6673928</v>
+        <v>6673930</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8087,7 +8091,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8097,7 +8101,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8124,10 +8128,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301074</v>
+        <v>122301066</v>
       </c>
       <c r="B63" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8168,10 +8172,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>651855</v>
+        <v>652079</v>
       </c>
       <c r="R63" t="n">
-        <v>6673907</v>
+        <v>6673929</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8203,7 +8207,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8213,7 +8217,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8240,10 +8244,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301079</v>
+        <v>122301081</v>
       </c>
       <c r="B64" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8284,10 +8288,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>652014</v>
+        <v>652036</v>
       </c>
       <c r="R64" t="n">
-        <v>6673954</v>
+        <v>6673988</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8319,7 +8323,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8329,7 +8333,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8356,10 +8360,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301026</v>
+        <v>122301063</v>
       </c>
       <c r="B65" t="n">
-        <v>57536</v>
+        <v>100506</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8368,39 +8372,31 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -8408,13 +8404,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651977</v>
+        <v>651949</v>
       </c>
       <c r="R65" t="n">
-        <v>6673906</v>
+        <v>6673910</v>
       </c>
       <c r="S65" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8443,7 +8439,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8453,7 +8449,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8480,10 +8476,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301050</v>
+        <v>122301080</v>
       </c>
       <c r="B66" t="n">
-        <v>98237</v>
+        <v>100506</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8492,37 +8488,29 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
@@ -8532,10 +8520,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>651948</v>
+        <v>652011</v>
       </c>
       <c r="R66" t="n">
-        <v>6673906</v>
+        <v>6673969</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8567,7 +8555,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8577,7 +8565,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8604,10 +8592,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301067</v>
+        <v>122301073</v>
       </c>
       <c r="B67" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8648,10 +8636,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>652040</v>
+        <v>651817</v>
       </c>
       <c r="R67" t="n">
-        <v>6673920</v>
+        <v>6673939</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8683,7 +8671,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8693,7 +8681,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8720,10 +8708,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301081</v>
+        <v>122301025</v>
       </c>
       <c r="B68" t="n">
-        <v>100503</v>
+        <v>57536</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8732,45 +8720,53 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>652036</v>
+        <v>651941</v>
       </c>
       <c r="R68" t="n">
-        <v>6673988</v>
+        <v>6674093</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8799,7 +8795,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8809,7 +8805,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8836,10 +8832,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301065</v>
+        <v>122301017</v>
       </c>
       <c r="B69" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8848,31 +8844,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8880,10 +8884,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>652034</v>
+        <v>651776</v>
       </c>
       <c r="R69" t="n">
-        <v>6673906</v>
+        <v>6673944</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8915,7 +8919,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8925,7 +8929,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8952,10 +8956,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301073</v>
+        <v>122301015</v>
       </c>
       <c r="B70" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8964,31 +8968,39 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8996,10 +9008,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651817</v>
+        <v>651777</v>
       </c>
       <c r="R70" t="n">
-        <v>6673939</v>
+        <v>6673975</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -9031,7 +9043,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9041,7 +9053,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9068,10 +9080,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301025</v>
+        <v>122301079</v>
       </c>
       <c r="B71" t="n">
-        <v>57536</v>
+        <v>100506</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9080,53 +9092,45 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651941</v>
+        <v>652014</v>
       </c>
       <c r="R71" t="n">
-        <v>6674093</v>
+        <v>6673954</v>
       </c>
       <c r="S71" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9155,7 +9159,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9165,7 +9169,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9192,10 +9196,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301027</v>
+        <v>122301050</v>
       </c>
       <c r="B72" t="n">
-        <v>57753</v>
+        <v>98240</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9204,35 +9208,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9240,13 +9248,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651983</v>
+        <v>651948</v>
       </c>
       <c r="R72" t="n">
-        <v>6673930</v>
+        <v>6673906</v>
       </c>
       <c r="S72" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9275,7 +9283,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9285,7 +9293,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9312,10 +9320,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301066</v>
+        <v>122301065</v>
       </c>
       <c r="B73" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9356,10 +9364,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>652079</v>
+        <v>652034</v>
       </c>
       <c r="R73" t="n">
-        <v>6673929</v>
+        <v>6673906</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9391,7 +9399,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9401,7 +9409,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9428,10 +9436,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301080</v>
+        <v>122301013</v>
       </c>
       <c r="B74" t="n">
-        <v>100503</v>
+        <v>57399</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9440,31 +9448,39 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9472,10 +9488,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>652011</v>
+        <v>651745</v>
       </c>
       <c r="R74" t="n">
-        <v>6673969</v>
+        <v>6673922</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9507,7 +9523,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9517,7 +9533,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9544,10 +9560,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301013</v>
+        <v>122301067</v>
       </c>
       <c r="B75" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9556,39 +9572,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9596,10 +9604,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651745</v>
+        <v>652040</v>
       </c>
       <c r="R75" t="n">
-        <v>6673922</v>
+        <v>6673920</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9631,7 +9639,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9641,7 +9649,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9668,10 +9676,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301063</v>
+        <v>122301074</v>
       </c>
       <c r="B76" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9712,10 +9720,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651949</v>
+        <v>651855</v>
       </c>
       <c r="R76" t="n">
-        <v>6673910</v>
+        <v>6673907</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9747,7 +9755,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9757,7 +9765,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9784,10 +9792,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301015</v>
+        <v>122301075</v>
       </c>
       <c r="B77" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9796,39 +9804,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651777</v>
+        <v>651975</v>
       </c>
       <c r="R77" t="n">
-        <v>6673975</v>
+        <v>6673928</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9911,7 +9911,7 @@
         <v>122260107</v>
       </c>
       <c r="B78" t="n">
-        <v>95784</v>
+        <v>95786</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122301001</v>
+        <v>122301037</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>91230</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651873</v>
+        <v>651917</v>
       </c>
       <c r="R2" t="n">
-        <v>6673779</v>
+        <v>6673853</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +748,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +758,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122301062</v>
+        <v>122300995</v>
       </c>
       <c r="B3" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,39 +797,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651973</v>
+        <v>651899</v>
       </c>
       <c r="R3" t="n">
-        <v>6673897</v>
+        <v>6673777</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -886,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122301053</v>
+        <v>122301056</v>
       </c>
       <c r="B4" t="n">
         <v>98240</v>
@@ -958,7 +944,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -975,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651986</v>
+        <v>651930</v>
       </c>
       <c r="R4" t="n">
-        <v>6673841</v>
+        <v>6673898</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1010,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,12 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122301019</v>
+        <v>122301062</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,39 +1045,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1104,10 +1085,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>652004</v>
+        <v>651973</v>
       </c>
       <c r="R5" t="n">
-        <v>6673869</v>
+        <v>6673897</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1139,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1149,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,7 +1157,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122301078</v>
+        <v>122301064</v>
       </c>
       <c r="B6" t="n">
         <v>100506</v>
@@ -1220,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>652006</v>
+        <v>651993</v>
       </c>
       <c r="R6" t="n">
-        <v>6673876</v>
+        <v>6673896</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1255,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122300993</v>
+        <v>122301078</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1304,39 +1285,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1344,13 +1317,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651962</v>
+        <v>652006</v>
       </c>
       <c r="R7" t="n">
-        <v>6673882</v>
+        <v>6673876</v>
       </c>
       <c r="S7" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1379,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1389,12 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122301071</v>
+        <v>122300993</v>
       </c>
       <c r="B8" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,31 +1401,39 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1465,13 +1441,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651840</v>
+        <v>651962</v>
       </c>
       <c r="R8" t="n">
-        <v>6673881</v>
+        <v>6673882</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1500,7 +1476,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1510,7 +1486,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1537,10 +1518,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122301056</v>
+        <v>122301036</v>
       </c>
       <c r="B9" t="n">
-        <v>98240</v>
+        <v>90833</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1549,39 +1530,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1589,10 +1561,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651930</v>
+        <v>652047</v>
       </c>
       <c r="R9" t="n">
-        <v>6673898</v>
+        <v>6673893</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1624,7 +1596,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1634,7 +1606,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,7 +1633,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122301021</v>
+        <v>122300991</v>
       </c>
       <c r="B10" t="n">
         <v>57399</v>
@@ -1709,14 +1681,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>652056</v>
+        <v>651958</v>
       </c>
       <c r="R10" t="n">
-        <v>6673872</v>
+        <v>6673868</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1748,7 +1720,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1758,7 +1730,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1785,10 +1757,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301060</v>
+        <v>122301020</v>
       </c>
       <c r="B11" t="n">
-        <v>98240</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1797,39 +1769,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1837,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>652000</v>
+        <v>652017</v>
       </c>
       <c r="R11" t="n">
-        <v>6673848</v>
+        <v>6673872</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1872,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1882,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1909,10 +1881,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301006</v>
+        <v>122301060</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1921,39 +1893,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1961,10 +1933,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651860</v>
+        <v>652000</v>
       </c>
       <c r="R12" t="n">
-        <v>6673862</v>
+        <v>6673848</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1996,7 +1968,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2006,7 +1978,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2033,7 +2005,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122300995</v>
+        <v>122300994</v>
       </c>
       <c r="B13" t="n">
         <v>57399</v>
@@ -2085,10 +2057,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651899</v>
+        <v>651915</v>
       </c>
       <c r="R13" t="n">
-        <v>6673777</v>
+        <v>6673888</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2120,7 +2092,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2130,7 +2102,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2157,10 +2129,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301020</v>
+        <v>122301071</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2169,39 +2141,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2209,10 +2173,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>652017</v>
+        <v>651840</v>
       </c>
       <c r="R14" t="n">
-        <v>6673872</v>
+        <v>6673881</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2244,7 +2208,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2254,7 +2218,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2281,10 +2245,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122300994</v>
+        <v>122301077</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2293,39 +2257,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2333,10 +2289,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651915</v>
+        <v>651993</v>
       </c>
       <c r="R15" t="n">
-        <v>6673888</v>
+        <v>6673867</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2368,7 +2324,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2378,7 +2334,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2405,10 +2361,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301058</v>
+        <v>122301068</v>
       </c>
       <c r="B16" t="n">
-        <v>98240</v>
+        <v>100506</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2417,50 +2373,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651981</v>
+        <v>651906</v>
       </c>
       <c r="R16" t="n">
-        <v>6673859</v>
+        <v>6673752</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2492,7 +2440,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2502,7 +2450,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2529,10 +2477,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301068</v>
+        <v>122301019</v>
       </c>
       <c r="B17" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2541,42 +2489,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651906</v>
+        <v>652004</v>
       </c>
       <c r="R17" t="n">
-        <v>6673752</v>
+        <v>6673869</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2608,7 +2564,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2618,7 +2574,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2645,10 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122300997</v>
+        <v>122301058</v>
       </c>
       <c r="B18" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2657,50 +2613,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651883</v>
+        <v>651981</v>
       </c>
       <c r="R18" t="n">
-        <v>6673732</v>
+        <v>6673859</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2732,7 +2688,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2742,7 +2698,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2769,7 +2725,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122300999</v>
+        <v>122301006</v>
       </c>
       <c r="B19" t="n">
         <v>57399</v>
@@ -2821,10 +2777,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651879</v>
+        <v>651860</v>
       </c>
       <c r="R19" t="n">
-        <v>6673776</v>
+        <v>6673862</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2856,7 +2812,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2866,7 +2822,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2893,10 +2849,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122301037</v>
+        <v>122300999</v>
       </c>
       <c r="B20" t="n">
-        <v>91230</v>
+        <v>57399</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2909,21 +2865,35 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040162</v>
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2931,10 +2901,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651917</v>
+        <v>651879</v>
       </c>
       <c r="R20" t="n">
-        <v>6673853</v>
+        <v>6673776</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2966,7 +2936,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2976,7 +2946,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3003,7 +2973,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122300991</v>
+        <v>122301007</v>
       </c>
       <c r="B21" t="n">
         <v>57399</v>
@@ -3045,7 +3015,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3055,10 +3025,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651958</v>
+        <v>651778</v>
       </c>
       <c r="R21" t="n">
-        <v>6673868</v>
+        <v>6673895</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3090,7 +3060,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3100,7 +3070,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3127,10 +3097,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122301064</v>
+        <v>122301004</v>
       </c>
       <c r="B22" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3139,31 +3109,39 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3171,10 +3149,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651993</v>
+        <v>651888</v>
       </c>
       <c r="R22" t="n">
-        <v>6673896</v>
+        <v>6673877</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3206,7 +3184,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3216,7 +3194,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3243,10 +3221,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122300988</v>
+        <v>122301053</v>
       </c>
       <c r="B23" t="n">
-        <v>5193</v>
+        <v>98240</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3255,36 +3233,39 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3292,10 +3273,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651926</v>
+        <v>651986</v>
       </c>
       <c r="R23" t="n">
-        <v>6673844</v>
+        <v>6673841</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3327,7 +3308,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3337,7 +3318,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3364,10 +3350,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122301031</v>
+        <v>122300988</v>
       </c>
       <c r="B24" t="n">
-        <v>74696</v>
+        <v>5193</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3380,26 +3366,32 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3407,10 +3399,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651805</v>
+        <v>651926</v>
       </c>
       <c r="R24" t="n">
-        <v>6673899</v>
+        <v>6673844</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3442,7 +3434,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3452,7 +3444,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3479,10 +3471,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301004</v>
+        <v>122301031</v>
       </c>
       <c r="B25" t="n">
-        <v>57399</v>
+        <v>74696</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3491,39 +3483,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3531,10 +3514,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651888</v>
+        <v>651805</v>
       </c>
       <c r="R25" t="n">
-        <v>6673877</v>
+        <v>6673899</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3566,7 +3549,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3576,7 +3559,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3603,10 +3586,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301077</v>
+        <v>122301021</v>
       </c>
       <c r="B26" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3615,42 +3598,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651993</v>
+        <v>652056</v>
       </c>
       <c r="R26" t="n">
-        <v>6673867</v>
+        <v>6673872</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3682,7 +3673,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3692,7 +3683,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3719,7 +3710,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301007</v>
+        <v>122301001</v>
       </c>
       <c r="B27" t="n">
         <v>57399</v>
@@ -3771,10 +3762,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>651778</v>
+        <v>651873</v>
       </c>
       <c r="R27" t="n">
-        <v>6673895</v>
+        <v>6673779</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3806,7 +3797,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3816,7 +3807,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3843,10 +3834,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122301036</v>
+        <v>122300997</v>
       </c>
       <c r="B28" t="n">
-        <v>90833</v>
+        <v>57399</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3859,37 +3850,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>652047</v>
+        <v>651883</v>
       </c>
       <c r="R28" t="n">
-        <v>6673893</v>
+        <v>6673732</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,7 +3958,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122260117</v>
+        <v>122260125</v>
       </c>
       <c r="B29" t="n">
         <v>100506</v>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651906</v>
+        <v>651973</v>
       </c>
       <c r="R29" t="n">
-        <v>6674571</v>
+        <v>6674332</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4074,10 +4074,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122260115</v>
+        <v>122260068</v>
       </c>
       <c r="B30" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4086,31 +4086,39 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4118,10 +4126,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651891</v>
+        <v>651928</v>
       </c>
       <c r="R30" t="n">
-        <v>6674645</v>
+        <v>6674457</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4153,7 +4161,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4163,7 +4171,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4190,10 +4198,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260100</v>
+        <v>122260084</v>
       </c>
       <c r="B31" t="n">
-        <v>90833</v>
+        <v>57536</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4206,26 +4214,35 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4233,13 +4250,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>652034</v>
+        <v>651900</v>
       </c>
       <c r="R31" t="n">
-        <v>6674236</v>
+        <v>6674551</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4268,7 +4285,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4278,7 +4295,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4289,21 +4306,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4320,7 +4322,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260121</v>
+        <v>122260117</v>
       </c>
       <c r="B32" t="n">
         <v>100506</v>
@@ -4364,10 +4366,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651955</v>
+        <v>651906</v>
       </c>
       <c r="R32" t="n">
-        <v>6674222</v>
+        <v>6674571</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4399,7 +4401,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4409,7 +4411,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4436,10 +4438,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260126</v>
+        <v>122260111</v>
       </c>
       <c r="B33" t="n">
-        <v>100506</v>
+        <v>98240</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4448,29 +4450,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -4480,10 +4490,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651941</v>
+        <v>651949</v>
       </c>
       <c r="R33" t="n">
-        <v>6674469</v>
+        <v>6674415</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4515,7 +4525,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4525,7 +4535,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4552,10 +4562,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260070</v>
+        <v>122260113</v>
       </c>
       <c r="B34" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4564,39 +4574,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4604,10 +4614,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651967</v>
+        <v>651906</v>
       </c>
       <c r="R34" t="n">
-        <v>6674433</v>
+        <v>6674392</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4639,7 +4649,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4649,7 +4659,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4676,10 +4686,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122260085</v>
+        <v>122260074</v>
       </c>
       <c r="B35" t="n">
-        <v>57753</v>
+        <v>57399</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4688,20 +4698,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4728,13 +4738,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651895</v>
+        <v>651923</v>
       </c>
       <c r="R35" t="n">
-        <v>6674630</v>
+        <v>6674436</v>
       </c>
       <c r="S35" t="n">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4763,7 +4773,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4773,7 +4783,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Hörd i norr.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4800,7 +4815,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122260066</v>
+        <v>122260080</v>
       </c>
       <c r="B36" t="n">
         <v>57399</v>
@@ -4852,10 +4867,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>651934</v>
+        <v>652019</v>
       </c>
       <c r="R36" t="n">
-        <v>6674510</v>
+        <v>6674239</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4887,7 +4902,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4897,7 +4912,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4924,10 +4939,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122260096</v>
+        <v>122260110</v>
       </c>
       <c r="B37" t="n">
-        <v>80613</v>
+        <v>98240</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4936,30 +4951,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4967,10 +4991,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651930</v>
+        <v>651949</v>
       </c>
       <c r="R37" t="n">
-        <v>6674592</v>
+        <v>6674420</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5002,7 +5026,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5012,7 +5036,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5039,10 +5068,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122260118</v>
+        <v>122260077</v>
       </c>
       <c r="B38" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5051,31 +5080,39 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5083,10 +5120,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651893</v>
+        <v>651964</v>
       </c>
       <c r="R38" t="n">
-        <v>6674508</v>
+        <v>6674220</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5118,7 +5155,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5128,7 +5165,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5155,10 +5192,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260061</v>
+        <v>122260121</v>
       </c>
       <c r="B39" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5167,39 +5204,31 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5207,10 +5236,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651886</v>
+        <v>651955</v>
       </c>
       <c r="R39" t="n">
-        <v>6674654</v>
+        <v>6674222</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5242,7 +5271,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5252,7 +5281,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5279,10 +5308,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260080</v>
+        <v>122260115</v>
       </c>
       <c r="B40" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5291,39 +5320,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5331,10 +5352,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>652019</v>
+        <v>651891</v>
       </c>
       <c r="R40" t="n">
-        <v>6674239</v>
+        <v>6674645</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5366,7 +5387,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5376,7 +5397,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5403,10 +5424,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260103</v>
+        <v>122260075</v>
       </c>
       <c r="B41" t="n">
-        <v>91278</v>
+        <v>57399</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5415,30 +5436,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5446,10 +5476,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651855</v>
+        <v>651900</v>
       </c>
       <c r="R41" t="n">
-        <v>6674655</v>
+        <v>6674390</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5481,7 +5511,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5491,12 +5521,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På klibbtickelåga.</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5507,21 +5532,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5538,7 +5548,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122260064</v>
+        <v>122260076</v>
       </c>
       <c r="B42" t="n">
         <v>57399</v>
@@ -5590,10 +5600,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651845</v>
+        <v>651949</v>
       </c>
       <c r="R42" t="n">
-        <v>6674626</v>
+        <v>6674279</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5625,7 +5635,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5635,7 +5645,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5662,7 +5672,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260071</v>
+        <v>122260072</v>
       </c>
       <c r="B43" t="n">
         <v>57399</v>
@@ -5714,10 +5724,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651930</v>
+        <v>651927</v>
       </c>
       <c r="R43" t="n">
-        <v>6674444</v>
+        <v>6674447</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5749,7 +5759,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5759,7 +5769,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5786,10 +5796,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260120</v>
+        <v>122260100</v>
       </c>
       <c r="B44" t="n">
-        <v>100506</v>
+        <v>90833</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5798,31 +5808,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5830,10 +5839,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>651967</v>
+        <v>652034</v>
       </c>
       <c r="R44" t="n">
-        <v>6674316</v>
+        <v>6674236</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5865,7 +5874,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5875,7 +5884,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5886,6 +5895,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5902,10 +5926,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122260077</v>
+        <v>122260114</v>
       </c>
       <c r="B45" t="n">
-        <v>57399</v>
+        <v>98240</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5914,39 +5938,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5954,7 +5978,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>651964</v>
+        <v>652010</v>
       </c>
       <c r="R45" t="n">
         <v>6674220</v>
@@ -5989,7 +6013,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5999,7 +6023,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6026,10 +6050,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122260063</v>
+        <v>122260103</v>
       </c>
       <c r="B46" t="n">
-        <v>57399</v>
+        <v>91278</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6038,39 +6062,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6078,10 +6093,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651872</v>
+        <v>651855</v>
       </c>
       <c r="R46" t="n">
-        <v>6674674</v>
+        <v>6674655</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6113,7 +6128,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6123,7 +6138,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På klibbtickelåga.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6134,6 +6154,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6150,7 +6185,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260072</v>
+        <v>122260064</v>
       </c>
       <c r="B47" t="n">
         <v>57399</v>
@@ -6192,7 +6227,7 @@
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -6202,10 +6237,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651927</v>
+        <v>651845</v>
       </c>
       <c r="R47" t="n">
-        <v>6674447</v>
+        <v>6674626</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6237,7 +6272,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6247,7 +6282,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6274,10 +6309,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260076</v>
+        <v>122260118</v>
       </c>
       <c r="B48" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6286,39 +6321,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6326,10 +6353,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>651949</v>
+        <v>651893</v>
       </c>
       <c r="R48" t="n">
-        <v>6674279</v>
+        <v>6674508</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6361,7 +6388,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6371,7 +6398,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6398,10 +6425,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260084</v>
+        <v>122260126</v>
       </c>
       <c r="B49" t="n">
-        <v>57536</v>
+        <v>100506</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6410,39 +6437,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6450,13 +6469,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651900</v>
+        <v>651941</v>
       </c>
       <c r="R49" t="n">
-        <v>6674551</v>
+        <v>6674469</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6485,7 +6504,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6495,7 +6514,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6522,10 +6541,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260068</v>
+        <v>122260116</v>
       </c>
       <c r="B50" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6534,39 +6553,31 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6574,10 +6585,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651928</v>
+        <v>651859</v>
       </c>
       <c r="R50" t="n">
-        <v>6674457</v>
+        <v>6674654</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6609,7 +6620,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6619,7 +6630,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6646,10 +6657,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122260075</v>
+        <v>122260096</v>
       </c>
       <c r="B51" t="n">
-        <v>57399</v>
+        <v>80613</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6662,35 +6673,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6698,10 +6700,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651900</v>
+        <v>651930</v>
       </c>
       <c r="R51" t="n">
-        <v>6674390</v>
+        <v>6674592</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6733,7 +6735,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6743,7 +6745,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6770,10 +6772,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260113</v>
+        <v>122260070</v>
       </c>
       <c r="B52" t="n">
-        <v>98240</v>
+        <v>57399</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6782,39 +6784,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6822,10 +6824,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651906</v>
+        <v>651967</v>
       </c>
       <c r="R52" t="n">
-        <v>6674392</v>
+        <v>6674433</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6857,7 +6859,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6867,7 +6869,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6894,10 +6896,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260125</v>
+        <v>122260061</v>
       </c>
       <c r="B53" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6906,31 +6908,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6938,10 +6948,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651973</v>
+        <v>651886</v>
       </c>
       <c r="R53" t="n">
-        <v>6674332</v>
+        <v>6674654</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6973,7 +6983,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6983,7 +6993,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7010,10 +7020,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260114</v>
+        <v>122260066</v>
       </c>
       <c r="B54" t="n">
-        <v>98240</v>
+        <v>57399</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7022,39 +7032,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7062,10 +7072,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>652010</v>
+        <v>651934</v>
       </c>
       <c r="R54" t="n">
-        <v>6674220</v>
+        <v>6674510</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7097,7 +7107,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7107,7 +7117,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7134,10 +7144,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122260110</v>
+        <v>122260119</v>
       </c>
       <c r="B55" t="n">
-        <v>98240</v>
+        <v>100506</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7146,37 +7156,29 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -7186,10 +7188,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651949</v>
+        <v>651950</v>
       </c>
       <c r="R55" t="n">
-        <v>6674420</v>
+        <v>6674465</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7221,7 +7223,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7231,12 +7233,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7263,10 +7260,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260119</v>
+        <v>122260071</v>
       </c>
       <c r="B56" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7275,31 +7272,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7307,10 +7312,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>651950</v>
+        <v>651930</v>
       </c>
       <c r="R56" t="n">
-        <v>6674465</v>
+        <v>6674444</v>
       </c>
       <c r="S56" t="n">
         <v>4</v>
@@ -7342,7 +7347,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7352,7 +7357,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7379,10 +7384,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260111</v>
+        <v>122260063</v>
       </c>
       <c r="B57" t="n">
-        <v>98240</v>
+        <v>57399</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7391,39 +7396,39 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7431,10 +7436,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651949</v>
+        <v>651872</v>
       </c>
       <c r="R57" t="n">
-        <v>6674415</v>
+        <v>6674674</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7466,7 +7471,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7476,7 +7481,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7503,10 +7508,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260058</v>
+        <v>122260085</v>
       </c>
       <c r="B58" t="n">
-        <v>5193</v>
+        <v>57753</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7519,16 +7524,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105930</v>
+        <v>103015</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7536,13 +7541,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7552,13 +7560,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>652031</v>
+        <v>651895</v>
       </c>
       <c r="R58" t="n">
-        <v>6674226</v>
+        <v>6674630</v>
       </c>
       <c r="S58" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7587,7 +7595,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7597,7 +7605,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7608,21 +7616,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7639,10 +7632,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260074</v>
+        <v>122260120</v>
       </c>
       <c r="B59" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7651,39 +7644,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7691,13 +7676,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651923</v>
+        <v>651967</v>
       </c>
       <c r="R59" t="n">
-        <v>6674436</v>
+        <v>6674316</v>
       </c>
       <c r="S59" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7726,7 +7711,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7736,12 +7721,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Hörd i norr.</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7768,10 +7748,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260116</v>
+        <v>122260058</v>
       </c>
       <c r="B60" t="n">
-        <v>100506</v>
+        <v>5193</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7784,27 +7764,32 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7812,10 +7797,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>651859</v>
+        <v>652031</v>
       </c>
       <c r="R60" t="n">
-        <v>6674654</v>
+        <v>6674226</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7847,7 +7832,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7857,7 +7842,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7868,6 +7853,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7884,10 +7884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301026</v>
+        <v>122301074</v>
       </c>
       <c r="B61" t="n">
-        <v>57536</v>
+        <v>100506</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7896,39 +7896,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7936,13 +7928,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651977</v>
+        <v>651855</v>
       </c>
       <c r="R61" t="n">
-        <v>6673906</v>
+        <v>6673907</v>
       </c>
       <c r="S61" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7971,7 +7963,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7981,7 +7973,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8008,10 +8000,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301027</v>
+        <v>122301050</v>
       </c>
       <c r="B62" t="n">
-        <v>57753</v>
+        <v>98240</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8020,35 +8012,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8056,13 +8052,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651983</v>
+        <v>651948</v>
       </c>
       <c r="R62" t="n">
-        <v>6673930</v>
+        <v>6673906</v>
       </c>
       <c r="S62" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8091,7 +8087,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8101,7 +8097,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8128,7 +8124,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301066</v>
+        <v>122301073</v>
       </c>
       <c r="B63" t="n">
         <v>100506</v>
@@ -8172,10 +8168,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>652079</v>
+        <v>651817</v>
       </c>
       <c r="R63" t="n">
-        <v>6673929</v>
+        <v>6673939</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8207,7 +8203,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8217,7 +8213,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8244,7 +8240,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301081</v>
+        <v>122301079</v>
       </c>
       <c r="B64" t="n">
         <v>100506</v>
@@ -8288,10 +8284,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>652036</v>
+        <v>652014</v>
       </c>
       <c r="R64" t="n">
-        <v>6673988</v>
+        <v>6673954</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8323,7 +8319,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8333,7 +8329,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8360,10 +8356,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301063</v>
+        <v>122301025</v>
       </c>
       <c r="B65" t="n">
-        <v>100506</v>
+        <v>57536</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8372,45 +8368,53 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651949</v>
+        <v>651941</v>
       </c>
       <c r="R65" t="n">
-        <v>6673910</v>
+        <v>6674093</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8439,7 +8443,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8449,7 +8453,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8476,7 +8480,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301080</v>
+        <v>122301067</v>
       </c>
       <c r="B66" t="n">
         <v>100506</v>
@@ -8520,10 +8524,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>652011</v>
+        <v>652040</v>
       </c>
       <c r="R66" t="n">
-        <v>6673969</v>
+        <v>6673920</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8555,7 +8559,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8565,7 +8569,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8592,7 +8596,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301073</v>
+        <v>122301063</v>
       </c>
       <c r="B67" t="n">
         <v>100506</v>
@@ -8636,10 +8640,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>651817</v>
+        <v>651949</v>
       </c>
       <c r="R67" t="n">
-        <v>6673939</v>
+        <v>6673910</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8671,7 +8675,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8681,7 +8685,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8708,10 +8712,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301025</v>
+        <v>122301017</v>
       </c>
       <c r="B68" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8724,49 +8728,49 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651941</v>
+        <v>651776</v>
       </c>
       <c r="R68" t="n">
-        <v>6674093</v>
+        <v>6673944</v>
       </c>
       <c r="S68" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8795,7 +8799,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8805,7 +8809,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8832,10 +8836,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301017</v>
+        <v>122301080</v>
       </c>
       <c r="B69" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8844,39 +8848,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8884,10 +8880,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651776</v>
+        <v>652011</v>
       </c>
       <c r="R69" t="n">
-        <v>6673944</v>
+        <v>6673969</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8919,7 +8915,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8929,7 +8925,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8956,10 +8952,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301015</v>
+        <v>122301027</v>
       </c>
       <c r="B70" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8968,20 +8964,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8991,16 +8987,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9008,13 +9000,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651777</v>
+        <v>651983</v>
       </c>
       <c r="R70" t="n">
-        <v>6673975</v>
+        <v>6673930</v>
       </c>
       <c r="S70" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9043,7 +9035,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9053,7 +9045,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9080,7 +9072,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301079</v>
+        <v>122301066</v>
       </c>
       <c r="B71" t="n">
         <v>100506</v>
@@ -9124,10 +9116,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>652014</v>
+        <v>652079</v>
       </c>
       <c r="R71" t="n">
-        <v>6673954</v>
+        <v>6673929</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9159,7 +9151,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9169,7 +9161,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9196,10 +9188,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301050</v>
+        <v>122301065</v>
       </c>
       <c r="B72" t="n">
-        <v>98240</v>
+        <v>100506</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9208,37 +9200,29 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
@@ -9248,7 +9232,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651948</v>
+        <v>652034</v>
       </c>
       <c r="R72" t="n">
         <v>6673906</v>
@@ -9283,7 +9267,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9293,7 +9277,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9320,7 +9304,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301065</v>
+        <v>122301081</v>
       </c>
       <c r="B73" t="n">
         <v>100506</v>
@@ -9364,10 +9348,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>652034</v>
+        <v>652036</v>
       </c>
       <c r="R73" t="n">
-        <v>6673906</v>
+        <v>6673988</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9399,7 +9383,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9409,7 +9393,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9436,10 +9420,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301013</v>
+        <v>122301075</v>
       </c>
       <c r="B74" t="n">
-        <v>57399</v>
+        <v>100506</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9448,39 +9432,31 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9488,10 +9464,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>651745</v>
+        <v>651975</v>
       </c>
       <c r="R74" t="n">
-        <v>6673922</v>
+        <v>6673928</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9523,7 +9499,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9533,7 +9509,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9560,10 +9536,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301067</v>
+        <v>122301013</v>
       </c>
       <c r="B75" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9572,31 +9548,39 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9604,10 +9588,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>652040</v>
+        <v>651745</v>
       </c>
       <c r="R75" t="n">
-        <v>6673920</v>
+        <v>6673922</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9639,7 +9623,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9649,7 +9633,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9676,10 +9660,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301074</v>
+        <v>122301015</v>
       </c>
       <c r="B76" t="n">
-        <v>100506</v>
+        <v>57399</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9688,31 +9672,39 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9720,10 +9712,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651855</v>
+        <v>651777</v>
       </c>
       <c r="R76" t="n">
-        <v>6673907</v>
+        <v>6673975</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9755,7 +9747,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9765,7 +9757,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9792,10 +9784,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301075</v>
+        <v>122301026</v>
       </c>
       <c r="B77" t="n">
-        <v>100506</v>
+        <v>57536</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9804,31 +9796,39 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9836,13 +9836,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651975</v>
+        <v>651977</v>
       </c>
       <c r="R77" t="n">
-        <v>6673928</v>
+        <v>6673906</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122301037</v>
+        <v>122301006</v>
       </c>
       <c r="B2" t="n">
-        <v>91230</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6040162</v>
+        <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651917</v>
+        <v>651860</v>
       </c>
       <c r="R2" t="n">
-        <v>6673853</v>
+        <v>6673862</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -748,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122300995</v>
+        <v>122300991</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,7 +841,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651899</v>
+        <v>651958</v>
       </c>
       <c r="R3" t="n">
-        <v>6673777</v>
+        <v>6673868</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -872,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122301056</v>
+        <v>122301058</v>
       </c>
       <c r="B4" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,12 +958,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -961,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651930</v>
+        <v>651981</v>
       </c>
       <c r="R4" t="n">
-        <v>6673898</v>
+        <v>6673859</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -996,7 +1010,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +1020,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,10 +1047,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122301062</v>
+        <v>122300993</v>
       </c>
       <c r="B5" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,39 +1059,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1085,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651973</v>
+        <v>651962</v>
       </c>
       <c r="R5" t="n">
-        <v>6673897</v>
+        <v>6673882</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1144,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,10 +1176,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122301064</v>
+        <v>122301062</v>
       </c>
       <c r="B6" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,8 +1209,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1201,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651993</v>
+        <v>651973</v>
       </c>
       <c r="R6" t="n">
-        <v>6673896</v>
+        <v>6673897</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1236,7 +1263,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1273,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122301078</v>
+        <v>122301031</v>
       </c>
       <c r="B7" t="n">
-        <v>100506</v>
+        <v>74697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,27 +1316,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1317,10 +1343,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>652006</v>
+        <v>651805</v>
       </c>
       <c r="R7" t="n">
-        <v>6673876</v>
+        <v>6673899</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1352,7 +1378,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1388,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122300993</v>
+        <v>122300999</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1431,7 +1457,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1441,13 +1467,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651962</v>
+        <v>651879</v>
       </c>
       <c r="R8" t="n">
-        <v>6673882</v>
+        <v>6673776</v>
       </c>
       <c r="S8" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,7 +1502,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,12 +1512,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122301036</v>
+        <v>122301001</v>
       </c>
       <c r="B9" t="n">
-        <v>90833</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1534,26 +1555,35 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1561,10 +1591,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>652047</v>
+        <v>651873</v>
       </c>
       <c r="R9" t="n">
-        <v>6673893</v>
+        <v>6673779</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1596,7 +1626,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1606,7 +1636,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122300991</v>
+        <v>122301064</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,39 +1675,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1685,10 +1707,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651958</v>
+        <v>651993</v>
       </c>
       <c r="R10" t="n">
-        <v>6673868</v>
+        <v>6673896</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1720,7 +1742,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1730,7 +1752,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,10 +1779,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301020</v>
+        <v>122301077</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1769,39 +1791,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1809,10 +1823,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>652017</v>
+        <v>651993</v>
       </c>
       <c r="R11" t="n">
-        <v>6673872</v>
+        <v>6673867</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1844,7 +1858,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1868,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,10 +1895,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301060</v>
+        <v>122301068</v>
       </c>
       <c r="B12" t="n">
-        <v>98240</v>
+        <v>100507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,50 +1907,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>652000</v>
+        <v>651906</v>
       </c>
       <c r="R12" t="n">
-        <v>6673848</v>
+        <v>6673752</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1968,7 +1974,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1978,7 +1984,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2005,10 +2011,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122300994</v>
+        <v>122301053</v>
       </c>
       <c r="B13" t="n">
-        <v>57399</v>
+        <v>98241</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,39 +2023,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2057,10 +2063,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651915</v>
+        <v>651986</v>
       </c>
       <c r="R13" t="n">
-        <v>6673888</v>
+        <v>6673841</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2092,7 +2098,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2102,7 +2108,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2129,10 +2140,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301071</v>
+        <v>122301021</v>
       </c>
       <c r="B14" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2141,42 +2152,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651840</v>
+        <v>652056</v>
       </c>
       <c r="R14" t="n">
-        <v>6673881</v>
+        <v>6673872</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2208,7 +2227,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2218,7 +2237,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2245,10 +2264,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122301077</v>
+        <v>122301020</v>
       </c>
       <c r="B15" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2257,31 +2276,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2289,10 +2316,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651993</v>
+        <v>652017</v>
       </c>
       <c r="R15" t="n">
-        <v>6673867</v>
+        <v>6673872</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2324,7 +2351,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2334,7 +2361,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2361,10 +2388,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301068</v>
+        <v>122300995</v>
       </c>
       <c r="B16" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2373,42 +2400,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651906</v>
+        <v>651899</v>
       </c>
       <c r="R16" t="n">
-        <v>6673752</v>
+        <v>6673777</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2440,7 +2475,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2450,7 +2485,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2477,10 +2512,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301019</v>
+        <v>122301004</v>
       </c>
       <c r="B17" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2529,10 +2564,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>652004</v>
+        <v>651888</v>
       </c>
       <c r="R17" t="n">
-        <v>6673869</v>
+        <v>6673877</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2564,7 +2599,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2574,7 +2609,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2601,10 +2636,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122301058</v>
+        <v>122300988</v>
       </c>
       <c r="B18" t="n">
-        <v>98240</v>
+        <v>5193</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2613,39 +2648,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2653,10 +2685,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651981</v>
+        <v>651926</v>
       </c>
       <c r="R18" t="n">
-        <v>6673859</v>
+        <v>6673844</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2688,7 +2720,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2698,7 +2730,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2725,10 +2757,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122301006</v>
+        <v>122301036</v>
       </c>
       <c r="B19" t="n">
-        <v>57399</v>
+        <v>90834</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2741,35 +2773,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2777,10 +2800,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651860</v>
+        <v>652047</v>
       </c>
       <c r="R19" t="n">
-        <v>6673862</v>
+        <v>6673893</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2812,7 +2835,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2822,7 +2845,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2849,10 +2872,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122300999</v>
+        <v>122301078</v>
       </c>
       <c r="B20" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2861,39 +2884,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2901,10 +2916,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651879</v>
+        <v>652006</v>
       </c>
       <c r="R20" t="n">
-        <v>6673776</v>
+        <v>6673876</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2936,7 +2951,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2946,7 +2961,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2973,10 +2988,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122301007</v>
+        <v>122301056</v>
       </c>
       <c r="B21" t="n">
-        <v>57399</v>
+        <v>98241</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2985,39 +3000,39 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3025,10 +3040,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651778</v>
+        <v>651930</v>
       </c>
       <c r="R21" t="n">
-        <v>6673895</v>
+        <v>6673898</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3060,7 +3075,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3070,7 +3085,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3097,10 +3112,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122301004</v>
+        <v>122301019</v>
       </c>
       <c r="B22" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3149,10 +3164,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651888</v>
+        <v>652004</v>
       </c>
       <c r="R22" t="n">
-        <v>6673877</v>
+        <v>6673869</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3184,7 +3199,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3194,7 +3209,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3221,10 +3236,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122301053</v>
+        <v>122300997</v>
       </c>
       <c r="B23" t="n">
-        <v>98240</v>
+        <v>57400</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3233,50 +3248,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651986</v>
+        <v>651883</v>
       </c>
       <c r="R23" t="n">
-        <v>6673841</v>
+        <v>6673732</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3308,7 +3323,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3318,12 +3333,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3350,10 +3360,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122300988</v>
+        <v>122301007</v>
       </c>
       <c r="B24" t="n">
-        <v>5193</v>
+        <v>57400</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3362,20 +3372,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3383,13 +3393,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3399,10 +3412,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651926</v>
+        <v>651778</v>
       </c>
       <c r="R24" t="n">
-        <v>6673844</v>
+        <v>6673895</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3434,7 +3447,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3444,7 +3457,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3471,10 +3484,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301031</v>
+        <v>122300994</v>
       </c>
       <c r="B25" t="n">
-        <v>74696</v>
+        <v>57400</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3483,30 +3496,39 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3514,10 +3536,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651805</v>
+        <v>651915</v>
       </c>
       <c r="R25" t="n">
-        <v>6673899</v>
+        <v>6673888</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3549,7 +3571,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3559,7 +3581,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3586,10 +3608,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301021</v>
+        <v>122301037</v>
       </c>
       <c r="B26" t="n">
-        <v>57399</v>
+        <v>91231</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3602,46 +3624,32 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>652056</v>
+        <v>651917</v>
       </c>
       <c r="R26" t="n">
-        <v>6673872</v>
+        <v>6673853</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3673,7 +3681,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3683,7 +3691,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3710,10 +3718,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301001</v>
+        <v>122301060</v>
       </c>
       <c r="B27" t="n">
-        <v>57399</v>
+        <v>98241</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3722,39 +3730,39 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3762,10 +3770,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>651873</v>
+        <v>652000</v>
       </c>
       <c r="R27" t="n">
-        <v>6673779</v>
+        <v>6673848</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3797,7 +3805,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3807,7 +3815,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3834,10 +3842,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122300997</v>
+        <v>122301071</v>
       </c>
       <c r="B28" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3846,50 +3854,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651883</v>
+        <v>651840</v>
       </c>
       <c r="R28" t="n">
-        <v>6673732</v>
+        <v>6673881</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122260125</v>
+        <v>122260076</v>
       </c>
       <c r="B29" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3970,31 +3970,39 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -4002,10 +4010,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>651973</v>
+        <v>651949</v>
       </c>
       <c r="R29" t="n">
-        <v>6674332</v>
+        <v>6674279</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4037,7 +4045,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4047,7 +4055,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4074,10 +4082,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122260068</v>
+        <v>122260085</v>
       </c>
       <c r="B30" t="n">
-        <v>57399</v>
+        <v>57754</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4086,20 +4094,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -4116,7 +4124,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -4126,13 +4134,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>651928</v>
+        <v>651895</v>
       </c>
       <c r="R30" t="n">
-        <v>6674457</v>
+        <v>6674630</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4161,7 +4169,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4171,7 +4179,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4198,10 +4206,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122260084</v>
+        <v>122260110</v>
       </c>
       <c r="B31" t="n">
-        <v>57536</v>
+        <v>98241</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4210,39 +4218,39 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4250,13 +4258,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>651900</v>
+        <v>651949</v>
       </c>
       <c r="R31" t="n">
-        <v>6674551</v>
+        <v>6674420</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4285,7 +4293,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4295,7 +4303,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst. Räknade en och en.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4322,10 +4335,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122260117</v>
+        <v>122260072</v>
       </c>
       <c r="B32" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4334,31 +4347,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4366,10 +4387,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651906</v>
+        <v>651927</v>
       </c>
       <c r="R32" t="n">
-        <v>6674571</v>
+        <v>6674447</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4401,7 +4422,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4411,7 +4432,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4438,10 +4459,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122260111</v>
+        <v>122260114</v>
       </c>
       <c r="B33" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4473,7 +4494,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4490,10 +4511,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651949</v>
+        <v>652010</v>
       </c>
       <c r="R33" t="n">
-        <v>6674415</v>
+        <v>6674220</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4525,7 +4546,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4535,7 +4556,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4562,10 +4583,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122260113</v>
+        <v>122260096</v>
       </c>
       <c r="B34" t="n">
-        <v>98240</v>
+        <v>80614</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4574,39 +4595,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4614,10 +4626,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>651906</v>
+        <v>651930</v>
       </c>
       <c r="R34" t="n">
-        <v>6674392</v>
+        <v>6674592</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4649,7 +4661,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4659,7 +4671,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4686,10 +4698,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122260074</v>
+        <v>122260119</v>
       </c>
       <c r="B35" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4698,39 +4710,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4738,13 +4742,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>651923</v>
+        <v>651950</v>
       </c>
       <c r="R35" t="n">
-        <v>6674436</v>
+        <v>6674465</v>
       </c>
       <c r="S35" t="n">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4773,7 +4777,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4783,12 +4787,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:10</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Hörd i norr.</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4815,10 +4814,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122260080</v>
+        <v>122260063</v>
       </c>
       <c r="B36" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4867,10 +4866,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>652019</v>
+        <v>651872</v>
       </c>
       <c r="R36" t="n">
-        <v>6674239</v>
+        <v>6674674</v>
       </c>
       <c r="S36" t="n">
         <v>4</v>
@@ -4902,7 +4901,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4912,7 +4911,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4939,10 +4938,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122260110</v>
+        <v>122260061</v>
       </c>
       <c r="B37" t="n">
-        <v>98240</v>
+        <v>57400</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4951,39 +4950,39 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4991,10 +4990,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>651949</v>
+        <v>651886</v>
       </c>
       <c r="R37" t="n">
-        <v>6674420</v>
+        <v>6674654</v>
       </c>
       <c r="S37" t="n">
         <v>4</v>
@@ -5026,7 +5025,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5036,12 +5035,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst. Räknade en och en.</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5068,10 +5062,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122260077</v>
+        <v>122260066</v>
       </c>
       <c r="B38" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5110,7 +5104,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5120,10 +5114,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>651964</v>
+        <v>651934</v>
       </c>
       <c r="R38" t="n">
-        <v>6674220</v>
+        <v>6674510</v>
       </c>
       <c r="S38" t="n">
         <v>4</v>
@@ -5155,7 +5149,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5165,7 +5159,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5192,10 +5186,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122260121</v>
+        <v>122260116</v>
       </c>
       <c r="B39" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5236,10 +5230,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>651955</v>
+        <v>651859</v>
       </c>
       <c r="R39" t="n">
-        <v>6674222</v>
+        <v>6674654</v>
       </c>
       <c r="S39" t="n">
         <v>4</v>
@@ -5271,7 +5265,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5281,7 +5275,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5308,10 +5302,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122260115</v>
+        <v>122260118</v>
       </c>
       <c r="B40" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5352,10 +5346,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>651891</v>
+        <v>651893</v>
       </c>
       <c r="R40" t="n">
-        <v>6674645</v>
+        <v>6674508</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
@@ -5387,7 +5381,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5397,7 +5391,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5424,10 +5418,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122260075</v>
+        <v>122260125</v>
       </c>
       <c r="B41" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5436,39 +5430,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5476,10 +5462,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>651900</v>
+        <v>651973</v>
       </c>
       <c r="R41" t="n">
-        <v>6674390</v>
+        <v>6674332</v>
       </c>
       <c r="S41" t="n">
         <v>4</v>
@@ -5511,7 +5497,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5521,7 +5507,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5548,10 +5534,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122260076</v>
+        <v>122260080</v>
       </c>
       <c r="B42" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5590,7 +5576,7 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -5600,10 +5586,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>651949</v>
+        <v>652019</v>
       </c>
       <c r="R42" t="n">
-        <v>6674279</v>
+        <v>6674239</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -5635,7 +5621,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5645,7 +5631,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5672,10 +5658,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122260072</v>
+        <v>122260070</v>
       </c>
       <c r="B43" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5714,7 +5700,7 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -5724,10 +5710,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>651927</v>
+        <v>651967</v>
       </c>
       <c r="R43" t="n">
-        <v>6674447</v>
+        <v>6674433</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5759,7 +5745,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5769,7 +5755,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5796,10 +5782,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122260100</v>
+        <v>122260120</v>
       </c>
       <c r="B44" t="n">
-        <v>90833</v>
+        <v>100507</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5808,30 +5794,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5839,10 +5826,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>652034</v>
+        <v>651967</v>
       </c>
       <c r="R44" t="n">
-        <v>6674236</v>
+        <v>6674316</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5874,7 +5861,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5884,7 +5871,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5895,21 +5882,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5926,10 +5898,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122260114</v>
+        <v>122260074</v>
       </c>
       <c r="B45" t="n">
-        <v>98240</v>
+        <v>57400</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5938,39 +5910,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5978,13 +5950,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>652010</v>
+        <v>651923</v>
       </c>
       <c r="R45" t="n">
-        <v>6674220</v>
+        <v>6674436</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>98</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6013,7 +5985,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6023,7 +5995,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Hörd i norr.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6050,10 +6027,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122260103</v>
+        <v>122260068</v>
       </c>
       <c r="B46" t="n">
-        <v>91278</v>
+        <v>57400</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6062,30 +6039,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6093,10 +6079,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>651855</v>
+        <v>651928</v>
       </c>
       <c r="R46" t="n">
-        <v>6674655</v>
+        <v>6674457</v>
       </c>
       <c r="S46" t="n">
         <v>4</v>
@@ -6128,7 +6114,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6138,12 +6124,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På klibbtickelåga.</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6154,21 +6135,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6185,10 +6151,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122260064</v>
+        <v>122260111</v>
       </c>
       <c r="B47" t="n">
-        <v>57399</v>
+        <v>98241</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6197,39 +6163,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6237,10 +6203,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>651845</v>
+        <v>651949</v>
       </c>
       <c r="R47" t="n">
-        <v>6674626</v>
+        <v>6674415</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6272,7 +6238,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6282,7 +6248,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6309,10 +6275,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122260118</v>
+        <v>122260103</v>
       </c>
       <c r="B48" t="n">
-        <v>100506</v>
+        <v>91279</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6321,31 +6287,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6353,10 +6318,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>651893</v>
+        <v>651855</v>
       </c>
       <c r="R48" t="n">
-        <v>6674508</v>
+        <v>6674655</v>
       </c>
       <c r="S48" t="n">
         <v>4</v>
@@ -6388,7 +6353,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6398,7 +6363,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På klibbtickelåga.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6409,6 +6379,21 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6425,10 +6410,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122260126</v>
+        <v>122260064</v>
       </c>
       <c r="B49" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6437,31 +6422,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6469,10 +6462,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>651941</v>
+        <v>651845</v>
       </c>
       <c r="R49" t="n">
-        <v>6674469</v>
+        <v>6674626</v>
       </c>
       <c r="S49" t="n">
         <v>4</v>
@@ -6504,7 +6497,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6514,7 +6507,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6541,10 +6534,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122260116</v>
+        <v>122260075</v>
       </c>
       <c r="B50" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6553,31 +6546,39 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -6585,10 +6586,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>651859</v>
+        <v>651900</v>
       </c>
       <c r="R50" t="n">
-        <v>6674654</v>
+        <v>6674390</v>
       </c>
       <c r="S50" t="n">
         <v>4</v>
@@ -6620,7 +6621,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6630,7 +6631,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6657,10 +6658,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122260096</v>
+        <v>122260117</v>
       </c>
       <c r="B51" t="n">
-        <v>80613</v>
+        <v>100507</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6669,30 +6670,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1049</v>
+        <v>222498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -6700,10 +6702,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>651930</v>
+        <v>651906</v>
       </c>
       <c r="R51" t="n">
-        <v>6674592</v>
+        <v>6674571</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -6735,7 +6737,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6745,7 +6747,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6772,10 +6774,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122260070</v>
+        <v>122260058</v>
       </c>
       <c r="B52" t="n">
-        <v>57399</v>
+        <v>5193</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6784,20 +6786,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6805,16 +6807,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6824,10 +6823,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>651967</v>
+        <v>652031</v>
       </c>
       <c r="R52" t="n">
-        <v>6674433</v>
+        <v>6674226</v>
       </c>
       <c r="S52" t="n">
         <v>4</v>
@@ -6859,7 +6858,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6869,7 +6868,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6880,6 +6879,21 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6896,10 +6910,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122260061</v>
+        <v>122260113</v>
       </c>
       <c r="B53" t="n">
-        <v>57399</v>
+        <v>98241</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6908,39 +6922,39 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -6948,10 +6962,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>651886</v>
+        <v>651906</v>
       </c>
       <c r="R53" t="n">
-        <v>6674654</v>
+        <v>6674392</v>
       </c>
       <c r="S53" t="n">
         <v>4</v>
@@ -6983,7 +6997,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6993,7 +7007,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7020,10 +7034,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122260066</v>
+        <v>122260126</v>
       </c>
       <c r="B54" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7032,39 +7046,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -7072,10 +7078,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>651934</v>
+        <v>651941</v>
       </c>
       <c r="R54" t="n">
-        <v>6674510</v>
+        <v>6674469</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -7107,7 +7113,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7117,7 +7123,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7144,10 +7150,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122260119</v>
+        <v>122260077</v>
       </c>
       <c r="B55" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7156,31 +7162,39 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7188,10 +7202,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>651950</v>
+        <v>651964</v>
       </c>
       <c r="R55" t="n">
-        <v>6674465</v>
+        <v>6674220</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -7223,7 +7237,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7233,7 +7247,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7260,10 +7274,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122260071</v>
+        <v>122260084</v>
       </c>
       <c r="B56" t="n">
-        <v>57399</v>
+        <v>57537</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7276,33 +7290,33 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -7312,13 +7326,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>651930</v>
+        <v>651900</v>
       </c>
       <c r="R56" t="n">
-        <v>6674444</v>
+        <v>6674551</v>
       </c>
       <c r="S56" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7347,7 +7361,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7357,7 +7371,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7384,10 +7398,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122260063</v>
+        <v>122260071</v>
       </c>
       <c r="B57" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7436,10 +7450,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>651872</v>
+        <v>651930</v>
       </c>
       <c r="R57" t="n">
-        <v>6674674</v>
+        <v>6674444</v>
       </c>
       <c r="S57" t="n">
         <v>4</v>
@@ -7471,7 +7485,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7481,7 +7495,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7508,10 +7522,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122260085</v>
+        <v>122260100</v>
       </c>
       <c r="B58" t="n">
-        <v>57753</v>
+        <v>90834</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7520,39 +7534,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7560,13 +7565,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>651895</v>
+        <v>652034</v>
       </c>
       <c r="R58" t="n">
-        <v>6674630</v>
+        <v>6674236</v>
       </c>
       <c r="S58" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7595,7 +7600,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7605,7 +7610,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7616,6 +7621,21 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7632,10 +7652,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122260120</v>
+        <v>122260121</v>
       </c>
       <c r="B59" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7676,10 +7696,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>651967</v>
+        <v>651955</v>
       </c>
       <c r="R59" t="n">
-        <v>6674316</v>
+        <v>6674222</v>
       </c>
       <c r="S59" t="n">
         <v>4</v>
@@ -7711,7 +7731,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7721,7 +7741,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7748,10 +7768,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122260058</v>
+        <v>122260115</v>
       </c>
       <c r="B60" t="n">
-        <v>5193</v>
+        <v>100507</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7764,32 +7784,27 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7797,10 +7812,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>652031</v>
+        <v>651891</v>
       </c>
       <c r="R60" t="n">
-        <v>6674226</v>
+        <v>6674645</v>
       </c>
       <c r="S60" t="n">
         <v>4</v>
@@ -7832,7 +7847,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7842,7 +7857,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7853,21 +7868,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7884,10 +7884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301074</v>
+        <v>122301065</v>
       </c>
       <c r="B61" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7928,10 +7928,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>651855</v>
+        <v>652034</v>
       </c>
       <c r="R61" t="n">
-        <v>6673907</v>
+        <v>6673906</v>
       </c>
       <c r="S61" t="n">
         <v>4</v>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8000,10 +8000,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301050</v>
+        <v>122301017</v>
       </c>
       <c r="B62" t="n">
-        <v>98240</v>
+        <v>57400</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8012,39 +8012,39 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8052,10 +8052,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651948</v>
+        <v>651776</v>
       </c>
       <c r="R62" t="n">
-        <v>6673906</v>
+        <v>6673944</v>
       </c>
       <c r="S62" t="n">
         <v>4</v>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8124,10 +8124,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301073</v>
+        <v>122301025</v>
       </c>
       <c r="B63" t="n">
-        <v>100506</v>
+        <v>57537</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8136,45 +8136,53 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>651817</v>
+        <v>651941</v>
       </c>
       <c r="R63" t="n">
-        <v>6673939</v>
+        <v>6674093</v>
       </c>
       <c r="S63" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8203,7 +8211,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8213,7 +8221,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8240,10 +8248,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301079</v>
+        <v>122301074</v>
       </c>
       <c r="B64" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8284,10 +8292,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>652014</v>
+        <v>651855</v>
       </c>
       <c r="R64" t="n">
-        <v>6673954</v>
+        <v>6673907</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8319,7 +8327,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8329,7 +8337,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8356,10 +8364,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301025</v>
+        <v>122301081</v>
       </c>
       <c r="B65" t="n">
-        <v>57536</v>
+        <v>100507</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8368,53 +8376,45 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651941</v>
+        <v>652036</v>
       </c>
       <c r="R65" t="n">
-        <v>6674093</v>
+        <v>6673988</v>
       </c>
       <c r="S65" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8480,10 +8480,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301067</v>
+        <v>122301079</v>
       </c>
       <c r="B66" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8524,10 +8524,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>652040</v>
+        <v>652014</v>
       </c>
       <c r="R66" t="n">
-        <v>6673920</v>
+        <v>6673954</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8559,7 +8559,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8596,10 +8596,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301063</v>
+        <v>122301015</v>
       </c>
       <c r="B67" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8608,31 +8608,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8640,10 +8648,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>651949</v>
+        <v>651777</v>
       </c>
       <c r="R67" t="n">
-        <v>6673910</v>
+        <v>6673975</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8675,7 +8683,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8685,7 +8693,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8712,10 +8720,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301017</v>
+        <v>122301075</v>
       </c>
       <c r="B68" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8724,39 +8732,31 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8764,10 +8764,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651776</v>
+        <v>651975</v>
       </c>
       <c r="R68" t="n">
-        <v>6673944</v>
+        <v>6673928</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8836,10 +8836,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301080</v>
+        <v>122301013</v>
       </c>
       <c r="B69" t="n">
-        <v>100506</v>
+        <v>57400</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8848,31 +8848,39 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8880,10 +8888,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>652011</v>
+        <v>651745</v>
       </c>
       <c r="R69" t="n">
-        <v>6673969</v>
+        <v>6673922</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8915,7 +8923,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8925,7 +8933,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8952,10 +8960,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301027</v>
+        <v>122301026</v>
       </c>
       <c r="B70" t="n">
-        <v>57753</v>
+        <v>57537</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8964,35 +8972,39 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9000,13 +9012,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651983</v>
+        <v>651977</v>
       </c>
       <c r="R70" t="n">
-        <v>6673930</v>
+        <v>6673906</v>
       </c>
       <c r="S70" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9035,7 +9047,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9045,7 +9057,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9075,7 +9087,7 @@
         <v>122301066</v>
       </c>
       <c r="B71" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9188,10 +9200,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301065</v>
+        <v>122301063</v>
       </c>
       <c r="B72" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9232,10 +9244,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>652034</v>
+        <v>651949</v>
       </c>
       <c r="R72" t="n">
-        <v>6673906</v>
+        <v>6673910</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9267,7 +9279,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9277,7 +9289,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9304,10 +9316,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301081</v>
+        <v>122301050</v>
       </c>
       <c r="B73" t="n">
-        <v>100506</v>
+        <v>98241</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9316,29 +9328,37 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
@@ -9348,10 +9368,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>652036</v>
+        <v>651948</v>
       </c>
       <c r="R73" t="n">
-        <v>6673988</v>
+        <v>6673906</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9383,7 +9403,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9393,7 +9413,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9420,10 +9440,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301075</v>
+        <v>122301073</v>
       </c>
       <c r="B74" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9464,10 +9484,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>651975</v>
+        <v>651817</v>
       </c>
       <c r="R74" t="n">
-        <v>6673928</v>
+        <v>6673939</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -9499,7 +9519,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9509,7 +9529,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9536,10 +9556,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301013</v>
+        <v>122301027</v>
       </c>
       <c r="B75" t="n">
-        <v>57399</v>
+        <v>57754</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9548,20 +9568,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9571,16 +9591,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9588,13 +9604,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651745</v>
+        <v>651983</v>
       </c>
       <c r="R75" t="n">
-        <v>6673922</v>
+        <v>6673930</v>
       </c>
       <c r="S75" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9623,7 +9639,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9633,7 +9649,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9660,10 +9676,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301015</v>
+        <v>122301067</v>
       </c>
       <c r="B76" t="n">
-        <v>57399</v>
+        <v>100507</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9672,39 +9688,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9712,10 +9720,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651777</v>
+        <v>652040</v>
       </c>
       <c r="R76" t="n">
-        <v>6673975</v>
+        <v>6673920</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9747,7 +9755,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9757,7 +9765,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9784,10 +9792,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301026</v>
+        <v>122301080</v>
       </c>
       <c r="B77" t="n">
-        <v>57536</v>
+        <v>100507</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9796,39 +9804,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9836,13 +9836,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651977</v>
+        <v>652011</v>
       </c>
       <c r="R77" t="n">
-        <v>6673906</v>
+        <v>6673969</v>
       </c>
       <c r="S77" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9911,7 +9911,7 @@
         <v>122260107</v>
       </c>
       <c r="B78" t="n">
-        <v>95786</v>
+        <v>95787</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -2872,10 +2872,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122301078</v>
+        <v>122301056</v>
       </c>
       <c r="B20" t="n">
-        <v>100507</v>
+        <v>98241</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,29 +2884,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2916,10 +2924,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>652006</v>
+        <v>651930</v>
       </c>
       <c r="R20" t="n">
-        <v>6673876</v>
+        <v>6673898</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2951,7 +2959,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2961,7 +2969,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2988,10 +2996,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122301056</v>
+        <v>122301078</v>
       </c>
       <c r="B21" t="n">
-        <v>98241</v>
+        <v>100507</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3000,37 +3008,29 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651930</v>
+        <v>652006</v>
       </c>
       <c r="R21" t="n">
-        <v>6673898</v>
+        <v>6673876</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -8960,10 +8960,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301026</v>
+        <v>122301066</v>
       </c>
       <c r="B70" t="n">
-        <v>57537</v>
+        <v>100507</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8972,39 +8972,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9012,13 +9004,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651977</v>
+        <v>652079</v>
       </c>
       <c r="R70" t="n">
-        <v>6673906</v>
+        <v>6673929</v>
       </c>
       <c r="S70" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -9047,7 +9039,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9057,7 +9049,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9084,7 +9076,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301066</v>
+        <v>122301063</v>
       </c>
       <c r="B71" t="n">
         <v>100507</v>
@@ -9128,10 +9120,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>652079</v>
+        <v>651949</v>
       </c>
       <c r="R71" t="n">
-        <v>6673929</v>
+        <v>6673910</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9163,7 +9155,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9173,7 +9165,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9200,10 +9192,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301063</v>
+        <v>122301026</v>
       </c>
       <c r="B72" t="n">
-        <v>100507</v>
+        <v>57537</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9212,31 +9204,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9244,13 +9244,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651949</v>
+        <v>651977</v>
       </c>
       <c r="R72" t="n">
-        <v>6673910</v>
+        <v>6673906</v>
       </c>
       <c r="S72" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122301006</v>
+        <v>122301021</v>
       </c>
       <c r="B2" t="n">
         <v>57400</v>
@@ -717,20 +717,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>651860</v>
+        <v>652056</v>
       </c>
       <c r="R2" t="n">
-        <v>6673862</v>
+        <v>6673872</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122300991</v>
+        <v>122301077</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,39 +811,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651958</v>
+        <v>651993</v>
       </c>
       <c r="R3" t="n">
-        <v>6673868</v>
+        <v>6673867</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -886,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +888,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122301058</v>
+        <v>122301007</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,39 +927,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -975,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651981</v>
+        <v>651778</v>
       </c>
       <c r="R4" t="n">
-        <v>6673859</v>
+        <v>6673895</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1010,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1020,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122300993</v>
+        <v>122300995</v>
       </c>
       <c r="B5" t="n">
         <v>57400</v>
@@ -1089,7 +1081,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1099,13 +1091,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651962</v>
+        <v>651899</v>
       </c>
       <c r="R5" t="n">
-        <v>6673882</v>
+        <v>6673777</v>
       </c>
       <c r="S5" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1126,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,12 +1136,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1176,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122301062</v>
+        <v>122301037</v>
       </c>
       <c r="B6" t="n">
-        <v>100507</v>
+        <v>91234</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1188,39 +1175,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1228,10 +1201,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651973</v>
+        <v>651917</v>
       </c>
       <c r="R6" t="n">
-        <v>6673897</v>
+        <v>6673853</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1263,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1273,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122301031</v>
+        <v>122301062</v>
       </c>
       <c r="B7" t="n">
-        <v>74697</v>
+        <v>100510</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1316,26 +1289,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1343,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>651805</v>
+        <v>651973</v>
       </c>
       <c r="R7" t="n">
-        <v>6673899</v>
+        <v>6673897</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1378,7 +1360,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1388,7 +1370,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,7 +1397,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122300999</v>
+        <v>122301020</v>
       </c>
       <c r="B8" t="n">
         <v>57400</v>
@@ -1457,7 +1439,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1467,10 +1449,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>651879</v>
+        <v>652017</v>
       </c>
       <c r="R8" t="n">
-        <v>6673776</v>
+        <v>6673872</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1502,7 +1484,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1512,7 +1494,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,10 +1521,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122301001</v>
+        <v>122301060</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1551,39 +1533,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1591,10 +1573,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>651873</v>
+        <v>652000</v>
       </c>
       <c r="R9" t="n">
-        <v>6673779</v>
+        <v>6673848</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1626,7 +1608,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1636,7 +1618,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1663,10 +1645,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122301064</v>
+        <v>122301004</v>
       </c>
       <c r="B10" t="n">
-        <v>100507</v>
+        <v>57400</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,31 +1657,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1707,10 +1697,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651993</v>
+        <v>651888</v>
       </c>
       <c r="R10" t="n">
-        <v>6673896</v>
+        <v>6673877</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1742,7 +1732,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1752,7 +1742,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1779,10 +1769,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301077</v>
+        <v>122301078</v>
       </c>
       <c r="B11" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1823,10 +1813,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>651993</v>
+        <v>652006</v>
       </c>
       <c r="R11" t="n">
-        <v>6673867</v>
+        <v>6673876</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1858,7 +1848,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1868,7 +1858,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1895,10 +1885,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301068</v>
+        <v>122301031</v>
       </c>
       <c r="B12" t="n">
-        <v>100507</v>
+        <v>74700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,38 +1901,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651906</v>
+        <v>651805</v>
       </c>
       <c r="R12" t="n">
-        <v>6673752</v>
+        <v>6673899</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1974,7 +1963,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1984,7 +1973,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2011,10 +2000,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122301053</v>
+        <v>122300994</v>
       </c>
       <c r="B13" t="n">
-        <v>98241</v>
+        <v>57400</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2023,39 +2012,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2063,10 +2052,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651986</v>
+        <v>651915</v>
       </c>
       <c r="R13" t="n">
-        <v>6673841</v>
+        <v>6673888</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2098,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2108,12 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2140,10 +2124,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301021</v>
+        <v>122301056</v>
       </c>
       <c r="B14" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2152,50 +2136,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>652056</v>
+        <v>651930</v>
       </c>
       <c r="R14" t="n">
-        <v>6673872</v>
+        <v>6673898</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2227,7 +2211,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2237,7 +2221,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122301020</v>
+        <v>122301058</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2276,39 +2260,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2316,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>652017</v>
+        <v>651981</v>
       </c>
       <c r="R15" t="n">
-        <v>6673872</v>
+        <v>6673859</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2351,7 +2335,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2361,7 +2345,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2388,7 +2372,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122300995</v>
+        <v>122301019</v>
       </c>
       <c r="B16" t="n">
         <v>57400</v>
@@ -2440,10 +2424,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>651899</v>
+        <v>652004</v>
       </c>
       <c r="R16" t="n">
-        <v>6673777</v>
+        <v>6673869</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2475,7 +2459,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2485,7 +2469,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2512,7 +2496,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122301004</v>
+        <v>122300997</v>
       </c>
       <c r="B17" t="n">
         <v>57400</v>
@@ -2554,20 +2538,20 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651888</v>
+        <v>651883</v>
       </c>
       <c r="R17" t="n">
-        <v>6673877</v>
+        <v>6673732</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2599,7 +2583,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2609,7 +2593,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2636,10 +2620,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122300988</v>
+        <v>122301001</v>
       </c>
       <c r="B18" t="n">
-        <v>5193</v>
+        <v>57400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2648,20 +2632,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2669,13 +2653,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -2685,10 +2672,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651926</v>
+        <v>651873</v>
       </c>
       <c r="R18" t="n">
-        <v>6673844</v>
+        <v>6673779</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2720,7 +2707,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2730,7 +2717,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2757,10 +2744,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122301036</v>
+        <v>122300993</v>
       </c>
       <c r="B19" t="n">
-        <v>90834</v>
+        <v>57400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2773,26 +2760,35 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2800,13 +2796,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652047</v>
+        <v>651962</v>
       </c>
       <c r="R19" t="n">
-        <v>6673893</v>
+        <v>6673882</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2835,7 +2831,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2845,7 +2841,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2872,10 +2873,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122301056</v>
+        <v>122301071</v>
       </c>
       <c r="B20" t="n">
-        <v>98241</v>
+        <v>100510</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2884,37 +2885,29 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -2924,10 +2917,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651930</v>
+        <v>651840</v>
       </c>
       <c r="R20" t="n">
-        <v>6673898</v>
+        <v>6673881</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2959,7 +2952,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2969,7 +2962,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2996,10 +2989,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122301078</v>
+        <v>122301064</v>
       </c>
       <c r="B21" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3040,10 +3033,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652006</v>
+        <v>651993</v>
       </c>
       <c r="R21" t="n">
-        <v>6673876</v>
+        <v>6673896</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3075,7 +3068,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3085,7 +3078,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3112,10 +3105,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122301019</v>
+        <v>122300988</v>
       </c>
       <c r="B22" t="n">
-        <v>57400</v>
+        <v>5193</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3124,20 +3117,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3145,16 +3138,13 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3164,10 +3154,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652004</v>
+        <v>651926</v>
       </c>
       <c r="R22" t="n">
-        <v>6673869</v>
+        <v>6673844</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3199,7 +3189,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3209,7 +3199,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3236,7 +3226,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122300997</v>
+        <v>122300999</v>
       </c>
       <c r="B23" t="n">
         <v>57400</v>
@@ -3278,20 +3268,20 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651883</v>
+        <v>651879</v>
       </c>
       <c r="R23" t="n">
-        <v>6673732</v>
+        <v>6673776</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3323,7 +3313,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3333,7 +3323,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3360,10 +3350,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122301007</v>
+        <v>122301036</v>
       </c>
       <c r="B24" t="n">
-        <v>57400</v>
+        <v>90837</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3376,35 +3366,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3412,10 +3393,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>651778</v>
+        <v>652047</v>
       </c>
       <c r="R24" t="n">
-        <v>6673895</v>
+        <v>6673893</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3447,7 +3428,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3457,7 +3438,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3484,7 +3465,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122300994</v>
+        <v>122301006</v>
       </c>
       <c r="B25" t="n">
         <v>57400</v>
@@ -3536,10 +3517,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651915</v>
+        <v>651860</v>
       </c>
       <c r="R25" t="n">
-        <v>6673888</v>
+        <v>6673862</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3571,7 +3552,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3581,7 +3562,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3608,10 +3589,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122301037</v>
+        <v>122300991</v>
       </c>
       <c r="B26" t="n">
-        <v>91231</v>
+        <v>57400</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3624,21 +3605,35 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6040162</v>
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3646,10 +3641,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651917</v>
+        <v>651958</v>
       </c>
       <c r="R26" t="n">
-        <v>6673853</v>
+        <v>6673868</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3681,7 +3676,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3691,7 +3686,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3718,10 +3713,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301060</v>
+        <v>122301053</v>
       </c>
       <c r="B27" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3753,7 +3748,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3770,10 +3765,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>652000</v>
+        <v>651986</v>
       </c>
       <c r="R27" t="n">
-        <v>6673848</v>
+        <v>6673841</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3805,7 +3800,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3815,7 +3810,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122301071</v>
+        <v>122301068</v>
       </c>
       <c r="B28" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3882,14 +3882,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651840</v>
+        <v>651906</v>
       </c>
       <c r="R28" t="n">
-        <v>6673881</v>
+        <v>6673752</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -7884,10 +7884,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122301065</v>
+        <v>122301050</v>
       </c>
       <c r="B61" t="n">
-        <v>100507</v>
+        <v>98244</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7896,29 +7896,37 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -7928,7 +7936,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>652034</v>
+        <v>651948</v>
       </c>
       <c r="R61" t="n">
         <v>6673906</v>
@@ -7963,7 +7971,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7973,7 +7981,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8000,10 +8008,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301017</v>
+        <v>122301026</v>
       </c>
       <c r="B62" t="n">
-        <v>57400</v>
+        <v>57537</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8016,21 +8024,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -8042,7 +8050,7 @@
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
@@ -8052,13 +8060,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651776</v>
+        <v>651977</v>
       </c>
       <c r="R62" t="n">
-        <v>6673944</v>
+        <v>6673906</v>
       </c>
       <c r="S62" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8087,7 +8095,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8097,7 +8105,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8124,10 +8132,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301025</v>
+        <v>122301081</v>
       </c>
       <c r="B63" t="n">
-        <v>57537</v>
+        <v>100510</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8136,53 +8144,45 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>651941</v>
+        <v>652036</v>
       </c>
       <c r="R63" t="n">
-        <v>6674093</v>
+        <v>6673988</v>
       </c>
       <c r="S63" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8248,10 +8248,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301074</v>
+        <v>122301075</v>
       </c>
       <c r="B64" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8292,10 +8292,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651855</v>
+        <v>651975</v>
       </c>
       <c r="R64" t="n">
-        <v>6673907</v>
+        <v>6673928</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8364,10 +8364,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301081</v>
+        <v>122301025</v>
       </c>
       <c r="B65" t="n">
-        <v>100507</v>
+        <v>57537</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8376,45 +8376,53 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>652036</v>
+        <v>651941</v>
       </c>
       <c r="R65" t="n">
-        <v>6673988</v>
+        <v>6674093</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8443,7 +8451,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8453,7 +8461,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8480,10 +8488,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301079</v>
+        <v>122301067</v>
       </c>
       <c r="B66" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8524,10 +8532,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>652014</v>
+        <v>652040</v>
       </c>
       <c r="R66" t="n">
-        <v>6673954</v>
+        <v>6673920</v>
       </c>
       <c r="S66" t="n">
         <v>4</v>
@@ -8559,7 +8567,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8569,7 +8577,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8596,10 +8604,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301015</v>
+        <v>122301080</v>
       </c>
       <c r="B67" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8608,39 +8616,31 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8648,10 +8648,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>651777</v>
+        <v>652011</v>
       </c>
       <c r="R67" t="n">
-        <v>6673975</v>
+        <v>6673969</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8720,10 +8720,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301075</v>
+        <v>122301065</v>
       </c>
       <c r="B68" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8764,10 +8764,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>651975</v>
+        <v>652034</v>
       </c>
       <c r="R68" t="n">
-        <v>6673928</v>
+        <v>6673906</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8836,7 +8836,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301013</v>
+        <v>122301017</v>
       </c>
       <c r="B69" t="n">
         <v>57400</v>
@@ -8888,10 +8888,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651745</v>
+        <v>651776</v>
       </c>
       <c r="R69" t="n">
-        <v>6673922</v>
+        <v>6673944</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8923,7 +8923,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8960,10 +8960,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301066</v>
+        <v>122301015</v>
       </c>
       <c r="B70" t="n">
-        <v>100507</v>
+        <v>57400</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8972,31 +8972,39 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9004,10 +9012,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>652079</v>
+        <v>651777</v>
       </c>
       <c r="R70" t="n">
-        <v>6673929</v>
+        <v>6673975</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -9039,7 +9047,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9049,7 +9057,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9079,7 +9087,7 @@
         <v>122301063</v>
       </c>
       <c r="B71" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9192,10 +9200,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301026</v>
+        <v>122301066</v>
       </c>
       <c r="B72" t="n">
-        <v>57537</v>
+        <v>100510</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9204,39 +9212,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9244,13 +9244,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>651977</v>
+        <v>652079</v>
       </c>
       <c r="R72" t="n">
-        <v>6673906</v>
+        <v>6673929</v>
       </c>
       <c r="S72" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9316,10 +9316,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301050</v>
+        <v>122301079</v>
       </c>
       <c r="B73" t="n">
-        <v>98241</v>
+        <v>100510</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9328,37 +9328,29 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
@@ -9368,10 +9360,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>651948</v>
+        <v>652014</v>
       </c>
       <c r="R73" t="n">
-        <v>6673906</v>
+        <v>6673954</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9403,7 +9395,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9413,7 +9405,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9440,10 +9432,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301073</v>
+        <v>122301027</v>
       </c>
       <c r="B74" t="n">
-        <v>100507</v>
+        <v>57754</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9456,27 +9448,31 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9484,13 +9480,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>651817</v>
+        <v>651983</v>
       </c>
       <c r="R74" t="n">
-        <v>6673939</v>
+        <v>6673930</v>
       </c>
       <c r="S74" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9519,7 +9515,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9529,7 +9525,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9556,10 +9552,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301027</v>
+        <v>122301013</v>
       </c>
       <c r="B75" t="n">
-        <v>57754</v>
+        <v>57400</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9568,20 +9564,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9591,12 +9587,16 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9604,13 +9604,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651983</v>
+        <v>651745</v>
       </c>
       <c r="R75" t="n">
-        <v>6673930</v>
+        <v>6673922</v>
       </c>
       <c r="S75" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9676,10 +9676,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301067</v>
+        <v>122301074</v>
       </c>
       <c r="B76" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9720,10 +9720,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>652040</v>
+        <v>651855</v>
       </c>
       <c r="R76" t="n">
-        <v>6673920</v>
+        <v>6673907</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9765,7 +9765,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9792,10 +9792,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301080</v>
+        <v>122301073</v>
       </c>
       <c r="B77" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9836,10 +9836,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>652011</v>
+        <v>651817</v>
       </c>
       <c r="R77" t="n">
-        <v>6673969</v>
+        <v>6673939</v>
       </c>
       <c r="S77" t="n">
         <v>4</v>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9911,7 +9911,7 @@
         <v>122260107</v>
       </c>
       <c r="B78" t="n">
-        <v>95787</v>
+        <v>95790</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122301021</v>
+        <v>122300995</v>
       </c>
       <c r="B2" t="n">
         <v>57400</v>
@@ -717,20 +717,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>652056</v>
+        <v>651899</v>
       </c>
       <c r="R2" t="n">
-        <v>6673872</v>
+        <v>6673777</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122301077</v>
+        <v>122301019</v>
       </c>
       <c r="B3" t="n">
-        <v>100510</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,31 +811,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -843,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>651993</v>
+        <v>652004</v>
       </c>
       <c r="R3" t="n">
-        <v>6673867</v>
+        <v>6673869</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -878,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122301007</v>
+        <v>122301064</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,39 +935,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>651778</v>
+        <v>651993</v>
       </c>
       <c r="R4" t="n">
-        <v>6673895</v>
+        <v>6673896</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122300995</v>
+        <v>122301071</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,39 +1051,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1091,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>651899</v>
+        <v>651840</v>
       </c>
       <c r="R5" t="n">
-        <v>6673777</v>
+        <v>6673881</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1126,7 +1118,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1136,7 +1128,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122301037</v>
+        <v>122300999</v>
       </c>
       <c r="B6" t="n">
-        <v>91234</v>
+        <v>57400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,21 +1171,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040162</v>
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1201,10 +1207,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>651917</v>
+        <v>651879</v>
       </c>
       <c r="R6" t="n">
-        <v>6673853</v>
+        <v>6673776</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1236,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1252,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1397,7 +1403,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122301020</v>
+        <v>122300993</v>
       </c>
       <c r="B8" t="n">
         <v>57400</v>
@@ -1439,7 +1445,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1449,13 +1455,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>652017</v>
+        <v>651962</v>
       </c>
       <c r="R8" t="n">
-        <v>6673872</v>
+        <v>6673882</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1484,7 +1490,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1494,7 +1500,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hörs locka i närheten.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1645,7 +1656,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122301004</v>
+        <v>122301007</v>
       </c>
       <c r="B10" t="n">
         <v>57400</v>
@@ -1697,10 +1708,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>651888</v>
+        <v>651778</v>
       </c>
       <c r="R10" t="n">
-        <v>6673877</v>
+        <v>6673895</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1732,7 +1743,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1742,7 +1753,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1769,10 +1780,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122301078</v>
+        <v>122300988</v>
       </c>
       <c r="B11" t="n">
-        <v>100510</v>
+        <v>5193</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1785,27 +1796,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1813,10 +1829,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>652006</v>
+        <v>651926</v>
       </c>
       <c r="R11" t="n">
-        <v>6673876</v>
+        <v>6673844</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1848,7 +1864,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1858,7 +1874,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1885,10 +1901,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122301031</v>
+        <v>122301020</v>
       </c>
       <c r="B12" t="n">
-        <v>74700</v>
+        <v>57400</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1897,30 +1913,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1928,10 +1953,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>651805</v>
+        <v>652017</v>
       </c>
       <c r="R12" t="n">
-        <v>6673899</v>
+        <v>6673872</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1963,7 +1988,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1973,7 +1998,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2000,10 +2025,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122300994</v>
+        <v>122301056</v>
       </c>
       <c r="B13" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2012,39 +2037,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2052,10 +2077,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>651915</v>
+        <v>651930</v>
       </c>
       <c r="R13" t="n">
-        <v>6673888</v>
+        <v>6673898</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2087,7 +2112,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2122,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2124,10 +2149,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122301056</v>
+        <v>122300997</v>
       </c>
       <c r="B14" t="n">
-        <v>98244</v>
+        <v>57400</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2136,50 +2161,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>651930</v>
+        <v>651883</v>
       </c>
       <c r="R14" t="n">
-        <v>6673898</v>
+        <v>6673732</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2211,7 +2236,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2221,7 +2246,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,10 +2273,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122301058</v>
+        <v>122301001</v>
       </c>
       <c r="B15" t="n">
-        <v>98244</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2260,39 +2285,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2300,10 +2325,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>651981</v>
+        <v>651873</v>
       </c>
       <c r="R15" t="n">
-        <v>6673859</v>
+        <v>6673779</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2335,7 +2360,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,7 +2370,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,7 +2397,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122301019</v>
+        <v>122301021</v>
       </c>
       <c r="B16" t="n">
         <v>57400</v>
@@ -2414,20 +2439,20 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>652004</v>
+        <v>652056</v>
       </c>
       <c r="R16" t="n">
-        <v>6673869</v>
+        <v>6673872</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2459,7 +2484,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2469,7 +2494,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2496,10 +2521,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122300997</v>
+        <v>122301037</v>
       </c>
       <c r="B17" t="n">
-        <v>57400</v>
+        <v>91234</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2512,46 +2537,32 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>651883</v>
+        <v>651917</v>
       </c>
       <c r="R17" t="n">
-        <v>6673732</v>
+        <v>6673853</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2583,7 +2594,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2593,7 +2604,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2620,10 +2631,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122301001</v>
+        <v>122301058</v>
       </c>
       <c r="B18" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2632,39 +2643,39 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2672,10 +2683,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>651873</v>
+        <v>651981</v>
       </c>
       <c r="R18" t="n">
-        <v>6673779</v>
+        <v>6673859</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2707,7 +2718,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2717,7 +2728,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2744,7 +2755,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122300993</v>
+        <v>122301004</v>
       </c>
       <c r="B19" t="n">
         <v>57400</v>
@@ -2786,7 +2797,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2796,13 +2807,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>651962</v>
+        <v>651888</v>
       </c>
       <c r="R19" t="n">
-        <v>6673882</v>
+        <v>6673877</v>
       </c>
       <c r="S19" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2831,7 +2842,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2841,12 +2852,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hörs locka i närheten.</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2873,7 +2879,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122301071</v>
+        <v>122301078</v>
       </c>
       <c r="B20" t="n">
         <v>100510</v>
@@ -2917,10 +2923,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>651840</v>
+        <v>652006</v>
       </c>
       <c r="R20" t="n">
-        <v>6673881</v>
+        <v>6673876</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2952,7 +2958,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2962,7 +2968,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2989,7 +2995,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122301064</v>
+        <v>122301068</v>
       </c>
       <c r="B21" t="n">
         <v>100510</v>
@@ -3029,14 +3035,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Kvarnmyren, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>651993</v>
+        <v>651906</v>
       </c>
       <c r="R21" t="n">
-        <v>6673896</v>
+        <v>6673752</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3068,7 +3074,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3078,7 +3084,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3105,10 +3111,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122300988</v>
+        <v>122301036</v>
       </c>
       <c r="B22" t="n">
-        <v>5193</v>
+        <v>90837</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3117,36 +3123,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>651926</v>
+        <v>652047</v>
       </c>
       <c r="R22" t="n">
-        <v>6673844</v>
+        <v>6673893</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3226,7 +3226,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122300999</v>
+        <v>122300994</v>
       </c>
       <c r="B23" t="n">
         <v>57400</v>
@@ -3278,10 +3278,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>651879</v>
+        <v>651915</v>
       </c>
       <c r="R23" t="n">
-        <v>6673776</v>
+        <v>6673888</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122301036</v>
+        <v>122300991</v>
       </c>
       <c r="B24" t="n">
-        <v>90837</v>
+        <v>57400</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3366,26 +3366,35 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3393,10 +3402,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>652047</v>
+        <v>651958</v>
       </c>
       <c r="R24" t="n">
-        <v>6673893</v>
+        <v>6673868</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3428,7 +3437,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3438,7 +3447,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3465,10 +3474,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122301006</v>
+        <v>122301077</v>
       </c>
       <c r="B25" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3477,39 +3486,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3517,10 +3518,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>651860</v>
+        <v>651993</v>
       </c>
       <c r="R25" t="n">
-        <v>6673862</v>
+        <v>6673867</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3552,7 +3553,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3562,7 +3563,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3589,10 +3590,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122300991</v>
+        <v>122301053</v>
       </c>
       <c r="B26" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3601,39 +3602,39 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3641,10 +3642,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>651958</v>
+        <v>651986</v>
       </c>
       <c r="R26" t="n">
-        <v>6673868</v>
+        <v>6673841</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3676,7 +3677,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3686,7 +3687,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3713,10 +3719,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122301053</v>
+        <v>122301031</v>
       </c>
       <c r="B27" t="n">
-        <v>98244</v>
+        <v>74700</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3725,39 +3731,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3765,10 +3762,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>651986</v>
+        <v>651805</v>
       </c>
       <c r="R27" t="n">
-        <v>6673841</v>
+        <v>6673899</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3800,7 +3797,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3810,12 +3807,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Med ett gigantiskt hygge till granne. Några av plantorna som växer mer exponerat för en tynande tillvaro.</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3842,10 +3834,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122301068</v>
+        <v>122301006</v>
       </c>
       <c r="B28" t="n">
-        <v>100510</v>
+        <v>57400</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3854,42 +3846,50 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kvarnmyren, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>651906</v>
+        <v>651860</v>
       </c>
       <c r="R28" t="n">
-        <v>6673752</v>
+        <v>6673862</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -8008,10 +8008,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122301026</v>
+        <v>122301079</v>
       </c>
       <c r="B62" t="n">
-        <v>57537</v>
+        <v>100510</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8020,39 +8020,31 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -8060,13 +8052,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>651977</v>
+        <v>652014</v>
       </c>
       <c r="R62" t="n">
-        <v>6673906</v>
+        <v>6673954</v>
       </c>
       <c r="S62" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8095,7 +8087,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8105,7 +8097,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8132,7 +8124,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122301081</v>
+        <v>122301066</v>
       </c>
       <c r="B63" t="n">
         <v>100510</v>
@@ -8176,10 +8168,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>652036</v>
+        <v>652079</v>
       </c>
       <c r="R63" t="n">
-        <v>6673988</v>
+        <v>6673929</v>
       </c>
       <c r="S63" t="n">
         <v>4</v>
@@ -8211,7 +8203,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8221,7 +8213,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8248,7 +8240,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122301075</v>
+        <v>122301080</v>
       </c>
       <c r="B64" t="n">
         <v>100510</v>
@@ -8292,10 +8284,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>651975</v>
+        <v>652011</v>
       </c>
       <c r="R64" t="n">
-        <v>6673928</v>
+        <v>6673969</v>
       </c>
       <c r="S64" t="n">
         <v>4</v>
@@ -8327,7 +8319,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8337,7 +8329,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8364,10 +8356,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122301025</v>
+        <v>122301063</v>
       </c>
       <c r="B65" t="n">
-        <v>57537</v>
+        <v>100510</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8376,53 +8368,45 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Slubbolskärret, Upl</t>
+          <t>Ackareåsen, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>651941</v>
+        <v>651949</v>
       </c>
       <c r="R65" t="n">
-        <v>6674093</v>
+        <v>6673910</v>
       </c>
       <c r="S65" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8451,7 +8435,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8461,7 +8445,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8488,10 +8472,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122301067</v>
+        <v>122301026</v>
       </c>
       <c r="B66" t="n">
-        <v>100510</v>
+        <v>57537</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8500,31 +8484,39 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8532,13 +8524,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>652040</v>
+        <v>651977</v>
       </c>
       <c r="R66" t="n">
-        <v>6673920</v>
+        <v>6673906</v>
       </c>
       <c r="S66" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8567,7 +8559,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8577,7 +8569,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8604,10 +8596,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122301080</v>
+        <v>122301013</v>
       </c>
       <c r="B67" t="n">
-        <v>100510</v>
+        <v>57400</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8616,31 +8608,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8648,10 +8648,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>652011</v>
+        <v>651745</v>
       </c>
       <c r="R67" t="n">
-        <v>6673969</v>
+        <v>6673922</v>
       </c>
       <c r="S67" t="n">
         <v>4</v>
@@ -8683,7 +8683,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8720,10 +8720,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122301065</v>
+        <v>122301027</v>
       </c>
       <c r="B68" t="n">
-        <v>100510</v>
+        <v>57754</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8736,27 +8736,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222498</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8764,13 +8768,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>652034</v>
+        <v>651983</v>
       </c>
       <c r="R68" t="n">
-        <v>6673906</v>
+        <v>6673930</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8799,7 +8803,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8809,7 +8813,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8836,7 +8840,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122301017</v>
+        <v>122301015</v>
       </c>
       <c r="B69" t="n">
         <v>57400</v>
@@ -8888,10 +8892,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>651776</v>
+        <v>651777</v>
       </c>
       <c r="R69" t="n">
-        <v>6673944</v>
+        <v>6673975</v>
       </c>
       <c r="S69" t="n">
         <v>4</v>
@@ -8923,7 +8927,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8933,7 +8937,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8960,10 +8964,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122301015</v>
+        <v>122301067</v>
       </c>
       <c r="B70" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8972,39 +8976,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -9012,10 +9008,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>651777</v>
+        <v>652040</v>
       </c>
       <c r="R70" t="n">
-        <v>6673975</v>
+        <v>6673920</v>
       </c>
       <c r="S70" t="n">
         <v>4</v>
@@ -9047,7 +9043,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9057,7 +9053,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9084,7 +9080,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122301063</v>
+        <v>122301065</v>
       </c>
       <c r="B71" t="n">
         <v>100510</v>
@@ -9128,10 +9124,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>651949</v>
+        <v>652034</v>
       </c>
       <c r="R71" t="n">
-        <v>6673910</v>
+        <v>6673906</v>
       </c>
       <c r="S71" t="n">
         <v>4</v>
@@ -9163,7 +9159,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9173,7 +9169,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9200,10 +9196,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122301066</v>
+        <v>122301017</v>
       </c>
       <c r="B72" t="n">
-        <v>100510</v>
+        <v>57400</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9212,31 +9208,39 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -9244,10 +9248,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>652079</v>
+        <v>651776</v>
       </c>
       <c r="R72" t="n">
-        <v>6673929</v>
+        <v>6673944</v>
       </c>
       <c r="S72" t="n">
         <v>4</v>
@@ -9279,7 +9283,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9289,7 +9293,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9316,7 +9320,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122301079</v>
+        <v>122301074</v>
       </c>
       <c r="B73" t="n">
         <v>100510</v>
@@ -9360,10 +9364,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>652014</v>
+        <v>651855</v>
       </c>
       <c r="R73" t="n">
-        <v>6673954</v>
+        <v>6673907</v>
       </c>
       <c r="S73" t="n">
         <v>4</v>
@@ -9395,7 +9399,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9405,7 +9409,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9432,10 +9436,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122301027</v>
+        <v>122301081</v>
       </c>
       <c r="B74" t="n">
-        <v>57754</v>
+        <v>100510</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9448,31 +9452,27 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103015</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9480,13 +9480,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>651983</v>
+        <v>652036</v>
       </c>
       <c r="R74" t="n">
-        <v>6673930</v>
+        <v>6673988</v>
       </c>
       <c r="S74" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9552,10 +9552,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122301013</v>
+        <v>122301075</v>
       </c>
       <c r="B75" t="n">
-        <v>57400</v>
+        <v>100510</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9564,39 +9564,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9604,10 +9596,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>651745</v>
+        <v>651975</v>
       </c>
       <c r="R75" t="n">
-        <v>6673922</v>
+        <v>6673928</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -9639,7 +9631,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9649,7 +9641,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9676,7 +9668,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122301074</v>
+        <v>122301073</v>
       </c>
       <c r="B76" t="n">
         <v>100510</v>
@@ -9720,10 +9712,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>651855</v>
+        <v>651817</v>
       </c>
       <c r="R76" t="n">
-        <v>6673907</v>
+        <v>6673939</v>
       </c>
       <c r="S76" t="n">
         <v>4</v>
@@ -9755,7 +9747,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9765,7 +9757,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9792,10 +9784,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122301073</v>
+        <v>122301025</v>
       </c>
       <c r="B77" t="n">
-        <v>100510</v>
+        <v>57537</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9804,45 +9796,53 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ackareåsen, Upl</t>
+          <t>Slubbolskärret, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>651817</v>
+        <v>651941</v>
       </c>
       <c r="R77" t="n">
-        <v>6673939</v>
+        <v>6674093</v>
       </c>
       <c r="S77" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10022,6 +10022,4231 @@
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127786478</v>
+      </c>
+      <c r="B79" t="n">
+        <v>101536</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>651968</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6674476</v>
+      </c>
+      <c r="S79" t="n">
+        <v>4</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Minst!</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127786487</v>
+      </c>
+      <c r="B80" t="n">
+        <v>105488</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>651950</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6674353</v>
+      </c>
+      <c r="S80" t="n">
+        <v>4</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127786471</v>
+      </c>
+      <c r="B81" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>651909</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6674658</v>
+      </c>
+      <c r="S81" t="n">
+        <v>4</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127786413</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>651946</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6674598</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127786417</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>651998</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6674425</v>
+      </c>
+      <c r="S83" t="n">
+        <v>4</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127786419</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>651988</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6674523</v>
+      </c>
+      <c r="S84" t="n">
+        <v>4</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127786466</v>
+      </c>
+      <c r="B85" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>651937</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6674398</v>
+      </c>
+      <c r="S85" t="n">
+        <v>4</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127786436</v>
+      </c>
+      <c r="B86" t="n">
+        <v>91104</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>651976</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6674471</v>
+      </c>
+      <c r="S86" t="n">
+        <v>4</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127786473</v>
+      </c>
+      <c r="B87" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>652012</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6674422</v>
+      </c>
+      <c r="S87" t="n">
+        <v>4</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127786482</v>
+      </c>
+      <c r="B88" t="n">
+        <v>101536</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>652012</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6674454</v>
+      </c>
+      <c r="S88" t="n">
+        <v>4</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127786475</v>
+      </c>
+      <c r="B89" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>651955</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6674475</v>
+      </c>
+      <c r="S89" t="n">
+        <v>4</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127786474</v>
+      </c>
+      <c r="B90" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>652011</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6674446</v>
+      </c>
+      <c r="S90" t="n">
+        <v>4</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127786416</v>
+      </c>
+      <c r="B91" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>651903</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6674574</v>
+      </c>
+      <c r="S91" t="n">
+        <v>4</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>127786457</v>
+      </c>
+      <c r="B92" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>651935</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6674576</v>
+      </c>
+      <c r="S92" t="n">
+        <v>4</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>127786483</v>
+      </c>
+      <c r="B93" t="n">
+        <v>101536</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>651950</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6674474</v>
+      </c>
+      <c r="S93" t="n">
+        <v>4</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>127786462</v>
+      </c>
+      <c r="B94" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>651923</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6674461</v>
+      </c>
+      <c r="S94" t="n">
+        <v>4</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>127786477</v>
+      </c>
+      <c r="B95" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>651880</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6674598</v>
+      </c>
+      <c r="S95" t="n">
+        <v>4</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>127786463</v>
+      </c>
+      <c r="B96" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>651974</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6674401</v>
+      </c>
+      <c r="S96" t="n">
+        <v>4</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>127786464</v>
+      </c>
+      <c r="B97" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>652028</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6674476</v>
+      </c>
+      <c r="S97" t="n">
+        <v>4</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>127786470</v>
+      </c>
+      <c r="B98" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>651844</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6674682</v>
+      </c>
+      <c r="S98" t="n">
+        <v>4</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>127786472</v>
+      </c>
+      <c r="B99" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>651976</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6674481</v>
+      </c>
+      <c r="S99" t="n">
+        <v>4</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>127786465</v>
+      </c>
+      <c r="B100" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>652028</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6674484</v>
+      </c>
+      <c r="S100" t="n">
+        <v>4</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>127786468</v>
+      </c>
+      <c r="B101" t="n">
+        <v>100632</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>651849</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6674645</v>
+      </c>
+      <c r="S101" t="n">
+        <v>4</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>127786430</v>
+      </c>
+      <c r="B102" t="n">
+        <v>58033</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>651913</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6674473</v>
+      </c>
+      <c r="S102" t="n">
+        <v>35</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>127786479</v>
+      </c>
+      <c r="B103" t="n">
+        <v>101536</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>651996</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6674470</v>
+      </c>
+      <c r="S103" t="n">
+        <v>4</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>127786441</v>
+      </c>
+      <c r="B104" t="n">
+        <v>92267</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>651973</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6674465</v>
+      </c>
+      <c r="S104" t="n">
+        <v>4</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färgen på bilderna något missvisande. Ljusgul mjölksaft.</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>127786444</v>
+      </c>
+      <c r="B105" t="n">
+        <v>92656</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>651913</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6674473</v>
+      </c>
+      <c r="S105" t="n">
+        <v>35</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Både tall och gran i närheten men uppenbart kalkrik mark här då vårärt och kransmossa växer alldeles intill.</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>127786421</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>651978</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6674504</v>
+      </c>
+      <c r="S106" t="n">
+        <v>4</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>127786429</v>
+      </c>
+      <c r="B107" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>652026</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6674488</v>
+      </c>
+      <c r="S107" t="n">
+        <v>59</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>127786422</v>
+      </c>
+      <c r="B108" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>651823</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6674594</v>
+      </c>
+      <c r="S108" t="n">
+        <v>4</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>127786486</v>
+      </c>
+      <c r="B109" t="n">
+        <v>105488</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>651896</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6674581</v>
+      </c>
+      <c r="S109" t="n">
+        <v>4</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>127786481</v>
+      </c>
+      <c r="B110" t="n">
+        <v>101536</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>652011</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6674447</v>
+      </c>
+      <c r="S110" t="n">
+        <v>4</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>127786403</v>
+      </c>
+      <c r="B111" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>651940</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6674275</v>
+      </c>
+      <c r="S111" t="n">
+        <v>4</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>127786438</v>
+      </c>
+      <c r="B112" t="n">
+        <v>91297</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>651961</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6674370</v>
+      </c>
+      <c r="S112" t="n">
+        <v>4</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Gammal och intorkad, ingen doft.</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>127786410</v>
+      </c>
+      <c r="B113" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>651907</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6674624</v>
+      </c>
+      <c r="S113" t="n">
+        <v>4</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>127786418</v>
+      </c>
+      <c r="B114" t="n">
+        <v>57660</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Slubbolskärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>651997</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6674524</v>
+      </c>
+      <c r="S114" t="n">
+        <v>4</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Dannemora</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -10378,7 +10378,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127786413</v>
+        <v>127786417</v>
       </c>
       <c r="B82" t="n">
         <v>57660</v>
@@ -10425,10 +10425,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>651946</v>
+        <v>651998</v>
       </c>
       <c r="R82" t="n">
-        <v>6674598</v>
+        <v>6674425</v>
       </c>
       <c r="S82" t="n">
         <v>4</v>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10497,7 +10497,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127786417</v>
+        <v>127786413</v>
       </c>
       <c r="B83" t="n">
         <v>57660</v>
@@ -10544,10 +10544,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>651998</v>
+        <v>651946</v>
       </c>
       <c r="R83" t="n">
-        <v>6674425</v>
+        <v>6674598</v>
       </c>
       <c r="S83" t="n">
         <v>4</v>
@@ -10579,7 +10579,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10854,10 +10854,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127786436</v>
+        <v>127786473</v>
       </c>
       <c r="B86" t="n">
-        <v>91104</v>
+        <v>100632</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10865,26 +10865,27 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10892,10 +10893,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>651976</v>
+        <v>652012</v>
       </c>
       <c r="R86" t="n">
-        <v>6674471</v>
+        <v>6674422</v>
       </c>
       <c r="S86" t="n">
         <v>4</v>
@@ -10927,7 +10928,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10937,7 +10938,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10964,10 +10965,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127786473</v>
+        <v>127786436</v>
       </c>
       <c r="B87" t="n">
-        <v>100632</v>
+        <v>91104</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10975,27 +10976,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11003,10 +11003,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>652012</v>
+        <v>651976</v>
       </c>
       <c r="R87" t="n">
-        <v>6674422</v>
+        <v>6674471</v>
       </c>
       <c r="S87" t="n">
         <v>4</v>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11075,10 +11075,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127786482</v>
+        <v>127786475</v>
       </c>
       <c r="B88" t="n">
-        <v>101536</v>
+        <v>100632</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11086,26 +11086,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11122,10 +11122,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>652012</v>
+        <v>651955</v>
       </c>
       <c r="R88" t="n">
-        <v>6674454</v>
+        <v>6674475</v>
       </c>
       <c r="S88" t="n">
         <v>4</v>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11194,10 +11194,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127786475</v>
+        <v>127786482</v>
       </c>
       <c r="B89" t="n">
-        <v>100632</v>
+        <v>101536</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11205,26 +11205,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>222498</v>
+        <v>221235</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11241,10 +11241,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>651955</v>
+        <v>652012</v>
       </c>
       <c r="R89" t="n">
-        <v>6674475</v>
+        <v>6674454</v>
       </c>
       <c r="S89" t="n">
         <v>4</v>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11313,38 +11313,46 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127786474</v>
+        <v>127786416</v>
       </c>
       <c r="B90" t="n">
-        <v>100632</v>
+        <v>57660</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -11352,10 +11360,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>652011</v>
+        <v>651903</v>
       </c>
       <c r="R90" t="n">
-        <v>6674446</v>
+        <v>6674574</v>
       </c>
       <c r="S90" t="n">
         <v>4</v>
@@ -11387,7 +11395,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11397,7 +11405,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11424,46 +11432,38 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127786416</v>
+        <v>127786474</v>
       </c>
       <c r="B91" t="n">
-        <v>57660</v>
+        <v>100632</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -11471,10 +11471,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>651903</v>
+        <v>652011</v>
       </c>
       <c r="R91" t="n">
-        <v>6674574</v>
+        <v>6674446</v>
       </c>
       <c r="S91" t="n">
         <v>4</v>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11543,44 +11543,40 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127786457</v>
+        <v>127786483</v>
       </c>
       <c r="B92" t="n">
-        <v>98450</v>
+        <v>101536</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
@@ -11590,10 +11586,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>651935</v>
+        <v>651950</v>
       </c>
       <c r="R92" t="n">
-        <v>6674576</v>
+        <v>6674474</v>
       </c>
       <c r="S92" t="n">
         <v>4</v>
@@ -11625,7 +11621,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11635,7 +11631,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11662,10 +11658,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127786483</v>
+        <v>127786477</v>
       </c>
       <c r="B93" t="n">
-        <v>101536</v>
+        <v>100632</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11673,28 +11669,24 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
@@ -11705,10 +11697,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>651950</v>
+        <v>651880</v>
       </c>
       <c r="R93" t="n">
-        <v>6674474</v>
+        <v>6674598</v>
       </c>
       <c r="S93" t="n">
         <v>4</v>
@@ -11740,7 +11732,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11750,7 +11742,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11777,7 +11769,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127786462</v>
+        <v>127786457</v>
       </c>
       <c r="B94" t="n">
         <v>98450</v>
@@ -11807,12 +11799,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -11824,10 +11816,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>651923</v>
+        <v>651935</v>
       </c>
       <c r="R94" t="n">
-        <v>6674461</v>
+        <v>6674576</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -11859,7 +11851,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11869,7 +11861,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11896,36 +11888,44 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127786477</v>
+        <v>127786462</v>
       </c>
       <c r="B95" t="n">
-        <v>100632</v>
+        <v>98450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
@@ -11935,10 +11935,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>651880</v>
+        <v>651923</v>
       </c>
       <c r="R95" t="n">
-        <v>6674598</v>
+        <v>6674461</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12007,49 +12007,37 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127786463</v>
+        <v>127786470</v>
       </c>
       <c r="B96" t="n">
-        <v>98450</v>
+        <v>100632</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
@@ -12058,10 +12046,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>651974</v>
+        <v>651844</v>
       </c>
       <c r="R96" t="n">
-        <v>6674401</v>
+        <v>6674682</v>
       </c>
       <c r="S96" t="n">
         <v>4</v>
@@ -12093,7 +12081,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12103,7 +12091,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12130,7 +12118,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127786464</v>
+        <v>127786463</v>
       </c>
       <c r="B97" t="n">
         <v>98450</v>
@@ -12160,7 +12148,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12168,7 +12156,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -12177,10 +12169,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>652028</v>
+        <v>651974</v>
       </c>
       <c r="R97" t="n">
-        <v>6674476</v>
+        <v>6674401</v>
       </c>
       <c r="S97" t="n">
         <v>4</v>
@@ -12212,7 +12204,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12222,7 +12214,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12249,36 +12241,44 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127786470</v>
+        <v>127786464</v>
       </c>
       <c r="B98" t="n">
-        <v>100632</v>
+        <v>98450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>651844</v>
+        <v>652028</v>
       </c>
       <c r="R98" t="n">
-        <v>6674682</v>
+        <v>6674476</v>
       </c>
       <c r="S98" t="n">
         <v>4</v>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12360,36 +12360,44 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127786472</v>
+        <v>127786465</v>
       </c>
       <c r="B99" t="n">
-        <v>100632</v>
+        <v>98450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
@@ -12399,10 +12407,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>651976</v>
+        <v>652028</v>
       </c>
       <c r="R99" t="n">
-        <v>6674481</v>
+        <v>6674484</v>
       </c>
       <c r="S99" t="n">
         <v>4</v>
@@ -12434,7 +12442,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12444,7 +12452,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12471,44 +12479,36 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127786465</v>
+        <v>127786472</v>
       </c>
       <c r="B100" t="n">
-        <v>98450</v>
+        <v>100632</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
@@ -12518,10 +12518,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>652028</v>
+        <v>651976</v>
       </c>
       <c r="R100" t="n">
-        <v>6674484</v>
+        <v>6674481</v>
       </c>
       <c r="S100" t="n">
         <v>4</v>
@@ -12553,7 +12553,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -13058,45 +13058,46 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127786444</v>
+        <v>127786421</v>
       </c>
       <c r="B105" t="n">
-        <v>92656</v>
+        <v>57660</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
@@ -13104,13 +13105,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>651913</v>
+        <v>651978</v>
       </c>
       <c r="R105" t="n">
-        <v>6674473</v>
+        <v>6674504</v>
       </c>
       <c r="S105" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13139,7 +13140,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13149,12 +13150,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:39</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Både tall och gran i närheten men uppenbart kalkrik mark här då vårärt och kransmossa växer alldeles intill.</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13181,46 +13177,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127786421</v>
+        <v>127786444</v>
       </c>
       <c r="B106" t="n">
-        <v>57660</v>
+        <v>92656</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -13228,13 +13223,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>651978</v>
+        <v>651913</v>
       </c>
       <c r="R106" t="n">
-        <v>6674504</v>
+        <v>6674473</v>
       </c>
       <c r="S106" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13263,7 +13258,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13273,7 +13268,12 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Både tall och gran i närheten men uppenbart kalkrik mark här då vårärt och kransmossa växer alldeles intill.</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13661,10 +13661,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127786481</v>
+        <v>127786403</v>
       </c>
       <c r="B110" t="n">
-        <v>101536</v>
+        <v>5197</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13672,35 +13672,32 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221235</v>
+        <v>105930</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -13708,10 +13705,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>652011</v>
+        <v>651940</v>
       </c>
       <c r="R110" t="n">
-        <v>6674447</v>
+        <v>6674275</v>
       </c>
       <c r="S110" t="n">
         <v>4</v>
@@ -13743,7 +13740,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13753,7 +13750,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13780,10 +13777,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127786403</v>
+        <v>127786481</v>
       </c>
       <c r="B111" t="n">
-        <v>5197</v>
+        <v>101536</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13791,32 +13788,35 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>105930</v>
+        <v>221235</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="J111" t="inlineStr"/>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
@@ -13824,10 +13824,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>651940</v>
+        <v>652011</v>
       </c>
       <c r="R111" t="n">
-        <v>6674275</v>
+        <v>6674447</v>
       </c>
       <c r="S111" t="n">
         <v>4</v>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13896,37 +13896,46 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127786438</v>
+        <v>127786418</v>
       </c>
       <c r="B112" t="n">
-        <v>91297</v>
+        <v>57660</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
-      <c r="J112" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -13934,10 +13943,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>651961</v>
+        <v>651997</v>
       </c>
       <c r="R112" t="n">
-        <v>6674370</v>
+        <v>6674524</v>
       </c>
       <c r="S112" t="n">
         <v>4</v>
@@ -13969,7 +13978,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13979,12 +13988,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Gammal och intorkad, ingen doft.</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14130,46 +14134,37 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127786418</v>
+        <v>127786438</v>
       </c>
       <c r="B114" t="n">
-        <v>57660</v>
+        <v>91297</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -14177,10 +14172,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>651997</v>
+        <v>651961</v>
       </c>
       <c r="R114" t="n">
-        <v>6674524</v>
+        <v>6674370</v>
       </c>
       <c r="S114" t="n">
         <v>4</v>
@@ -14212,7 +14207,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14222,7 +14217,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:42</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Gammal och intorkad, ingen doft.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14231,6 +14231,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -10027,7 +10027,7 @@
         <v>127786478</v>
       </c>
       <c r="B79" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>127786487</v>
       </c>
       <c r="B80" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10270,7 +10270,7 @@
         <v>127786471</v>
       </c>
       <c r="B81" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>127786466</v>
       </c>
       <c r="B85" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127786473</v>
+        <v>127786436</v>
       </c>
       <c r="B86" t="n">
-        <v>100632</v>
+        <v>91110</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10865,27 +10865,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222498</v>
+        <v>3215</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -10893,10 +10892,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>652012</v>
+        <v>651976</v>
       </c>
       <c r="R86" t="n">
-        <v>6674422</v>
+        <v>6674471</v>
       </c>
       <c r="S86" t="n">
         <v>4</v>
@@ -10928,7 +10927,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10938,7 +10937,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10965,10 +10964,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127786436</v>
+        <v>127786473</v>
       </c>
       <c r="B87" t="n">
-        <v>91104</v>
+        <v>100638</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10976,26 +10975,27 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3215</v>
+        <v>222498</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -11003,10 +11003,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>651976</v>
+        <v>652012</v>
       </c>
       <c r="R87" t="n">
-        <v>6674471</v>
+        <v>6674422</v>
       </c>
       <c r="S87" t="n">
         <v>4</v>
@@ -11038,7 +11038,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11048,7 +11048,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11078,7 +11078,7 @@
         <v>127786475</v>
       </c>
       <c r="B88" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>127786482</v>
       </c>
       <c r="B89" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11435,7 +11435,7 @@
         <v>127786474</v>
       </c>
       <c r="B91" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11543,10 +11543,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127786483</v>
+        <v>127786477</v>
       </c>
       <c r="B92" t="n">
-        <v>101536</v>
+        <v>100638</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11554,28 +11554,24 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
@@ -11586,10 +11582,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>651950</v>
+        <v>651880</v>
       </c>
       <c r="R92" t="n">
-        <v>6674474</v>
+        <v>6674598</v>
       </c>
       <c r="S92" t="n">
         <v>4</v>
@@ -11621,7 +11617,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11631,7 +11627,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11658,36 +11654,44 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127786477</v>
+        <v>127786457</v>
       </c>
       <c r="B93" t="n">
-        <v>100632</v>
+        <v>98456</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
@@ -11697,10 +11701,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>651880</v>
+        <v>651935</v>
       </c>
       <c r="R93" t="n">
-        <v>6674598</v>
+        <v>6674576</v>
       </c>
       <c r="S93" t="n">
         <v>4</v>
@@ -11732,7 +11736,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11742,7 +11746,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11769,10 +11773,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127786457</v>
+        <v>127786462</v>
       </c>
       <c r="B94" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11799,12 +11803,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -11816,10 +11820,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>651935</v>
+        <v>651923</v>
       </c>
       <c r="R94" t="n">
-        <v>6674576</v>
+        <v>6674461</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -11851,7 +11855,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11861,7 +11865,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11888,44 +11892,40 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127786462</v>
+        <v>127786483</v>
       </c>
       <c r="B95" t="n">
-        <v>98450</v>
+        <v>101542</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>221235</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
@@ -11935,10 +11935,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>651923</v>
+        <v>651950</v>
       </c>
       <c r="R95" t="n">
-        <v>6674461</v>
+        <v>6674474</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12010,7 +12010,7 @@
         <v>127786470</v>
       </c>
       <c r="B96" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12118,10 +12118,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127786463</v>
+        <v>127786464</v>
       </c>
       <c r="B97" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12156,11 +12156,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -12169,10 +12165,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>651974</v>
+        <v>652028</v>
       </c>
       <c r="R97" t="n">
-        <v>6674401</v>
+        <v>6674476</v>
       </c>
       <c r="S97" t="n">
         <v>4</v>
@@ -12204,7 +12200,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12214,7 +12210,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12241,10 +12237,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127786464</v>
+        <v>127786463</v>
       </c>
       <c r="B98" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12271,7 +12267,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12279,7 +12275,11 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
@@ -12288,10 +12288,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>652028</v>
+        <v>651974</v>
       </c>
       <c r="R98" t="n">
-        <v>6674476</v>
+        <v>6674401</v>
       </c>
       <c r="S98" t="n">
         <v>4</v>
@@ -12323,7 +12323,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12360,44 +12360,36 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127786465</v>
+        <v>127786468</v>
       </c>
       <c r="B99" t="n">
-        <v>98450</v>
+        <v>100638</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
@@ -12407,10 +12399,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>652028</v>
+        <v>651849</v>
       </c>
       <c r="R99" t="n">
-        <v>6674484</v>
+        <v>6674645</v>
       </c>
       <c r="S99" t="n">
         <v>4</v>
@@ -12442,7 +12434,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12452,7 +12444,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12482,7 +12474,7 @@
         <v>127786472</v>
       </c>
       <c r="B100" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12590,36 +12582,44 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127786468</v>
+        <v>127786465</v>
       </c>
       <c r="B101" t="n">
-        <v>100632</v>
+        <v>98456</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
       <c r="N101" t="inlineStr"/>
@@ -12629,10 +12629,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>651849</v>
+        <v>652028</v>
       </c>
       <c r="R101" t="n">
-        <v>6674645</v>
+        <v>6674484</v>
       </c>
       <c r="S101" t="n">
         <v>4</v>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12816,10 +12816,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127786479</v>
+        <v>127786441</v>
       </c>
       <c r="B103" t="n">
-        <v>101536</v>
+        <v>92273</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12827,35 +12827,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221235</v>
+        <v>4769</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
@@ -12863,10 +12862,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>651996</v>
+        <v>651973</v>
       </c>
       <c r="R103" t="n">
-        <v>6674470</v>
+        <v>6674465</v>
       </c>
       <c r="S103" t="n">
         <v>4</v>
@@ -12898,7 +12897,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12908,7 +12907,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Färgen på bilderna något missvisande. Ljusgul mjölksaft.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12935,10 +12939,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127786441</v>
+        <v>127786479</v>
       </c>
       <c r="B104" t="n">
-        <v>92267</v>
+        <v>101542</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12946,34 +12950,35 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4769</v>
+        <v>221235</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12981,10 +12986,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>651973</v>
+        <v>651996</v>
       </c>
       <c r="R104" t="n">
-        <v>6674465</v>
+        <v>6674470</v>
       </c>
       <c r="S104" t="n">
         <v>4</v>
@@ -13016,7 +13021,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13026,12 +13031,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:51</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Färgen på bilderna något missvisande. Ljusgul mjölksaft.</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13180,7 +13180,7 @@
         <v>127786444</v>
       </c>
       <c r="B106" t="n">
-        <v>92656</v>
+        <v>92662</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>127786486</v>
       </c>
       <c r="B109" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>127786481</v>
       </c>
       <c r="B111" t="n">
-        <v>101536</v>
+        <v>101542</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>127786438</v>
       </c>
       <c r="B114" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>

--- a/artfynd/A 260-2025 artfynd.xlsx
+++ b/artfynd/A 260-2025 artfynd.xlsx
@@ -4311,7 +4311,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128089321</v>
+        <v>128089320</v>
       </c>
       <c r="B32" t="n">
         <v>100649</v>
@@ -4350,10 +4350,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>651896</v>
+        <v>651925</v>
       </c>
       <c r="R32" t="n">
-        <v>6673736</v>
+        <v>6673733</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4422,7 +4422,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128089320</v>
+        <v>128089321</v>
       </c>
       <c r="B33" t="n">
         <v>100649</v>
@@ -4461,10 +4461,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>651925</v>
+        <v>651896</v>
       </c>
       <c r="R33" t="n">
-        <v>6673733</v>
+        <v>6673736</v>
       </c>
       <c r="S33" t="n">
         <v>4</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -11641,10 +11641,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127786478</v>
+        <v>127786487</v>
       </c>
       <c r="B93" t="n">
-        <v>101545</v>
+        <v>105505</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11652,26 +11652,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221235</v>
+        <v>221144</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11688,10 +11688,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>651968</v>
+        <v>651950</v>
       </c>
       <c r="R93" t="n">
-        <v>6674476</v>
+        <v>6674353</v>
       </c>
       <c r="S93" t="n">
         <v>4</v>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11733,12 +11733,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Minst!</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11765,10 +11760,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127786487</v>
+        <v>127786478</v>
       </c>
       <c r="B94" t="n">
-        <v>105497</v>
+        <v>101553</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11776,26 +11771,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>221144</v>
+        <v>221235</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11812,10 +11807,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>651950</v>
+        <v>651968</v>
       </c>
       <c r="R94" t="n">
-        <v>6674353</v>
+        <v>6674476</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -11847,7 +11842,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11857,7 +11852,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Minst!</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11887,7 +11887,7 @@
         <v>127786471</v>
       </c>
       <c r="B95" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11995,10 +11995,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127786419</v>
+        <v>127786417</v>
       </c>
       <c r="B96" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12042,10 +12042,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>651988</v>
+        <v>651998</v>
       </c>
       <c r="R96" t="n">
-        <v>6674523</v>
+        <v>6674425</v>
       </c>
       <c r="S96" t="n">
         <v>4</v>
@@ -12077,7 +12077,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12087,7 +12087,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12114,10 +12114,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127786417</v>
+        <v>127786413</v>
       </c>
       <c r="B97" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12161,10 +12161,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>651998</v>
+        <v>651946</v>
       </c>
       <c r="R97" t="n">
-        <v>6674425</v>
+        <v>6674598</v>
       </c>
       <c r="S97" t="n">
         <v>4</v>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12233,10 +12233,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127786413</v>
+        <v>127786419</v>
       </c>
       <c r="B98" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>651946</v>
+        <v>651988</v>
       </c>
       <c r="R98" t="n">
-        <v>6674598</v>
+        <v>6674523</v>
       </c>
       <c r="S98" t="n">
         <v>4</v>
@@ -12315,7 +12315,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12325,7 +12325,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12355,7 +12355,7 @@
         <v>127786466</v>
       </c>
       <c r="B99" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>127786436</v>
       </c>
       <c r="B100" t="n">
-        <v>91113</v>
+        <v>91121</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>127786473</v>
       </c>
       <c r="B101" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>127786482</v>
       </c>
       <c r="B102" t="n">
-        <v>101545</v>
+        <v>101553</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>127786475</v>
       </c>
       <c r="B103" t="n">
-        <v>100641</v>
+        <v>100649</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12930,46 +12930,38 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127786416</v>
+        <v>127786474</v>
       </c>
       <c r="B104" t="n">
-        <v>57663</v>
+        <v>100649</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>222498</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12977,10 +12969,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>651903</v>
+        <v>652011</v>
       </c>
       <c r="R104" t="n">
-        <v>6674574</v>
+        <v>6674446</v>
       </c>
       <c r="S104" t="n">
         <v>4</v>
@@ -13012,7 +13004,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -13022,7 +13014,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13049,38 +13041,46 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127786474</v>
+        <v>127786416</v>
       </c>
       <c r="B105" t="n">
-        <v>100641</v>
+        <v>57669</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105